--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0&quot; %&quot;"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -63,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -73,9 +75,11 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -599,7 +603,7 @@
           <t>CORBEILLE (DIFFUSION) (30) ; INCONNU (30)</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J2" s="3" t="n">
@@ -670,7 +674,7 @@
           <t>CORBEILLE (DIFFUSION) (50) ; INCONNU (47)</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="5" t="n">
         <v>51.5</v>
       </c>
       <c r="J3" s="3" t="n">
@@ -741,7 +745,7 @@
           <t>INCONNU (6) ; CORBEILLE (DIFFUSION) (6)</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J4" s="3" t="n">
@@ -812,7 +816,7 @@
           <t>INCONNU (23)</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
@@ -878,7 +882,7 @@
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
@@ -949,7 +953,7 @@
           <t>TRANSFERT_S3_OK (15703)</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J7" s="3" t="n">
@@ -1020,7 +1024,7 @@
           <t>INCONNU (7)</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
@@ -1091,7 +1095,7 @@
           <t>INCONNU (11)</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
@@ -1162,7 +1166,7 @@
           <t>INCONNU (272) ; CORBEILLE (DIFFUSION) (24)</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="5" t="n">
         <v>8.1</v>
       </c>
       <c r="J10" s="3" t="n">
@@ -1233,7 +1237,7 @@
           <t>INCONNU (27)</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
@@ -1304,7 +1308,7 @@
           <t>INCONNU (14)</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
@@ -1375,7 +1379,7 @@
           <t>INCONNU (5)</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
@@ -1446,7 +1450,7 @@
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
@@ -1517,7 +1521,7 @@
           <t>INCONNU (496)</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="3" t="n">
@@ -1583,7 +1587,7 @@
           <t>INCONNU (2)</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
@@ -1654,7 +1658,7 @@
           <t>INCONNU (3)</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
@@ -1725,7 +1729,7 @@
           <t>TRANSFERT_S3_OK (76590)</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J18" s="3" t="n">
@@ -1796,7 +1800,7 @@
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
@@ -1867,7 +1871,7 @@
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
@@ -1938,7 +1942,7 @@
           <t>INCONNU (145)</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
@@ -2009,7 +2013,7 @@
           <t>TRANSFERT_S3_OK (1076) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="I22" s="5" t="n">
         <v>74.7</v>
       </c>
       <c r="J22" s="3" t="n">
@@ -2080,7 +2084,7 @@
           <t>INCONNU (604)</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="I23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
@@ -2141,7 +2145,7 @@
           <t>TRANSFERT_S3_OK (159)</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="I24" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J24" s="3" t="n">
@@ -2207,7 +2211,7 @@
           <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I25" s="5" t="n">
         <v>47.8</v>
       </c>
       <c r="J25" s="3" t="n">
@@ -2278,7 +2282,7 @@
           <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I26" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="J26" s="3" t="n">
@@ -2349,7 +2353,7 @@
           <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="I27" s="5" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="J27" s="3" t="n">
@@ -2420,7 +2424,7 @@
           <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I28" s="5" t="n">
         <v>73.7</v>
       </c>
       <c r="J28" s="3" t="n">
@@ -2491,7 +2495,7 @@
           <t>TRANSFERT_S3_OK (122555) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (398) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="I29" s="5" t="n">
         <v>86</v>
       </c>
       <c r="J29" s="3" t="n">
@@ -2562,7 +2566,7 @@
           <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="I30" s="5" t="n">
         <v>49.9</v>
       </c>
       <c r="J30" s="3" t="n">
@@ -2633,7 +2637,7 @@
           <t>TRANSFERT_S3_OK (249012) ; CORBEILLE (85333) ; INCONNU (23761) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="I31" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
       <c r="J31" s="3" t="n">
@@ -2699,7 +2703,7 @@
           <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J32" s="3" t="n">
@@ -2770,7 +2774,7 @@
           <t>EN LIGNE - À TRANSFERER ? (678)</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="3" t="n">
@@ -2841,7 +2845,7 @@
           <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I34" s="5" t="n">
         <v>48.9</v>
       </c>
       <c r="J34" s="3" t="n">
@@ -2912,7 +2916,7 @@
           <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I35" s="5" t="n">
         <v>19.4</v>
       </c>
       <c r="J35" s="3" t="n">
@@ -2983,7 +2987,7 @@
           <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="I36" s="5" t="n">
         <v>96.2</v>
       </c>
       <c r="J36" s="3" t="n">
@@ -3054,7 +3058,7 @@
           <t>CORBEILLE (DIFFUSION) (6428) ; À SUPPRIMER (doublons S3 - az) (1901) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (RENOMMAGE) (238)</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I37" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J37" s="3" t="n">
@@ -3120,7 +3124,7 @@
           <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
         </is>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J38" s="3" t="n">
@@ -3186,7 +3190,7 @@
           <t>INCONNU (9293) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="I39" s="5" t="n">
         <v>50</v>
       </c>
       <c r="J39" s="3" t="n">
@@ -3252,7 +3256,7 @@
           <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="I40" s="5" t="n">
         <v>35.1</v>
       </c>
       <c r="J40" s="3" t="n">
@@ -3323,7 +3327,7 @@
           <t>TRANSFERT_S3_OK (85759) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
         </is>
       </c>
-      <c r="I41" t="n">
+      <c r="I41" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
       <c r="J41" s="3" t="n">
@@ -3389,7 +3393,7 @@
           <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I42" t="n">
+      <c r="I42" s="5" t="n">
         <v>27.8</v>
       </c>
       <c r="J42" s="3" t="n">
@@ -3460,7 +3464,7 @@
           <t>INCONNU (16034) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I43" s="5" t="n">
         <v>16.4</v>
       </c>
       <c r="J43" s="3" t="n">
@@ -3531,7 +3535,7 @@
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="I44" t="n">
+      <c r="I44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="3" t="n">
@@ -3602,7 +3606,7 @@
           <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I45" s="5" t="n">
         <v>49.3</v>
       </c>
       <c r="J45" s="3" t="n">
@@ -3673,7 +3677,7 @@
           <t>TRANSFERT_S3_OK (37053)</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J46" s="3" t="n">
@@ -3734,7 +3738,7 @@
           <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
         </is>
       </c>
-      <c r="I47" t="n">
+      <c r="I47" s="5" t="n">
         <v>42.8</v>
       </c>
       <c r="J47" s="3" t="n">
@@ -3805,7 +3809,7 @@
           <t>INCONNU (7072)</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
@@ -3861,7 +3865,7 @@
           <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
         </is>
       </c>
-      <c r="I49" t="n">
+      <c r="I49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
@@ -3917,7 +3921,7 @@
           <t>TRANSFERT_S3_OK (242)</t>
         </is>
       </c>
-      <c r="I50" t="n">
+      <c r="I50" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J50" s="3" t="n">
@@ -3973,7 +3977,7 @@
           <t>TRANSFERT_S3_OK (1697) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="I51" s="5" t="n">
         <v>90</v>
       </c>
       <c r="J51" s="3" t="n">
@@ -4029,7 +4033,7 @@
           <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="I52" s="5" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="J52" s="3" t="n">
@@ -4085,7 +4089,7 @@
           <t>TRANSFERT_S3_OK (18)</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="I53" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J53" s="3" t="n">
@@ -4141,7 +4145,7 @@
           <t>CORBEILLE (DIFFUSION) (5176) ; EN LIGNE - À TRANSFERER ? (5114) ; INCONNU (573) ; TRANSFERT_S3_OK (175)</t>
         </is>
       </c>
-      <c r="I54" t="n">
+      <c r="I54" s="5" t="n">
         <v>48.5</v>
       </c>
       <c r="J54" s="3" t="n">
@@ -4197,7 +4201,7 @@
           <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J55" s="3" t="n">
@@ -4253,7 +4257,7 @@
           <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
         </is>
       </c>
-      <c r="I56" t="n">
+      <c r="I56" s="5" t="n">
         <v>50.2</v>
       </c>
       <c r="J56" s="3" t="n">
@@ -4309,7 +4313,7 @@
           <t>TRANSFERT_S3_OK (4534) ; INCONNU (651) ; À SUPPRIMER (doublons S3 - az) (536) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I57" s="5" t="n">
         <v>86.09999999999999</v>
       </c>
       <c r="J57" s="3" t="n">
@@ -4365,7 +4369,7 @@
           <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="I58" s="5" t="n">
         <v>12.1</v>
       </c>
       <c r="J58" s="3" t="n">
@@ -4421,7 +4425,7 @@
           <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
         </is>
       </c>
-      <c r="I59" t="n">
+      <c r="I59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
@@ -4477,7 +4481,7 @@
           <t>INCONNU (2666)</t>
         </is>
       </c>
-      <c r="I60" t="n">
+      <c r="I60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J60" s="3" t="n">
@@ -4533,7 +4537,7 @@
           <t>TRANSFERT_S3_OK (8485)</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="I61" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J61" s="3" t="n">
@@ -4589,7 +4593,7 @@
           <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="I62" t="n">
+      <c r="I62" s="5" t="n">
         <v>12.2</v>
       </c>
       <c r="J62" s="3" t="n">
@@ -4645,7 +4649,7 @@
           <t>EN LIGNE - À TRANSFERER ? (8684) ; TRANSFERT_S3_OK (750) ; INCONNU (264) ; À SUPPRIMER (doublons S3 - az) (113) ; CORBEILLE (DIFFUSION) (45)</t>
         </is>
       </c>
-      <c r="I63" t="n">
+      <c r="I63" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
@@ -4701,7 +4705,7 @@
           <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
         </is>
       </c>
-      <c r="I64" t="n">
+      <c r="I64" s="5" t="n">
         <v>91.8</v>
       </c>
       <c r="J64" s="3" t="n">
@@ -4757,7 +4761,7 @@
           <t>TRANSFERT_S3_OK (605)</t>
         </is>
       </c>
-      <c r="I65" t="n">
+      <c r="I65" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J65" s="3" t="n">
@@ -4813,7 +4817,7 @@
           <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
         </is>
       </c>
-      <c r="I66" t="n">
+      <c r="I66" s="5" t="n">
         <v>49.7</v>
       </c>
       <c r="J66" s="3" t="n">
@@ -4869,7 +4873,7 @@
           <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
         </is>
       </c>
-      <c r="I67" t="n">
+      <c r="I67" s="5" t="n">
         <v>98.8</v>
       </c>
       <c r="J67" s="3" t="n">
@@ -4925,7 +4929,7 @@
           <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (1814) ; INCONNU (1784) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
-      <c r="I68" t="n">
+      <c r="I68" s="5" t="n">
         <v>92.2</v>
       </c>
       <c r="J68" s="3" t="n">
@@ -4981,7 +4985,7 @@
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="I69" t="n">
+      <c r="I69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="3" t="n">
@@ -5037,7 +5041,7 @@
           <t>TRANSFERT_S3_OK (5035) ; À SUPPRIMER (686) ; CORBEILLE (DIFFUSION) (21) ; INCONNU (20) ; EN LIGNE - À TRANSFERER ? (6) ; À SUPPRIMER (RENOMMAGE) (1)</t>
         </is>
       </c>
-      <c r="I70" t="n">
+      <c r="I70" s="5" t="n">
         <v>99.5</v>
       </c>
       <c r="J70" s="3" t="n">
@@ -5093,7 +5097,7 @@
           <t>INCONNU (1084)</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="I71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
@@ -5149,7 +5153,7 @@
           <t>TRANSFERT_S3_OK (1596)</t>
         </is>
       </c>
-      <c r="I72" t="n">
+      <c r="I72" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J72" s="3" t="n">
@@ -5205,7 +5209,7 @@
           <t>INCONNU (1949)</t>
         </is>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
@@ -5261,7 +5265,7 @@
           <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="I74" t="n">
+      <c r="I74" s="5" t="n">
         <v>5.7</v>
       </c>
       <c r="J74" s="3" t="n">
@@ -5317,7 +5321,7 @@
           <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
         </is>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="5" t="n">
         <v>49.8</v>
       </c>
       <c r="J75" s="3" t="n">
@@ -5373,7 +5377,7 @@
           <t>EN LIGNE - À TRANSFERER ? (2419)</t>
         </is>
       </c>
-      <c r="I76" t="n">
+      <c r="I76" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="3" t="n">
@@ -5429,7 +5433,7 @@
           <t>INCONNU (238)</t>
         </is>
       </c>
-      <c r="I77" t="n">
+      <c r="I77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="3" t="n">
@@ -5485,7 +5489,7 @@
           <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I78" t="n">
+      <c r="I78" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J78" s="3" t="n">
@@ -5541,7 +5545,7 @@
           <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
         </is>
       </c>
-      <c r="I79" t="n">
+      <c r="I79" s="5" t="n">
         <v>48.4</v>
       </c>
       <c r="J79" s="3" t="n">
@@ -5597,7 +5601,7 @@
           <t>TRANSFERT_S3_OK (318)</t>
         </is>
       </c>
-      <c r="I80" t="n">
+      <c r="I80" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J80" s="3" t="n">
@@ -5653,7 +5657,7 @@
           <t>TRANSFERT_S3_OK (1918)</t>
         </is>
       </c>
-      <c r="I81" t="n">
+      <c r="I81" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J81" s="3" t="n">
@@ -5709,7 +5713,7 @@
           <t>INCONNU (375)</t>
         </is>
       </c>
-      <c r="I82" t="n">
+      <c r="I82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="3" t="n">
@@ -5765,7 +5769,7 @@
           <t>TRANSFERT_S3_OK (1925) ; EN LIGNE - À TRANSFERER ? (868) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (4)</t>
         </is>
       </c>
-      <c r="I83" t="n">
+      <c r="I83" s="5" t="n">
         <v>68.8</v>
       </c>
       <c r="J83" s="3" t="n">
@@ -5821,7 +5825,7 @@
           <t>TRANSFERT_S3_OK (638)</t>
         </is>
       </c>
-      <c r="I84" t="n">
+      <c r="I84" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J84" s="3" t="n">
@@ -5877,7 +5881,7 @@
           <t>TRANSFERT_S3_OK (8790)</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="I85" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J85" s="3" t="n">
@@ -5933,7 +5937,7 @@
           <t>EN LIGNE - À TRANSFERER ? (265)</t>
         </is>
       </c>
-      <c r="I86" t="n">
+      <c r="I86" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="3" t="n">
@@ -5989,7 +5993,7 @@
           <t>TRANSFERT_S3_OK (89)</t>
         </is>
       </c>
-      <c r="I87" t="n">
+      <c r="I87" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J87" s="3" t="n">
@@ -6045,7 +6049,7 @@
           <t>EN LIGNE - À TRANSFERER ? (40)</t>
         </is>
       </c>
-      <c r="I88" t="n">
+      <c r="I88" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="3" t="n">
@@ -6101,7 +6105,7 @@
           <t>TRANSFERT_S3_OK (35)</t>
         </is>
       </c>
-      <c r="I89" t="n">
+      <c r="I89" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J89" s="3" t="n">
@@ -6157,7 +6161,7 @@
           <t>EN LIGNE - À TRANSFERER ? (96)</t>
         </is>
       </c>
-      <c r="I90" t="n">
+      <c r="I90" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="3" t="n">
@@ -6213,7 +6217,7 @@
           <t>TRANSFERT_S3_OK (23)</t>
         </is>
       </c>
-      <c r="I91" t="n">
+      <c r="I91" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J91" s="3" t="n">
@@ -6269,7 +6273,7 @@
           <t>TRANSFERT_S3_OK (148)</t>
         </is>
       </c>
-      <c r="I92" t="n">
+      <c r="I92" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J92" s="3" t="n">
@@ -6325,7 +6329,7 @@
           <t>EN LIGNE - À TRANSFERER ? (3414) ; INCONNU (296)</t>
         </is>
       </c>
-      <c r="I93" t="n">
+      <c r="I93" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="3" t="n">
@@ -6381,7 +6385,7 @@
           <t>TRANSFERT_S3_OK (524)</t>
         </is>
       </c>
-      <c r="I94" t="n">
+      <c r="I94" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J94" s="3" t="n">
@@ -6437,7 +6441,7 @@
           <t>TRANSFERT_S3_OK (884)</t>
         </is>
       </c>
-      <c r="I95" t="n">
+      <c r="I95" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J95" s="3" t="n">
@@ -6493,7 +6497,7 @@
           <t>TRANSFERT_S3_OK (48) ; À SUPPRIMER (doublons S3 - az) (2)</t>
         </is>
       </c>
-      <c r="I96" t="n">
+      <c r="I96" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J96" s="3" t="n">
@@ -6549,7 +6553,7 @@
           <t>TRANSFERT_S3_OK (1461)</t>
         </is>
       </c>
-      <c r="I97" t="n">
+      <c r="I97" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J97" s="3" t="n">
@@ -6605,7 +6609,7 @@
           <t>TRANSFERT_S3_OK (176340)</t>
         </is>
       </c>
-      <c r="I98" t="n">
+      <c r="I98" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J98" s="3" t="n">
@@ -6661,7 +6665,7 @@
           <t>INCONNU (2781) ; À SUPPRIMER (doublons S3 - az) (178) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I99" t="n">
+      <c r="I99" s="5" t="n">
         <v>11.4</v>
       </c>
       <c r="J99" s="3" t="n">
@@ -6717,7 +6721,7 @@
           <t>TRANSFERT_S3_OK (116806)</t>
         </is>
       </c>
-      <c r="I100" t="n">
+      <c r="I100" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J100" s="3" t="n">
@@ -6773,7 +6777,7 @@
           <t>TRANSFERT_S3_OK (5752)</t>
         </is>
       </c>
-      <c r="I101" t="n">
+      <c r="I101" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J101" s="3" t="n">
@@ -6829,7 +6833,7 @@
           <t>TRANSFERT_S3_OK (377078)</t>
         </is>
       </c>
-      <c r="I102" t="n">
+      <c r="I102" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J102" s="3" t="n">
@@ -6885,7 +6889,7 @@
           <t>TRANSFERT_S3_OK (64400)</t>
         </is>
       </c>
-      <c r="I103" t="n">
+      <c r="I103" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J103" s="3" t="n">
@@ -6941,7 +6945,7 @@
           <t>TRANSFERT_S3_OK (595291)</t>
         </is>
       </c>
-      <c r="I104" t="n">
+      <c r="I104" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J104" s="3" t="n">
@@ -6997,7 +7001,7 @@
           <t>TRANSFERT_S3_OK (3367)</t>
         </is>
       </c>
-      <c r="I105" t="n">
+      <c r="I105" s="5" t="n">
         <v>100</v>
       </c>
       <c r="J105" s="3" t="n">
@@ -7053,7 +7057,7 @@
           <t>EN LIGNE - À TRANSFERER ? (457)</t>
         </is>
       </c>
-      <c r="I106" t="n">
+      <c r="I106" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J106" s="3" t="n">
@@ -7104,7 +7108,7 @@
           <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; TRANSFERT_S3_OK (345) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
         </is>
       </c>
-      <c r="I107" t="n">
+      <c r="I107" s="5" t="n">
         <v>62.5</v>
       </c>
       <c r="J107" s="3" t="n">
@@ -7139,57 +7143,57 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr"/>
-      <c r="C108" s="5" t="inlineStr"/>
-      <c r="D108" s="5" t="inlineStr"/>
-      <c r="E108" s="5" t="inlineStr"/>
-      <c r="F108" s="6" t="n">
+      <c r="B108" s="6" t="inlineStr"/>
+      <c r="C108" s="6" t="inlineStr"/>
+      <c r="D108" s="6" t="inlineStr"/>
+      <c r="E108" s="6" t="inlineStr"/>
+      <c r="F108" s="7" t="n">
         <v>2430327</v>
       </c>
-      <c r="G108" s="7" t="n">
+      <c r="G108" s="8" t="n">
         <v>20914.25</v>
       </c>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (2068905) ; INCONNU (138238) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37324) ; EN LIGNE - À TRANSFERER ? (26280) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; À SUPPRIMER (doublons S3 - az) (6149) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118)</t>
         </is>
       </c>
-      <c r="I108" s="5" t="n">
+      <c r="I108" s="9" t="n">
         <v>93.2</v>
       </c>
-      <c r="J108" s="6" t="n">
+      <c r="J108" s="7" t="n">
         <v>992367</v>
       </c>
-      <c r="K108" s="6" t="n">
+      <c r="K108" s="7" t="n">
         <v>7347</v>
       </c>
-      <c r="L108" s="6" t="n">
+      <c r="L108" s="7" t="n">
         <v>2453</v>
       </c>
-      <c r="M108" s="6" t="n">
+      <c r="M108" s="7" t="n">
         <v>673674</v>
       </c>
-      <c r="N108" s="6" t="n">
+      <c r="N108" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="O108" s="6" t="n">
+      <c r="O108" s="7" t="n">
         <v>334782</v>
       </c>
-      <c r="P108" s="6" t="n">
+      <c r="P108" s="7" t="n">
         <v>452908</v>
       </c>
-      <c r="Q108" s="6" t="n">
+      <c r="Q108" s="7" t="n">
         <v>338162</v>
       </c>
-      <c r="R108" s="6" t="n">
+      <c r="R108" s="7" t="n">
         <v>620516</v>
       </c>
-      <c r="S108" s="6" t="n">
+      <c r="S108" s="7" t="n">
         <v>465</v>
       </c>
     </row>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -3260,7 +3260,7 @@
         <v>35.1</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3331,7 +3331,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>65304</v>
+        <v>65349</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
@@ -4142,14 +4142,14 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (5176) ; EN LIGNE - À TRANSFERER ? (5114) ; INCONNU (573) ; TRANSFERT_S3_OK (175)</t>
+          <t>EN LIGNE - À TRANSFERER ? (5576) ; CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (175) ; INCONNU (111)</t>
         </is>
       </c>
       <c r="I54" s="5" t="n">
         <v>48.5</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>5280</v>
+        <v>5742</v>
       </c>
       <c r="K54" s="3" t="n">
         <v>0</v>
@@ -4646,14 +4646,14 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (8684) ; TRANSFERT_S3_OK (750) ; INCONNU (264) ; À SUPPRIMER (doublons S3 - az) (113) ; CORBEILLE (DIFFUSION) (45)</t>
+          <t>EN LIGNE - À TRANSFERER ? (8900) ; TRANSFERT_S3_OK (750) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45)</t>
         </is>
       </c>
       <c r="I63" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>9407</v>
+        <v>9623</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>0</v>
@@ -4926,14 +4926,14 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (1814) ; INCONNU (1784) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (doublons S3 - az) (157)</t>
+          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
       <c r="I68" s="5" t="n">
         <v>92.2</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>31676</v>
+        <v>33302</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>0</v>
@@ -7160,14 +7160,14 @@
       </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (2068905) ; INCONNU (138238) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37324) ; EN LIGNE - À TRANSFERER ? (26280) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; À SUPPRIMER (doublons S3 - az) (6149) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118)</t>
+          <t>TRANSFERT_S3_OK (2068905) ; INCONNU (135934) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37324) ; EN LIGNE - À TRANSFERER ? (28584) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; À SUPPRIMER (doublons S3 - az) (6149) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118)</t>
         </is>
       </c>
       <c r="I108" s="9" t="n">
         <v>93.2</v>
       </c>
       <c r="J108" s="7" t="n">
-        <v>992367</v>
+        <v>994727</v>
       </c>
       <c r="K108" s="7" t="n">
         <v>7347</v>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S108"/>
+  <dimension ref="A1:U108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -454,12 +454,12 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -467,6 +467,8 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,70 +499,80 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>ir</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>collection_bnr</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>fichiers</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>volume_go</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>conservation_statut</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>traitement_s3</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>fichiers_publies</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>audio</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>autre</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>jpeg</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>jpeg2000</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>ocr txt</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>ocr xml</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>pdf</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>tiff</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>video</t>
         </is>
@@ -592,38 +604,32 @@
           <t>1AEFi</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="I2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (30) ; INCONNU (30)</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="K2" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" s="3" t="n">
         <v>0</v>
       </c>
@@ -634,6 +640,12 @@
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -663,38 +675,32 @@
           <t>1I</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="I3" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (50) ; INCONNU (47)</t>
         </is>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="K3" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="N3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" s="3" t="n">
         <v>0</v>
       </c>
@@ -705,6 +711,12 @@
         <v>0</v>
       </c>
       <c r="S3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -734,38 +746,32 @@
           <t>1NumFi</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="H4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="I4" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>INCONNU (6) ; CORBEILLE (DIFFUSION) (6)</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="K4" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P4" s="3" t="n">
         <v>0</v>
       </c>
@@ -773,9 +779,15 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="U4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -805,48 +817,48 @@
           <t>1PER3</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>INCONNU (23)</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="P5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="U5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -871,24 +883,18 @@
           <t>2F</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="I6" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -910,9 +916,15 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S6" s="3" t="n">
+      <c r="U6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -942,38 +954,32 @@
           <t>2I</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>15703</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="I7" s="4" t="n">
         <v>9.08</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (15703)</t>
         </is>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
         <v>15703</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P7" s="3" t="n">
         <v>0</v>
       </c>
@@ -984,6 +990,12 @@
         <v>0</v>
       </c>
       <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1013,24 +1025,18 @@
           <t>308W</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="H8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>INCONNU (7)</t>
         </is>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1049,12 +1055,18 @@
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="R8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="3" t="n">
+      <c r="T8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1084,24 +1096,18 @@
           <t>381W</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="H9" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="I9" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>INCONNU (11)</t>
         </is>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1123,9 +1129,15 @@
         <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="S9" s="3" t="n">
+      <c r="U9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1155,48 +1167,48 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>3.16</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>INCONNU (272) ; CORBEILLE (DIFFUSION) (24)</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>8.1</v>
       </c>
-      <c r="J10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="N10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="T10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="S10" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1226,24 +1238,18 @@
           <t>3O</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="H11" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>2.71</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>INCONNU (27)</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1262,12 +1268,18 @@
         <v>0</v>
       </c>
       <c r="Q11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="T11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="U11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1297,24 +1309,18 @@
           <t>3R</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="H12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="I12" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>INCONNU (14)</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1336,9 +1342,15 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="S12" s="3" t="n">
+      <c r="U12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1368,24 +1380,18 @@
           <t>4H</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="I13" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>INCONNU (5)</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1407,9 +1413,15 @@
         <v>0</v>
       </c>
       <c r="R13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="S13" s="3" t="n">
+      <c r="U13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1439,24 +1451,18 @@
           <t>4M</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="I14" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
@@ -1478,9 +1484,15 @@
         <v>0</v>
       </c>
       <c r="R14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="U14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1510,24 +1522,18 @@
           <t>507W</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>INCONNU (496)</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1549,9 +1555,15 @@
         <v>0</v>
       </c>
       <c r="R15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="S15" s="3" t="n">
+      <c r="U15" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1576,24 +1588,18 @@
           <t>5Fi</t>
         </is>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="H16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>INCONNU (2)</t>
         </is>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -1615,9 +1621,15 @@
         <v>0</v>
       </c>
       <c r="R16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="S16" s="3" t="n">
+      <c r="U16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1647,38 +1659,32 @@
           <t>5M</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>INCONNU (3)</t>
         </is>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3" t="n">
+      <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" s="3" t="n">
         <v>0</v>
       </c>
@@ -1686,9 +1692,15 @@
         <v>0</v>
       </c>
       <c r="R17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="3" t="n">
+      <c r="U17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1718,37 +1730,31 @@
           <t>6H</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>76590</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (76590)</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
+      <c r="H18" s="3" t="n">
+        <v>76933</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (76933)</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>76590</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0</v>
+        <v>76933</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0</v>
@@ -1760,6 +1766,12 @@
         <v>0</v>
       </c>
       <c r="S18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1789,24 +1801,18 @@
           <t>6M</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="H19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="I19" s="4" t="n">
         <v>0.19</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
@@ -1825,12 +1831,18 @@
         <v>0</v>
       </c>
       <c r="Q19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="T19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1860,24 +1872,18 @@
           <t>8C</t>
         </is>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
@@ -1899,9 +1905,15 @@
         <v>0</v>
       </c>
       <c r="R20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="U20" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1931,38 +1943,32 @@
           <t>8J</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>2.28</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>INCONNU (145)</t>
         </is>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="N21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
       </c>
@@ -1970,9 +1976,15 @@
         <v>0</v>
       </c>
       <c r="R21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="S21" s="3" t="n">
+      <c r="U21" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2002,48 +2014,53 @@
           <t>4H</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_AFF </t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>3650</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="I22" s="4" t="n">
         <v>219.66</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1076) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
         </is>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="K22" s="5" t="n">
         <v>74.7</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="L22" s="3" t="n">
         <v>1007</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
         <v>643</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="n">
+      <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="R22" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="S22" s="3" t="n">
         <v>554</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="T22" s="3" t="n">
         <v>1508</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="U22" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2073,38 +2090,32 @@
           <t>8O</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="H23" s="3" t="n">
         <v>604</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="I23" s="4" t="n">
         <v>83.84999999999999</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>INCONNU (604)</t>
         </is>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="N23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" s="3" t="n">
         <v>0</v>
       </c>
@@ -2112,9 +2123,15 @@
         <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="S23" s="3" t="n">
+      <c r="U23" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2134,26 +2151,20 @@
           <t>?</t>
         </is>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="H24" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>255.07</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (159)</t>
         </is>
       </c>
-      <c r="I24" s="5" t="n">
+      <c r="K24" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" s="3" t="n">
         <v>0</v>
       </c>
@@ -2176,6 +2187,12 @@
         <v>0</v>
       </c>
       <c r="S24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="n">
         <v>159</v>
       </c>
     </row>
@@ -2200,38 +2217,32 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="H25" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="I25" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
         </is>
       </c>
-      <c r="I25" s="5" t="n">
+      <c r="K25" s="5" t="n">
         <v>47.8</v>
       </c>
-      <c r="J25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P25" s="3" t="n">
         <v>0</v>
       </c>
@@ -2239,9 +2250,15 @@
         <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="U25" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2271,48 +2288,53 @@
           <t>1G</t>
         </is>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_CAD </t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>515</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="I26" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="L26" s="3" t="n">
         <v>247</v>
       </c>
-      <c r="K26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3" t="n">
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="O26" s="3" t="n">
         <v>433</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="T26" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="S26" s="3" t="n">
+      <c r="U26" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2342,26 +2364,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="F27" s="3" t="n">
+      <c r="H27" s="3" t="n">
         <v>18982</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="I27" s="4" t="n">
         <v>315.8</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
         </is>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="K27" s="5" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="J27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" s="3" t="n">
         <v>0</v>
       </c>
@@ -2381,9 +2397,15 @@
         <v>0</v>
       </c>
       <c r="R27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3" t="n">
         <v>18982</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="U27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2413,48 +2435,48 @@
           <t>4H</t>
         </is>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="H28" s="3" t="n">
         <v>358</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="I28" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
         </is>
       </c>
-      <c r="I28" s="5" t="n">
+      <c r="K28" s="5" t="n">
         <v>73.7</v>
       </c>
-      <c r="J28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="N28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="S28" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="T28" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="U28" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2484,48 +2506,53 @@
           <t>1D</t>
         </is>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_DEL </t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>170586</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="I29" s="4" t="n">
         <v>2435.11</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (122555) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (398) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
+      <c r="K29" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="L29" s="3" t="n">
         <v>122552</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3" t="n">
+      <c r="M29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="O29" s="3" t="n">
         <v>23676</v>
       </c>
-      <c r="N29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>140</v>
-      </c>
       <c r="P29" s="3" t="n">
-        <v>79005</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>140</v>
       </c>
       <c r="R29" s="3" t="n">
+        <v>79005</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="T29" s="3" t="n">
         <v>67624</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="U29" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2555,38 +2582,32 @@
           <t>9Fi</t>
         </is>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="H30" s="3" t="n">
         <v>1761</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="I30" s="4" t="n">
         <v>44.68</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
         </is>
       </c>
-      <c r="I30" s="5" t="n">
+      <c r="K30" s="5" t="n">
         <v>49.9</v>
       </c>
-      <c r="J30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3" t="n">
         <v>879</v>
       </c>
-      <c r="N30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P30" s="3" t="n">
         <v>0</v>
       </c>
@@ -2594,9 +2615,15 @@
         <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3" t="n">
         <v>882</v>
       </c>
-      <c r="S30" s="3" t="n">
+      <c r="U30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2626,48 +2653,48 @@
           <t>E</t>
         </is>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="H31" s="3" t="n">
         <v>358109</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>760.01</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (249012) ; CORBEILLE (85333) ; INCONNU (23761) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="I31" s="5" t="n">
+      <c r="K31" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="J31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="O31" s="3" t="n">
         <v>358080</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="3" t="n">
+      <c r="P31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="P31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2692,38 +2719,32 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="H32" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="K32" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="N32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P32" s="3" t="n">
         <v>0</v>
       </c>
@@ -2734,6 +2755,12 @@
         <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2763,48 +2790,53 @@
           <t>5H</t>
         </is>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_GUE </t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
         <v>678</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="I33" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (678)</t>
         </is>
       </c>
-      <c r="I33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="n">
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>678</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3" t="n">
         <v>339</v>
       </c>
-      <c r="N33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3" t="n">
         <v>339</v>
       </c>
-      <c r="Q33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2834,38 +2866,37 @@
           <t>11J</t>
         </is>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_LEB </t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="I34" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
         </is>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="K34" s="5" t="n">
         <v>48.9</v>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P34" s="3" t="n">
         <v>0</v>
       </c>
@@ -2873,9 +2904,15 @@
         <v>0</v>
       </c>
       <c r="R34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="S34" s="3" t="n">
+      <c r="U34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2905,38 +2942,32 @@
           <t>3O</t>
         </is>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="H35" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="K35" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="J35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="O35" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
@@ -2944,9 +2975,15 @@
         <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="U35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2976,29 +3013,28 @@
           <t>1Obj</t>
         </is>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_OBJ </t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="I36" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="K36" s="5" t="n">
         <v>96.2</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="L36" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" s="3" t="n">
         <v>0</v>
       </c>
@@ -3015,9 +3051,15 @@
         <v>0</v>
       </c>
       <c r="R36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="S36" s="3" t="n">
+      <c r="U36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3047,38 +3089,32 @@
           <t>J ?</t>
         </is>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="H37" s="3" t="n">
         <v>8812</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>21.27</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (6428) ; À SUPPRIMER (doublons S3 - az) (1901) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (RENOMMAGE) (238)</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="K37" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="3" t="n">
         <v>7093</v>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P37" s="3" t="n">
         <v>0</v>
       </c>
@@ -3086,9 +3122,15 @@
         <v>0</v>
       </c>
       <c r="R37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="3" t="n">
         <v>1719</v>
       </c>
-      <c r="S37" s="3" t="n">
+      <c r="U37" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3113,38 +3155,32 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="H38" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>3.87</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="K38" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="N38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" s="3" t="n">
         <v>0</v>
       </c>
@@ -3155,6 +3191,12 @@
         <v>0</v>
       </c>
       <c r="S38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3179,38 +3221,37 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PHO </t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="n">
         <v>18595</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="I39" s="4" t="n">
         <v>135.98</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>INCONNU (9293) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="I39" s="5" t="n">
+      <c r="K39" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="L39" s="3" t="n">
         <v>1194</v>
       </c>
-      <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="3" t="n">
+      <c r="M39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="O39" s="3" t="n">
         <v>8035</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" s="3" t="n">
         <v>0</v>
       </c>
@@ -3218,9 +3259,15 @@
         <v>0</v>
       </c>
       <c r="R39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="3" t="n">
         <v>10558</v>
       </c>
-      <c r="S39" s="3" t="n">
+      <c r="U39" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3245,38 +3292,37 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PLA </t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>376</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="I40" s="4" t="n">
         <v>48.9</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n">
+      <c r="K40" s="5" t="n">
         <v>35.1</v>
       </c>
-      <c r="J40" s="3" t="n">
+      <c r="L40" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P40" s="3" t="n">
         <v>0</v>
       </c>
@@ -3284,9 +3330,15 @@
         <v>0</v>
       </c>
       <c r="R40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="S40" s="3" t="n">
+      <c r="U40" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3316,48 +3368,48 @@
           <t>1F</t>
         </is>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="H41" s="3" t="n">
         <v>122308</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="I41" s="4" t="n">
         <v>504.56</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (85759) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n">
+      <c r="K41" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="L41" s="3" t="n">
         <v>65349</v>
       </c>
-      <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3" t="n">
         <v>114168</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="n">
+      <c r="P41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+      <c r="R41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="T41" s="3" t="n">
         <v>8135</v>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="U41" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3382,48 +3434,53 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PR </t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>4326</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>166.36</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n">
+      <c r="K42" s="5" t="n">
         <v>27.8</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="L42" s="3" t="n">
         <v>668</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="n">
+      <c r="M42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="O42" s="3" t="n">
         <v>786</v>
       </c>
-      <c r="N42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3" t="n">
+      <c r="S42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3" t="n">
         <v>3533</v>
       </c>
-      <c r="S42" s="3" t="n">
+      <c r="U42" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3453,48 +3510,53 @@
           <t>58-59PER</t>
         </is>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PUV </t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>19188</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="I43" s="4" t="n">
         <v>338.52</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>INCONNU (16034) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="K43" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="J43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="O43" s="3" t="n">
         <v>6302</v>
       </c>
-      <c r="N43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P43" s="3" t="n">
-        <v>6302</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>6302</v>
       </c>
       <c r="S43" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>6302</v>
+      </c>
+      <c r="U43" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3524,38 +3586,32 @@
           <t>8Fi</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="H44" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="I44" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="n">
+      <c r="K44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P44" s="3" t="n">
         <v>0</v>
       </c>
@@ -3563,9 +3619,15 @@
         <v>0</v>
       </c>
       <c r="R44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="S44" s="3" t="n">
+      <c r="U44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,48 +3657,48 @@
           <t>246W</t>
         </is>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="H45" s="3" t="n">
         <v>19170</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="I45" s="4" t="n">
         <v>42.81</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
         </is>
       </c>
-      <c r="I45" s="5" t="n">
+      <c r="K45" s="5" t="n">
         <v>49.3</v>
       </c>
-      <c r="J45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3" t="n">
         <v>9444</v>
       </c>
-      <c r="N45" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>141</v>
-      </c>
       <c r="P45" s="3" t="n">
-        <v>9444</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>141</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>0</v>
+        <v>9444</v>
       </c>
       <c r="S45" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3666,29 +3728,28 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_RAM </t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>37053</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="I46" s="4" t="n">
         <v>448.11</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (37053)</t>
         </is>
       </c>
-      <c r="I46" s="5" t="n">
+      <c r="K46" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="L46" s="3" t="n">
         <v>37053</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M46" s="3" t="n">
         <v>0</v>
       </c>
@@ -3699,15 +3760,21 @@
         <v>0</v>
       </c>
       <c r="P46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3" t="n">
         <v>18527</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="n">
+      <c r="S46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3" t="n">
         <v>18526</v>
       </c>
-      <c r="S46" s="3" t="n">
+      <c r="U46" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3727,38 +3794,32 @@
           <t>?</t>
         </is>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="H47" s="3" t="n">
         <v>449</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>5.17</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
         </is>
       </c>
-      <c r="I47" s="5" t="n">
+      <c r="K47" s="5" t="n">
         <v>42.8</v>
       </c>
-      <c r="J47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="N47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P47" s="3" t="n">
         <v>0</v>
       </c>
@@ -3766,9 +3827,15 @@
         <v>0</v>
       </c>
       <c r="R47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="S47" s="3" t="n">
+      <c r="U47" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3798,38 +3865,37 @@
           <t>5H</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_VIC </t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="n">
         <v>7072</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="I48" s="4" t="n">
         <v>12.12</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>INCONNU (7072)</t>
         </is>
       </c>
-      <c r="I48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3" t="n">
+      <c r="K48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3" t="n">
         <v>7072</v>
       </c>
-      <c r="N48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
       </c>
@@ -3840,6 +3906,12 @@
         <v>0</v>
       </c>
       <c r="S48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3854,38 +3926,37 @@
           <t>ARA - Cartes postales sonores de l'ARA</t>
         </is>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_ARA_CPS </t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="I49" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
         </is>
       </c>
-      <c r="I49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="n">
+      <c r="K49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="K49" s="3" t="n">
+      <c r="M49" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="L49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="n">
+      <c r="N49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="N49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P49" s="3" t="n">
         <v>0</v>
       </c>
@@ -3896,6 +3967,12 @@
         <v>0</v>
       </c>
       <c r="S49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3910,29 +3987,28 @@
           <t>Conservatoire - Palmarès annuels</t>
         </is>
       </c>
-      <c r="F50" s="3" t="n">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_CSV_PAL </t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="I50" s="4" t="n">
         <v>6.65</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (242)</t>
         </is>
       </c>
-      <c r="I50" s="5" t="n">
+      <c r="K50" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J50" s="3" t="n">
+      <c r="L50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="K50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M50" s="3" t="n">
         <v>0</v>
       </c>
@@ -3949,9 +4025,15 @@
         <v>0</v>
       </c>
       <c r="R50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="S50" s="3" t="n">
+      <c r="U50" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3966,29 +4048,28 @@
           <t>Association des Amis de la Lainière et du Textile - Collection</t>
         </is>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_LAI </t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="n">
         <v>2422</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>61.97</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1697) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
         </is>
       </c>
-      <c r="I51" s="5" t="n">
+      <c r="K51" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="J51" s="3" t="n">
+      <c r="L51" s="3" t="n">
         <v>1181</v>
       </c>
-      <c r="K51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" s="3" t="n">
         <v>0</v>
       </c>
@@ -3996,18 +4077,24 @@
         <v>0</v>
       </c>
       <c r="O51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3" t="n">
         <v>2421</v>
       </c>
-      <c r="S51" s="3" t="n">
+      <c r="U51" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4022,29 +4109,28 @@
           <t>Lire à Roubaix - Publications</t>
         </is>
       </c>
-      <c r="F52" s="3" t="n">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_LAR_PUB </t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="I52" s="4" t="n">
         <v>18.33</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
         </is>
       </c>
-      <c r="I52" s="5" t="n">
+      <c r="K52" s="5" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="J52" s="3" t="n">
+      <c r="L52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="K52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M52" s="3" t="n">
         <v>0</v>
       </c>
@@ -4061,9 +4147,15 @@
         <v>0</v>
       </c>
       <c r="R52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="S52" s="3" t="n">
+      <c r="U52" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4078,29 +4170,28 @@
           <t>Manufacture des Flandres - Collectes de la mémoire des travailleurs du textile</t>
         </is>
       </c>
-      <c r="F53" s="3" t="n">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MDF_MTX </t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="I53" s="4" t="n">
         <v>76.03</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (18)</t>
         </is>
       </c>
-      <c r="I53" s="5" t="n">
+      <c r="K53" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J53" s="3" t="n">
+      <c r="L53" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="K53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M53" s="3" t="n">
         <v>0</v>
       </c>
@@ -4120,6 +4211,12 @@
         <v>0</v>
       </c>
       <c r="S53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4134,38 +4231,37 @@
           <t>Médiathèque - Affiches de la Médiathèque</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_AFF </t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="n">
         <v>11038</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="I54" s="4" t="n">
         <v>529.5599999999999</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (5576) ; CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (175) ; INCONNU (111)</t>
         </is>
       </c>
-      <c r="I54" s="5" t="n">
+      <c r="K54" s="5" t="n">
         <v>48.5</v>
       </c>
-      <c r="J54" s="3" t="n">
+      <c r="L54" s="3" t="n">
         <v>5742</v>
       </c>
-      <c r="K54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3" t="n">
         <v>5176</v>
       </c>
-      <c r="N54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P54" s="3" t="n">
         <v>0</v>
       </c>
@@ -4173,9 +4269,15 @@
         <v>0</v>
       </c>
       <c r="R54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="3" t="n">
         <v>5862</v>
       </c>
-      <c r="S54" s="3" t="n">
+      <c r="U54" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4190,35 +4292,29 @@
           <t>Médiathèque - Vidéos</t>
         </is>
       </c>
-      <c r="F55" s="3" t="n">
+      <c r="H55" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="I55" s="4" t="n">
         <v>48.21</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n">
+      <c r="K55" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O55" s="3" t="n">
         <v>0</v>
       </c>
@@ -4232,6 +4328,12 @@
         <v>0</v>
       </c>
       <c r="S55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="3" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4246,29 +4348,28 @@
           <t>Médiathèque - Chansons de la Médiathèque de Roubaix</t>
         </is>
       </c>
-      <c r="F56" s="3" t="n">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_CHA </t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="I56" s="4" t="n">
         <v>17.58</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="K56" s="5" t="n">
         <v>50.2</v>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="L56" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="K56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M56" s="3" t="n">
         <v>0</v>
       </c>
@@ -4285,9 +4386,15 @@
         <v>0</v>
       </c>
       <c r="R56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="S56" s="3" t="n">
+      <c r="U56" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4302,48 +4409,53 @@
           <t>Médiathèque - Cartes postales de Roubaix</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_CP </t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="I57" s="4" t="n">
         <v>34.89</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (4534) ; INCONNU (651) ; À SUPPRIMER (doublons S3 - az) (536) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
         </is>
       </c>
-      <c r="I57" s="5" t="n">
+      <c r="K57" s="5" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="J57" s="3" t="n">
+      <c r="L57" s="3" t="n">
         <v>4672</v>
       </c>
-      <c r="K57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3" t="n">
         <v>307</v>
       </c>
-      <c r="N57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="n">
+      <c r="P57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3" t="n">
         <v>5702</v>
       </c>
-      <c r="S57" s="3" t="n">
+      <c r="U57" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4358,38 +4470,37 @@
           <t>Médiathèque - Fonds d'archives d'André Diligent</t>
         </is>
       </c>
-      <c r="F58" s="3" t="n">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_DIL </t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="I58" s="4" t="n">
         <v>480.6</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
         </is>
       </c>
-      <c r="I58" s="5" t="n">
+      <c r="K58" s="5" t="n">
         <v>12.1</v>
       </c>
-      <c r="J58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="M58" s="3" t="n">
+      <c r="O58" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="N58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P58" s="3" t="n">
         <v>0</v>
       </c>
@@ -4397,9 +4508,15 @@
         <v>0</v>
       </c>
       <c r="R58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="S58" s="3" t="n">
+      <c r="U58" s="3" t="n">
         <v>177</v>
       </c>
     </row>
@@ -4414,29 +4531,28 @@
           <t>Médiathèque - Ephémères de la Médiathèque</t>
         </is>
       </c>
-      <c r="F59" s="3" t="n">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_EPH </t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="n">
         <v>846</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="I59" s="4" t="n">
         <v>10.17</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="n">
+      <c r="K59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="K59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M59" s="3" t="n">
         <v>0</v>
       </c>
@@ -4453,9 +4569,15 @@
         <v>0</v>
       </c>
       <c r="R59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3" t="n">
         <v>846</v>
       </c>
-      <c r="S59" s="3" t="n">
+      <c r="U59" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4470,24 +4592,18 @@
           <t>Médiathèque - Cartes postales fantaisie</t>
         </is>
       </c>
-      <c r="F60" s="3" t="n">
+      <c r="H60" s="3" t="n">
         <v>2666</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="I60" s="4" t="n">
         <v>32.93</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>INCONNU (2666)</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="3" t="n">
+      <c r="K60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="3" t="n">
@@ -4509,9 +4625,15 @@
         <v>0</v>
       </c>
       <c r="R60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3" t="n">
         <v>2666</v>
       </c>
-      <c r="S60" s="3" t="n">
+      <c r="U60" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4526,38 +4648,37 @@
           <t>Médiathèque - Documents sonores régionaux</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n">
-        <v>8485</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>303.24</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (8485)</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="n">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_FLR </t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>8487</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>304.96</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (8487)</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J61" s="3" t="n">
+      <c r="L61" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K61" s="3" t="n">
-        <v>7226</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M61" s="3" t="n">
+        <v>7228</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3" t="n">
         <v>478</v>
       </c>
-      <c r="N61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P61" s="3" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4686,15 @@
         <v>0</v>
       </c>
       <c r="R61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3" t="n">
         <v>781</v>
       </c>
-      <c r="S61" s="3" t="n">
+      <c r="U61" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4582,38 +4709,37 @@
           <t>Médiathèque - Souvenirs de foot</t>
         </is>
       </c>
-      <c r="F62" s="3" t="n">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_FOO </t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="I62" s="5" t="n">
+      <c r="K62" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="J62" s="3" t="n">
+      <c r="L62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K62" s="3" t="n">
+      <c r="M62" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="L62" s="3" t="n">
+      <c r="N62" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M62" s="3" t="n">
+      <c r="O62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P62" s="3" t="n">
         <v>0</v>
       </c>
@@ -4624,6 +4750,12 @@
         <v>0</v>
       </c>
       <c r="S62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4638,38 +4770,37 @@
           <t>Médiathèque - Imagettes de la Médiathèque</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_IMA </t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="n">
         <v>9856</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="I63" s="4" t="n">
         <v>131.47</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (8900) ; TRANSFERT_S3_OK (750) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45)</t>
         </is>
       </c>
-      <c r="I63" s="5" t="n">
+      <c r="K63" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J63" s="3" t="n">
+      <c r="L63" s="3" t="n">
         <v>9623</v>
       </c>
-      <c r="K63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="N63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P63" s="3" t="n">
         <v>0</v>
       </c>
@@ -4677,9 +4808,15 @@
         <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3" t="n">
         <v>9631</v>
       </c>
-      <c r="S63" s="3" t="n">
+      <c r="U63" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4694,26 +4831,20 @@
           <t>Médiathèque - Journaux</t>
         </is>
       </c>
-      <c r="F64" s="3" t="n">
+      <c r="H64" s="3" t="n">
         <v>2174</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="I64" s="4" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n">
+      <c r="K64" s="5" t="n">
         <v>91.8</v>
       </c>
-      <c r="J64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
       </c>
@@ -4733,9 +4864,15 @@
         <v>0</v>
       </c>
       <c r="R64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3" t="n">
         <v>2174</v>
       </c>
-      <c r="S64" s="3" t="n">
+      <c r="U64" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4750,29 +4887,28 @@
           <t>Médiathèque - Lettres à en-tête des commerces et industries roubaisiens</t>
         </is>
       </c>
-      <c r="F65" s="3" t="n">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_LET </t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="I65" s="4" t="n">
         <v>12.84</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (605)</t>
         </is>
       </c>
-      <c r="I65" s="5" t="n">
+      <c r="K65" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J65" s="3" t="n">
+      <c r="L65" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="K65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M65" s="3" t="n">
         <v>0</v>
       </c>
@@ -4789,9 +4925,15 @@
         <v>0</v>
       </c>
       <c r="R65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="S65" s="3" t="n">
+      <c r="U65" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4806,38 +4948,37 @@
           <t>Médiathèque - Marionnettes</t>
         </is>
       </c>
-      <c r="F66" s="3" t="n">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_MAR </t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="I66" s="4" t="n">
         <v>7.07</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
         </is>
       </c>
-      <c r="I66" s="5" t="n">
+      <c r="K66" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="L66" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="K66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="N66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P66" s="3" t="n">
         <v>0</v>
       </c>
@@ -4845,9 +4986,15 @@
         <v>0</v>
       </c>
       <c r="R66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="S66" s="3" t="n">
+      <c r="U66" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4862,29 +5009,28 @@
           <t>Médiathèque - Livres et brochures</t>
         </is>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_MON </t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="n">
         <v>7553</v>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="I67" s="4" t="n">
         <v>205.74</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n">
+      <c r="K67" s="5" t="n">
         <v>98.8</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="L67" s="3" t="n">
         <v>1384</v>
       </c>
-      <c r="K67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
       </c>
@@ -4895,15 +5041,21 @@
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="3" t="n">
         <v>2721</v>
       </c>
-      <c r="Q67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="3" t="n">
+      <c r="S67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="3" t="n">
         <v>4832</v>
       </c>
-      <c r="S67" s="3" t="n">
+      <c r="U67" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4918,38 +5070,37 @@
           <t>Médiathèque - Manuscrits de la Médiathèque de Roubaix</t>
         </is>
       </c>
-      <c r="F68" s="3" t="n">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_MS </t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="n">
         <v>46262</v>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="I68" s="4" t="n">
         <v>1061.94</v>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n">
+      <c r="K68" s="5" t="n">
         <v>92.2</v>
       </c>
-      <c r="J68" s="3" t="n">
+      <c r="L68" s="3" t="n">
         <v>33302</v>
       </c>
-      <c r="K68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3" t="n">
         <v>12786</v>
       </c>
-      <c r="N68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P68" s="3" t="n">
         <v>0</v>
       </c>
@@ -4957,9 +5108,15 @@
         <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3" t="n">
         <v>33476</v>
       </c>
-      <c r="S68" s="3" t="n">
+      <c r="U68" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4974,24 +5131,18 @@
           <t>Médiathèque - Documents non patrimoniaux</t>
         </is>
       </c>
-      <c r="F69" s="3" t="n">
+      <c r="H69" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="I69" s="4" t="n">
         <v>17.09</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3" t="n">
+      <c r="K69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="3" t="n">
@@ -5016,6 +5167,12 @@
         <v>0</v>
       </c>
       <c r="S69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5030,38 +5187,37 @@
           <t>Médiathèque - Collections de particuliers</t>
         </is>
       </c>
-      <c r="F70" s="3" t="n">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PAR </t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="n">
         <v>5769</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="I70" s="4" t="n">
         <v>93.51000000000001</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (5035) ; À SUPPRIMER (686) ; CORBEILLE (DIFFUSION) (21) ; INCONNU (20) ; EN LIGNE - À TRANSFERER ? (6) ; À SUPPRIMER (RENOMMAGE) (1)</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n">
+      <c r="K70" s="5" t="n">
         <v>99.5</v>
       </c>
-      <c r="J70" s="3" t="n">
+      <c r="L70" s="3" t="n">
         <v>5041</v>
       </c>
-      <c r="K70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3" t="n">
         <v>292</v>
       </c>
-      <c r="N70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P70" s="3" t="n">
         <v>0</v>
       </c>
@@ -5069,9 +5225,15 @@
         <v>0</v>
       </c>
       <c r="R70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3" t="n">
         <v>5477</v>
       </c>
-      <c r="S70" s="3" t="n">
+      <c r="U70" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5086,24 +5248,18 @@
           <t>Médiathèque - Collections de particuliers (suite)</t>
         </is>
       </c>
-      <c r="F71" s="3" t="n">
+      <c r="H71" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="I71" s="4" t="n">
         <v>7.94</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>INCONNU (1084)</t>
         </is>
       </c>
-      <c r="I71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="3" t="n">
+      <c r="K71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
@@ -5125,9 +5281,15 @@
         <v>0</v>
       </c>
       <c r="R71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="S71" s="3" t="n">
+      <c r="U71" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5142,26 +5304,20 @@
           <t>Médiathèque - Périodiques</t>
         </is>
       </c>
-      <c r="F72" s="3" t="n">
+      <c r="H72" s="3" t="n">
         <v>1596</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="I72" s="4" t="n">
         <v>29.68</v>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1596)</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n">
+      <c r="K72" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" s="3" t="n">
         <v>0</v>
       </c>
@@ -5175,15 +5331,21 @@
         <v>0</v>
       </c>
       <c r="P72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3" t="n">
         <v>829</v>
       </c>
-      <c r="Q72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" s="3" t="n">
+      <c r="S72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3" t="n">
         <v>767</v>
       </c>
-      <c r="S72" s="3" t="n">
+      <c r="U72" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5198,24 +5360,18 @@
           <t>Médiathèque - Collections de photographies</t>
         </is>
       </c>
-      <c r="F73" s="3" t="n">
+      <c r="H73" s="3" t="n">
         <v>1949</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="I73" s="4" t="n">
         <v>28.52</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>INCONNU (1949)</t>
         </is>
       </c>
-      <c r="I73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3" t="n">
+      <c r="K73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="3" t="n">
@@ -5237,9 +5393,15 @@
         <v>0</v>
       </c>
       <c r="R73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3" t="n">
         <v>1949</v>
       </c>
-      <c r="S73" s="3" t="n">
+      <c r="U73" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5254,48 +5416,53 @@
           <t>Médiathèque - Regards de photographes</t>
         </is>
       </c>
-      <c r="F74" s="3" t="n">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PHO </t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="n">
         <v>18844</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="I74" s="4" t="n">
         <v>69.83</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n">
+      <c r="K74" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="J74" s="3" t="n">
+      <c r="L74" s="3" t="n">
         <v>1140</v>
       </c>
-      <c r="K74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="3" t="n">
+      <c r="M74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="M74" s="3" t="n">
+      <c r="O74" s="3" t="n">
         <v>13861</v>
       </c>
-      <c r="N74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R74" s="3" t="n">
+      <c r="T74" s="3" t="n">
         <v>4804</v>
       </c>
-      <c r="S74" s="3" t="n">
+      <c r="U74" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5310,38 +5477,37 @@
           <t>Médiathèque - Collection des cartes et plans de la Médiathèque</t>
         </is>
       </c>
-      <c r="F75" s="3" t="n">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PLA </t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="n">
         <v>548</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="I75" s="4" t="n">
         <v>38.23</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n">
+      <c r="K75" s="5" t="n">
         <v>49.8</v>
       </c>
-      <c r="J75" s="3" t="n">
+      <c r="L75" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="K75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="N75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
       </c>
@@ -5349,9 +5515,15 @@
         <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="S75" s="3" t="n">
+      <c r="U75" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5366,29 +5538,28 @@
           <t>Médiathèque - Publications de la Médiathèque</t>
         </is>
       </c>
-      <c r="F76" s="3" t="n">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PUB </t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="I76" s="4" t="n">
         <v>49.96</v>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (2419)</t>
         </is>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="3" t="n">
+      <c r="K76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="K76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M76" s="3" t="n">
         <v>0</v>
       </c>
@@ -5405,9 +5576,15 @@
         <v>0</v>
       </c>
       <c r="R76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="S76" s="3" t="n">
+      <c r="U76" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5422,24 +5599,18 @@
           <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
-      <c r="F77" s="3" t="n">
+      <c r="H77" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="I77" s="4" t="n">
         <v>9.57</v>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>INCONNU (238)</t>
         </is>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3" t="n">
+      <c r="K77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="3" t="n">
@@ -5461,9 +5632,15 @@
         <v>0</v>
       </c>
       <c r="R77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="S77" s="3" t="n">
+      <c r="U77" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5478,48 +5655,53 @@
           <t>Médiathèque - Fonds d'archives de Maxence Van der Meersch</t>
         </is>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_VDM </t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="n">
         <v>38231</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="I78" s="4" t="n">
         <v>956.36</v>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I78" s="5" t="n">
+      <c r="K78" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J78" s="3" t="n">
+      <c r="L78" s="3" t="n">
         <v>31272</v>
       </c>
-      <c r="K78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="3" t="n">
+      <c r="M78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="3" t="n">
         <v>38229</v>
       </c>
-      <c r="S78" s="3" t="n">
+      <c r="U78" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5534,35 +5716,29 @@
           <t>Médiathèque - Documents vidéos</t>
         </is>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="H79" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="I79" s="4" t="n">
         <v>8.82</v>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
         </is>
       </c>
-      <c r="I79" s="5" t="n">
+      <c r="K79" s="5" t="n">
         <v>48.4</v>
       </c>
-      <c r="J79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O79" s="3" t="n">
         <v>0</v>
       </c>
@@ -5570,12 +5746,18 @@
         <v>0</v>
       </c>
       <c r="Q79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" s="3" t="n">
+      <c r="T79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5590,38 +5772,37 @@
           <t>Musée La Piscine - Archives</t>
         </is>
       </c>
-      <c r="F80" s="3" t="n">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MUS_ARC </t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="n">
         <v>318</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="I80" s="4" t="n">
         <v>3.42</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (318)</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n">
+      <c r="K80" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J80" s="3" t="n">
+      <c r="L80" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="K80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="N80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P80" s="3" t="n">
         <v>0</v>
       </c>
@@ -5629,9 +5810,15 @@
         <v>0</v>
       </c>
       <c r="R80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="S80" s="3" t="n">
+      <c r="U80" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5646,38 +5833,37 @@
           <t>Musée La Piscine - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MUS_VAI </t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="n">
         <v>1918</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="I81" s="4" t="n">
         <v>47.42</v>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1918)</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n">
+      <c r="K81" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J81" s="3" t="n">
+      <c r="L81" s="3" t="n">
         <v>1859</v>
       </c>
-      <c r="K81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="N81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P81" s="3" t="n">
         <v>0</v>
       </c>
@@ -5685,9 +5871,15 @@
         <v>0</v>
       </c>
       <c r="R81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="3" t="n">
         <v>1514</v>
       </c>
-      <c r="S81" s="3" t="n">
+      <c r="U81" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5702,38 +5894,32 @@
           <t>Musée La Piscine - nouveau versement</t>
         </is>
       </c>
-      <c r="F82" s="3" t="n">
+      <c r="H82" s="3" t="n">
         <v>375</v>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="I82" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>INCONNU (375)</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3" t="n">
+      <c r="K82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="3" t="n">
         <v>375</v>
       </c>
-      <c r="N82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P82" s="3" t="n">
         <v>0</v>
       </c>
@@ -5744,6 +5930,12 @@
         <v>0</v>
       </c>
       <c r="S82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5758,48 +5950,53 @@
           <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
         </is>
       </c>
-      <c r="F83" s="3" t="n">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_OBS_JOU </t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="n">
         <v>2802</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="I83" s="4" t="n">
         <v>31.32</v>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1925) ; EN LIGNE - À TRANSFERER ? (868) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (4)</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n">
+      <c r="K83" s="5" t="n">
         <v>68.8</v>
       </c>
-      <c r="J83" s="3" t="n">
+      <c r="L83" s="3" t="n">
         <v>2238</v>
       </c>
-      <c r="K83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="n">
         <v>1808</v>
       </c>
-      <c r="N83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="R83" s="3" t="n">
+      <c r="T83" s="3" t="n">
         <v>920</v>
       </c>
-      <c r="S83" s="3" t="n">
+      <c r="U83" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5814,29 +6011,23 @@
           <t>Particuliers - Bohée</t>
         </is>
       </c>
-      <c r="F84" s="3" t="n">
+      <c r="H84" s="3" t="n">
         <v>638</v>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="I84" s="4" t="n">
         <v>17.59</v>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (638)</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n">
+      <c r="K84" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J84" s="3" t="n">
+      <c r="L84" s="3" t="n">
         <v>382</v>
       </c>
-      <c r="K84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M84" s="3" t="n">
         <v>0</v>
       </c>
@@ -5853,9 +6044,15 @@
         <v>0</v>
       </c>
       <c r="R84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3" t="n">
         <v>638</v>
       </c>
-      <c r="S84" s="3" t="n">
+      <c r="U84" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5870,29 +6067,23 @@
           <t>Particuliers - Boussac</t>
         </is>
       </c>
-      <c r="F85" s="3" t="n">
+      <c r="H85" s="3" t="n">
         <v>8790</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="I85" s="4" t="n">
         <v>331.23</v>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (8790)</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n">
+      <c r="K85" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J85" s="3" t="n">
+      <c r="L85" s="3" t="n">
         <v>8435</v>
       </c>
-      <c r="K85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M85" s="3" t="n">
         <v>0</v>
       </c>
@@ -5909,9 +6100,15 @@
         <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3" t="n">
         <v>8790</v>
       </c>
-      <c r="S85" s="3" t="n">
+      <c r="U85" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5926,38 +6123,32 @@
           <t>Particuliers - Catrice</t>
         </is>
       </c>
-      <c r="F86" s="3" t="n">
+      <c r="H86" s="3" t="n">
         <v>265</v>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="I86" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (265)</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="n">
+      <c r="K86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3" t="n">
         <v>265</v>
       </c>
-      <c r="K86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="N86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P86" s="3" t="n">
         <v>0</v>
       </c>
@@ -5965,9 +6156,15 @@
         <v>0</v>
       </c>
       <c r="R86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="S86" s="3" t="n">
+      <c r="U86" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5982,29 +6179,23 @@
           <t>Particuliers - Chirez</t>
         </is>
       </c>
-      <c r="F87" s="3" t="n">
+      <c r="H87" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="I87" s="4" t="n">
         <v>1.7</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (89)</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n">
+      <c r="K87" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J87" s="3" t="n">
+      <c r="L87" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="K87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M87" s="3" t="n">
         <v>0</v>
       </c>
@@ -6021,9 +6212,15 @@
         <v>0</v>
       </c>
       <c r="R87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="S87" s="3" t="n">
+      <c r="U87" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6038,29 +6235,23 @@
           <t>Particuliers - Dedaele</t>
         </is>
       </c>
-      <c r="F88" s="3" t="n">
+      <c r="H88" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="I88" s="4" t="n">
         <v>0.24</v>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (40)</t>
         </is>
       </c>
-      <c r="I88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="n">
+      <c r="K88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="K88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M88" s="3" t="n">
         <v>0</v>
       </c>
@@ -6077,9 +6268,15 @@
         <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="S88" s="3" t="n">
+      <c r="U88" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6094,29 +6291,23 @@
           <t>Particuliers - Latu</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n">
+      <c r="H89" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="I89" s="4" t="n">
         <v>0.89</v>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (35)</t>
         </is>
       </c>
-      <c r="I89" s="5" t="n">
+      <c r="K89" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="L89" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="K89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M89" s="3" t="n">
         <v>0</v>
       </c>
@@ -6133,9 +6324,15 @@
         <v>0</v>
       </c>
       <c r="R89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="S89" s="3" t="n">
+      <c r="U89" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,38 +6347,32 @@
           <t>Particuliers - Une Roubaisienne</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="H90" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="I90" s="4" t="n">
         <v>1.69</v>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (96)</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="3" t="n">
+      <c r="K90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="K90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="N90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P90" s="3" t="n">
         <v>0</v>
       </c>
@@ -6192,6 +6383,12 @@
         <v>0</v>
       </c>
       <c r="S90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6206,29 +6403,23 @@
           <t>Particuliers - Najberg</t>
         </is>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="H91" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="I91" s="4" t="n">
         <v>6.59</v>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (23)</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n">
+      <c r="K91" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J91" s="3" t="n">
+      <c r="L91" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="K91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M91" s="3" t="n">
         <v>0</v>
       </c>
@@ -6245,9 +6436,15 @@
         <v>0</v>
       </c>
       <c r="R91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S91" s="3" t="n">
+      <c r="U91" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6262,29 +6459,23 @@
           <t>Particuliers - Nielsen</t>
         </is>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="H92" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="I92" s="4" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (148)</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n">
+      <c r="K92" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J92" s="3" t="n">
+      <c r="L92" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
       </c>
@@ -6301,9 +6492,15 @@
         <v>0</v>
       </c>
       <c r="R92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="S92" s="3" t="n">
+      <c r="U92" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6318,38 +6515,32 @@
           <t>Particuliers - Prevost</t>
         </is>
       </c>
-      <c r="F93" s="3" t="n">
+      <c r="H93" s="3" t="n">
         <v>3710</v>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="I93" s="4" t="n">
         <v>4.42</v>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (3414) ; INCONNU (296)</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="n">
+      <c r="K93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3" t="n">
         <v>3414</v>
       </c>
-      <c r="K93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="3" t="n">
+      <c r="M93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="M93" s="3" t="n">
+      <c r="O93" s="3" t="n">
         <v>3233</v>
       </c>
-      <c r="N93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P93" s="3" t="n">
         <v>0</v>
       </c>
@@ -6357,9 +6548,15 @@
         <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3" t="n">
         <v>475</v>
       </c>
-      <c r="S93" s="3" t="n">
+      <c r="U93" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6374,29 +6571,23 @@
           <t>Particuliers - Destombes</t>
         </is>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="H94" s="3" t="n">
         <v>524</v>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="I94" s="4" t="n">
         <v>8.279999999999999</v>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (524)</t>
         </is>
       </c>
-      <c r="I94" s="5" t="n">
+      <c r="K94" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J94" s="3" t="n">
+      <c r="L94" s="3" t="n">
         <v>524</v>
       </c>
-      <c r="K94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M94" s="3" t="n">
         <v>0</v>
       </c>
@@ -6413,9 +6604,15 @@
         <v>0</v>
       </c>
       <c r="R94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="n">
         <v>524</v>
       </c>
-      <c r="S94" s="3" t="n">
+      <c r="U94" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6430,38 +6627,32 @@
           <t>Particuliers - Termeulen</t>
         </is>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="H95" s="3" t="n">
         <v>884</v>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="I95" s="4" t="n">
         <v>0.43</v>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (884)</t>
         </is>
       </c>
-      <c r="I95" s="5" t="n">
+      <c r="K95" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J95" s="3" t="n">
+      <c r="L95" s="3" t="n">
         <v>884</v>
       </c>
-      <c r="K95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3" t="n">
         <v>884</v>
       </c>
-      <c r="N95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P95" s="3" t="n">
         <v>0</v>
       </c>
@@ -6472,6 +6663,12 @@
         <v>0</v>
       </c>
       <c r="S95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6486,29 +6683,23 @@
           <t>Particuliers - Triail</t>
         </is>
       </c>
-      <c r="F96" s="3" t="n">
+      <c r="H96" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="I96" s="4" t="n">
         <v>2.87</v>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (48) ; À SUPPRIMER (doublons S3 - az) (2)</t>
         </is>
       </c>
-      <c r="I96" s="5" t="n">
+      <c r="K96" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J96" s="3" t="n">
+      <c r="L96" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="K96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M96" s="3" t="n">
         <v>0</v>
       </c>
@@ -6525,9 +6716,15 @@
         <v>0</v>
       </c>
       <c r="R96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="S96" s="3" t="n">
+      <c r="U96" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6542,29 +6739,23 @@
           <t>Particuliers - Turgot</t>
         </is>
       </c>
-      <c r="F97" s="3" t="n">
+      <c r="H97" s="3" t="n">
         <v>1461</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="I97" s="4" t="n">
         <v>53.41</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1461)</t>
         </is>
       </c>
-      <c r="I97" s="5" t="n">
+      <c r="K97" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J97" s="3" t="n">
+      <c r="L97" s="3" t="n">
         <v>1444</v>
       </c>
-      <c r="K97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M97" s="3" t="n">
         <v>0</v>
       </c>
@@ -6581,9 +6772,15 @@
         <v>0</v>
       </c>
       <c r="R97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3" t="n">
         <v>1461</v>
       </c>
-      <c r="S97" s="3" t="n">
+      <c r="U97" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6598,29 +6795,33 @@
           <t>Presse - L’Avenir de Roubaix Tourcoing</t>
         </is>
       </c>
-      <c r="F98" s="3" t="n">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_AVE </t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="n">
         <v>176340</v>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="I98" s="4" t="n">
         <v>778.75</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (176340)</t>
         </is>
       </c>
-      <c r="I98" s="5" t="n">
+      <c r="K98" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J98" s="3" t="n">
+      <c r="L98" s="3" t="n">
         <v>87510</v>
       </c>
-      <c r="K98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M98" s="3" t="n">
         <v>0</v>
       </c>
@@ -6628,18 +6829,24 @@
         <v>0</v>
       </c>
       <c r="O98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3" t="n">
         <v>44271</v>
       </c>
-      <c r="P98" s="3" t="n">
+      <c r="R98" s="3" t="n">
         <v>43519</v>
       </c>
-      <c r="Q98" s="3" t="n">
+      <c r="S98" s="3" t="n">
         <v>44275</v>
       </c>
-      <c r="R98" s="3" t="n">
+      <c r="T98" s="3" t="n">
         <v>44275</v>
       </c>
-      <c r="S98" s="3" t="n">
+      <c r="U98" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6654,48 +6861,48 @@
           <t>Presse - Bulletin de Roubaix</t>
         </is>
       </c>
-      <c r="F99" s="3" t="n">
+      <c r="H99" s="3" t="n">
         <v>3138</v>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="I99" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>INCONNU (2781) ; À SUPPRIMER (doublons S3 - az) (178) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="I99" s="5" t="n">
+      <c r="K99" s="5" t="n">
         <v>11.4</v>
       </c>
-      <c r="J99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M99" s="3" t="n">
+      <c r="O99" s="3" t="n">
         <v>523</v>
       </c>
-      <c r="N99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="3" t="n">
+      <c r="P99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3" t="n">
         <v>406</v>
       </c>
-      <c r="P99" s="3" t="n">
+      <c r="R99" s="3" t="n">
         <v>407</v>
       </c>
-      <c r="Q99" s="3" t="n">
+      <c r="S99" s="3" t="n">
         <v>1218</v>
       </c>
-      <c r="R99" s="3" t="n">
+      <c r="T99" s="3" t="n">
         <v>583</v>
       </c>
-      <c r="S99" s="3" t="n">
+      <c r="U99" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6710,29 +6917,33 @@
           <t>Presse - La Croix de Roubaix-Tourcoing</t>
         </is>
       </c>
-      <c r="F100" s="3" t="n">
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_CRT </t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="n">
         <v>116806</v>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="I100" s="4" t="n">
         <v>1024.92</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (116806)</t>
         </is>
       </c>
-      <c r="I100" s="5" t="n">
+      <c r="K100" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J100" s="3" t="n">
+      <c r="L100" s="3" t="n">
         <v>48452</v>
       </c>
-      <c r="K100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
       </c>
@@ -6740,18 +6951,24 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>29202</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>29200</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="n">
         <v>29202</v>
       </c>
       <c r="R100" s="3" t="n">
+        <v>29200</v>
+      </c>
+      <c r="S100" s="3" t="n">
         <v>29202</v>
       </c>
-      <c r="S100" s="3" t="n">
+      <c r="T100" s="3" t="n">
+        <v>29202</v>
+      </c>
+      <c r="U100" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6766,29 +6983,33 @@
           <t>Presse - Le Courrier de Tourcoing</t>
         </is>
       </c>
-      <c r="F101" s="3" t="n">
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_CTG </t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="n">
         <v>5752</v>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="I101" s="4" t="n">
         <v>45.98</v>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (5752)</t>
         </is>
       </c>
-      <c r="I101" s="5" t="n">
+      <c r="K101" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J101" s="3" t="n">
+      <c r="L101" s="3" t="n">
         <v>2876</v>
       </c>
-      <c r="K101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M101" s="3" t="n">
         <v>0</v>
       </c>
@@ -6796,10 +7017,10 @@
         <v>0</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>1438</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>1438</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="n">
         <v>1438</v>
@@ -6808,6 +7029,12 @@
         <v>1438</v>
       </c>
       <c r="S101" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="T101" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="U101" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6822,29 +7049,33 @@
           <t>Presse - L’Egalité Roubaix-Tourcoing</t>
         </is>
       </c>
-      <c r="F102" s="3" t="n">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_ERT </t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="n">
         <v>377078</v>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="I102" s="4" t="n">
         <v>3103.47</v>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (377078)</t>
         </is>
       </c>
-      <c r="I102" s="5" t="n">
+      <c r="K102" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J102" s="3" t="n">
+      <c r="L102" s="3" t="n">
         <v>185403</v>
       </c>
-      <c r="K102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M102" s="3" t="n">
         <v>0</v>
       </c>
@@ -6852,18 +7083,24 @@
         <v>0</v>
       </c>
       <c r="O102" s="3" t="n">
-        <v>94387</v>
+        <v>0</v>
       </c>
       <c r="P102" s="3" t="n">
-        <v>93918</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="n">
         <v>94387</v>
       </c>
       <c r="R102" s="3" t="n">
+        <v>93918</v>
+      </c>
+      <c r="S102" s="3" t="n">
+        <v>94387</v>
+      </c>
+      <c r="T102" s="3" t="n">
         <v>94386</v>
       </c>
-      <c r="S102" s="3" t="n">
+      <c r="U102" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6878,29 +7115,33 @@
           <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
         </is>
       </c>
-      <c r="F103" s="3" t="n">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_IND </t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="n">
         <v>64400</v>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="I103" s="4" t="n">
         <v>199.84</v>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (64400)</t>
         </is>
       </c>
-      <c r="I103" s="5" t="n">
+      <c r="K103" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J103" s="3" t="n">
+      <c r="L103" s="3" t="n">
         <v>32665</v>
       </c>
-      <c r="K103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M103" s="3" t="n">
         <v>0</v>
       </c>
@@ -6908,18 +7149,24 @@
         <v>0</v>
       </c>
       <c r="O103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="3" t="n">
         <v>15377</v>
       </c>
-      <c r="P103" s="3" t="n">
+      <c r="R103" s="3" t="n">
         <v>16307</v>
       </c>
-      <c r="Q103" s="3" t="n">
+      <c r="S103" s="3" t="n">
         <v>16358</v>
       </c>
-      <c r="R103" s="3" t="n">
+      <c r="T103" s="3" t="n">
         <v>16358</v>
       </c>
-      <c r="S103" s="3" t="n">
+      <c r="U103" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6934,29 +7181,33 @@
           <t>Presse - Journal de Roubaix</t>
         </is>
       </c>
-      <c r="F104" s="3" t="n">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_JRX </t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="n">
         <v>595291</v>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="I104" s="4" t="n">
         <v>4704.6</v>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (595291)</t>
         </is>
       </c>
-      <c r="I104" s="5" t="n">
+      <c r="K104" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J104" s="3" t="n">
+      <c r="L104" s="3" t="n">
         <v>284717</v>
       </c>
-      <c r="K104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M104" s="3" t="n">
         <v>0</v>
       </c>
@@ -6964,18 +7215,24 @@
         <v>0</v>
       </c>
       <c r="O104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="3" t="n">
         <v>148174</v>
       </c>
-      <c r="P104" s="3" t="n">
+      <c r="R104" s="3" t="n">
         <v>148814</v>
       </c>
-      <c r="Q104" s="3" t="n">
+      <c r="S104" s="3" t="n">
         <v>149132</v>
       </c>
-      <c r="R104" s="3" t="n">
+      <c r="T104" s="3" t="n">
         <v>149171</v>
       </c>
-      <c r="S104" s="3" t="n">
+      <c r="U104" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6990,29 +7247,33 @@
           <t>Presse - Roubaix-Tourcoing</t>
         </is>
       </c>
-      <c r="F105" s="3" t="n">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_VAH_PUB </t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="n">
         <v>3367</v>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="I105" s="4" t="n">
         <v>19.37</v>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (3367)</t>
         </is>
       </c>
-      <c r="I105" s="5" t="n">
+      <c r="K105" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="J105" s="3" t="n">
+      <c r="L105" s="3" t="n">
         <v>1671</v>
       </c>
-      <c r="K105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M105" s="3" t="n">
         <v>0</v>
       </c>
@@ -7020,18 +7281,24 @@
         <v>0</v>
       </c>
       <c r="O105" s="3" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="P105" s="3" t="n">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="3" t="n">
         <v>848</v>
       </c>
       <c r="R105" s="3" t="n">
+        <v>823</v>
+      </c>
+      <c r="S105" s="3" t="n">
         <v>848</v>
       </c>
-      <c r="S105" s="3" t="n">
+      <c r="T105" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="U105" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7046,29 +7313,28 @@
           <t>Ville d'art et d'histoire  - Publications</t>
         </is>
       </c>
-      <c r="F106" s="3" t="n">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_VAH_PUB </t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="I106" s="4" t="n">
         <v>13.49</v>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (457)</t>
         </is>
       </c>
-      <c r="I106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="n">
+      <c r="K106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="K106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M106" s="3" t="n">
         <v>0</v>
       </c>
@@ -7085,9 +7351,15 @@
         <v>0</v>
       </c>
       <c r="R106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="S106" s="3" t="n">
+      <c r="U106" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7097,48 +7369,48 @@
           <t>_INCONNU</t>
         </is>
       </c>
-      <c r="F107" s="3" t="n">
-        <v>4425</v>
-      </c>
-      <c r="G107" s="4" t="n">
-        <v>88.61</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; TRANSFERT_S3_OK (345) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
-        </is>
-      </c>
-      <c r="I107" s="5" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="3" t="n">
-        <v>8</v>
+      <c r="H107" s="3" t="n">
+        <v>4080</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>59.3</v>
       </c>
       <c r="L107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N107" s="3" t="n">
         <v>2244</v>
       </c>
-      <c r="M107" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="N107" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O107" s="3" t="n">
+        <v>857</v>
+      </c>
+      <c r="P107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P107" s="3" t="n">
+      <c r="R107" s="3" t="n">
         <v>726</v>
       </c>
-      <c r="Q107" s="3" t="n">
+      <c r="S107" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R107" s="3" t="n">
+      <c r="T107" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="S107" s="3" t="n">
+      <c r="U107" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7152,53 +7424,55 @@
       <c r="C108" s="6" t="inlineStr"/>
       <c r="D108" s="6" t="inlineStr"/>
       <c r="E108" s="6" t="inlineStr"/>
-      <c r="F108" s="7" t="n">
+      <c r="F108" s="6" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="7" t="n">
         <v>2430327</v>
       </c>
-      <c r="G108" s="8" t="n">
+      <c r="I108" s="8" t="n">
         <v>20914.25</v>
       </c>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="J108" s="6" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (2068905) ; INCONNU (135934) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37324) ; EN LIGNE - À TRANSFERER ? (28584) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; À SUPPRIMER (doublons S3 - az) (6149) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118)</t>
         </is>
       </c>
-      <c r="I108" s="9" t="n">
+      <c r="K108" s="9" t="n">
         <v>93.2</v>
       </c>
-      <c r="J108" s="7" t="n">
+      <c r="L108" s="7" t="n">
         <v>994727</v>
       </c>
-      <c r="K108" s="7" t="n">
+      <c r="M108" s="7" t="n">
         <v>7347</v>
       </c>
-      <c r="L108" s="7" t="n">
+      <c r="N108" s="7" t="n">
         <v>2453</v>
       </c>
-      <c r="M108" s="7" t="n">
+      <c r="O108" s="7" t="n">
         <v>673674</v>
       </c>
-      <c r="N108" s="7" t="n">
+      <c r="P108" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="O108" s="7" t="n">
+      <c r="Q108" s="7" t="n">
         <v>334782</v>
       </c>
-      <c r="P108" s="7" t="n">
+      <c r="R108" s="7" t="n">
         <v>452908</v>
       </c>
-      <c r="Q108" s="7" t="n">
+      <c r="S108" s="7" t="n">
         <v>338162</v>
       </c>
-      <c r="R108" s="7" t="n">
+      <c r="T108" s="7" t="n">
         <v>620516</v>
       </c>
-      <c r="S108" s="7" t="n">
+      <c r="U108" s="7" t="n">
         <v>465</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I108">
+  <conditionalFormatting sqref="K2:K108">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U108"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -457,10 +457,10 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
@@ -469,6 +469,7 @@
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,70 +510,75 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>fichiers</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>volume_go</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>conservation_statut</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>traitement_s3</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>fichiers_publies</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>audio</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>autre</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>jpeg</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>jpeg2000</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>ocr txt</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>ocr xml</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>pdf</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>tiff</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>video</t>
         </is>
@@ -604,23 +610,20 @@
           <t>1AEFi</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="I2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="J2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (30) ; INCONNU (30)</t>
         </is>
       </c>
-      <c r="K2" s="5" t="n">
+      <c r="L2" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="L2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" s="3" t="n">
         <v>0</v>
       </c>
@@ -628,11 +631,11 @@
         <v>0</v>
       </c>
       <c r="O2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" s="3" t="n">
         <v>0</v>
       </c>
@@ -646,6 +649,9 @@
         <v>0</v>
       </c>
       <c r="U2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -675,23 +681,20 @@
           <t>1I</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="I3" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="J3" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (50) ; INCONNU (47)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="L3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" s="3" t="n">
         <v>0</v>
       </c>
@@ -699,11 +702,11 @@
         <v>0</v>
       </c>
       <c r="O3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q3" s="3" t="n">
         <v>0</v>
       </c>
@@ -717,6 +720,9 @@
         <v>0</v>
       </c>
       <c r="U3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -746,23 +752,20 @@
           <t>1NumFi</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="I4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>INCONNU (6) ; CORBEILLE (DIFFUSION) (6)</t>
         </is>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="L4" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" s="3" t="n">
         <v>0</v>
       </c>
@@ -770,11 +773,11 @@
         <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" s="3" t="n">
         <v>0</v>
       </c>
@@ -785,9 +788,12 @@
         <v>0</v>
       </c>
       <c r="T4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="U4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -817,21 +823,18 @@
           <t>1PER3</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="I5" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="J5" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>INCONNU (23)</t>
         </is>
       </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="3" t="n">
@@ -841,14 +844,14 @@
         <v>0</v>
       </c>
       <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="Q5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" s="3" t="n">
         <v>0</v>
       </c>
@@ -856,9 +859,12 @@
         <v>0</v>
       </c>
       <c r="T5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U5" s="3" t="n">
+      <c r="V5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -883,21 +889,18 @@
           <t>2F</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="J6" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -922,9 +925,12 @@
         <v>0</v>
       </c>
       <c r="T6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="V6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -954,23 +960,20 @@
           <t>2I</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="I7" s="3" t="n">
         <v>15703</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="J7" s="4" t="n">
         <v>9.08</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (15703)</t>
         </is>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" s="3" t="n">
         <v>0</v>
       </c>
@@ -978,11 +981,11 @@
         <v>0</v>
       </c>
       <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>15703</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" s="3" t="n">
         <v>0</v>
       </c>
@@ -996,6 +999,9 @@
         <v>0</v>
       </c>
       <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1025,21 +1031,18 @@
           <t>308W</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="I8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="J8" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>INCONNU (7)</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
@@ -1061,12 +1064,15 @@
         <v>0</v>
       </c>
       <c r="S8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="T8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1096,21 +1102,18 @@
           <t>381W</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="I9" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="J9" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>INCONNU (11)</t>
         </is>
       </c>
-      <c r="K9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
@@ -1135,9 +1138,12 @@
         <v>0</v>
       </c>
       <c r="T9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="U9" s="3" t="n">
+      <c r="V9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1167,23 +1173,20 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="I10" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="J10" s="4" t="n">
         <v>3.16</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>INCONNU (272) ; CORBEILLE (DIFFUSION) (24)</t>
         </is>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>8.1</v>
       </c>
-      <c r="L10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" s="3" t="n">
         <v>0</v>
       </c>
@@ -1191,11 +1194,11 @@
         <v>0</v>
       </c>
       <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="P10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
@@ -1203,12 +1206,15 @@
         <v>0</v>
       </c>
       <c r="S10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="T10" s="3" t="n">
+      <c r="U10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1238,21 +1244,18 @@
           <t>3O</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="I11" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="J11" s="4" t="n">
         <v>2.71</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>INCONNU (27)</t>
         </is>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
@@ -1274,12 +1277,15 @@
         <v>0</v>
       </c>
       <c r="S11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="T11" s="3" t="n">
+      <c r="U11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="V11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1309,21 +1315,18 @@
           <t>3R</t>
         </is>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="I12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="J12" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>INCONNU (14)</t>
         </is>
       </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
@@ -1348,9 +1351,12 @@
         <v>0</v>
       </c>
       <c r="T12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="V12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1380,21 +1386,18 @@
           <t>4H</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="I13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="J13" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>INCONNU (5)</t>
         </is>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1419,9 +1422,12 @@
         <v>0</v>
       </c>
       <c r="T13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="U13" s="3" t="n">
+      <c r="V13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1451,21 +1457,18 @@
           <t>4M</t>
         </is>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="I14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="J14" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="K14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
@@ -1490,9 +1493,12 @@
         <v>0</v>
       </c>
       <c r="T14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U14" s="3" t="n">
+      <c r="V14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1522,21 +1528,18 @@
           <t>507W</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="I15" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="J15" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>INCONNU (496)</t>
         </is>
       </c>
-      <c r="K15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
@@ -1561,9 +1564,12 @@
         <v>0</v>
       </c>
       <c r="T15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="V15" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1588,21 +1594,18 @@
           <t>5Fi</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="I16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="J16" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>INCONNU (2)</t>
         </is>
       </c>
-      <c r="K16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
@@ -1627,9 +1630,12 @@
         <v>0</v>
       </c>
       <c r="T16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U16" s="3" t="n">
+      <c r="V16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1659,21 +1665,18 @@
           <t>5M</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="I17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="J17" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>INCONNU (3)</t>
         </is>
       </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
@@ -1683,11 +1686,11 @@
         <v>0</v>
       </c>
       <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" s="3" t="n">
         <v>0</v>
       </c>
@@ -1698,9 +1701,12 @@
         <v>0</v>
       </c>
       <c r="T17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="V17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1730,23 +1736,20 @@
           <t>6H</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="I18" s="3" t="n">
         <v>76933</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="J18" s="4" t="n">
         <v>54.36</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (76933)</t>
         </is>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="L18" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
       </c>
@@ -1754,11 +1757,11 @@
         <v>0</v>
       </c>
       <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
         <v>76933</v>
       </c>
-      <c r="P18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" s="3" t="n">
         <v>0</v>
       </c>
@@ -1772,6 +1775,9 @@
         <v>0</v>
       </c>
       <c r="U18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1801,21 +1807,18 @@
           <t>6M</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="J19" s="4" t="n">
         <v>0.19</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -1837,12 +1840,15 @@
         <v>0</v>
       </c>
       <c r="S19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="T19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1872,21 +1878,18 @@
           <t>8C</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="J20" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -1911,9 +1914,12 @@
         <v>0</v>
       </c>
       <c r="T20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="U20" s="3" t="n">
+      <c r="V20" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1943,21 +1949,18 @@
           <t>8J</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="I21" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="J21" s="4" t="n">
         <v>2.28</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>INCONNU (145)</t>
         </is>
       </c>
-      <c r="K21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="n">
+      <c r="L21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -1967,11 +1970,11 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="P21" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" s="3" t="n">
         <v>0</v>
       </c>
@@ -1982,9 +1985,12 @@
         <v>0</v>
       </c>
       <c r="T21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="U21" s="3" t="n">
+      <c r="V21" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2019,48 +2025,48 @@
           <t xml:space="preserve">RBX_AMR_AFF </t>
         </is>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="I22" s="3" t="n">
         <v>3650</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="J22" s="4" t="n">
         <v>219.66</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1076) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
         </is>
       </c>
-      <c r="K22" s="5" t="n">
+      <c r="L22" s="5" t="n">
         <v>74.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="M22" s="3" t="n">
         <v>1007</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>643</v>
       </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="S22" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="T22" s="3" t="n">
         <v>554</v>
       </c>
-      <c r="T22" s="3" t="n">
+      <c r="U22" s="3" t="n">
         <v>1508</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="V22" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2090,21 +2096,18 @@
           <t>8O</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="I23" s="3" t="n">
         <v>604</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="J23" s="4" t="n">
         <v>83.84999999999999</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>INCONNU (604)</t>
         </is>
       </c>
-      <c r="K23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="3" t="n">
@@ -2114,11 +2117,11 @@
         <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" s="3" t="n">
         <v>0</v>
       </c>
@@ -2129,9 +2132,12 @@
         <v>0</v>
       </c>
       <c r="T23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="U23" s="3" t="n">
+      <c r="V23" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2151,23 +2157,20 @@
           <t>?</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="I24" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="J24" s="4" t="n">
         <v>255.07</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (159)</t>
         </is>
       </c>
-      <c r="K24" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" s="3" t="n">
         <v>0</v>
       </c>
@@ -2193,6 +2196,9 @@
         <v>0</v>
       </c>
       <c r="U24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>159</v>
       </c>
     </row>
@@ -2217,23 +2223,20 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="I25" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="I25" s="4" t="n">
+      <c r="J25" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
         </is>
       </c>
-      <c r="K25" s="5" t="n">
+      <c r="L25" s="5" t="n">
         <v>47.8</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" s="3" t="n">
         <v>0</v>
       </c>
@@ -2241,11 +2244,11 @@
         <v>0</v>
       </c>
       <c r="O25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="P25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" s="3" t="n">
         <v>0</v>
       </c>
@@ -2256,9 +2259,12 @@
         <v>0</v>
       </c>
       <c r="T25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="U25" s="3" t="n">
+      <c r="V25" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2293,35 +2299,32 @@
           <t xml:space="preserve">RBX_AMR_CAD </t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="I26" s="3" t="n">
         <v>515</v>
       </c>
-      <c r="I26" s="4" t="n">
+      <c r="J26" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="K26" s="5" t="n">
+      <c r="L26" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="M26" s="3" t="n">
         <v>247</v>
       </c>
-      <c r="M26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O26" s="3" t="n">
+      <c r="P26" s="3" t="n">
         <v>433</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3" t="n">
         <v>0</v>
       </c>
@@ -2329,12 +2332,15 @@
         <v>0</v>
       </c>
       <c r="S26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="T26" s="3" t="n">
+      <c r="U26" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="V26" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2364,23 +2370,20 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="I27" s="3" t="n">
         <v>18982</v>
       </c>
-      <c r="I27" s="4" t="n">
+      <c r="J27" s="4" t="n">
         <v>315.8</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
         </is>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="L27" s="5" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="L27" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" s="3" t="n">
         <v>0</v>
       </c>
@@ -2403,9 +2406,12 @@
         <v>0</v>
       </c>
       <c r="T27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3" t="n">
         <v>18982</v>
       </c>
-      <c r="U27" s="3" t="n">
+      <c r="V27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2435,23 +2441,20 @@
           <t>4H</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="I28" s="3" t="n">
         <v>358</v>
       </c>
-      <c r="I28" s="4" t="n">
+      <c r="J28" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
         </is>
       </c>
-      <c r="K28" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>73.7</v>
       </c>
-      <c r="L28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
       </c>
@@ -2459,24 +2462,27 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="P28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
         <v>3</v>
       </c>
       <c r="T28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="U28" s="3" t="n">
+      <c r="V28" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2506,53 +2512,58 @@
           <t>1D</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t xml:space="preserve">RBX_AMR_DEL </t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="I29" s="3" t="n">
         <v>170586</v>
       </c>
-      <c r="I29" s="4" t="n">
+      <c r="J29" s="4" t="n">
         <v>2435.11</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (122555) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (398) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n">
+      <c r="L29" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="M29" s="3" t="n">
         <v>122552</v>
       </c>
-      <c r="M29" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O29" s="3" t="n">
+      <c r="P29" s="3" t="n">
         <v>23676</v>
       </c>
-      <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="S29" s="3" t="n">
         <v>79005</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="T29" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="T29" s="3" t="n">
+      <c r="U29" s="3" t="n">
         <v>67624</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="V29" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2582,23 +2593,20 @@
           <t>9Fi</t>
         </is>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="I30" s="3" t="n">
         <v>1761</v>
       </c>
-      <c r="I30" s="4" t="n">
+      <c r="J30" s="4" t="n">
         <v>44.68</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
         </is>
       </c>
-      <c r="K30" s="5" t="n">
+      <c r="L30" s="5" t="n">
         <v>49.9</v>
       </c>
-      <c r="L30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" s="3" t="n">
         <v>0</v>
       </c>
@@ -2606,11 +2614,11 @@
         <v>0</v>
       </c>
       <c r="O30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3" t="n">
         <v>879</v>
       </c>
-      <c r="P30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q30" s="3" t="n">
         <v>0</v>
       </c>
@@ -2621,9 +2629,12 @@
         <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3" t="n">
         <v>882</v>
       </c>
-      <c r="U30" s="3" t="n">
+      <c r="V30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2653,41 +2664,38 @@
           <t>E</t>
         </is>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="I31" s="3" t="n">
         <v>358109</v>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="J31" s="4" t="n">
         <v>760.01</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (249012) ; CORBEILLE (85333) ; INCONNU (23761) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n">
+      <c r="L31" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="L31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="O31" s="3" t="n">
+      <c r="P31" s="3" t="n">
         <v>358080</v>
       </c>
-      <c r="P31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" s="3" t="n">
         <v>0</v>
       </c>
@@ -2695,6 +2703,9 @@
         <v>0</v>
       </c>
       <c r="U31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2719,23 +2730,20 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="I32" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="J32" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="L32" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="L32" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" s="3" t="n">
         <v>0</v>
       </c>
@@ -2743,11 +2751,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3" t="n">
         <v>0</v>
       </c>
@@ -2761,6 +2769,9 @@
         <v>0</v>
       </c>
       <c r="U32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2795,48 +2806,48 @@
           <t xml:space="preserve">RBX_AMR_GUE </t>
         </is>
       </c>
-      <c r="H33" s="3" t="n">
+      <c r="I33" s="3" t="n">
         <v>678</v>
       </c>
-      <c r="I33" s="4" t="n">
+      <c r="J33" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (678)</t>
         </is>
       </c>
-      <c r="K33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="n">
         <v>678</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="n">
         <v>339</v>
       </c>
-      <c r="P33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>339</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2871,23 +2882,20 @@
           <t xml:space="preserve">RBX_AMR_LEB </t>
         </is>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="I34" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="J34" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
         </is>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="L34" s="5" t="n">
         <v>48.9</v>
       </c>
-      <c r="L34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" s="3" t="n">
         <v>0</v>
       </c>
@@ -2895,11 +2903,11 @@
         <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q34" s="3" t="n">
         <v>0</v>
       </c>
@@ -2910,9 +2918,12 @@
         <v>0</v>
       </c>
       <c r="T34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="V34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2942,35 +2953,32 @@
           <t>3O</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="I35" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="J35" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="K35" s="5" t="n">
+      <c r="L35" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="L35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O35" s="3" t="n">
+      <c r="P35" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3" t="n">
         <v>0</v>
       </c>
@@ -2981,9 +2989,12 @@
         <v>0</v>
       </c>
       <c r="T35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="U35" s="3" t="n">
+      <c r="V35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3018,26 +3029,23 @@
           <t xml:space="preserve">RBX_AMR_OBJ </t>
         </is>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="I36" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="I36" s="4" t="n">
+      <c r="J36" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
         </is>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="L36" s="5" t="n">
         <v>96.2</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="M36" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
@@ -3057,9 +3065,12 @@
         <v>0</v>
       </c>
       <c r="T36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="U36" s="3" t="n">
+      <c r="V36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3089,23 +3100,20 @@
           <t>J ?</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
-        <v>8812</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>21.27</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>CORBEILLE (DIFFUSION) (6428) ; À SUPPRIMER (doublons S3 - az) (1901) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (RENOMMAGE) (238)</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="n">
+      <c r="I37" s="3" t="n">
+        <v>6901</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>CORBEILLE (DIFFUSION) (6428) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (doublons S3 - az) (228)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" s="3" t="n">
         <v>0</v>
       </c>
@@ -3113,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>7093</v>
+        <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>6668</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>0</v>
@@ -3128,9 +3136,12 @@
         <v>0</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1719</v>
+        <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="V37" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3155,23 +3166,20 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="I38" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="I38" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>3.87</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
         </is>
       </c>
-      <c r="K38" s="5" t="n">
+      <c r="L38" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="L38" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" s="3" t="n">
         <v>0</v>
       </c>
@@ -3179,11 +3187,11 @@
         <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="P38" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q38" s="3" t="n">
         <v>0</v>
       </c>
@@ -3197,6 +3205,9 @@
         <v>0</v>
       </c>
       <c r="U38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3226,35 +3237,32 @@
           <t xml:space="preserve">RBX_AMR_PHO </t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="I39" s="3" t="n">
         <v>18595</v>
       </c>
-      <c r="I39" s="4" t="n">
+      <c r="J39" s="4" t="n">
         <v>135.98</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>INCONNU (9293) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="K39" s="5" t="n">
+      <c r="L39" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="M39" s="3" t="n">
         <v>1194</v>
       </c>
-      <c r="M39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O39" s="3" t="n">
+      <c r="P39" s="3" t="n">
         <v>8035</v>
       </c>
-      <c r="P39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" s="3" t="n">
         <v>0</v>
       </c>
@@ -3265,9 +3273,12 @@
         <v>0</v>
       </c>
       <c r="T39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="3" t="n">
         <v>10558</v>
       </c>
-      <c r="U39" s="3" t="n">
+      <c r="V39" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3297,35 +3308,32 @@
           <t xml:space="preserve">RBX_AMR_PLA </t>
         </is>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="I40" s="3" t="n">
         <v>376</v>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="J40" s="4" t="n">
         <v>48.9</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="K40" s="5" t="n">
+      <c r="L40" s="5" t="n">
         <v>35.1</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="M40" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="M40" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="P40" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q40" s="3" t="n">
         <v>0</v>
       </c>
@@ -3336,9 +3344,12 @@
         <v>0</v>
       </c>
       <c r="T40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="U40" s="3" t="n">
+      <c r="V40" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3368,48 +3379,48 @@
           <t>1F</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="I41" s="3" t="n">
         <v>122308</v>
       </c>
-      <c r="I41" s="4" t="n">
+      <c r="J41" s="4" t="n">
         <v>504.56</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (85759) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
         </is>
       </c>
-      <c r="K41" s="5" t="n">
+      <c r="L41" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="M41" s="3" t="n">
         <v>65349</v>
       </c>
-      <c r="M41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3" t="n">
         <v>114168</v>
       </c>
-      <c r="P41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T41" s="3" t="n">
+      <c r="U41" s="3" t="n">
         <v>8135</v>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="V41" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3439,48 +3450,48 @@
           <t xml:space="preserve">RBX_AMR_PR </t>
         </is>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="I42" s="3" t="n">
         <v>4326</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="J42" s="4" t="n">
         <v>166.36</v>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="K42" s="5" t="n">
+      <c r="L42" s="5" t="n">
         <v>27.8</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="M42" s="3" t="n">
         <v>668</v>
       </c>
-      <c r="M42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O42" s="3" t="n">
+      <c r="P42" s="3" t="n">
         <v>786</v>
       </c>
-      <c r="P42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>3533</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="V42" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3515,48 +3526,48 @@
           <t xml:space="preserve">RBX_AMR_PUV </t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="I43" s="3" t="n">
         <v>19188</v>
       </c>
-      <c r="I43" s="4" t="n">
+      <c r="J43" s="4" t="n">
         <v>338.52</v>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>INCONNU (16034) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="K43" s="5" t="n">
+      <c r="L43" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="L43" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="O43" s="3" t="n">
+      <c r="P43" s="3" t="n">
         <v>6302</v>
       </c>
-      <c r="P43" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3" t="n">
         <v>6302</v>
       </c>
-      <c r="S43" s="3" t="n">
+      <c r="T43" s="3" t="n">
         <v>279</v>
       </c>
-      <c r="T43" s="3" t="n">
+      <c r="U43" s="3" t="n">
         <v>6302</v>
       </c>
-      <c r="U43" s="3" t="n">
+      <c r="V43" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3586,21 +3597,18 @@
           <t>8Fi</t>
         </is>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="I44" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I44" s="4" t="n">
+      <c r="J44" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="K44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="3" t="n">
@@ -3610,11 +3618,11 @@
         <v>0</v>
       </c>
       <c r="O44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P44" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q44" s="3" t="n">
         <v>0</v>
       </c>
@@ -3625,9 +3633,12 @@
         <v>0</v>
       </c>
       <c r="T44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="U44" s="3" t="n">
+      <c r="V44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3657,23 +3668,20 @@
           <t>246W</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="I45" s="3" t="n">
         <v>19170</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="J45" s="4" t="n">
         <v>42.81</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
         </is>
       </c>
-      <c r="K45" s="5" t="n">
+      <c r="L45" s="5" t="n">
         <v>49.3</v>
       </c>
-      <c r="L45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" s="3" t="n">
         <v>0</v>
       </c>
@@ -3681,24 +3689,27 @@
         <v>0</v>
       </c>
       <c r="O45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3" t="n">
         <v>9444</v>
       </c>
-      <c r="P45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="S45" s="3" t="n">
         <v>9444</v>
       </c>
-      <c r="S45" s="3" t="n">
+      <c r="T45" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="T45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3728,31 +3739,33 @@
           <t>3D</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">RBX_AMR_RAM </t>
         </is>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="I46" s="3" t="n">
         <v>37053</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="J46" s="4" t="n">
         <v>448.11</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (37053)</t>
         </is>
       </c>
-      <c r="K46" s="5" t="n">
+      <c r="L46" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="M46" s="3" t="n">
         <v>37053</v>
       </c>
-      <c r="M46" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N46" s="3" t="n">
         <v>0</v>
       </c>
@@ -3766,15 +3779,18 @@
         <v>0</v>
       </c>
       <c r="R46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3" t="n">
         <v>18527</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>18526</v>
       </c>
-      <c r="U46" s="3" t="n">
+      <c r="V46" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3794,23 +3810,20 @@
           <t>?</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="I47" s="3" t="n">
         <v>449</v>
       </c>
-      <c r="I47" s="4" t="n">
+      <c r="J47" s="4" t="n">
         <v>5.17</v>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
         </is>
       </c>
-      <c r="K47" s="5" t="n">
+      <c r="L47" s="5" t="n">
         <v>42.8</v>
       </c>
-      <c r="L47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" s="3" t="n">
         <v>0</v>
       </c>
@@ -3818,11 +3831,11 @@
         <v>0</v>
       </c>
       <c r="O47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="P47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3" t="n">
         <v>0</v>
       </c>
@@ -3833,9 +3846,12 @@
         <v>0</v>
       </c>
       <c r="T47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="U47" s="3" t="n">
+      <c r="V47" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3870,21 +3886,18 @@
           <t xml:space="preserve">RBX_AMR_VIC </t>
         </is>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="I48" s="3" t="n">
         <v>7072</v>
       </c>
-      <c r="I48" s="4" t="n">
+      <c r="J48" s="4" t="n">
         <v>12.12</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>INCONNU (7072)</t>
         </is>
       </c>
-      <c r="K48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3" t="n">
+      <c r="L48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
@@ -3894,11 +3907,11 @@
         <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="3" t="n">
         <v>7072</v>
       </c>
-      <c r="P48" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
       </c>
@@ -3912,6 +3925,9 @@
         <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3931,35 +3947,32 @@
           <t xml:space="preserve">RBX_ARA_CPS </t>
         </is>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="I49" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="I49" s="4" t="n">
+      <c r="J49" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
         </is>
       </c>
-      <c r="K49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3" t="n">
+      <c r="L49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="M49" s="3" t="n">
+      <c r="N49" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="N49" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P49" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q49" s="3" t="n">
         <v>0</v>
       </c>
@@ -3973,6 +3986,9 @@
         <v>0</v>
       </c>
       <c r="U49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3992,26 +4008,23 @@
           <t xml:space="preserve">RBX_CSV_PAL </t>
         </is>
       </c>
-      <c r="H50" s="3" t="n">
+      <c r="I50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="I50" s="4" t="n">
+      <c r="J50" s="4" t="n">
         <v>6.65</v>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (242)</t>
         </is>
       </c>
-      <c r="K50" s="5" t="n">
+      <c r="L50" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L50" s="3" t="n">
+      <c r="M50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="M50" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N50" s="3" t="n">
         <v>0</v>
       </c>
@@ -4031,9 +4044,12 @@
         <v>0</v>
       </c>
       <c r="T50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="U50" s="3" t="n">
+      <c r="V50" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4053,26 +4069,23 @@
           <t xml:space="preserve">RBX_LAI </t>
         </is>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="I51" s="3" t="n">
         <v>2422</v>
       </c>
-      <c r="I51" s="4" t="n">
+      <c r="J51" s="4" t="n">
         <v>61.97</v>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1697) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
         </is>
       </c>
-      <c r="K51" s="5" t="n">
+      <c r="L51" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="M51" s="3" t="n">
         <v>1181</v>
       </c>
-      <c r="M51" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N51" s="3" t="n">
         <v>0</v>
       </c>
@@ -4083,18 +4096,21 @@
         <v>0</v>
       </c>
       <c r="Q51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R51" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3" t="n">
         <v>2421</v>
       </c>
-      <c r="U51" s="3" t="n">
+      <c r="V51" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4114,26 +4130,23 @@
           <t xml:space="preserve">RBX_LAR_PUB </t>
         </is>
       </c>
-      <c r="H52" s="3" t="n">
+      <c r="I52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="I52" s="4" t="n">
+      <c r="J52" s="4" t="n">
         <v>18.33</v>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
         </is>
       </c>
-      <c r="K52" s="5" t="n">
+      <c r="L52" s="5" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="L52" s="3" t="n">
+      <c r="M52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="M52" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N52" s="3" t="n">
         <v>0</v>
       </c>
@@ -4153,9 +4166,12 @@
         <v>0</v>
       </c>
       <c r="T52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="U52" s="3" t="n">
+      <c r="V52" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4175,26 +4191,23 @@
           <t xml:space="preserve">RBX_MDF_MTX </t>
         </is>
       </c>
-      <c r="H53" s="3" t="n">
+      <c r="I53" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="I53" s="4" t="n">
+      <c r="J53" s="4" t="n">
         <v>76.03</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (18)</t>
         </is>
       </c>
-      <c r="K53" s="5" t="n">
+      <c r="L53" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L53" s="3" t="n">
+      <c r="M53" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="M53" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N53" s="3" t="n">
         <v>0</v>
       </c>
@@ -4217,6 +4230,9 @@
         <v>0</v>
       </c>
       <c r="U53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4236,35 +4252,32 @@
           <t xml:space="preserve">RBX_MED_AFF </t>
         </is>
       </c>
-      <c r="H54" s="3" t="n">
+      <c r="I54" s="3" t="n">
         <v>11038</v>
       </c>
-      <c r="I54" s="4" t="n">
+      <c r="J54" s="4" t="n">
         <v>529.5599999999999</v>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (5576) ; CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (175) ; INCONNU (111)</t>
         </is>
       </c>
-      <c r="K54" s="5" t="n">
+      <c r="L54" s="5" t="n">
         <v>48.5</v>
       </c>
-      <c r="L54" s="3" t="n">
+      <c r="M54" s="3" t="n">
         <v>5742</v>
       </c>
-      <c r="M54" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="3" t="n">
         <v>5176</v>
       </c>
-      <c r="P54" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q54" s="3" t="n">
         <v>0</v>
       </c>
@@ -4275,9 +4288,12 @@
         <v>0</v>
       </c>
       <c r="T54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="3" t="n">
         <v>5862</v>
       </c>
-      <c r="U54" s="3" t="n">
+      <c r="V54" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4292,32 +4308,29 @@
           <t>Médiathèque - Vidéos</t>
         </is>
       </c>
-      <c r="H55" s="3" t="n">
+      <c r="I55" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="I55" s="4" t="n">
+      <c r="J55" s="4" t="n">
         <v>48.21</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="K55" s="5" t="n">
+      <c r="L55" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P55" s="3" t="n">
         <v>0</v>
       </c>
@@ -4334,6 +4347,9 @@
         <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="3" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4353,26 +4369,23 @@
           <t xml:space="preserve">RBX_MED_CHA </t>
         </is>
       </c>
-      <c r="H56" s="3" t="n">
+      <c r="I56" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="J56" s="4" t="n">
         <v>17.58</v>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
         </is>
       </c>
-      <c r="K56" s="5" t="n">
+      <c r="L56" s="5" t="n">
         <v>50.2</v>
       </c>
-      <c r="L56" s="3" t="n">
+      <c r="M56" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="M56" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N56" s="3" t="n">
         <v>0</v>
       </c>
@@ -4392,9 +4405,12 @@
         <v>0</v>
       </c>
       <c r="T56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="U56" s="3" t="n">
+      <c r="V56" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4414,48 +4430,48 @@
           <t xml:space="preserve">RBX_MED_CP </t>
         </is>
       </c>
-      <c r="H57" s="3" t="n">
+      <c r="I57" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="J57" s="4" t="n">
         <v>34.89</v>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (4534) ; INCONNU (651) ; À SUPPRIMER (doublons S3 - az) (536) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
         </is>
       </c>
-      <c r="K57" s="5" t="n">
+      <c r="L57" s="5" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="L57" s="3" t="n">
+      <c r="M57" s="3" t="n">
         <v>4672</v>
       </c>
-      <c r="M57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3" t="n">
         <v>307</v>
       </c>
-      <c r="P57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3" t="n">
         <v>5702</v>
       </c>
-      <c r="U57" s="3" t="n">
+      <c r="V57" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4475,35 +4491,32 @@
           <t xml:space="preserve">RBX_MED_DIL </t>
         </is>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="I58" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="J58" s="4" t="n">
         <v>480.6</v>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
         </is>
       </c>
-      <c r="K58" s="5" t="n">
+      <c r="L58" s="5" t="n">
         <v>12.1</v>
       </c>
-      <c r="L58" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="O58" s="3" t="n">
+      <c r="P58" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P58" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3" t="n">
         <v>0</v>
       </c>
@@ -4514,9 +4527,12 @@
         <v>0</v>
       </c>
       <c r="T58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="U58" s="3" t="n">
+      <c r="V58" s="3" t="n">
         <v>177</v>
       </c>
     </row>
@@ -4536,26 +4552,23 @@
           <t xml:space="preserve">RBX_MED_EPH </t>
         </is>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="I59" s="3" t="n">
         <v>846</v>
       </c>
-      <c r="I59" s="4" t="n">
+      <c r="J59" s="4" t="n">
         <v>10.17</v>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
         </is>
       </c>
-      <c r="K59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="n">
+      <c r="L59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="M59" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N59" s="3" t="n">
         <v>0</v>
       </c>
@@ -4575,9 +4588,12 @@
         <v>0</v>
       </c>
       <c r="T59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3" t="n">
         <v>846</v>
       </c>
-      <c r="U59" s="3" t="n">
+      <c r="V59" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4592,21 +4608,18 @@
           <t>Médiathèque - Cartes postales fantaisie</t>
         </is>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="I60" s="3" t="n">
         <v>2666</v>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="J60" s="4" t="n">
         <v>32.93</v>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>INCONNU (2666)</t>
         </is>
       </c>
-      <c r="K60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3" t="n">
+      <c r="L60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M60" s="3" t="n">
@@ -4631,9 +4644,12 @@
         <v>0</v>
       </c>
       <c r="T60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3" t="n">
         <v>2666</v>
       </c>
-      <c r="U60" s="3" t="n">
+      <c r="V60" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4653,35 +4669,32 @@
           <t xml:space="preserve">RBX_MED_FLR </t>
         </is>
       </c>
-      <c r="H61" s="3" t="n">
+      <c r="I61" s="3" t="n">
         <v>8487</v>
       </c>
-      <c r="I61" s="4" t="n">
+      <c r="J61" s="4" t="n">
         <v>304.96</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (8487)</t>
         </is>
       </c>
-      <c r="K61" s="5" t="n">
+      <c r="L61" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L61" s="3" t="n">
+      <c r="M61" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M61" s="3" t="n">
+      <c r="N61" s="3" t="n">
         <v>7228</v>
       </c>
-      <c r="N61" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3" t="n">
         <v>478</v>
       </c>
-      <c r="P61" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3" t="n">
         <v>0</v>
       </c>
@@ -4692,9 +4705,12 @@
         <v>0</v>
       </c>
       <c r="T61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3" t="n">
         <v>781</v>
       </c>
-      <c r="U61" s="3" t="n">
+      <c r="V61" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4714,35 +4730,32 @@
           <t xml:space="preserve">RBX_MED_FOO </t>
         </is>
       </c>
-      <c r="H62" s="3" t="n">
+      <c r="I62" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="I62" s="4" t="n">
+      <c r="J62" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="K62" s="5" t="n">
+      <c r="L62" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="L62" s="3" t="n">
+      <c r="M62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M62" s="3" t="n">
+      <c r="N62" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="O62" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O62" s="3" t="n">
+      <c r="P62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P62" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3" t="n">
         <v>0</v>
       </c>
@@ -4756,6 +4769,9 @@
         <v>0</v>
       </c>
       <c r="U62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4775,35 +4791,32 @@
           <t xml:space="preserve">RBX_MED_IMA </t>
         </is>
       </c>
-      <c r="H63" s="3" t="n">
+      <c r="I63" s="3" t="n">
         <v>9856</v>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="J63" s="4" t="n">
         <v>131.47</v>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (8900) ; TRANSFERT_S3_OK (750) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45)</t>
         </is>
       </c>
-      <c r="K63" s="5" t="n">
+      <c r="L63" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="L63" s="3" t="n">
+      <c r="M63" s="3" t="n">
         <v>9623</v>
       </c>
-      <c r="M63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="P63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q63" s="3" t="n">
         <v>0</v>
       </c>
@@ -4814,9 +4827,12 @@
         <v>0</v>
       </c>
       <c r="T63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3" t="n">
         <v>9631</v>
       </c>
-      <c r="U63" s="3" t="n">
+      <c r="V63" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4831,23 +4847,20 @@
           <t>Médiathèque - Journaux</t>
         </is>
       </c>
-      <c r="H64" s="3" t="n">
+      <c r="I64" s="3" t="n">
         <v>2174</v>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="J64" s="4" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
         </is>
       </c>
-      <c r="K64" s="5" t="n">
+      <c r="L64" s="5" t="n">
         <v>91.8</v>
       </c>
-      <c r="L64" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M64" s="3" t="n">
         <v>0</v>
       </c>
@@ -4870,9 +4883,12 @@
         <v>0</v>
       </c>
       <c r="T64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3" t="n">
         <v>2174</v>
       </c>
-      <c r="U64" s="3" t="n">
+      <c r="V64" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4892,26 +4908,23 @@
           <t xml:space="preserve">RBX_MED_LET </t>
         </is>
       </c>
-      <c r="H65" s="3" t="n">
+      <c r="I65" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="J65" s="4" t="n">
         <v>12.84</v>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (605)</t>
         </is>
       </c>
-      <c r="K65" s="5" t="n">
+      <c r="L65" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L65" s="3" t="n">
+      <c r="M65" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="M65" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N65" s="3" t="n">
         <v>0</v>
       </c>
@@ -4931,9 +4944,12 @@
         <v>0</v>
       </c>
       <c r="T65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="U65" s="3" t="n">
+      <c r="V65" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4953,35 +4969,32 @@
           <t xml:space="preserve">RBX_MED_MAR </t>
         </is>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="I66" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="I66" s="4" t="n">
+      <c r="J66" s="4" t="n">
         <v>7.07</v>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
         </is>
       </c>
-      <c r="K66" s="5" t="n">
+      <c r="L66" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="L66" s="3" t="n">
+      <c r="M66" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="M66" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P66" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q66" s="3" t="n">
         <v>0</v>
       </c>
@@ -4992,9 +5005,12 @@
         <v>0</v>
       </c>
       <c r="T66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="U66" s="3" t="n">
+      <c r="V66" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5014,26 +5030,23 @@
           <t xml:space="preserve">RBX_MED_MON </t>
         </is>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="I67" s="3" t="n">
         <v>7553</v>
       </c>
-      <c r="I67" s="4" t="n">
+      <c r="J67" s="4" t="n">
         <v>205.74</v>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
         </is>
       </c>
-      <c r="K67" s="5" t="n">
+      <c r="L67" s="5" t="n">
         <v>98.8</v>
       </c>
-      <c r="L67" s="3" t="n">
+      <c r="M67" s="3" t="n">
         <v>1384</v>
       </c>
-      <c r="M67" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N67" s="3" t="n">
         <v>0</v>
       </c>
@@ -5047,15 +5060,18 @@
         <v>0</v>
       </c>
       <c r="R67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="3" t="n">
         <v>2721</v>
       </c>
-      <c r="S67" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="3" t="n">
         <v>4832</v>
       </c>
-      <c r="U67" s="3" t="n">
+      <c r="V67" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5075,35 +5091,32 @@
           <t xml:space="preserve">RBX_MED_MS </t>
         </is>
       </c>
-      <c r="H68" s="3" t="n">
+      <c r="I68" s="3" t="n">
         <v>46262</v>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="J68" s="4" t="n">
         <v>1061.94</v>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
-      <c r="K68" s="5" t="n">
+      <c r="L68" s="5" t="n">
         <v>92.2</v>
       </c>
-      <c r="L68" s="3" t="n">
+      <c r="M68" s="3" t="n">
         <v>33302</v>
       </c>
-      <c r="M68" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3" t="n">
         <v>12786</v>
       </c>
-      <c r="P68" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q68" s="3" t="n">
         <v>0</v>
       </c>
@@ -5114,9 +5127,12 @@
         <v>0</v>
       </c>
       <c r="T68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3" t="n">
         <v>33476</v>
       </c>
-      <c r="U68" s="3" t="n">
+      <c r="V68" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5131,21 +5147,18 @@
           <t>Médiathèque - Documents non patrimoniaux</t>
         </is>
       </c>
-      <c r="H69" s="3" t="n">
+      <c r="I69" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="I69" s="4" t="n">
+      <c r="J69" s="4" t="n">
         <v>17.09</v>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="K69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="3" t="n">
+      <c r="L69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M69" s="3" t="n">
@@ -5173,6 +5186,9 @@
         <v>0</v>
       </c>
       <c r="U69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5192,34 +5208,31 @@
           <t xml:space="preserve">RBX_MED_PAR </t>
         </is>
       </c>
-      <c r="H70" s="3" t="n">
-        <v>5769</v>
-      </c>
-      <c r="I70" s="4" t="n">
-        <v>93.51000000000001</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (5035) ; À SUPPRIMER (686) ; CORBEILLE (DIFFUSION) (21) ; INCONNU (20) ; EN LIGNE - À TRANSFERER ? (6) ; À SUPPRIMER (RENOMMAGE) (1)</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>5041</v>
+      <c r="I70" s="3" t="n">
+        <v>24433</v>
+      </c>
+      <c r="J70" s="4" t="n">
+        <v>543.4</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (17675) ; EN LIGNE - À TRANSFERER ? (3821) ; À SUPPRIMER (doublons S3 - az) (1675) ; À SUPPRIMER (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; CORBEILLE (DIFFUSION) (21)</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>20721</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>292</v>
+        <v>2</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>5156</v>
       </c>
       <c r="Q70" s="3" t="n">
         <v>0</v>
@@ -5231,10 +5244,13 @@
         <v>0</v>
       </c>
       <c r="T70" s="3" t="n">
-        <v>5477</v>
+        <v>0</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>0</v>
+        <v>19271</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -5248,21 +5264,18 @@
           <t>Médiathèque - Collections de particuliers (suite)</t>
         </is>
       </c>
-      <c r="H71" s="3" t="n">
+      <c r="I71" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="I71" s="4" t="n">
+      <c r="J71" s="4" t="n">
         <v>7.94</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>INCONNU (1084)</t>
         </is>
       </c>
-      <c r="K71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3" t="n">
+      <c r="L71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
@@ -5287,9 +5300,12 @@
         <v>0</v>
       </c>
       <c r="T71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="U71" s="3" t="n">
+      <c r="V71" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5304,23 +5320,20 @@
           <t>Médiathèque - Périodiques</t>
         </is>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="I72" s="3" t="n">
         <v>1596</v>
       </c>
-      <c r="I72" s="4" t="n">
+      <c r="J72" s="4" t="n">
         <v>29.68</v>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1596)</t>
         </is>
       </c>
-      <c r="K72" s="5" t="n">
+      <c r="L72" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L72" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M72" s="3" t="n">
         <v>0</v>
       </c>
@@ -5337,15 +5350,18 @@
         <v>0</v>
       </c>
       <c r="R72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3" t="n">
         <v>829</v>
       </c>
-      <c r="S72" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" s="3" t="n">
         <v>767</v>
       </c>
-      <c r="U72" s="3" t="n">
+      <c r="V72" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5360,21 +5376,18 @@
           <t>Médiathèque - Collections de photographies</t>
         </is>
       </c>
-      <c r="H73" s="3" t="n">
+      <c r="I73" s="3" t="n">
         <v>1949</v>
       </c>
-      <c r="I73" s="4" t="n">
+      <c r="J73" s="4" t="n">
         <v>28.52</v>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>INCONNU (1949)</t>
         </is>
       </c>
-      <c r="K73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="3" t="n">
+      <c r="L73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M73" s="3" t="n">
@@ -5399,9 +5412,12 @@
         <v>0</v>
       </c>
       <c r="T73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3" t="n">
         <v>1949</v>
       </c>
-      <c r="U73" s="3" t="n">
+      <c r="V73" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5421,35 +5437,32 @@
           <t xml:space="preserve">RBX_MED_PHO </t>
         </is>
       </c>
-      <c r="H74" s="3" t="n">
+      <c r="I74" s="3" t="n">
         <v>18844</v>
       </c>
-      <c r="I74" s="4" t="n">
+      <c r="J74" s="4" t="n">
         <v>69.83</v>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="K74" s="5" t="n">
+      <c r="L74" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="L74" s="3" t="n">
+      <c r="M74" s="3" t="n">
         <v>1140</v>
       </c>
-      <c r="M74" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="O74" s="3" t="n">
+      <c r="P74" s="3" t="n">
         <v>13861</v>
       </c>
-      <c r="P74" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q74" s="3" t="n">
         <v>0</v>
       </c>
@@ -5457,12 +5470,15 @@
         <v>0</v>
       </c>
       <c r="S74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="T74" s="3" t="n">
+      <c r="U74" s="3" t="n">
         <v>4804</v>
       </c>
-      <c r="U74" s="3" t="n">
+      <c r="V74" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5482,35 +5498,32 @@
           <t xml:space="preserve">RBX_MED_PLA </t>
         </is>
       </c>
-      <c r="H75" s="3" t="n">
+      <c r="I75" s="3" t="n">
         <v>548</v>
       </c>
-      <c r="I75" s="4" t="n">
+      <c r="J75" s="4" t="n">
         <v>38.23</v>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
         </is>
       </c>
-      <c r="K75" s="5" t="n">
+      <c r="L75" s="5" t="n">
         <v>49.8</v>
       </c>
-      <c r="L75" s="3" t="n">
+      <c r="M75" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="M75" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="P75" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q75" s="3" t="n">
         <v>0</v>
       </c>
@@ -5521,9 +5534,12 @@
         <v>0</v>
       </c>
       <c r="T75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="U75" s="3" t="n">
+      <c r="V75" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5543,26 +5559,23 @@
           <t xml:space="preserve">RBX_MED_PUB </t>
         </is>
       </c>
-      <c r="H76" s="3" t="n">
+      <c r="I76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="I76" s="4" t="n">
+      <c r="J76" s="4" t="n">
         <v>49.96</v>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (2419)</t>
         </is>
       </c>
-      <c r="K76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="3" t="n">
+      <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="M76" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N76" s="3" t="n">
         <v>0</v>
       </c>
@@ -5582,9 +5595,12 @@
         <v>0</v>
       </c>
       <c r="T76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="U76" s="3" t="n">
+      <c r="V76" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5599,21 +5615,18 @@
           <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
-      <c r="H77" s="3" t="n">
+      <c r="I77" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="I77" s="4" t="n">
+      <c r="J77" s="4" t="n">
         <v>9.57</v>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>INCONNU (238)</t>
         </is>
       </c>
-      <c r="K77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="3" t="n">
+      <c r="L77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M77" s="3" t="n">
@@ -5638,9 +5651,12 @@
         <v>0</v>
       </c>
       <c r="T77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="U77" s="3" t="n">
+      <c r="V77" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5660,48 +5676,48 @@
           <t xml:space="preserve">RBX_MED_VDM </t>
         </is>
       </c>
-      <c r="H78" s="3" t="n">
+      <c r="I78" s="3" t="n">
         <v>38231</v>
       </c>
-      <c r="I78" s="4" t="n">
+      <c r="J78" s="4" t="n">
         <v>956.36</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="K78" s="5" t="n">
+      <c r="L78" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L78" s="3" t="n">
+      <c r="M78" s="3" t="n">
         <v>31272</v>
       </c>
-      <c r="M78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="O78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="3" t="n">
         <v>38229</v>
       </c>
-      <c r="U78" s="3" t="n">
+      <c r="V78" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5716,32 +5732,29 @@
           <t>Médiathèque - Documents vidéos</t>
         </is>
       </c>
-      <c r="H79" s="3" t="n">
+      <c r="I79" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="I79" s="4" t="n">
+      <c r="J79" s="4" t="n">
         <v>8.82</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
         </is>
       </c>
-      <c r="K79" s="5" t="n">
+      <c r="L79" s="5" t="n">
         <v>48.4</v>
       </c>
-      <c r="L79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="M79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="O79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P79" s="3" t="n">
         <v>0</v>
       </c>
@@ -5752,12 +5765,15 @@
         <v>0</v>
       </c>
       <c r="S79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5777,35 +5793,32 @@
           <t xml:space="preserve">RBX_MUS_ARC </t>
         </is>
       </c>
-      <c r="H80" s="3" t="n">
+      <c r="I80" s="3" t="n">
         <v>318</v>
       </c>
-      <c r="I80" s="4" t="n">
+      <c r="J80" s="4" t="n">
         <v>3.42</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (318)</t>
         </is>
       </c>
-      <c r="K80" s="5" t="n">
+      <c r="L80" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L80" s="3" t="n">
+      <c r="M80" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="M80" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="P80" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q80" s="3" t="n">
         <v>0</v>
       </c>
@@ -5816,9 +5829,12 @@
         <v>0</v>
       </c>
       <c r="T80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="U80" s="3" t="n">
+      <c r="V80" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5838,35 +5854,32 @@
           <t xml:space="preserve">RBX_MUS_VAI </t>
         </is>
       </c>
-      <c r="H81" s="3" t="n">
+      <c r="I81" s="3" t="n">
         <v>1918</v>
       </c>
-      <c r="I81" s="4" t="n">
+      <c r="J81" s="4" t="n">
         <v>47.42</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1918)</t>
         </is>
       </c>
-      <c r="K81" s="5" t="n">
+      <c r="L81" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L81" s="3" t="n">
+      <c r="M81" s="3" t="n">
         <v>1859</v>
       </c>
-      <c r="M81" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="P81" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3" t="n">
         <v>0</v>
       </c>
@@ -5877,9 +5890,12 @@
         <v>0</v>
       </c>
       <c r="T81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3" t="n">
         <v>1514</v>
       </c>
-      <c r="U81" s="3" t="n">
+      <c r="V81" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5894,21 +5910,18 @@
           <t>Musée La Piscine - nouveau versement</t>
         </is>
       </c>
-      <c r="H82" s="3" t="n">
+      <c r="I82" s="3" t="n">
         <v>375</v>
       </c>
-      <c r="I82" s="4" t="n">
+      <c r="J82" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>INCONNU (375)</t>
         </is>
       </c>
-      <c r="K82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" s="3" t="n">
+      <c r="L82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M82" s="3" t="n">
@@ -5918,11 +5931,11 @@
         <v>0</v>
       </c>
       <c r="O82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="3" t="n">
         <v>375</v>
       </c>
-      <c r="P82" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q82" s="3" t="n">
         <v>0</v>
       </c>
@@ -5936,6 +5949,9 @@
         <v>0</v>
       </c>
       <c r="U82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5955,35 +5971,32 @@
           <t xml:space="preserve">RBX_OBS_JOU </t>
         </is>
       </c>
-      <c r="H83" s="3" t="n">
+      <c r="I83" s="3" t="n">
         <v>2802</v>
       </c>
-      <c r="I83" s="4" t="n">
+      <c r="J83" s="4" t="n">
         <v>31.32</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1925) ; EN LIGNE - À TRANSFERER ? (868) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (4)</t>
         </is>
       </c>
-      <c r="K83" s="5" t="n">
+      <c r="L83" s="5" t="n">
         <v>68.8</v>
       </c>
-      <c r="L83" s="3" t="n">
+      <c r="M83" s="3" t="n">
         <v>2238</v>
       </c>
-      <c r="M83" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="n">
         <v>1808</v>
       </c>
-      <c r="P83" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3" t="n">
         <v>0</v>
       </c>
@@ -5991,45 +6004,55 @@
         <v>0</v>
       </c>
       <c r="S83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="T83" s="3" t="n">
+      <c r="U83" s="3" t="n">
         <v>920</v>
       </c>
-      <c r="U83" s="3" t="n">
+      <c r="V83" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PAR_BOH</t>
+          <t>PRA_AVE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Particuliers - Bohée</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>638</v>
-      </c>
-      <c r="I84" s="4" t="n">
-        <v>17.59</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (638)</t>
-        </is>
-      </c>
-      <c r="K84" s="5" t="n">
+          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_AVE </t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>176340</v>
+      </c>
+      <c r="J84" s="4" t="n">
+        <v>778.75</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (176340)</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L84" s="3" t="n">
-        <v>382</v>
-      </c>
       <c r="M84" s="3" t="n">
-        <v>0</v>
+        <v>87510</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>0</v>
@@ -6044,45 +6067,45 @@
         <v>0</v>
       </c>
       <c r="R84" s="3" t="n">
-        <v>0</v>
+        <v>44271</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>0</v>
+        <v>43519</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>638</v>
+        <v>44275</v>
       </c>
       <c r="U84" s="3" t="n">
+        <v>44275</v>
+      </c>
+      <c r="V84" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PAR_BOU</t>
+          <t>PRA_BDR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Particuliers - Boussac</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>8790</v>
-      </c>
-      <c r="I85" s="4" t="n">
-        <v>331.23</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (8790)</t>
-        </is>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>8435</v>
+          <t>Presse - Bulletin de Roubaix</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>3138</v>
+      </c>
+      <c r="J85" s="4" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>INCONNU (2781) ; À SUPPRIMER (doublons S3 - az) (178) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>11.4</v>
       </c>
       <c r="M85" s="3" t="n">
         <v>0</v>
@@ -6091,63 +6114,73 @@
         <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="Q85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>0</v>
+        <v>407</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>8790</v>
+        <v>1218</v>
       </c>
       <c r="U85" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="V85" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PAR_CAT</t>
+          <t>PRA_CRT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Particuliers - Catrice</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>EN LIGNE - À TRANSFERER ? (265)</t>
-        </is>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>265</v>
+          <t>Presse - La Croix de Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_CRT </t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>116806</v>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>1024.92</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (116806)</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>0</v>
+        <v>48452</v>
       </c>
       <c r="N86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="3" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="P86" s="3" t="n">
         <v>0</v>
@@ -6156,48 +6189,58 @@
         <v>0</v>
       </c>
       <c r="R86" s="3" t="n">
-        <v>0</v>
+        <v>29202</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>0</v>
+        <v>29200</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>39</v>
+        <v>29202</v>
       </c>
       <c r="U86" s="3" t="n">
+        <v>29202</v>
+      </c>
+      <c r="V86" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PAR_CHI</t>
+          <t>PRA_CTG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Particuliers - Chirez</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (89)</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="n">
+          <t>Presse - Le Courrier de Tourcoing</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_CTG </t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>5752</v>
+      </c>
+      <c r="J87" s="4" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (5752)</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L87" s="3" t="n">
-        <v>88</v>
-      </c>
       <c r="M87" s="3" t="n">
-        <v>0</v>
+        <v>2876</v>
       </c>
       <c r="N87" s="3" t="n">
         <v>0</v>
@@ -6212,48 +6255,58 @@
         <v>0</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>0</v>
+        <v>1438</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>0</v>
+        <v>1438</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>89</v>
+        <v>1438</v>
       </c>
       <c r="U87" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="V87" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PAR_DED</t>
+          <t>PRA_ERT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Particuliers - Dedaele</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I88" s="4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>EN LIGNE - À TRANSFERER ? (40)</t>
-        </is>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>40</v>
+          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_ERT </t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>377078</v>
+      </c>
+      <c r="J88" s="4" t="n">
+        <v>3103.47</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (377078)</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>185403</v>
       </c>
       <c r="N88" s="3" t="n">
         <v>0</v>
@@ -6268,48 +6321,58 @@
         <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
-        <v>0</v>
+        <v>94387</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>0</v>
+        <v>93918</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>40</v>
+        <v>94387</v>
       </c>
       <c r="U88" s="3" t="n">
+        <v>94386</v>
+      </c>
+      <c r="V88" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PAR_LAT</t>
+          <t>PRA_IND</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Particuliers - Latu</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (35)</t>
-        </is>
-      </c>
-      <c r="K89" s="5" t="n">
+          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_IND </t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>64400</v>
+      </c>
+      <c r="J89" s="4" t="n">
+        <v>199.84</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (64400)</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L89" s="3" t="n">
-        <v>35</v>
-      </c>
       <c r="M89" s="3" t="n">
-        <v>0</v>
+        <v>32665</v>
       </c>
       <c r="N89" s="3" t="n">
         <v>0</v>
@@ -6324,54 +6387,64 @@
         <v>0</v>
       </c>
       <c r="R89" s="3" t="n">
-        <v>0</v>
+        <v>15377</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>0</v>
+        <v>16307</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>35</v>
+        <v>16358</v>
       </c>
       <c r="U89" s="3" t="n">
+        <v>16358</v>
+      </c>
+      <c r="V89" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PAR_MOR</t>
+          <t>PRA_JRX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Particuliers - Une Roubaisienne</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>EN LIGNE - À TRANSFERER ? (96)</t>
-        </is>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>96</v>
+          <t>Presse - Journal de Roubaix</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_JRX </t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>595291</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>4704.6</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (595291)</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>0</v>
+        <v>284717</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="3" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="P90" s="3" t="n">
         <v>0</v>
@@ -6380,48 +6453,58 @@
         <v>0</v>
       </c>
       <c r="R90" s="3" t="n">
-        <v>0</v>
+        <v>148174</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>0</v>
+        <v>148814</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>0</v>
+        <v>149132</v>
       </c>
       <c r="U90" s="3" t="n">
+        <v>149171</v>
+      </c>
+      <c r="V90" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PAR_NAJ</t>
+          <t>PRA_RTG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Particuliers - Najberg</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="I91" s="4" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (23)</t>
-        </is>
-      </c>
-      <c r="K91" s="5" t="n">
+          <t>Presse - Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_VAH_PUB </t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>3367</v>
+      </c>
+      <c r="J91" s="4" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (3367)</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="L91" s="3" t="n">
-        <v>23</v>
-      </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>1671</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>0</v>
@@ -6436,48 +6519,53 @@
         <v>0</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>23</v>
+        <v>848</v>
       </c>
       <c r="U91" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="V91" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PAR_NIE</t>
+          <t>VAH_PUB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Particuliers - Nielsen</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>148</v>
-      </c>
-      <c r="I92" s="4" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (148)</t>
-        </is>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>4</v>
+          <t>Ville d'art et d'histoire  - Publications</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_VAH_PUB </t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="J92" s="4" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>EN LIGNE - À TRANSFERER ? (457)</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>0</v>
@@ -6498,981 +6586,126 @@
         <v>0</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="U92" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="V92" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PAR_PRE</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Particuliers - Prevost</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>3710</v>
-      </c>
-      <c r="I93" s="4" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>EN LIGNE - À TRANSFERER ? (3414) ; INCONNU (296)</t>
-        </is>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>3414</v>
+          <t>_INCONNU</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>4080</v>
+      </c>
+      <c r="J93" s="4" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>59.3</v>
       </c>
       <c r="M93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>3233</v>
+        <v>2244</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="Q93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>475</v>
+        <v>29</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>0</v>
+        <v>212</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>PAR_RAI</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Particuliers - Destombes</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>524</v>
-      </c>
-      <c r="I94" s="4" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (524)</t>
-        </is>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>524</v>
-      </c>
-      <c r="M94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="n">
-        <v>524</v>
-      </c>
-      <c r="U94" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>PAR_TER</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Particuliers - Termeulen</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>884</v>
-      </c>
-      <c r="I95" s="4" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (884)</t>
-        </is>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>884</v>
-      </c>
-      <c r="M95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="3" t="n">
-        <v>884</v>
-      </c>
-      <c r="P95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>PAR_TRI</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Particuliers - Triail</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (48) ; À SUPPRIMER (doublons S3 - az) (2)</t>
-        </is>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="M96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="U96" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>PAR_TUR</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Particuliers - Turgot</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>1461</v>
-      </c>
-      <c r="I97" s="4" t="n">
-        <v>53.41</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (1461)</t>
-        </is>
-      </c>
-      <c r="K97" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L97" s="3" t="n">
-        <v>1444</v>
-      </c>
-      <c r="M97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" s="3" t="n">
-        <v>1461</v>
-      </c>
-      <c r="U97" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>PRA_AVE</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_AVE </t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>176340</v>
-      </c>
-      <c r="I98" s="4" t="n">
-        <v>778.75</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (176340)</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L98" s="3" t="n">
-        <v>87510</v>
-      </c>
-      <c r="M98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="3" t="n">
-        <v>44271</v>
-      </c>
-      <c r="R98" s="3" t="n">
-        <v>43519</v>
-      </c>
-      <c r="S98" s="3" t="n">
-        <v>44275</v>
-      </c>
-      <c r="T98" s="3" t="n">
-        <v>44275</v>
-      </c>
-      <c r="U98" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>PRA_BDR</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Presse - Bulletin de Roubaix</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="n">
-        <v>3138</v>
-      </c>
-      <c r="I99" s="4" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>INCONNU (2781) ; À SUPPRIMER (doublons S3 - az) (178) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
-        </is>
-      </c>
-      <c r="K99" s="5" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O99" s="3" t="n">
-        <v>523</v>
-      </c>
-      <c r="P99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="3" t="n">
-        <v>406</v>
-      </c>
-      <c r="R99" s="3" t="n">
-        <v>407</v>
-      </c>
-      <c r="S99" s="3" t="n">
-        <v>1218</v>
-      </c>
-      <c r="T99" s="3" t="n">
-        <v>583</v>
-      </c>
-      <c r="U99" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>PRA_CRT</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Presse - La Croix de Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_CRT </t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="n">
-        <v>116806</v>
-      </c>
-      <c r="I100" s="4" t="n">
-        <v>1024.92</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (116806)</t>
-        </is>
-      </c>
-      <c r="K100" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>48452</v>
-      </c>
-      <c r="M100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="n">
-        <v>29202</v>
-      </c>
-      <c r="R100" s="3" t="n">
-        <v>29200</v>
-      </c>
-      <c r="S100" s="3" t="n">
-        <v>29202</v>
-      </c>
-      <c r="T100" s="3" t="n">
-        <v>29202</v>
-      </c>
-      <c r="U100" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>PRA_CTG</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Presse - Le Courrier de Tourcoing</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_CTG </t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="n">
-        <v>5752</v>
-      </c>
-      <c r="I101" s="4" t="n">
-        <v>45.98</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (5752)</t>
-        </is>
-      </c>
-      <c r="K101" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L101" s="3" t="n">
-        <v>2876</v>
-      </c>
-      <c r="M101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="n">
-        <v>1438</v>
-      </c>
-      <c r="R101" s="3" t="n">
-        <v>1438</v>
-      </c>
-      <c r="S101" s="3" t="n">
-        <v>1438</v>
-      </c>
-      <c r="T101" s="3" t="n">
-        <v>1438</v>
-      </c>
-      <c r="U101" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>PRA_ERT</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_ERT </t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="n">
-        <v>377078</v>
-      </c>
-      <c r="I102" s="4" t="n">
-        <v>3103.47</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (377078)</t>
-        </is>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L102" s="3" t="n">
-        <v>185403</v>
-      </c>
-      <c r="M102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3" t="n">
-        <v>94387</v>
-      </c>
-      <c r="R102" s="3" t="n">
-        <v>93918</v>
-      </c>
-      <c r="S102" s="3" t="n">
-        <v>94387</v>
-      </c>
-      <c r="T102" s="3" t="n">
-        <v>94386</v>
-      </c>
-      <c r="U102" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>PRA_IND</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_IND </t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="n">
-        <v>64400</v>
-      </c>
-      <c r="I103" s="4" t="n">
-        <v>199.84</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (64400)</t>
-        </is>
-      </c>
-      <c r="K103" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L103" s="3" t="n">
-        <v>32665</v>
-      </c>
-      <c r="M103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="3" t="n">
-        <v>15377</v>
-      </c>
-      <c r="R103" s="3" t="n">
-        <v>16307</v>
-      </c>
-      <c r="S103" s="3" t="n">
-        <v>16358</v>
-      </c>
-      <c r="T103" s="3" t="n">
-        <v>16358</v>
-      </c>
-      <c r="U103" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>PRA_JRX</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Presse - Journal de Roubaix</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_JRX </t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>595291</v>
-      </c>
-      <c r="I104" s="4" t="n">
-        <v>4704.6</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (595291)</t>
-        </is>
-      </c>
-      <c r="K104" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L104" s="3" t="n">
-        <v>284717</v>
-      </c>
-      <c r="M104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="3" t="n">
-        <v>148174</v>
-      </c>
-      <c r="R104" s="3" t="n">
-        <v>148814</v>
-      </c>
-      <c r="S104" s="3" t="n">
-        <v>149132</v>
-      </c>
-      <c r="T104" s="3" t="n">
-        <v>149171</v>
-      </c>
-      <c r="U104" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>PRA_RTG</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Presse - Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_VAH_PUB </t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>3367</v>
-      </c>
-      <c r="I105" s="4" t="n">
-        <v>19.37</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (3367)</t>
-        </is>
-      </c>
-      <c r="K105" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L105" s="3" t="n">
-        <v>1671</v>
-      </c>
-      <c r="M105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="3" t="n">
-        <v>848</v>
-      </c>
-      <c r="R105" s="3" t="n">
-        <v>823</v>
-      </c>
-      <c r="S105" s="3" t="n">
-        <v>848</v>
-      </c>
-      <c r="T105" s="3" t="n">
-        <v>848</v>
-      </c>
-      <c r="U105" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>VAH_PUB</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Ville d'art et d'histoire  - Publications</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_VAH_PUB </t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>457</v>
-      </c>
-      <c r="I106" s="4" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>EN LIGNE - À TRANSFERER ? (457)</t>
-        </is>
-      </c>
-      <c r="K106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="3" t="n">
-        <v>457</v>
-      </c>
-      <c r="M106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" s="3" t="n">
-        <v>457</v>
-      </c>
-      <c r="U106" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>_INCONNU</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>4080</v>
-      </c>
-      <c r="I107" s="4" t="n">
-        <v>86.63</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
-        </is>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="L107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N107" s="3" t="n">
-        <v>2244</v>
-      </c>
-      <c r="O107" s="3" t="n">
-        <v>857</v>
-      </c>
-      <c r="P107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R107" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="S107" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="T107" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="U107" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B108" s="6" t="inlineStr"/>
-      <c r="C108" s="6" t="inlineStr"/>
-      <c r="D108" s="6" t="inlineStr"/>
-      <c r="E108" s="6" t="inlineStr"/>
-      <c r="F108" s="6" t="inlineStr"/>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="7" t="n">
+      <c r="B94" s="6" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr"/>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+      <c r="I94" s="7" t="n">
         <v>2430327</v>
       </c>
-      <c r="I108" s="8" t="n">
+      <c r="J94" s="8" t="n">
         <v>20914.25</v>
       </c>
-      <c r="J108" s="6" t="inlineStr">
+      <c r="K94" s="6" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (2068905) ; INCONNU (135934) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37324) ; EN LIGNE - À TRANSFERER ? (28584) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; À SUPPRIMER (doublons S3 - az) (6149) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118)</t>
         </is>
       </c>
-      <c r="K108" s="9" t="n">
+      <c r="L94" s="9" t="n">
         <v>93.2</v>
       </c>
-      <c r="L108" s="7" t="n">
+      <c r="M94" s="7" t="n">
         <v>994727</v>
       </c>
-      <c r="M108" s="7" t="n">
+      <c r="N94" s="7" t="n">
         <v>7347</v>
       </c>
-      <c r="N108" s="7" t="n">
+      <c r="O94" s="7" t="n">
         <v>2453</v>
       </c>
-      <c r="O108" s="7" t="n">
+      <c r="P94" s="7" t="n">
         <v>673674</v>
       </c>
-      <c r="P108" s="7" t="n">
+      <c r="Q94" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="Q108" s="7" t="n">
+      <c r="R94" s="7" t="n">
         <v>334782</v>
       </c>
-      <c r="R108" s="7" t="n">
+      <c r="S94" s="7" t="n">
         <v>452908</v>
       </c>
-      <c r="S108" s="7" t="n">
+      <c r="T94" s="7" t="n">
         <v>338162</v>
       </c>
-      <c r="T108" s="7" t="n">
+      <c r="U94" s="7" t="n">
         <v>620516</v>
       </c>
-      <c r="U108" s="7" t="n">
+      <c r="V94" s="7" t="n">
         <v>465</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K2:K108">
+  <conditionalFormatting sqref="L2:L94">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V94"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -458,10 +458,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -470,6 +470,7 @@
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,70 +516,75 @@
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
+          <t>en ligne</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
           <t>fichiers</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>volume_go</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>conservation_statut</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>traitement_s3</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>fichiers_publies</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>audio</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>autre</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>jpeg</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>jpeg2000</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>ocr txt</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>ocr xml</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>pdf</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>tiff</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>video</t>
         </is>
@@ -610,23 +616,25 @@
           <t>1AEFi</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="K2" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (30) ; INCONNU (30)</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="M2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" s="3" t="n">
         <v>0</v>
       </c>
@@ -634,11 +642,11 @@
         <v>0</v>
       </c>
       <c r="P2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="Q2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
       </c>
@@ -652,6 +660,9 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -681,23 +692,25 @@
           <t>1I</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (50) ; INCONNU (47)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>51.5</v>
       </c>
-      <c r="M3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" s="3" t="n">
         <v>0</v>
       </c>
@@ -705,11 +718,11 @@
         <v>0</v>
       </c>
       <c r="P3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="Q3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" s="3" t="n">
         <v>0</v>
       </c>
@@ -723,6 +736,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -752,23 +768,25 @@
           <t>1NumFi</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="K4" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>INCONNU (6) ; CORBEILLE (DIFFUSION) (6)</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
@@ -776,11 +794,11 @@
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
@@ -791,9 +809,12 @@
         <v>0</v>
       </c>
       <c r="U4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="W4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -823,21 +844,23 @@
           <t>1PER3</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="K5" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>INCONNU (23)</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -847,14 +870,14 @@
         <v>0</v>
       </c>
       <c r="P5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="R5" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" s="3" t="n">
         <v>0</v>
       </c>
@@ -862,9 +885,12 @@
         <v>0</v>
       </c>
       <c r="U5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="W5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -889,21 +915,23 @@
           <t>2F</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>0.26</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -928,9 +956,12 @@
         <v>0</v>
       </c>
       <c r="U6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="W6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -960,23 +991,25 @@
           <t>2I</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>15703</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>9.08</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (15703)</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" s="3" t="n">
         <v>0</v>
       </c>
@@ -984,11 +1017,11 @@
         <v>0</v>
       </c>
       <c r="P7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>15703</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" s="3" t="n">
         <v>0</v>
       </c>
@@ -1002,6 +1035,9 @@
         <v>0</v>
       </c>
       <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1031,21 +1067,23 @@
           <t>308W</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="K8" s="4" t="n">
         <v>0.05</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>INCONNU (7)</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1067,12 +1105,15 @@
         <v>0</v>
       </c>
       <c r="T8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="U8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1102,21 +1143,23 @@
           <t>381W</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>INCONNU (11)</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1141,9 +1184,12 @@
         <v>0</v>
       </c>
       <c r="U9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="W9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1173,23 +1219,25 @@
           <t>3D</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n">
         <v>296</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="K10" s="4" t="n">
         <v>3.16</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>INCONNU (272) ; CORBEILLE (DIFFUSION) (24)</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>8.1</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" s="3" t="n">
         <v>0</v>
       </c>
@@ -1197,11 +1245,11 @@
         <v>0</v>
       </c>
       <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
       </c>
@@ -1209,12 +1257,15 @@
         <v>0</v>
       </c>
       <c r="T10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="W10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,21 +1295,23 @@
           <t>3O</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>2.71</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>INCONNU (27)</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1280,12 +1333,15 @@
         <v>0</v>
       </c>
       <c r="T11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="V11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="W11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1315,21 +1371,23 @@
           <t>3R</t>
         </is>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="K12" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>INCONNU (14)</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1354,9 +1412,12 @@
         <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="W12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1386,21 +1447,23 @@
           <t>4H</t>
         </is>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>0.12</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>INCONNU (5)</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1425,9 +1488,12 @@
         <v>0</v>
       </c>
       <c r="U13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="W13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1457,21 +1523,23 @@
           <t>4M</t>
         </is>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="K14" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>INCONNU (1)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1496,9 +1564,12 @@
         <v>0</v>
       </c>
       <c r="U14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="W14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1528,21 +1599,23 @@
           <t>507W</t>
         </is>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>INCONNU (496)</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1567,9 +1640,12 @@
         <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>496</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="W15" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1594,21 +1670,23 @@
           <t>5Fi</t>
         </is>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="K16" s="4" t="n">
         <v>0.17</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>INCONNU (2)</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1633,9 +1711,12 @@
         <v>0</v>
       </c>
       <c r="U16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="W16" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1665,21 +1746,23 @@
           <t>5M</t>
         </is>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="K17" s="4" t="n">
         <v>0.27</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>INCONNU (3)</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1689,11 +1772,11 @@
         <v>0</v>
       </c>
       <c r="P17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="3" t="n">
         <v>0</v>
       </c>
@@ -1704,9 +1787,12 @@
         <v>0</v>
       </c>
       <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="W17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1736,23 +1822,25 @@
           <t>6H</t>
         </is>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n">
         <v>76933</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="K18" s="4" t="n">
         <v>54.36</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (76933)</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" s="3" t="n">
         <v>0</v>
       </c>
@@ -1760,11 +1848,11 @@
         <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>76933</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" s="3" t="n">
         <v>0</v>
       </c>
@@ -1778,6 +1866,9 @@
         <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1807,21 +1898,23 @@
           <t>6M</t>
         </is>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="K19" s="4" t="n">
         <v>0.19</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -1843,12 +1936,15 @@
         <v>0</v>
       </c>
       <c r="T19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="V19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1878,21 +1974,23 @@
           <t>8C</t>
         </is>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="K20" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>INCONNU (10)</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -1917,9 +2015,12 @@
         <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="W20" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1949,21 +2050,23 @@
           <t>8J</t>
         </is>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="K21" s="4" t="n">
         <v>2.28</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>INCONNU (145)</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -1973,11 +2076,11 @@
         <v>0</v>
       </c>
       <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" s="3" t="n">
         <v>0</v>
       </c>
@@ -1988,9 +2091,12 @@
         <v>0</v>
       </c>
       <c r="U21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="W21" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2025,48 +2131,53 @@
           <t xml:space="preserve">RBX_AMR_AFF </t>
         </is>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>3650</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="K22" s="4" t="n">
         <v>219.66</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1076) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="M22" s="5" t="n">
         <v>74.7</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="N22" s="3" t="n">
         <v>1007</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>643</v>
       </c>
-      <c r="Q22" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="S22" s="3" t="n">
+      <c r="T22" s="3" t="n">
         <v>580</v>
       </c>
-      <c r="T22" s="3" t="n">
+      <c r="U22" s="3" t="n">
         <v>554</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="V22" s="3" t="n">
         <v>1508</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="W22" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2096,21 +2207,23 @@
           <t>8O</t>
         </is>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>604</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="K23" s="4" t="n">
         <v>83.84999999999999</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>INCONNU (604)</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2120,11 +2233,11 @@
         <v>0</v>
       </c>
       <c r="P23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="Q23" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" s="3" t="n">
         <v>0</v>
       </c>
@@ -2135,9 +2248,12 @@
         <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3" t="n">
         <v>302</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="W23" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2157,23 +2273,25 @@
           <t>?</t>
         </is>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="K24" s="4" t="n">
         <v>255.07</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (159)</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="M24" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" s="3" t="n">
         <v>0</v>
       </c>
@@ -2199,6 +2317,9 @@
         <v>0</v>
       </c>
       <c r="V24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="n">
         <v>159</v>
       </c>
     </row>
@@ -2223,23 +2344,25 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="K25" s="4" t="n">
         <v>2.9</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="M25" s="5" t="n">
         <v>47.8</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" s="3" t="n">
         <v>0</v>
       </c>
@@ -2247,11 +2370,11 @@
         <v>0</v>
       </c>
       <c r="P25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="Q25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
       </c>
@@ -2262,9 +2385,12 @@
         <v>0</v>
       </c>
       <c r="U25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="W25" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2299,35 +2425,37 @@
           <t xml:space="preserve">RBX_AMR_CAD </t>
         </is>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="n">
         <v>515</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="K26" s="4" t="n">
         <v>26.3</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="M26" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="N26" s="3" t="n">
         <v>247</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P26" s="3" t="n">
+      <c r="Q26" s="3" t="n">
         <v>433</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" s="3" t="n">
         <v>0</v>
       </c>
@@ -2335,12 +2463,15 @@
         <v>0</v>
       </c>
       <c r="T26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="V26" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="W26" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2370,23 +2501,25 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>18982</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="K27" s="4" t="n">
         <v>315.8</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="M27" s="5" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="M27" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" s="3" t="n">
         <v>0</v>
       </c>
@@ -2409,9 +2542,12 @@
         <v>0</v>
       </c>
       <c r="U27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>18982</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="W27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2441,23 +2577,25 @@
           <t>4H</t>
         </is>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>358</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="K28" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="M28" s="5" t="n">
         <v>73.7</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
       </c>
@@ -2465,24 +2603,27 @@
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3" t="n">
         <v>264</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>3</v>
       </c>
       <c r="U28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="W28" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2522,48 +2663,53 @@
           <t xml:space="preserve">RBX_AMR_DEL </t>
         </is>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="n">
         <v>170586</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="K29" s="4" t="n">
         <v>2435.11</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (122555) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (398) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="M29" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="N29" s="3" t="n">
         <v>122552</v>
       </c>
-      <c r="N29" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P29" s="3" t="n">
+      <c r="Q29" s="3" t="n">
         <v>23676</v>
       </c>
-      <c r="Q29" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="T29" s="3" t="n">
         <v>79005</v>
       </c>
-      <c r="T29" s="3" t="n">
+      <c r="U29" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="V29" s="3" t="n">
         <v>67624</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="W29" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2593,23 +2739,25 @@
           <t>9Fi</t>
         </is>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="n">
         <v>1761</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="K30" s="4" t="n">
         <v>44.68</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="M30" s="5" t="n">
         <v>49.9</v>
       </c>
-      <c r="M30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" s="3" t="n">
         <v>0</v>
       </c>
@@ -2617,11 +2765,11 @@
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3" t="n">
         <v>879</v>
       </c>
-      <c r="Q30" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
       </c>
@@ -2632,9 +2780,12 @@
         <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3" t="n">
         <v>882</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="W30" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2664,41 +2815,43 @@
           <t>E</t>
         </is>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>358109</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="K31" s="4" t="n">
         <v>760.01</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (249012) ; CORBEILLE (85333) ; INCONNU (23761) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="M31" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="Q31" s="3" t="n">
         <v>358080</v>
       </c>
-      <c r="Q31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="S31" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T31" s="3" t="n">
         <v>0</v>
       </c>
@@ -2706,6 +2859,9 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2730,23 +2886,25 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="K32" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="M32" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="M32" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" s="3" t="n">
         <v>0</v>
       </c>
@@ -2754,11 +2912,11 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" s="3" t="n">
         <v>0</v>
       </c>
@@ -2772,6 +2930,9 @@
         <v>0</v>
       </c>
       <c r="V32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2806,48 +2967,53 @@
           <t xml:space="preserve">RBX_AMR_GUE </t>
         </is>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="n">
         <v>678</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="K33" s="4" t="n">
         <v>1.78</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (678)</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
         <v>678</v>
       </c>
-      <c r="N33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>339</v>
       </c>
-      <c r="Q33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="n">
         <v>339</v>
       </c>
-      <c r="T33" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2882,23 +3048,25 @@
           <t xml:space="preserve">RBX_AMR_LEB </t>
         </is>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="K34" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="M34" s="5" t="n">
         <v>48.9</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
       </c>
@@ -2906,11 +3074,11 @@
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="Q34" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
       </c>
@@ -2921,9 +3089,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="W34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2953,35 +3124,37 @@
           <t>3O</t>
         </is>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="K35" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="M35" s="5" t="n">
         <v>19.4</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="3" t="n">
+      <c r="Q35" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Q35" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" s="3" t="n">
         <v>0</v>
       </c>
@@ -2992,9 +3165,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="W35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3029,26 +3205,28 @@
           <t xml:space="preserve">RBX_AMR_OBJ </t>
         </is>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="K36" s="4" t="n">
         <v>0.92</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="M36" s="5" t="n">
         <v>96.2</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="N36" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
       </c>
@@ -3068,9 +3246,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="W36" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3100,23 +3281,25 @@
           <t>J ?</t>
         </is>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
         <v>6901</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="K37" s="4" t="n">
         <v>9.25</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (6428) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (doublons S3 - az) (228)</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="M37" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" s="3" t="n">
         <v>0</v>
       </c>
@@ -3124,11 +3307,11 @@
         <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="3" t="n">
         <v>6668</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" s="3" t="n">
         <v>0</v>
       </c>
@@ -3139,9 +3322,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="W37" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3166,23 +3352,25 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>3.87</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="M38" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="M38" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N38" s="3" t="n">
         <v>0</v>
       </c>
@@ -3190,11 +3378,11 @@
         <v>0</v>
       </c>
       <c r="P38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" s="3" t="n">
         <v>0</v>
       </c>
@@ -3208,6 +3396,9 @@
         <v>0</v>
       </c>
       <c r="V38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3237,35 +3428,37 @@
           <t xml:space="preserve">RBX_AMR_PHO </t>
         </is>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="n">
         <v>18595</v>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="K39" s="4" t="n">
         <v>135.98</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>INCONNU (9293) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n">
+      <c r="M39" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="N39" s="3" t="n">
         <v>1194</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P39" s="3" t="n">
+      <c r="Q39" s="3" t="n">
         <v>8035</v>
       </c>
-      <c r="Q39" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
       </c>
@@ -3276,9 +3469,12 @@
         <v>0</v>
       </c>
       <c r="U39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="3" t="n">
         <v>10558</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="W39" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3308,35 +3504,37 @@
           <t xml:space="preserve">RBX_AMR_PLA </t>
         </is>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n">
         <v>376</v>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="K40" s="4" t="n">
         <v>48.9</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n">
+      <c r="M40" s="5" t="n">
         <v>35.1</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="N40" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="Q40" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
       </c>
@@ -3347,9 +3545,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="W40" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3379,48 +3580,53 @@
           <t>1F</t>
         </is>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="n">
         <v>122308</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="K41" s="4" t="n">
         <v>504.56</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (85759) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n">
+      <c r="M41" s="5" t="n">
         <v>93.40000000000001</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="N41" s="3" t="n">
         <v>65349</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="3" t="n">
         <v>114168</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="V41" s="3" t="n">
         <v>8135</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="W41" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3450,48 +3656,53 @@
           <t xml:space="preserve">RBX_AMR_PR </t>
         </is>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n">
         <v>4326</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="K42" s="4" t="n">
         <v>166.36</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="n">
+      <c r="M42" s="5" t="n">
         <v>27.8</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="N42" s="3" t="n">
         <v>668</v>
       </c>
-      <c r="N42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P42" s="3" t="n">
+      <c r="Q42" s="3" t="n">
         <v>786</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="T42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3" t="n">
         <v>3533</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="W42" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3526,48 +3737,53 @@
           <t xml:space="preserve">RBX_AMR_PUV </t>
         </is>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="n">
         <v>19188</v>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="K43" s="4" t="n">
         <v>338.52</v>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>INCONNU (16034) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
-      <c r="L43" s="5" t="n">
+      <c r="M43" s="5" t="n">
         <v>16.4</v>
       </c>
-      <c r="M43" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P43" s="3" t="n">
+      <c r="Q43" s="3" t="n">
         <v>6302</v>
       </c>
-      <c r="Q43" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3" t="n">
         <v>6302</v>
       </c>
-      <c r="T43" s="3" t="n">
+      <c r="U43" s="3" t="n">
         <v>279</v>
       </c>
-      <c r="U43" s="3" t="n">
+      <c r="V43" s="3" t="n">
         <v>6302</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="W43" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3597,21 +3813,23 @@
           <t>8Fi</t>
         </is>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="K44" s="4" t="n">
         <v>0.03</v>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="L44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -3621,11 +3839,11 @@
         <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" s="3" t="n">
         <v>0</v>
       </c>
@@ -3636,9 +3854,12 @@
         <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="W44" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3668,23 +3889,25 @@
           <t>246W</t>
         </is>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
         <v>19170</v>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="K45" s="4" t="n">
         <v>42.81</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
         </is>
       </c>
-      <c r="L45" s="5" t="n">
+      <c r="M45" s="5" t="n">
         <v>49.3</v>
       </c>
-      <c r="M45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" s="3" t="n">
         <v>0</v>
       </c>
@@ -3692,24 +3915,27 @@
         <v>0</v>
       </c>
       <c r="P45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3" t="n">
         <v>9444</v>
       </c>
-      <c r="Q45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="S45" s="3" t="n">
+      <c r="T45" s="3" t="n">
         <v>9444</v>
       </c>
-      <c r="T45" s="3" t="n">
+      <c r="U45" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="U45" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="V45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3749,26 +3975,28 @@
           <t xml:space="preserve">RBX_AMR_RAM </t>
         </is>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="n">
         <v>37053</v>
       </c>
-      <c r="J46" s="4" t="n">
+      <c r="K46" s="4" t="n">
         <v>448.11</v>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (37053)</t>
         </is>
       </c>
-      <c r="L46" s="5" t="n">
+      <c r="M46" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="N46" s="3" t="n">
         <v>37053</v>
       </c>
-      <c r="N46" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O46" s="3" t="n">
         <v>0</v>
       </c>
@@ -3782,15 +4010,18 @@
         <v>0</v>
       </c>
       <c r="S46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3" t="n">
         <v>18527</v>
       </c>
-      <c r="T46" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3" t="n">
         <v>18526</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="W46" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3810,23 +4041,25 @@
           <t>?</t>
         </is>
       </c>
-      <c r="I47" s="3" t="n">
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="n">
         <v>449</v>
       </c>
-      <c r="J47" s="4" t="n">
+      <c r="K47" s="4" t="n">
         <v>5.17</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
         </is>
       </c>
-      <c r="L47" s="5" t="n">
+      <c r="M47" s="5" t="n">
         <v>42.8</v>
       </c>
-      <c r="M47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N47" s="3" t="n">
         <v>0</v>
       </c>
@@ -3834,11 +4067,11 @@
         <v>0</v>
       </c>
       <c r="P47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="Q47" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" s="3" t="n">
         <v>0</v>
       </c>
@@ -3849,9 +4082,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="V47" s="3" t="n">
+      <c r="W47" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3886,21 +4122,23 @@
           <t xml:space="preserve">RBX_AMR_VIC </t>
         </is>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n">
         <v>7072</v>
       </c>
-      <c r="J48" s="4" t="n">
+      <c r="K48" s="4" t="n">
         <v>12.12</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>INCONNU (7072)</t>
         </is>
       </c>
-      <c r="L48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3" t="n">
+      <c r="M48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
@@ -3910,11 +4148,11 @@
         <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="3" t="n">
         <v>7072</v>
       </c>
-      <c r="Q48" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
       </c>
@@ -3928,6 +4166,9 @@
         <v>0</v>
       </c>
       <c r="V48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3947,35 +4188,37 @@
           <t xml:space="preserve">RBX_ARA_CPS </t>
         </is>
       </c>
-      <c r="I49" s="3" t="n">
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="J49" s="4" t="n">
+      <c r="K49" s="4" t="n">
         <v>1.26</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
         </is>
       </c>
-      <c r="L49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3" t="n">
+      <c r="M49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="N49" s="3" t="n">
+      <c r="O49" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="O49" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="Q49" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" s="3" t="n">
         <v>0</v>
       </c>
@@ -3989,6 +4232,9 @@
         <v>0</v>
       </c>
       <c r="V49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4008,26 +4254,28 @@
           <t xml:space="preserve">RBX_CSV_PAL </t>
         </is>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="J50" s="4" t="n">
+      <c r="K50" s="4" t="n">
         <v>6.65</v>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (242)</t>
         </is>
       </c>
-      <c r="L50" s="5" t="n">
+      <c r="M50" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M50" s="3" t="n">
+      <c r="N50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="N50" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O50" s="3" t="n">
         <v>0</v>
       </c>
@@ -4047,9 +4295,12 @@
         <v>0</v>
       </c>
       <c r="U50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="V50" s="3" t="n">
+      <c r="W50" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4069,26 +4320,28 @@
           <t xml:space="preserve">RBX_LAI </t>
         </is>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="n">
         <v>2422</v>
       </c>
-      <c r="J51" s="4" t="n">
+      <c r="K51" s="4" t="n">
         <v>61.97</v>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1697) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
         </is>
       </c>
-      <c r="L51" s="5" t="n">
+      <c r="M51" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="M51" s="3" t="n">
+      <c r="N51" s="3" t="n">
         <v>1181</v>
       </c>
-      <c r="N51" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O51" s="3" t="n">
         <v>0</v>
       </c>
@@ -4099,18 +4352,21 @@
         <v>0</v>
       </c>
       <c r="R51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S51" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3" t="n">
         <v>2421</v>
       </c>
-      <c r="V51" s="3" t="n">
+      <c r="W51" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4130,26 +4386,28 @@
           <t xml:space="preserve">RBX_LAR_PUB </t>
         </is>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="J52" s="4" t="n">
+      <c r="K52" s="4" t="n">
         <v>18.33</v>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
         </is>
       </c>
-      <c r="L52" s="5" t="n">
+      <c r="M52" s="5" t="n">
         <v>97.90000000000001</v>
       </c>
-      <c r="M52" s="3" t="n">
+      <c r="N52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="N52" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O52" s="3" t="n">
         <v>0</v>
       </c>
@@ -4169,9 +4427,12 @@
         <v>0</v>
       </c>
       <c r="U52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" t="n">
         <v>3811</v>
       </c>
-      <c r="V52" s="3" t="n">
+      <c r="W52" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4191,26 +4452,28 @@
           <t xml:space="preserve">RBX_MDF_MTX </t>
         </is>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J53" s="4" t="n">
+      <c r="K53" s="4" t="n">
         <v>76.03</v>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (18)</t>
         </is>
       </c>
-      <c r="L53" s="5" t="n">
+      <c r="M53" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M53" s="3" t="n">
+      <c r="N53" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="N53" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O53" s="3" t="n">
         <v>0</v>
       </c>
@@ -4233,6 +4496,9 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4252,35 +4518,37 @@
           <t xml:space="preserve">RBX_MED_AFF </t>
         </is>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="n">
         <v>11038</v>
       </c>
-      <c r="J54" s="4" t="n">
+      <c r="K54" s="4" t="n">
         <v>529.5599999999999</v>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (5576) ; CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (175) ; INCONNU (111)</t>
         </is>
       </c>
-      <c r="L54" s="5" t="n">
+      <c r="M54" s="5" t="n">
         <v>48.5</v>
       </c>
-      <c r="M54" s="3" t="n">
+      <c r="N54" s="3" t="n">
         <v>5742</v>
       </c>
-      <c r="N54" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="3" t="n">
         <v>5176</v>
       </c>
-      <c r="Q54" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" s="3" t="n">
         <v>0</v>
       </c>
@@ -4291,9 +4559,12 @@
         <v>0</v>
       </c>
       <c r="U54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="3" t="n">
         <v>5862</v>
       </c>
-      <c r="V54" s="3" t="n">
+      <c r="W54" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4308,32 +4579,34 @@
           <t>Médiathèque - Vidéos</t>
         </is>
       </c>
-      <c r="I55" s="3" t="n">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="J55" s="4" t="n">
+      <c r="K55" s="4" t="n">
         <v>48.21</v>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="L55" s="5" t="n">
+      <c r="M55" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q55" s="3" t="n">
         <v>0</v>
       </c>
@@ -4350,6 +4623,9 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="3" t="n">
         <v>31</v>
       </c>
     </row>
@@ -4369,26 +4645,28 @@
           <t xml:space="preserve">RBX_MED_CHA </t>
         </is>
       </c>
-      <c r="I56" s="3" t="n">
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="J56" s="4" t="n">
+      <c r="K56" s="4" t="n">
         <v>17.58</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
         </is>
       </c>
-      <c r="L56" s="5" t="n">
+      <c r="M56" s="5" t="n">
         <v>50.2</v>
       </c>
-      <c r="M56" s="3" t="n">
+      <c r="N56" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="N56" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O56" s="3" t="n">
         <v>0</v>
       </c>
@@ -4408,9 +4686,12 @@
         <v>0</v>
       </c>
       <c r="U56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="3" t="n">
         <v>723</v>
       </c>
-      <c r="V56" s="3" t="n">
+      <c r="W56" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4430,48 +4711,53 @@
           <t xml:space="preserve">RBX_MED_CP </t>
         </is>
       </c>
-      <c r="I57" s="3" t="n">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="n">
         <v>6010</v>
       </c>
-      <c r="J57" s="4" t="n">
+      <c r="K57" s="4" t="n">
         <v>34.89</v>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (4534) ; INCONNU (651) ; À SUPPRIMER (doublons S3 - az) (536) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
         </is>
       </c>
-      <c r="L57" s="5" t="n">
+      <c r="M57" s="5" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="M57" s="3" t="n">
+      <c r="N57" s="3" t="n">
         <v>4672</v>
       </c>
-      <c r="N57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3" t="n">
         <v>307</v>
       </c>
-      <c r="Q57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S57" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3" t="n">
         <v>5702</v>
       </c>
-      <c r="V57" s="3" t="n">
+      <c r="W57" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4491,35 +4777,37 @@
           <t xml:space="preserve">RBX_MED_DIL </t>
         </is>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="n">
         <v>365</v>
       </c>
-      <c r="J58" s="4" t="n">
+      <c r="K58" s="4" t="n">
         <v>480.6</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
         </is>
       </c>
-      <c r="L58" s="5" t="n">
+      <c r="M58" s="5" t="n">
         <v>12.1</v>
       </c>
-      <c r="M58" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="P58" s="3" t="n">
+      <c r="Q58" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="Q58" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" s="3" t="n">
         <v>0</v>
       </c>
@@ -4530,9 +4818,12 @@
         <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="V58" s="3" t="n">
+      <c r="W58" s="3" t="n">
         <v>177</v>
       </c>
     </row>
@@ -4552,26 +4843,28 @@
           <t xml:space="preserve">RBX_MED_EPH </t>
         </is>
       </c>
-      <c r="I59" s="3" t="n">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="n">
         <v>846</v>
       </c>
-      <c r="J59" s="4" t="n">
+      <c r="K59" s="4" t="n">
         <v>10.17</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
         </is>
       </c>
-      <c r="L59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="n">
+      <c r="M59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="n">
         <v>840</v>
       </c>
-      <c r="N59" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O59" s="3" t="n">
         <v>0</v>
       </c>
@@ -4591,9 +4884,12 @@
         <v>0</v>
       </c>
       <c r="U59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3" t="n">
         <v>846</v>
       </c>
-      <c r="V59" s="3" t="n">
+      <c r="W59" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4608,21 +4904,23 @@
           <t>Médiathèque - Cartes postales fantaisie</t>
         </is>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="n">
         <v>2666</v>
       </c>
-      <c r="J60" s="4" t="n">
+      <c r="K60" s="4" t="n">
         <v>32.93</v>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>INCONNU (2666)</t>
         </is>
       </c>
-      <c r="L60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3" t="n">
+      <c r="M60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="3" t="n">
@@ -4647,9 +4945,12 @@
         <v>0</v>
       </c>
       <c r="U60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3" t="n">
         <v>2666</v>
       </c>
-      <c r="V60" s="3" t="n">
+      <c r="W60" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4669,35 +4970,37 @@
           <t xml:space="preserve">RBX_MED_FLR </t>
         </is>
       </c>
-      <c r="I61" s="3" t="n">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n">
         <v>8487</v>
       </c>
-      <c r="J61" s="4" t="n">
+      <c r="K61" s="4" t="n">
         <v>304.96</v>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (8487)</t>
         </is>
       </c>
-      <c r="L61" s="5" t="n">
+      <c r="M61" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M61" s="3" t="n">
+      <c r="N61" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N61" s="3" t="n">
+      <c r="O61" s="3" t="n">
         <v>7228</v>
       </c>
-      <c r="O61" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="P61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3" t="n">
         <v>478</v>
       </c>
-      <c r="Q61" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" s="3" t="n">
         <v>0</v>
       </c>
@@ -4708,9 +5011,12 @@
         <v>0</v>
       </c>
       <c r="U61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3" t="n">
         <v>781</v>
       </c>
-      <c r="V61" s="3" t="n">
+      <c r="W61" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4730,35 +5036,37 @@
           <t xml:space="preserve">RBX_MED_FOO </t>
         </is>
       </c>
-      <c r="I62" s="3" t="n">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="J62" s="4" t="n">
+      <c r="K62" s="4" t="n">
         <v>0.66</v>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
-      <c r="L62" s="5" t="n">
+      <c r="M62" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="M62" s="3" t="n">
+      <c r="N62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N62" s="3" t="n">
+      <c r="O62" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="O62" s="3" t="n">
+      <c r="P62" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P62" s="3" t="n">
+      <c r="Q62" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q62" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" s="3" t="n">
         <v>0</v>
       </c>
@@ -4772,6 +5080,9 @@
         <v>0</v>
       </c>
       <c r="V62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4791,35 +5102,37 @@
           <t xml:space="preserve">RBX_MED_IMA </t>
         </is>
       </c>
-      <c r="I63" s="3" t="n">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="n">
         <v>9856</v>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="K63" s="4" t="n">
         <v>131.47</v>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (8900) ; TRANSFERT_S3_OK (750) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45)</t>
         </is>
       </c>
-      <c r="L63" s="5" t="n">
+      <c r="M63" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="M63" s="3" t="n">
+      <c r="N63" s="3" t="n">
         <v>9623</v>
       </c>
-      <c r="N63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O63" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="Q63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" s="3" t="n">
         <v>0</v>
       </c>
@@ -4830,9 +5143,12 @@
         <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3" t="n">
         <v>9631</v>
       </c>
-      <c r="V63" s="3" t="n">
+      <c r="W63" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4847,23 +5163,25 @@
           <t>Médiathèque - Journaux</t>
         </is>
       </c>
-      <c r="I64" s="3" t="n">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n">
         <v>2174</v>
       </c>
-      <c r="J64" s="4" t="n">
+      <c r="K64" s="4" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
         </is>
       </c>
-      <c r="L64" s="5" t="n">
+      <c r="M64" s="5" t="n">
         <v>91.8</v>
       </c>
-      <c r="M64" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N64" s="3" t="n">
         <v>0</v>
       </c>
@@ -4886,9 +5204,12 @@
         <v>0</v>
       </c>
       <c r="U64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3" t="n">
         <v>2174</v>
       </c>
-      <c r="V64" s="3" t="n">
+      <c r="W64" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4908,26 +5229,28 @@
           <t xml:space="preserve">RBX_MED_LET </t>
         </is>
       </c>
-      <c r="I65" s="3" t="n">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="J65" s="4" t="n">
+      <c r="K65" s="4" t="n">
         <v>12.84</v>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (605)</t>
         </is>
       </c>
-      <c r="L65" s="5" t="n">
+      <c r="M65" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M65" s="3" t="n">
+      <c r="N65" s="3" t="n">
         <v>560</v>
       </c>
-      <c r="N65" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O65" s="3" t="n">
         <v>0</v>
       </c>
@@ -4947,9 +5270,12 @@
         <v>0</v>
       </c>
       <c r="U65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3" t="n">
         <v>605</v>
       </c>
-      <c r="V65" s="3" t="n">
+      <c r="W65" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4969,35 +5295,37 @@
           <t xml:space="preserve">RBX_MED_MAR </t>
         </is>
       </c>
-      <c r="I66" s="3" t="n">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="J66" s="4" t="n">
+      <c r="K66" s="4" t="n">
         <v>7.07</v>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
         </is>
       </c>
-      <c r="L66" s="5" t="n">
+      <c r="M66" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="M66" s="3" t="n">
+      <c r="N66" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="N66" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="Q66" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" s="3" t="n">
         <v>0</v>
       </c>
@@ -5008,9 +5336,12 @@
         <v>0</v>
       </c>
       <c r="U66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="V66" s="3" t="n">
+      <c r="W66" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5030,26 +5361,28 @@
           <t xml:space="preserve">RBX_MED_MON </t>
         </is>
       </c>
-      <c r="I67" s="3" t="n">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="n">
         <v>7553</v>
       </c>
-      <c r="J67" s="4" t="n">
+      <c r="K67" s="4" t="n">
         <v>205.74</v>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
         </is>
       </c>
-      <c r="L67" s="5" t="n">
+      <c r="M67" s="5" t="n">
         <v>98.8</v>
       </c>
-      <c r="M67" s="3" t="n">
+      <c r="N67" s="3" t="n">
         <v>1384</v>
       </c>
-      <c r="N67" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
       </c>
@@ -5063,15 +5396,18 @@
         <v>0</v>
       </c>
       <c r="S67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="3" t="n">
         <v>2721</v>
       </c>
-      <c r="T67" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="3" t="n">
         <v>4832</v>
       </c>
-      <c r="V67" s="3" t="n">
+      <c r="W67" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5091,35 +5427,37 @@
           <t xml:space="preserve">RBX_MED_MS </t>
         </is>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="n">
         <v>46262</v>
       </c>
-      <c r="J68" s="4" t="n">
+      <c r="K68" s="4" t="n">
         <v>1061.94</v>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
-      <c r="L68" s="5" t="n">
+      <c r="M68" s="5" t="n">
         <v>92.2</v>
       </c>
-      <c r="M68" s="3" t="n">
+      <c r="N68" s="3" t="n">
         <v>33302</v>
       </c>
-      <c r="N68" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3" t="n">
         <v>12786</v>
       </c>
-      <c r="Q68" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" s="3" t="n">
         <v>0</v>
       </c>
@@ -5130,9 +5468,12 @@
         <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3" t="n">
         <v>33476</v>
       </c>
-      <c r="V68" s="3" t="n">
+      <c r="W68" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5147,21 +5488,23 @@
           <t>Médiathèque - Documents non patrimoniaux</t>
         </is>
       </c>
-      <c r="I69" s="3" t="n">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J69" s="4" t="n">
+      <c r="K69" s="4" t="n">
         <v>17.09</v>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>INCONNU (4)</t>
         </is>
       </c>
-      <c r="L69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="3" t="n">
+      <c r="M69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N69" s="3" t="n">
@@ -5189,6 +5532,9 @@
         <v>0</v>
       </c>
       <c r="V69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5208,35 +5554,37 @@
           <t xml:space="preserve">RBX_MED_PAR </t>
         </is>
       </c>
-      <c r="I70" s="3" t="n">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="n">
         <v>24433</v>
       </c>
-      <c r="J70" s="4" t="n">
+      <c r="K70" s="4" t="n">
         <v>543.4</v>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (17675) ; EN LIGNE - À TRANSFERER ? (3821) ; À SUPPRIMER (doublons S3 - az) (1675) ; À SUPPRIMER (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; CORBEILLE (DIFFUSION) (21)</t>
         </is>
       </c>
-      <c r="L70" s="5" t="n">
+      <c r="M70" s="5" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="M70" s="3" t="n">
+      <c r="N70" s="3" t="n">
         <v>20721</v>
       </c>
-      <c r="N70" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P70" s="3" t="n">
+      <c r="Q70" s="3" t="n">
         <v>5156</v>
       </c>
-      <c r="Q70" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" s="3" t="n">
         <v>0</v>
       </c>
@@ -5247,9 +5595,12 @@
         <v>0</v>
       </c>
       <c r="U70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3" t="n">
         <v>19271</v>
       </c>
-      <c r="V70" s="3" t="n">
+      <c r="W70" s="3" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5264,21 +5615,23 @@
           <t>Médiathèque - Collections de particuliers (suite)</t>
         </is>
       </c>
-      <c r="I71" s="3" t="n">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="J71" s="4" t="n">
+      <c r="K71" s="4" t="n">
         <v>7.94</v>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>INCONNU (1084)</t>
         </is>
       </c>
-      <c r="L71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="3" t="n">
+      <c r="M71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
@@ -5303,9 +5656,12 @@
         <v>0</v>
       </c>
       <c r="U71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3" t="n">
         <v>1084</v>
       </c>
-      <c r="V71" s="3" t="n">
+      <c r="W71" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5320,23 +5676,25 @@
           <t>Médiathèque - Périodiques</t>
         </is>
       </c>
-      <c r="I72" s="3" t="n">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="n">
         <v>1596</v>
       </c>
-      <c r="J72" s="4" t="n">
+      <c r="K72" s="4" t="n">
         <v>29.68</v>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1596)</t>
         </is>
       </c>
-      <c r="L72" s="5" t="n">
+      <c r="M72" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M72" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N72" s="3" t="n">
         <v>0</v>
       </c>
@@ -5353,15 +5711,18 @@
         <v>0</v>
       </c>
       <c r="S72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3" t="n">
         <v>829</v>
       </c>
-      <c r="T72" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="U72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="3" t="n">
         <v>767</v>
       </c>
-      <c r="V72" s="3" t="n">
+      <c r="W72" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5376,21 +5737,23 @@
           <t>Médiathèque - Collections de photographies</t>
         </is>
       </c>
-      <c r="I73" s="3" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="n">
         <v>1949</v>
       </c>
-      <c r="J73" s="4" t="n">
+      <c r="K73" s="4" t="n">
         <v>28.52</v>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>INCONNU (1949)</t>
         </is>
       </c>
-      <c r="L73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3" t="n">
+      <c r="M73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N73" s="3" t="n">
@@ -5415,9 +5778,12 @@
         <v>0</v>
       </c>
       <c r="U73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3" t="n">
         <v>1949</v>
       </c>
-      <c r="V73" s="3" t="n">
+      <c r="W73" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5437,35 +5803,37 @@
           <t xml:space="preserve">RBX_MED_PHO </t>
         </is>
       </c>
-      <c r="I74" s="3" t="n">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="n">
         <v>18844</v>
       </c>
-      <c r="J74" s="4" t="n">
+      <c r="K74" s="4" t="n">
         <v>69.83</v>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
-      <c r="L74" s="5" t="n">
+      <c r="M74" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="M74" s="3" t="n">
+      <c r="N74" s="3" t="n">
         <v>1140</v>
       </c>
-      <c r="N74" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="P74" s="3" t="n">
+      <c r="Q74" s="3" t="n">
         <v>13861</v>
       </c>
-      <c r="Q74" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" s="3" t="n">
         <v>0</v>
       </c>
@@ -5473,12 +5841,15 @@
         <v>0</v>
       </c>
       <c r="T74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="U74" s="3" t="n">
+      <c r="V74" s="3" t="n">
         <v>4804</v>
       </c>
-      <c r="V74" s="3" t="n">
+      <c r="W74" s="3" t="n">
         <v>67</v>
       </c>
     </row>
@@ -5498,35 +5869,37 @@
           <t xml:space="preserve">RBX_MED_PLA </t>
         </is>
       </c>
-      <c r="I75" s="3" t="n">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="n">
         <v>548</v>
       </c>
-      <c r="J75" s="4" t="n">
+      <c r="K75" s="4" t="n">
         <v>38.23</v>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
         </is>
       </c>
-      <c r="L75" s="5" t="n">
+      <c r="M75" s="5" t="n">
         <v>49.8</v>
       </c>
-      <c r="M75" s="3" t="n">
+      <c r="N75" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="N75" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="Q75" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
       </c>
@@ -5537,9 +5910,12 @@
         <v>0</v>
       </c>
       <c r="U75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3" t="n">
         <v>275</v>
       </c>
-      <c r="V75" s="3" t="n">
+      <c r="W75" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5559,26 +5935,28 @@
           <t xml:space="preserve">RBX_MED_PUB </t>
         </is>
       </c>
-      <c r="I76" s="3" t="n">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="J76" s="4" t="n">
+      <c r="K76" s="4" t="n">
         <v>49.96</v>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (2419)</t>
         </is>
       </c>
-      <c r="L76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="3" t="n">
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="N76" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O76" s="3" t="n">
         <v>0</v>
       </c>
@@ -5598,9 +5976,12 @@
         <v>0</v>
       </c>
       <c r="U76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="3" t="n">
         <v>2419</v>
       </c>
-      <c r="V76" s="3" t="n">
+      <c r="W76" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5615,21 +5996,23 @@
           <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
-      <c r="I77" s="3" t="n">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="J77" s="4" t="n">
+      <c r="K77" s="4" t="n">
         <v>9.57</v>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>INCONNU (238)</t>
         </is>
       </c>
-      <c r="L77" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="3" t="n">
+      <c r="M77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="3" t="n">
@@ -5654,9 +6037,12 @@
         <v>0</v>
       </c>
       <c r="U77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="V77" s="3" t="n">
+      <c r="W77" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5676,48 +6062,53 @@
           <t xml:space="preserve">RBX_MED_VDM </t>
         </is>
       </c>
-      <c r="I78" s="3" t="n">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="n">
         <v>38231</v>
       </c>
-      <c r="J78" s="4" t="n">
+      <c r="K78" s="4" t="n">
         <v>956.36</v>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="L78" s="5" t="n">
+      <c r="M78" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M78" s="3" t="n">
+      <c r="N78" s="3" t="n">
         <v>31272</v>
       </c>
-      <c r="N78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="T78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="3" t="n">
         <v>38229</v>
       </c>
-      <c r="V78" s="3" t="n">
+      <c r="W78" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5732,32 +6123,34 @@
           <t>Médiathèque - Documents vidéos</t>
         </is>
       </c>
-      <c r="I79" s="3" t="n">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="J79" s="4" t="n">
+      <c r="K79" s="4" t="n">
         <v>8.82</v>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
         </is>
       </c>
-      <c r="L79" s="5" t="n">
+      <c r="M79" s="5" t="n">
         <v>48.4</v>
       </c>
-      <c r="M79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="P79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q79" s="3" t="n">
         <v>0</v>
       </c>
@@ -5768,12 +6161,15 @@
         <v>0</v>
       </c>
       <c r="T79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="U79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="V79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5793,35 +6189,37 @@
           <t xml:space="preserve">RBX_MUS_ARC </t>
         </is>
       </c>
-      <c r="I80" s="3" t="n">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="n">
         <v>318</v>
       </c>
-      <c r="J80" s="4" t="n">
+      <c r="K80" s="4" t="n">
         <v>3.42</v>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (318)</t>
         </is>
       </c>
-      <c r="L80" s="5" t="n">
+      <c r="M80" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M80" s="3" t="n">
+      <c r="N80" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="N80" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="Q80" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" s="3" t="n">
         <v>0</v>
       </c>
@@ -5832,9 +6230,12 @@
         <v>0</v>
       </c>
       <c r="U80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="V80" s="3" t="n">
+      <c r="W80" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5854,35 +6255,37 @@
           <t xml:space="preserve">RBX_MUS_VAI </t>
         </is>
       </c>
-      <c r="I81" s="3" t="n">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="n">
         <v>1918</v>
       </c>
-      <c r="J81" s="4" t="n">
+      <c r="K81" s="4" t="n">
         <v>47.42</v>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1918)</t>
         </is>
       </c>
-      <c r="L81" s="5" t="n">
+      <c r="M81" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M81" s="3" t="n">
+      <c r="N81" s="3" t="n">
         <v>1859</v>
       </c>
-      <c r="N81" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3" t="n">
         <v>404</v>
       </c>
-      <c r="Q81" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" s="3" t="n">
         <v>0</v>
       </c>
@@ -5893,9 +6296,12 @@
         <v>0</v>
       </c>
       <c r="U81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3" t="n">
         <v>1514</v>
       </c>
-      <c r="V81" s="3" t="n">
+      <c r="W81" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5910,21 +6316,23 @@
           <t>Musée La Piscine - nouveau versement</t>
         </is>
       </c>
-      <c r="I82" s="3" t="n">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="n">
         <v>375</v>
       </c>
-      <c r="J82" s="4" t="n">
+      <c r="K82" s="4" t="n">
         <v>0.16</v>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>INCONNU (375)</t>
         </is>
       </c>
-      <c r="L82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="3" t="n">
+      <c r="M82" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="3" t="n">
@@ -5934,11 +6342,11 @@
         <v>0</v>
       </c>
       <c r="P82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="3" t="n">
         <v>375</v>
       </c>
-      <c r="Q82" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" s="3" t="n">
         <v>0</v>
       </c>
@@ -5952,6 +6360,9 @@
         <v>0</v>
       </c>
       <c r="V82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5971,35 +6382,37 @@
           <t xml:space="preserve">RBX_OBS_JOU </t>
         </is>
       </c>
-      <c r="I83" s="3" t="n">
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="n">
         <v>2802</v>
       </c>
-      <c r="J83" s="4" t="n">
+      <c r="K83" s="4" t="n">
         <v>31.32</v>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (1925) ; EN LIGNE - À TRANSFERER ? (868) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (4)</t>
         </is>
       </c>
-      <c r="L83" s="5" t="n">
+      <c r="M83" s="5" t="n">
         <v>68.8</v>
       </c>
-      <c r="M83" s="3" t="n">
+      <c r="N83" s="3" t="n">
         <v>2238</v>
       </c>
-      <c r="N83" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="n">
         <v>1808</v>
       </c>
-      <c r="Q83" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" s="3" t="n">
         <v>0</v>
       </c>
@@ -6007,12 +6420,15 @@
         <v>0</v>
       </c>
       <c r="T83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="U83" s="3" t="n">
+      <c r="V83" s="3" t="n">
         <v>920</v>
       </c>
-      <c r="V83" s="3" t="n">
+      <c r="W83" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6037,26 +6453,28 @@
           <t xml:space="preserve">RBX_PRA_AVE </t>
         </is>
       </c>
-      <c r="I84" s="3" t="n">
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="n">
         <v>176340</v>
       </c>
-      <c r="J84" s="4" t="n">
+      <c r="K84" s="4" t="n">
         <v>778.75</v>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (176340)</t>
         </is>
       </c>
-      <c r="L84" s="5" t="n">
+      <c r="M84" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M84" s="3" t="n">
+      <c r="N84" s="3" t="n">
         <v>87510</v>
       </c>
-      <c r="N84" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O84" s="3" t="n">
         <v>0</v>
       </c>
@@ -6067,18 +6485,21 @@
         <v>0</v>
       </c>
       <c r="R84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3" t="n">
         <v>44271</v>
       </c>
-      <c r="S84" s="3" t="n">
+      <c r="T84" s="3" t="n">
         <v>43519</v>
-      </c>
-      <c r="T84" s="3" t="n">
-        <v>44275</v>
       </c>
       <c r="U84" s="3" t="n">
         <v>44275</v>
       </c>
       <c r="V84" s="3" t="n">
+        <v>44275</v>
+      </c>
+      <c r="W84" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6093,48 +6514,53 @@
           <t>Presse - Bulletin de Roubaix</t>
         </is>
       </c>
-      <c r="I85" s="3" t="n">
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="n">
         <v>3138</v>
       </c>
-      <c r="J85" s="4" t="n">
+      <c r="K85" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>INCONNU (2781) ; À SUPPRIMER (doublons S3 - az) (178) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
-      <c r="L85" s="5" t="n">
+      <c r="M85" s="5" t="n">
         <v>11.4</v>
       </c>
-      <c r="M85" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P85" s="3" t="n">
+      <c r="Q85" s="3" t="n">
         <v>523</v>
       </c>
-      <c r="Q85" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3" t="n">
         <v>406</v>
       </c>
-      <c r="S85" s="3" t="n">
+      <c r="T85" s="3" t="n">
         <v>407</v>
       </c>
-      <c r="T85" s="3" t="n">
+      <c r="U85" s="3" t="n">
         <v>1218</v>
       </c>
-      <c r="U85" s="3" t="n">
+      <c r="V85" s="3" t="n">
         <v>583</v>
       </c>
-      <c r="V85" s="3" t="n">
+      <c r="W85" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6159,26 +6585,28 @@
           <t xml:space="preserve">RBX_PRA_CRT </t>
         </is>
       </c>
-      <c r="I86" s="3" t="n">
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="n">
         <v>116806</v>
       </c>
-      <c r="J86" s="4" t="n">
+      <c r="K86" s="4" t="n">
         <v>1024.92</v>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (116806)</t>
         </is>
       </c>
-      <c r="L86" s="5" t="n">
+      <c r="M86" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M86" s="3" t="n">
+      <c r="N86" s="3" t="n">
         <v>48452</v>
       </c>
-      <c r="N86" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O86" s="3" t="n">
         <v>0</v>
       </c>
@@ -6189,18 +6617,21 @@
         <v>0</v>
       </c>
       <c r="R86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3" t="n">
         <v>29202</v>
       </c>
-      <c r="S86" s="3" t="n">
+      <c r="T86" s="3" t="n">
         <v>29200</v>
-      </c>
-      <c r="T86" s="3" t="n">
-        <v>29202</v>
       </c>
       <c r="U86" s="3" t="n">
         <v>29202</v>
       </c>
       <c r="V86" s="3" t="n">
+        <v>29202</v>
+      </c>
+      <c r="W86" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6225,26 +6656,28 @@
           <t xml:space="preserve">RBX_PRA_CTG </t>
         </is>
       </c>
-      <c r="I87" s="3" t="n">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="n">
         <v>5752</v>
       </c>
-      <c r="J87" s="4" t="n">
+      <c r="K87" s="4" t="n">
         <v>45.98</v>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (5752)</t>
         </is>
       </c>
-      <c r="L87" s="5" t="n">
+      <c r="M87" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M87" s="3" t="n">
+      <c r="N87" s="3" t="n">
         <v>2876</v>
       </c>
-      <c r="N87" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O87" s="3" t="n">
         <v>0</v>
       </c>
@@ -6255,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="R87" s="3" t="n">
-        <v>1438</v>
+        <v>0</v>
       </c>
       <c r="S87" s="3" t="n">
         <v>1438</v>
@@ -6267,6 +6700,9 @@
         <v>1438</v>
       </c>
       <c r="V87" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="W87" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6291,26 +6727,28 @@
           <t xml:space="preserve">RBX_PRA_ERT </t>
         </is>
       </c>
-      <c r="I88" s="3" t="n">
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="n">
         <v>377078</v>
       </c>
-      <c r="J88" s="4" t="n">
+      <c r="K88" s="4" t="n">
         <v>3103.47</v>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (377078)</t>
         </is>
       </c>
-      <c r="L88" s="5" t="n">
+      <c r="M88" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M88" s="3" t="n">
+      <c r="N88" s="3" t="n">
         <v>185403</v>
       </c>
-      <c r="N88" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O88" s="3" t="n">
         <v>0</v>
       </c>
@@ -6321,18 +6759,21 @@
         <v>0</v>
       </c>
       <c r="R88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3" t="n">
         <v>94387</v>
       </c>
-      <c r="S88" s="3" t="n">
+      <c r="T88" s="3" t="n">
         <v>93918</v>
       </c>
-      <c r="T88" s="3" t="n">
+      <c r="U88" s="3" t="n">
         <v>94387</v>
       </c>
-      <c r="U88" s="3" t="n">
+      <c r="V88" s="3" t="n">
         <v>94386</v>
       </c>
-      <c r="V88" s="3" t="n">
+      <c r="W88" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6357,26 +6798,28 @@
           <t xml:space="preserve">RBX_PRA_IND </t>
         </is>
       </c>
-      <c r="I89" s="3" t="n">
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="n">
         <v>64400</v>
       </c>
-      <c r="J89" s="4" t="n">
+      <c r="K89" s="4" t="n">
         <v>199.84</v>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (64400)</t>
         </is>
       </c>
-      <c r="L89" s="5" t="n">
+      <c r="M89" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M89" s="3" t="n">
+      <c r="N89" s="3" t="n">
         <v>32665</v>
       </c>
-      <c r="N89" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O89" s="3" t="n">
         <v>0</v>
       </c>
@@ -6387,18 +6830,21 @@
         <v>0</v>
       </c>
       <c r="R89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="n">
         <v>15377</v>
       </c>
-      <c r="S89" s="3" t="n">
+      <c r="T89" s="3" t="n">
         <v>16307</v>
-      </c>
-      <c r="T89" s="3" t="n">
-        <v>16358</v>
       </c>
       <c r="U89" s="3" t="n">
         <v>16358</v>
       </c>
       <c r="V89" s="3" t="n">
+        <v>16358</v>
+      </c>
+      <c r="W89" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6423,26 +6869,28 @@
           <t xml:space="preserve">RBX_PRA_JRX </t>
         </is>
       </c>
-      <c r="I90" s="3" t="n">
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="n">
         <v>595291</v>
       </c>
-      <c r="J90" s="4" t="n">
+      <c r="K90" s="4" t="n">
         <v>4704.6</v>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (595291)</t>
         </is>
       </c>
-      <c r="L90" s="5" t="n">
+      <c r="M90" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M90" s="3" t="n">
+      <c r="N90" s="3" t="n">
         <v>284717</v>
       </c>
-      <c r="N90" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O90" s="3" t="n">
         <v>0</v>
       </c>
@@ -6453,18 +6901,21 @@
         <v>0</v>
       </c>
       <c r="R90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" s="3" t="n">
         <v>148174</v>
       </c>
-      <c r="S90" s="3" t="n">
+      <c r="T90" s="3" t="n">
         <v>148814</v>
       </c>
-      <c r="T90" s="3" t="n">
+      <c r="U90" s="3" t="n">
         <v>149132</v>
       </c>
-      <c r="U90" s="3" t="n">
+      <c r="V90" s="3" t="n">
         <v>149171</v>
       </c>
-      <c r="V90" s="3" t="n">
+      <c r="W90" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6489,26 +6940,28 @@
           <t xml:space="preserve">RBX_VAH_PUB </t>
         </is>
       </c>
-      <c r="I91" s="3" t="n">
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="n">
         <v>3367</v>
       </c>
-      <c r="J91" s="4" t="n">
+      <c r="K91" s="4" t="n">
         <v>19.37</v>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (3367)</t>
         </is>
       </c>
-      <c r="L91" s="5" t="n">
+      <c r="M91" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="M91" s="3" t="n">
+      <c r="N91" s="3" t="n">
         <v>1671</v>
       </c>
-      <c r="N91" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O91" s="3" t="n">
         <v>0</v>
       </c>
@@ -6519,18 +6972,21 @@
         <v>0</v>
       </c>
       <c r="R91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="n">
         <v>848</v>
       </c>
-      <c r="S91" s="3" t="n">
+      <c r="T91" s="3" t="n">
         <v>823</v>
-      </c>
-      <c r="T91" s="3" t="n">
-        <v>848</v>
       </c>
       <c r="U91" s="3" t="n">
         <v>848</v>
       </c>
       <c r="V91" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="W91" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6550,26 +7006,28 @@
           <t xml:space="preserve">RBX_VAH_PUB </t>
         </is>
       </c>
-      <c r="I92" s="3" t="n">
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="J92" s="4" t="n">
+      <c r="K92" s="4" t="n">
         <v>13.49</v>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>EN LIGNE - À TRANSFERER ? (457)</t>
         </is>
       </c>
-      <c r="L92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="3" t="n">
+      <c r="M92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="N92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
       </c>
@@ -6589,9 +7047,12 @@
         <v>0</v>
       </c>
       <c r="U92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="V92" s="3" t="n">
+      <c r="W92" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6601,48 +7062,53 @@
           <t>_INCONNU</t>
         </is>
       </c>
-      <c r="I93" s="3" t="n">
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="n">
         <v>4080</v>
       </c>
-      <c r="J93" s="4" t="n">
+      <c r="K93" s="4" t="n">
         <v>86.63</v>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
         </is>
       </c>
-      <c r="L93" s="5" t="n">
+      <c r="M93" s="5" t="n">
         <v>59.3</v>
       </c>
-      <c r="M93" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="N93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="O93" s="3" t="n">
+      <c r="P93" s="3" t="n">
         <v>2244</v>
       </c>
-      <c r="P93" s="3" t="n">
+      <c r="Q93" s="3" t="n">
         <v>857</v>
       </c>
-      <c r="Q93" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S93" s="3" t="n">
+      <c r="T93" s="3" t="n">
         <v>726</v>
       </c>
-      <c r="T93" s="3" t="n">
+      <c r="U93" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="U93" s="3" t="n">
+      <c r="V93" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="V93" s="3" t="n">
+      <c r="W93" s="3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6659,53 +7125,54 @@
       <c r="F94" s="6" t="inlineStr"/>
       <c r="G94" s="6" t="inlineStr"/>
       <c r="H94" s="6" t="inlineStr"/>
-      <c r="I94" s="7" t="n">
+      <c r="I94" s="6" t="inlineStr"/>
+      <c r="J94" s="7" t="n">
         <v>2430327</v>
       </c>
-      <c r="J94" s="8" t="n">
+      <c r="K94" s="8" t="n">
         <v>20914.25</v>
       </c>
-      <c r="K94" s="6" t="inlineStr">
+      <c r="L94" s="6" t="inlineStr">
         <is>
           <t>TRANSFERT_S3_OK (2068905) ; INCONNU (135934) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37324) ; EN LIGNE - À TRANSFERER ? (28584) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; À SUPPRIMER (doublons S3 - az) (6149) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118)</t>
         </is>
       </c>
-      <c r="L94" s="9" t="n">
+      <c r="M94" s="9" t="n">
         <v>93.2</v>
       </c>
-      <c r="M94" s="7" t="n">
+      <c r="N94" s="7" t="n">
         <v>994727</v>
       </c>
-      <c r="N94" s="7" t="n">
+      <c r="O94" s="7" t="n">
         <v>7347</v>
       </c>
-      <c r="O94" s="7" t="n">
+      <c r="P94" s="7" t="n">
         <v>2453</v>
       </c>
-      <c r="P94" s="7" t="n">
+      <c r="Q94" s="7" t="n">
         <v>673674</v>
       </c>
-      <c r="Q94" s="7" t="n">
+      <c r="R94" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="R94" s="7" t="n">
+      <c r="S94" s="7" t="n">
         <v>334782</v>
       </c>
-      <c r="S94" s="7" t="n">
+      <c r="T94" s="7" t="n">
         <v>452908</v>
       </c>
-      <c r="T94" s="7" t="n">
+      <c r="U94" s="7" t="n">
         <v>338162</v>
       </c>
-      <c r="U94" s="7" t="n">
+      <c r="V94" s="7" t="n">
         <v>620516</v>
       </c>
-      <c r="V94" s="7" t="n">
+      <c r="W94" s="7" t="n">
         <v>465</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:L94">
+  <conditionalFormatting sqref="M2:M94">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -629,7 +629,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (30) ; INCONNU (30)</t>
+          <t>INCONNU (30) ; CORBEILLE (DIFFUSION) (30)</t>
         </is>
       </c>
       <c r="M2" s="5" t="n">
@@ -1272,43 +1272,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMR_3O</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Archives - Permis de construire</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3O</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_3FI</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.71</v>
+        <v>0.02</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>INCONNU (27)</t>
+          <t>NON RENSEIGNÉ (1)</t>
         </is>
       </c>
       <c r="M11" s="5" t="n">
@@ -1336,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>0</v>
@@ -1348,12 +1323,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMR_3R</t>
+          <t>AMR_3O</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Archives - Sports</t>
+          <t>Archives - Permis de construire</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1363,12 +1338,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3R</t>
+          <t>3O</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1377,14 +1352,14 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.42</v>
+        <v>2.71</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>INCONNU (14)</t>
+          <t>INCONNU (27)</t>
         </is>
       </c>
       <c r="M12" s="5" t="n">
@@ -1412,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>0</v>
@@ -1424,12 +1399,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMR_4H</t>
+          <t>AMR_3R</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Archives - Guerres</t>
+          <t>Archives - Sports</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1439,12 +1414,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4H</t>
+          <t>3R</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1453,14 +1428,14 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>INCONNU (5)</t>
+          <t>INCONNU (14)</t>
         </is>
       </c>
       <c r="M13" s="5" t="n">
@@ -1491,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>0</v>
@@ -1500,12 +1475,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMR_4M</t>
+          <t>AMR_4H</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Archives - Edifices à usage d’enseignement</t>
+          <t>Archives - Guerres</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1515,12 +1490,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4M</t>
+          <t>4H</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1529,14 +1504,14 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>INCONNU (1)</t>
+          <t>INCONNU (5)</t>
         </is>
       </c>
       <c r="M14" s="5" t="n">
@@ -1567,7 +1542,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>0</v>
@@ -1576,27 +1551,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMR_507W</t>
+          <t>AMR_4M</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Archives - Vues aériennes provenant du service Aménagement</t>
+          <t>Archives - Edifices à usage d’enseignement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Archives contemporaines</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>507W</t>
+          <t>4M</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1605,14 +1580,14 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>21.3</v>
+        <v>0.21</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>INCONNU (496)</t>
+          <t>INCONNU (1)</t>
         </is>
       </c>
       <c r="M15" s="5" t="n">
@@ -1643,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>496</v>
+        <v>1</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1652,22 +1627,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMR_5FI</t>
+          <t>AMR_507W</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Archives - photographies (format supérieur à 32 x 42 cm)</t>
+          <t>Archives - Vues aériennes provenant du service Aménagement</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Archives contemporaines</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5Fi</t>
+          <t>507W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1676,14 +1656,14 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2</v>
+        <v>496</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.17</v>
+        <v>21.3</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>INCONNU (2)</t>
+          <t>INCONNU (496)</t>
         </is>
       </c>
       <c r="M16" s="5" t="n">
@@ -1714,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2</v>
+        <v>496</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0</v>
@@ -1723,27 +1703,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMR_5M</t>
+          <t>AMR_5FI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Archives - Bâtiments communaux</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
+          <t>Archives - photographies (format supérieur à 32 x 42 cm)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5M</t>
+          <t>5Fi</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1752,14 +1727,14 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>INCONNU (3)</t>
+          <t>INCONNU (2)</t>
         </is>
       </c>
       <c r="M17" s="5" t="n">
@@ -1775,22 +1750,22 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>0</v>
@@ -1799,12 +1774,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMR_6H</t>
+          <t>AMR_5M</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Archives - Recensement de population sous l’occupation allemande de 1914-1918</t>
+          <t>Archives - Bâtiments communaux</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1814,12 +1789,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6H</t>
+          <t>5M</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1828,18 +1803,18 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>76933</v>
+        <v>3</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>54.36</v>
+        <v>0.27</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (76933)</t>
+          <t>INCONNU (3)</t>
         </is>
       </c>
       <c r="M18" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0</v>
@@ -1851,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>76933</v>
+        <v>2</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0</v>
@@ -1866,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>0</v>
@@ -1875,12 +1850,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMR_6M</t>
+          <t>AMR_6H</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Archives - Édifices communaux, monuments et établissements publics (compléments)</t>
+          <t>Archives - Recensement de population sous l’occupation allemande de 1914-1918</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1890,12 +1865,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1904,18 +1879,18 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>10</v>
+        <v>76933</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.19</v>
+        <v>54.36</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>INCONNU (10)</t>
+          <t>TRANSFERT_S3_OK (76933)</t>
         </is>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>0</v>
@@ -1927,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>0</v>
+        <v>76933</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>0</v>
@@ -1939,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>0</v>
@@ -1951,27 +1926,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMR_8C</t>
+          <t>AMR_6M</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Archives - Dossiers documentaires</t>
+          <t>Archives - Édifices communaux, monuments et établissements publics (compléments)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Presse et ouvrages</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1983,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2015,10 +1990,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
@@ -2027,27 +2002,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMR_8J</t>
+          <t>AMR_8C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Archives - Petits fonds privés</t>
+          <t>Archives - Dossiers documentaires</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Archives privées</t>
+          <t>Presse et ouvrages</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8J</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2056,14 +2031,14 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>145</v>
+        <v>10</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.28</v>
+        <v>0.38</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>INCONNU (145)</t>
+          <t>INCONNU (10)</t>
         </is>
       </c>
       <c r="M21" s="5" t="n">
@@ -2079,7 +2054,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>0</v>
@@ -2094,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>0</v>
@@ -2103,55 +2078,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AMR_AFF</t>
+          <t>AMR_8J</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Archives - Affiches : la guerre 1914-1918 à Roubaix</t>
+          <t>Archives - Petits fonds privés</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4H</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_AFF </t>
+          <t>8J</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3650</v>
+        <v>145</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>219.66</v>
+        <v>2.28</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1076) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
+          <t>INCONNU (145)</t>
         </is>
       </c>
       <c r="M22" s="5" t="n">
-        <v>74.7</v>
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1007</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>0</v>
@@ -2160,22 +2130,22 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>643</v>
+        <v>33</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>1508</v>
+        <v>112</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2184,12 +2154,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMR_ALI</t>
+          <t>AMR_AFF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Archives - Plans d’alignement</t>
+          <t>Archives - Affiches : la guerre 1914-1918 à Roubaix</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2199,35 +2169,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8O</t>
+          <t>4H</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_AFF </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>604</v>
+        <v>3648</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>83.84999999999999</v>
+        <v>219.29</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>INCONNU (604)</t>
+          <t>TRANSFERT_S3_OK (1074) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
         </is>
       </c>
       <c r="M23" s="5" t="n">
-        <v>0</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>0</v>
@@ -2236,22 +2211,22 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>302</v>
+        <v>643</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>302</v>
+        <v>1506</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>0</v>
@@ -2260,17 +2235,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMR_AVI</t>
+          <t>AMR_ALI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Archives - Documents vidéos</t>
+          <t>Archives - Plans d’alignement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>8O</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2279,18 +2264,18 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>159</v>
+        <v>604</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>255.07</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (159)</t>
+          <t>INCONNU (604)</t>
         </is>
       </c>
       <c r="M24" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0</v>
@@ -2302,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>0</v>
@@ -2317,31 +2302,26 @@
         <v>0</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMR_BAR</t>
+          <t>AMR_AVI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Archives - Parc Barbieux</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>_collection</t>
+          <t>Archives - Documents vidéos</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>?</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2350,18 +2330,18 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.9</v>
+        <v>255.07</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
+          <t>TRANSFERT_S3_OK (159)</t>
         </is>
       </c>
       <c r="M25" s="5" t="n">
-        <v>47.8</v>
+        <v>100</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0</v>
@@ -2373,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2388,73 +2368,63 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMR_CAD</t>
+          <t>AMR_BAR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Archives - Plans cadastraux</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
+          <t>Archives - Parc Barbieux</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1G</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_CAD </t>
+          <t>collection</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>515</v>
+        <v>92</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>26.3</v>
+        <v>2.9</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
         </is>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.2</v>
+        <v>47.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>433</v>
+        <v>88</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>0</v>
@@ -2466,10 +2436,10 @@
         <v>0</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>0</v>
@@ -2478,12 +2448,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMR_CIM</t>
+          <t>AMR_CAD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Archives - Cimetière</t>
+          <t>Archives - Plans cadastraux</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2493,44 +2463,49 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>1G</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_CAD </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>18982</v>
+        <v>515</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>315.8</v>
+        <v>26.3</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
+          <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M27" s="5" t="n">
-        <v>99.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>0</v>
@@ -2542,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>18982</v>
+        <v>52</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>0</v>
@@ -2554,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMR_CLL</t>
+          <t>AMR_CIM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Archives - Comité local de libération</t>
+          <t>Archives - Cimetière</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2569,12 +2544,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4H</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2583,18 +2558,18 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>358</v>
+        <v>18982</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.8</v>
+        <v>315.8</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
+          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
         </is>
       </c>
       <c r="M28" s="5" t="n">
-        <v>73.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -2606,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2615,13 +2590,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>88</v>
+        <v>18982</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>0</v>
@@ -2630,12 +2605,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMR_DEL</t>
+          <t>AMR_CLL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Archives - Registres de délibérations</t>
+          <t>Archives - Comité local de libération</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2645,69 +2620,59 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1D</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_DEL </t>
+          <t>4H</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>170586</v>
+        <v>358</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2435.11</v>
+        <v>6.8</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (122555) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (398) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
         </is>
       </c>
       <c r="M29" s="5" t="n">
-        <v>86</v>
+        <v>73.7</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>122552</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>23676</v>
+        <v>264</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>79005</v>
+        <v>3</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>140</v>
+        <v>3</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>67624</v>
+        <v>88</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>0</v>
@@ -2716,74 +2681,84 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMR_DIA</t>
+          <t>AMR_DEL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Archives - Diapositives</t>
+          <t>Archives - Registres de délibérations</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Documents figurés</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9Fi</t>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_DEL </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1761</v>
+        <v>170130</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>44.68</v>
+        <v>2425.75</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
+          <t>TRANSFERT_S3_OK (122101) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (396) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M30" s="5" t="n">
-        <v>49.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0</v>
+        <v>122098</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>879</v>
+        <v>23676</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>0</v>
+        <v>78807</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>882</v>
+        <v>67366</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
@@ -2792,27 +2767,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMR_EC</t>
+          <t>AMR_DIA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Archives -  État civil</t>
+          <t>Archives - Diapositives</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Documents figurés</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>9Fi</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2821,18 +2796,18 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>358109</v>
+        <v>1761</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>760.01</v>
+        <v>44.68</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (249012) ; CORBEILLE (85333) ; INCONNU (23761) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
         </is>
       </c>
       <c r="M31" s="5" t="n">
-        <v>93.40000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
@@ -2841,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>358080</v>
+        <v>879</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>0</v>
@@ -2859,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>0</v>
+        <v>882</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>0</v>
@@ -2868,22 +2843,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMR_GDL</t>
+          <t>AMR_EC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Archives - Goutte de lait</t>
+          <t>Archives -  État civil</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2892,18 +2872,18 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>32</v>
+        <v>357990</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.97</v>
+        <v>759.84</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
+          <t>TRANSFERT_S3_OK (248890) ; CORBEILLE (85333) ; INCONNU (23325) ; NON RENSEIGNÉ (439) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M32" s="5" t="n">
-        <v>50</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0</v>
@@ -2912,16 +2892,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>32</v>
+        <v>357961</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>0</v>
@@ -2939,55 +2919,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AMR_GUE</t>
+          <t>AMR_GDL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Archives - La guerre 1939-1945 à Roubaix</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
+          <t>Archives - Goutte de lait</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5H</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_GUE </t>
+          <t>collection</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>678</v>
+        <v>32</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.78</v>
+        <v>0.97</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (678)</t>
+          <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>0</v>
@@ -2996,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>339</v>
+        <v>32</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
@@ -3005,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>0</v>
@@ -3020,55 +2990,55 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMR_LEB</t>
+          <t>AMR_GUE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Archives - Collection de la famille Lebas - Hennion</t>
+          <t>Archives - La guerre 1939-1945 à Roubaix</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Archives privées</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11J</t>
+          <t>5H</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_LEB </t>
+          <t xml:space="preserve">RBX_AMR_GUE </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>174</v>
+        <v>678</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
+          <t>EN LIGNE - À TRANSFERER ? (678)</t>
         </is>
       </c>
       <c r="M34" s="5" t="n">
-        <v>48.9</v>
+        <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
@@ -3077,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>85</v>
+        <v>339</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
@@ -3086,13 +3056,13 @@
         <v>0</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>0</v>
@@ -3101,27 +3071,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMR_O</t>
+          <t>AMR_LEB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Archives - Permis de construire</t>
+          <t>Archives - Collection de la famille Lebas - Hennion</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3O</t>
+          <t>11J</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_LEB </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3130,18 +3105,18 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>31</v>
+        <v>174</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
         </is>
       </c>
       <c r="M35" s="5" t="n">
-        <v>19.4</v>
+        <v>48.9</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -3150,10 +3125,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0</v>
@@ -3168,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3177,64 +3152,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMR_OBJ</t>
+          <t>AMR_O</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Archives -  Médailles et petits objets</t>
+          <t>Archives - Permis de construire</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Objets</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Obj</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1Obj</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_OBJ </t>
+          <t>3O</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>208</v>
+        <v>31</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.92</v>
+        <v>1.39</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
+          <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M36" s="5" t="n">
-        <v>96.2</v>
+        <v>19.4</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0</v>
@@ -3249,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>208</v>
+        <v>25</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0</v>
@@ -3258,50 +3228,55 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMR_PAR</t>
+          <t>AMR_OBJ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Archives - Particuliers</t>
+          <t>Archives -  Médailles et petits objets</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Archives privées</t>
+          <t>Objets</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>Obj</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>J ?</t>
+          <t>1Obj</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_OBJ </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>6901</v>
+        <v>208</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>9.25</v>
+        <v>0.92</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (6428) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (doublons S3 - az) (228)</t>
+          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
         </is>
       </c>
       <c r="M37" s="5" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>0</v>
@@ -3310,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>6668</v>
+        <v>0</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0</v>
@@ -3325,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>0</v>
@@ -3334,22 +3309,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMR_PDS</t>
+          <t>AMR_PAR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Archives - Parc des sports</t>
+          <t>Archives - Particuliers</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>J ?</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3358,18 +3338,18 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>68</v>
+        <v>6894</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>3.87</v>
+        <v>9.25</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
+          <t>CORBEILLE (DIFFUSION) (6421) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (doublons S3 - az) (228)</t>
         </is>
       </c>
       <c r="M38" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>0</v>
@@ -3381,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>68</v>
+        <v>6661</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0</v>
@@ -3396,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
@@ -3405,12 +3385,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMR_PHO</t>
+          <t>AMR_PDS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Archives - Photographies du service Communication de la Ville</t>
+          <t>Archives - Parc des sports</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3423,41 +3403,36 @@
           <t>collection</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_PHO </t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>18595</v>
+        <v>68</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>135.98</v>
+        <v>3.87</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>INCONNU (9293) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
         </is>
       </c>
       <c r="M39" s="5" t="n">
         <v>50</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>1194</v>
+        <v>0</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>8035</v>
+        <v>68</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3472,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>10558</v>
+        <v>0</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>0</v>
@@ -3481,12 +3456,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMR_PLA</t>
+          <t>AMR_PHO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Archives - Collection des cartes et plans des Archives</t>
+          <t>Archives - Photographies du service Communication de la Ville</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3501,7 +3476,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_PLA </t>
+          <t xml:space="preserve">RBX_AMR_PHO </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3510,30 +3485,30 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>376</v>
+        <v>18595</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>48.9</v>
+        <v>135.98</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
+          <t>INCONNU (9293) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M40" s="5" t="n">
-        <v>35.1</v>
+        <v>50</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>126</v>
+        <v>1194</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>250</v>
+        <v>8035</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -3548,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>126</v>
+        <v>10558</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
@@ -3557,27 +3532,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMR_POP</t>
+          <t>AMR_PLA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Archives - Recensements de population</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
+          <t>Archives - Collection des cartes et plans des Archives</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>collection</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PLA </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3586,21 +3561,21 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>122308</v>
+        <v>376</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>504.56</v>
+        <v>48.9</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (85759) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
+          <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
       <c r="M41" s="5" t="n">
-        <v>93.40000000000001</v>
+        <v>35.1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>65349</v>
+        <v>126</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>0</v>
@@ -3609,22 +3584,22 @@
         <v>0</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>114168</v>
+        <v>250</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>8135</v>
+        <v>126</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>0</v>
@@ -3633,27 +3608,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AMR_PR</t>
+          <t>AMR_POP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Archives - Pièces remarquables des Archives municipales</t>
+          <t>Archives - Recensements de population</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>collection</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_PR </t>
+          <t>1F</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3662,45 +3637,45 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>4326</v>
+        <v>121938</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>166.36</v>
+        <v>504.08</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (85449) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
         </is>
       </c>
       <c r="M42" s="5" t="n">
-        <v>27.8</v>
+        <v>93.3</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>668</v>
+        <v>65107</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>113798</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>786</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="V42" s="3" t="n">
-        <v>3533</v>
+        <v>8135</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>0</v>
@@ -3709,64 +3684,59 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMR_PUV</t>
+          <t>AMR_PR</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Archives - Bulletin municipal d'information</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Presse et ouvrages</t>
+          <t>Archives - Pièces remarquables des Archives municipales</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>58-59PER</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_PUV </t>
+          <t xml:space="preserve">RBX_AMR_PR </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>19188</v>
+        <v>4326</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>338.52</v>
+        <v>166.36</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>INCONNU (16034) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M43" s="5" t="n">
-        <v>16.4</v>
+        <v>27.8</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>0</v>
+        <v>668</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>6302</v>
+        <v>786</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>0</v>
@@ -3775,13 +3745,13 @@
         <v>0</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>6302</v>
+        <v>6</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>6302</v>
+        <v>3533</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0</v>
@@ -3790,27 +3760,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMR_PV</t>
+          <t>AMR_PUV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Archives - Plaques de verre</t>
+          <t>Archives - Bulletin municipal d'information</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Documents figurés</t>
+          <t>Presse et ouvrages</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8Fi</t>
+          <t>58-59PER</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PUV </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3819,18 +3794,18 @@
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>4</v>
+        <v>19189</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.03</v>
+        <v>338.53</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>INCONNU (4)</t>
+          <t>INCONNU (16034) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3) ; NON RENSEIGNÉ (1)</t>
         </is>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>0</v>
@@ -3839,10 +3814,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>2</v>
+        <v>6302</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>0</v>
@@ -3851,13 +3826,13 @@
         <v>0</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>0</v>
+        <v>6302</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>2</v>
+        <v>6302</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>0</v>
@@ -3866,27 +3841,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMR_PVC</t>
+          <t>AMR_PV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Archives - Procès verbaux du conseil municipal</t>
+          <t>Archives - Plaques de verre</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Archives contemporaines</t>
+          <t>Documents figurés</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>246W</t>
+          <t>8Fi</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3895,18 +3870,18 @@
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>19170</v>
+        <v>4</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>42.81</v>
+        <v>0.03</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
+          <t>INCONNU (4)</t>
         </is>
       </c>
       <c r="M45" s="5" t="n">
-        <v>49.3</v>
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>0</v>
@@ -3918,22 +3893,22 @@
         <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>9444</v>
+        <v>2</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>9444</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>0</v>
@@ -3942,60 +3917,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMR_RAM</t>
+          <t>AMR_PVC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Archives - Rapports du maire</t>
+          <t>Archives - Procès verbaux du conseil municipal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives contemporaines</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3D</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_RAM </t>
+          <t>246W</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>37053</v>
+        <v>19170</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>448.11</v>
+        <v>42.81</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (37053)</t>
+          <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
         </is>
       </c>
       <c r="M46" s="5" t="n">
-        <v>100</v>
+        <v>49.3</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>37053</v>
+        <v>0</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0</v>
@@ -4004,22 +3969,22 @@
         <v>0</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0</v>
+        <v>9444</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>18527</v>
+        <v>9444</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>18526</v>
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>0</v>
@@ -4028,40 +3993,60 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMR_ROU</t>
+          <t>AMR_RAM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Archives - Archives privées Roussel</t>
+          <t>Archives - Rapports du maire</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_RAM </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>449</v>
+        <v>36817</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>5.17</v>
+        <v>445.32</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
+          <t>TRANSFERT_S3_OK (36817)</t>
         </is>
       </c>
       <c r="M47" s="5" t="n">
-        <v>42.8</v>
+        <v>100</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>0</v>
+        <v>36817</v>
       </c>
       <c r="O47" s="3" t="n">
         <v>0</v>
@@ -4070,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>0</v>
@@ -4079,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="T47" s="3" t="n">
-        <v>0</v>
+        <v>18409</v>
       </c>
       <c r="U47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>257</v>
+        <v>18408</v>
       </c>
       <c r="W47" s="3" t="n">
         <v>0</v>
@@ -4094,32 +4079,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMR_VIC</t>
+          <t>AMR_ROU</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Archives - Roubaisiens victimes des guerres</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>H</t>
+          <t>Archives - Archives privées Roussel</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5H</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_VIC </t>
+          <t>?</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4128,18 +4098,18 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7072</v>
+        <v>449</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>12.12</v>
+        <v>5.17</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>INCONNU (7072)</t>
+          <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
         </is>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0</v>
+        <v>42.8</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -4151,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7072</v>
+        <v>192</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -4166,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="W48" s="3" t="n">
         <v>0</v>
@@ -4175,49 +4145,64 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ARA_CPS</t>
+          <t>AMR_VIC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ARA - Cartes postales sonores de l'ARA</t>
+          <t>Archives - Roubaisiens victimes des guerres</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>5H</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_ARA_CPS </t>
+          <t xml:space="preserve">RBX_AMR_VIC </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>174</v>
+        <v>7072</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1.26</v>
+        <v>12.12</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
+          <t>INCONNU (7072)</t>
         </is>
       </c>
       <c r="M49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>94</v>
+        <v>7072</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0</v>
@@ -4241,17 +4226,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CSV_PAL</t>
+          <t>ARA_CPS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Conservatoire - Palmarès annuels</t>
+          <t>ARA - Cartes postales sonores de l'ARA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_CSV_PAL </t>
+          <t xml:space="preserve">RBX_ARA_CPS </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4260,30 +4245,30 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>242</v>
+        <v>174</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>6.65</v>
+        <v>1.26</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (242)</t>
+          <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
         </is>
       </c>
       <c r="M50" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>0</v>
@@ -4298,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="W50" s="3" t="n">
         <v>0</v>
@@ -4307,17 +4292,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LAI</t>
+          <t>CSV_PAL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Association des Amis de la Lainière et du Textile - Collection</t>
+          <t>Conservatoire - Palmarès annuels</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_LAI </t>
+          <t xml:space="preserve">RBX_CSV_PAL </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4326,21 +4311,21 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2422</v>
+        <v>242</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>61.97</v>
+        <v>6.65</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1697) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
+          <t>TRANSFERT_S3_OK (242)</t>
         </is>
       </c>
       <c r="M51" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1181</v>
+        <v>242</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>0</v>
@@ -4355,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>0</v>
@@ -4364,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2421</v>
+        <v>242</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>0</v>
@@ -4373,17 +4358,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LAR_PUB</t>
+          <t>LAI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lire à Roubaix - Publications</t>
+          <t>Association des Amis de la Lainière et du Textile - Collection</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_LAR_PUB </t>
+          <t xml:space="preserve">RBX_LAI </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4392,21 +4377,21 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>3811</v>
+        <v>2386</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>18.33</v>
+        <v>60.87</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
+          <t>TRANSFERT_S3_OK (1661) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
         </is>
       </c>
       <c r="M52" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3811</v>
+        <v>1145</v>
       </c>
       <c r="O52" s="3" t="n">
         <v>0</v>
@@ -4421,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>0</v>
@@ -4430,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>3811</v>
+        <v>2385</v>
       </c>
       <c r="W52" s="3" t="n">
         <v>0</v>
@@ -4439,17 +4424,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MDF_MTX</t>
+          <t>LAR_PUB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Manufacture des Flandres - Collectes de la mémoire des travailleurs du textile</t>
+          <t>Lire à Roubaix - Publications</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MDF_MTX </t>
+          <t xml:space="preserve">RBX_LAR_PUB </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4458,21 +4443,21 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>18</v>
+        <v>3811</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>76.03</v>
+        <v>18.33</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (18)</t>
+          <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
         </is>
       </c>
       <c r="M53" s="5" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>17</v>
+        <v>3811</v>
       </c>
       <c r="O53" s="3" t="n">
         <v>0</v>
@@ -4496,26 +4481,26 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>0</v>
+        <v>3811</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MED_AFF</t>
+          <t>MDF_MTX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Médiathèque - Affiches de la Médiathèque</t>
+          <t>Manufacture des Flandres - Collectes de la mémoire des travailleurs du textile</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_AFF </t>
+          <t xml:space="preserve">RBX_MDF_MTX </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4524,21 +4509,21 @@
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>11038</v>
+        <v>18</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>529.5599999999999</v>
+        <v>76.03</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (5576) ; CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (175) ; INCONNU (111)</t>
+          <t>TRANSFERT_S3_OK (18)</t>
         </is>
       </c>
       <c r="M54" s="5" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>5742</v>
+        <v>17</v>
       </c>
       <c r="O54" s="3" t="n">
         <v>0</v>
@@ -4547,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>5176</v>
+        <v>0</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0</v>
@@ -4562,53 +4547,58 @@
         <v>0</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>5862</v>
+        <v>0</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MED_AVI</t>
+          <t>MED_AFF</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Médiathèque - Vidéos</t>
+          <t>Médiathèque - Affiches de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_AFF </t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>33</v>
+        <v>11038</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>48.21</v>
+        <v>529.5599999999999</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
+          <t>CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (4222) ; À SUPPRIMER (doublons AZ) (1606) ; DOUBLON - À VOIR (32) ; INCONNU (2)</t>
         </is>
       </c>
       <c r="M55" s="5" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>0</v>
+        <v>5742</v>
       </c>
       <c r="O55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>0</v>
+        <v>5176</v>
       </c>
       <c r="R55" s="3" t="n">
         <v>0</v>
@@ -4623,55 +4613,50 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>0</v>
+        <v>5862</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MED_CHA</t>
+          <t>MED_AVI</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Médiathèque - Chansons de la Médiathèque de Roubaix</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_CHA </t>
+          <t>Médiathèque - Vidéos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>723</v>
+        <v>33</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>17.58</v>
+        <v>48.21</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
+          <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M56" s="5" t="n">
-        <v>50.2</v>
+        <v>100</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>0</v>
@@ -4689,26 +4674,26 @@
         <v>0</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>723</v>
+        <v>0</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MED_CP</t>
+          <t>MED_CHA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Médiathèque - Cartes postales de Roubaix</t>
+          <t>Médiathèque - Chansons de la Médiathèque de Roubaix</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_CP </t>
+          <t xml:space="preserve">RBX_MED_CHA </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4717,21 +4702,21 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>6010</v>
+        <v>723</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>34.89</v>
+        <v>17.58</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (4534) ; INCONNU (651) ; À SUPPRIMER (doublons S3 - az) (536) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
+          <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
         </is>
       </c>
       <c r="M57" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>4672</v>
+        <v>360</v>
       </c>
       <c r="O57" s="3" t="n">
         <v>0</v>
@@ -4740,13 +4725,13 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>0</v>
@@ -4755,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="3" t="n">
-        <v>5702</v>
+        <v>723</v>
       </c>
       <c r="W57" s="3" t="n">
         <v>0</v>
@@ -4764,55 +4749,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MED_DIL</t>
+          <t>MED_CP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Médiathèque - Fonds d'archives d'André Diligent</t>
+          <t>Médiathèque - Cartes postales de Roubaix</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_DIL </t>
+          <t xml:space="preserve">RBX_MED_CP </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>365</v>
+        <v>5999</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>480.6</v>
+        <v>34.82</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
+          <t>TRANSFERT_S3_OK (4525) ; INCONNU (650) ; À SUPPRIMER (doublons S3 - az) (535) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
         </is>
       </c>
       <c r="M58" s="5" t="n">
-        <v>12.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>0</v>
+        <v>4663</v>
       </c>
       <c r="O58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>94</v>
+        <v>307</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>0</v>
@@ -4821,58 +4806,58 @@
         <v>0</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>45</v>
+        <v>5691</v>
       </c>
       <c r="W58" s="3" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MED_EPH</t>
+          <t>MED_DIL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Médiathèque - Ephémères de la Médiathèque</t>
+          <t>Médiathèque - Fonds d'archives d'André Diligent</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_EPH </t>
+          <t xml:space="preserve">RBX_MED_DIL </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>846</v>
+        <v>365</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>10.17</v>
+        <v>480.6</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
+          <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
         </is>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>0</v>
@@ -4887,44 +4872,49 @@
         <v>0</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>846</v>
+        <v>45</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MED_FAN</t>
+          <t>MED_EPH</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Médiathèque - Cartes postales fantaisie</t>
+          <t>Médiathèque - Ephémères de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_EPH </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>2666</v>
+        <v>846</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>32.93</v>
+        <v>10.17</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>INCONNU (2666)</t>
+          <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
         </is>
       </c>
       <c r="M60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="O60" s="3" t="n">
         <v>0</v>
@@ -4948,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>2666</v>
+        <v>846</v>
       </c>
       <c r="W60" s="3" t="n">
         <v>0</v>
@@ -4957,49 +4947,44 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MED_FLR</t>
+          <t>MED_FAN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents sonores régionaux</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_FLR </t>
+          <t>Médiathèque - Cartes postales fantaisie</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>8487</v>
+        <v>2666</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>304.96</v>
+        <v>32.93</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (8487)</t>
+          <t>INCONNU (2666)</t>
         </is>
       </c>
       <c r="M61" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>7228</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>0</v>
@@ -5014,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>781</v>
+        <v>2666</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>0</v>
@@ -5023,17 +5008,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MED_FOO</t>
+          <t>MED_FLR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Médiathèque - Souvenirs de foot</t>
+          <t>Médiathèque - Documents sonores régionaux</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_FOO </t>
+          <t xml:space="preserve">RBX_MED_FLR </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5042,30 +5027,30 @@
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>41</v>
+        <v>8487</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.66</v>
+        <v>304.96</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>TRANSFERT_S3_OK (8487)</t>
         </is>
       </c>
       <c r="M62" s="5" t="n">
-        <v>12.2</v>
+        <v>100</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>33</v>
+        <v>7228</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="n">
-        <v>6</v>
+        <v>478</v>
       </c>
       <c r="R62" s="3" t="n">
         <v>0</v>
@@ -5080,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="W62" s="3" t="n">
         <v>0</v>
@@ -5089,17 +5074,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MED_IMA</t>
+          <t>MED_FOO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Médiathèque - Imagettes de la Médiathèque</t>
+          <t>Médiathèque - Souvenirs de foot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_IMA </t>
+          <t xml:space="preserve">RBX_MED_FOO </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5108,30 +5093,30 @@
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>9856</v>
+        <v>41</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>131.47</v>
+        <v>0.66</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (8900) ; TRANSFERT_S3_OK (750) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45)</t>
+          <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M63" s="5" t="n">
-        <v>9.199999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>9623</v>
+        <v>6</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>0</v>
@@ -5146,7 +5131,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>9631</v>
+        <v>0</v>
       </c>
       <c r="W63" s="3" t="n">
         <v>0</v>
@@ -5155,35 +5140,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MED_JOU</t>
+          <t>MED_IMA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Médiathèque - Journaux</t>
+          <t>Médiathèque - Imagettes de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_IMA </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J64" s="3" t="n">
-        <v>2174</v>
+        <v>9852</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>67.51000000000001</v>
+        <v>131.45</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
+          <t>TRANSFERT_S3_OK (5614) ; À SUPPRIMER (doublons AZ) (3846) ; EN LIGNE - À TRANSFERER ? (180) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45) ; DOUBLON - À VOIR (6)</t>
         </is>
       </c>
       <c r="M64" s="5" t="n">
-        <v>91.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>9619</v>
       </c>
       <c r="O64" s="3" t="n">
         <v>0</v>
@@ -5192,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -5207,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>2174</v>
+        <v>9627</v>
       </c>
       <c r="W64" s="3" t="n">
         <v>0</v>
@@ -5216,40 +5206,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MED_LET</t>
+          <t>MED_JOU</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Médiathèque - Lettres à en-tête des commerces et industries roubaisiens</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_LET </t>
+          <t>Médiathèque - Journaux</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J65" s="3" t="n">
-        <v>605</v>
+        <v>2174</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>12.84</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (605)</t>
+          <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
         </is>
       </c>
       <c r="M65" s="5" t="n">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>560</v>
+        <v>0</v>
       </c>
       <c r="O65" s="3" t="n">
         <v>0</v>
@@ -5273,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="3" t="n">
-        <v>605</v>
+        <v>2174</v>
       </c>
       <c r="W65" s="3" t="n">
         <v>0</v>
@@ -5282,17 +5267,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MED_MAR</t>
+          <t>MED_LET</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Médiathèque - Marionnettes</t>
+          <t>Médiathèque - Lettres à en-tête des commerces et industries roubaisiens</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MAR </t>
+          <t xml:space="preserve">RBX_MED_LET </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5301,21 +5286,21 @@
         </is>
       </c>
       <c r="J66" s="3" t="n">
-        <v>197</v>
+        <v>604</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>7.07</v>
+        <v>12.81</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
+          <t>TRANSFERT_S3_OK (604)</t>
         </is>
       </c>
       <c r="M66" s="5" t="n">
-        <v>49.7</v>
+        <v>100</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>62</v>
+        <v>559</v>
       </c>
       <c r="O66" s="3" t="n">
         <v>0</v>
@@ -5324,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>0</v>
@@ -5339,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>99</v>
+        <v>604</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>0</v>
@@ -5348,17 +5333,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MED_MON</t>
+          <t>MED_MAR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Médiathèque - Livres et brochures</t>
+          <t>Médiathèque - Marionnettes</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MON </t>
+          <t xml:space="preserve">RBX_MED_MAR </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5367,21 +5352,21 @@
         </is>
       </c>
       <c r="J67" s="3" t="n">
-        <v>7553</v>
+        <v>197</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>205.74</v>
+        <v>7.07</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
+          <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
         </is>
       </c>
       <c r="M67" s="5" t="n">
-        <v>98.8</v>
+        <v>49.7</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>1384</v>
+        <v>62</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -5390,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -5399,13 +5384,13 @@
         <v>0</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>2721</v>
+        <v>0</v>
       </c>
       <c r="U67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="3" t="n">
-        <v>4832</v>
+        <v>99</v>
       </c>
       <c r="W67" s="3" t="n">
         <v>0</v>
@@ -5414,17 +5399,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MED_MS</t>
+          <t>MED_MON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Médiathèque - Manuscrits de la Médiathèque de Roubaix</t>
+          <t>Médiathèque - Livres et brochures</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MS </t>
+          <t xml:space="preserve">RBX_MED_MON </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5433,21 +5418,21 @@
         </is>
       </c>
       <c r="J68" s="3" t="n">
-        <v>46262</v>
+        <v>7553</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1061.94</v>
+        <v>205.74</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
+          <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
         </is>
       </c>
       <c r="M68" s="5" t="n">
-        <v>92.2</v>
+        <v>98.8</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>33302</v>
+        <v>1384</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>0</v>
@@ -5456,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>12786</v>
+        <v>0</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0</v>
@@ -5465,13 +5450,13 @@
         <v>0</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>0</v>
+        <v>2721</v>
       </c>
       <c r="U68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>33476</v>
+        <v>4832</v>
       </c>
       <c r="W68" s="3" t="n">
         <v>0</v>
@@ -5480,35 +5465,40 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MED_NPT</t>
+          <t>MED_MS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents non patrimoniaux</t>
+          <t>Médiathèque - Manuscrits de la Médiathèque de Roubaix</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_MS </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J69" s="3" t="n">
-        <v>4</v>
+        <v>46262</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>17.09</v>
+        <v>1061.94</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>INCONNU (4)</t>
+          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0</v>
+        <v>33302</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>0</v>
@@ -5517,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>0</v>
+        <v>12786</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>0</v>
@@ -5532,58 +5522,53 @@
         <v>0</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>0</v>
+        <v>33476</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MED_PAR</t>
+          <t>MED_NPT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de particuliers</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_PAR </t>
+          <t>Médiathèque - Documents non patrimoniaux</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J70" s="3" t="n">
-        <v>24433</v>
+        <v>4</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>543.4</v>
+        <v>17.09</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (17675) ; EN LIGNE - À TRANSFERER ? (3821) ; À SUPPRIMER (doublons S3 - az) (1675) ; À SUPPRIMER (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; CORBEILLE (DIFFUSION) (21)</t>
+          <t>INCONNU (4)</t>
         </is>
       </c>
       <c r="M70" s="5" t="n">
-        <v>83.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>20721</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>5156</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0</v>
@@ -5598,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>19271</v>
+        <v>0</v>
       </c>
       <c r="W70" s="3" t="n">
         <v>4</v>
@@ -5607,44 +5592,49 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MED_PBI</t>
+          <t>MED_PAR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de particuliers (suite)</t>
+          <t>Médiathèque - Collections de particuliers</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PAR </t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>1084</v>
+        <v>24426</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>7.94</v>
+        <v>543.34</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>INCONNU (1084)</t>
+          <t>TRANSFERT_S3_OK (18223) ; EN LIGNE - À TRANSFERER ? (3267) ; À SUPPRIMER (doublons S3 - az) (1674) ; À SUPPRIMER (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; CORBEILLE (DIFFUSION) (21)</t>
         </is>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>20715</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>5156</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0</v>
@@ -5659,21 +5649,21 @@
         <v>0</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>1084</v>
+        <v>19264</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MED_PER</t>
+          <t>MED_PBI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Médiathèque - Périodiques</t>
+          <t>Médiathèque - Collections de particuliers (suite)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5682,18 +5672,18 @@
         </is>
       </c>
       <c r="J72" s="3" t="n">
-        <v>1596</v>
+        <v>1084</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>29.68</v>
+        <v>7.94</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1596)</t>
+          <t>INCONNU (1084)</t>
         </is>
       </c>
       <c r="M72" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>0</v>
@@ -5714,13 +5704,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>767</v>
+        <v>1084</v>
       </c>
       <c r="W72" s="3" t="n">
         <v>0</v>
@@ -5729,12 +5719,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MED_PHD</t>
+          <t>MED_PER</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de photographies</t>
+          <t>Médiathèque - Périodiques</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5743,18 +5733,18 @@
         </is>
       </c>
       <c r="J73" s="3" t="n">
-        <v>1949</v>
+        <v>1596</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>28.52</v>
+        <v>29.68</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>INCONNU (1949)</t>
+          <t>TRANSFERT_S3_OK (1596)</t>
         </is>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N73" s="3" t="n">
         <v>0</v>
@@ -5775,13 +5765,13 @@
         <v>0</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="U73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>1949</v>
+        <v>767</v>
       </c>
       <c r="W73" s="3" t="n">
         <v>0</v>
@@ -5790,49 +5780,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MED_PHO</t>
+          <t>MED_PHD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Médiathèque - Regards de photographes</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_PHO </t>
+          <t>Médiathèque - Collections de photographies</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J74" s="3" t="n">
-        <v>18844</v>
+        <v>1946</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>69.83</v>
+        <v>28.49</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
+          <t>INCONNU (1946)</t>
         </is>
       </c>
       <c r="M74" s="5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="O74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>13861</v>
+        <v>0</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>0</v>
@@ -5844,29 +5829,29 @@
         <v>0</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>4804</v>
+        <v>1946</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MED_PLA</t>
+          <t>MED_PHO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Médiathèque - Collection des cartes et plans de la Médiathèque</t>
+          <t>Médiathèque - Regards de photographes</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_PLA </t>
+          <t xml:space="preserve">RBX_MED_PHO </t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5875,30 +5860,30 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>548</v>
+        <v>18844</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>38.23</v>
+        <v>69.83</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
+          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
       <c r="M75" s="5" t="n">
-        <v>49.8</v>
+        <v>5.7</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>271</v>
+        <v>1140</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>273</v>
+        <v>13861</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5910,29 +5895,29 @@
         <v>0</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>275</v>
+        <v>4804</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MED_PUB</t>
+          <t>MED_PLA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Médiathèque - Publications de la Médiathèque</t>
+          <t>Médiathèque - Collection des cartes et plans de la Médiathèque</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_PUB </t>
+          <t xml:space="preserve">RBX_MED_PLA </t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5941,21 +5926,21 @@
         </is>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2419</v>
+        <v>548</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>49.96</v>
+        <v>38.23</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (2419)</t>
+          <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
         </is>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0</v>
+        <v>49.8</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2419</v>
+        <v>271</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>0</v>
@@ -5964,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>0</v>
@@ -5979,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2419</v>
+        <v>275</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>0</v>
@@ -5988,35 +5973,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MED_VAI</t>
+          <t>MED_PUB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
+          <t>Médiathèque - Publications de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PUB </t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J77" s="3" t="n">
-        <v>238</v>
+        <v>2419</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>9.57</v>
+        <v>49.96</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>INCONNU (238)</t>
+          <t>EN LIGNE - À TRANSFERER ? (2419)</t>
         </is>
       </c>
       <c r="M77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>0</v>
+        <v>2419</v>
       </c>
       <c r="O77" s="3" t="n">
         <v>0</v>
@@ -6040,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>238</v>
+        <v>2419</v>
       </c>
       <c r="W77" s="3" t="n">
         <v>0</v>
@@ -6049,46 +6039,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MED_VDM</t>
+          <t>MED_VAI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Médiathèque - Fonds d'archives de Maxence Van der Meersch</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_VDM </t>
+          <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>38231</v>
+        <v>238</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>956.36</v>
+        <v>9.57</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (238)</t>
         </is>
       </c>
       <c r="M78" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>31272</v>
+        <v>0</v>
       </c>
       <c r="O78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
         <v>0</v>
@@ -6097,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T78" s="3" t="n">
         <v>0</v>
@@ -6106,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>38229</v>
+        <v>238</v>
       </c>
       <c r="W78" s="3" t="n">
         <v>0</v>
@@ -6115,41 +6100,46 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MED_VID</t>
+          <t>MED_VDM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents vidéos</t>
+          <t>Médiathèque - Fonds d'archives de Maxence Van der Meersch</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_VDM </t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J79" s="3" t="n">
-        <v>31</v>
+        <v>38231</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>8.82</v>
+        <v>956.36</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
+          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M79" s="5" t="n">
-        <v>48.4</v>
+        <v>100</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>0</v>
+        <v>31272</v>
       </c>
       <c r="O79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="Q79" s="3" t="n">
         <v>0</v>
@@ -6158,16 +6148,16 @@
         <v>0</v>
       </c>
       <c r="S79" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V79" s="3" t="n">
-        <v>0</v>
+        <v>38229</v>
       </c>
       <c r="W79" s="3" t="n">
         <v>0</v>
@@ -6176,49 +6166,44 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MUS_ARC</t>
+          <t>MED_VID</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Musée La Piscine - Archives</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MUS_ARC </t>
+          <t>Médiathèque - Documents vidéos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>318</v>
+        <v>31</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>3.42</v>
+        <v>8.82</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (318)</t>
+          <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
         </is>
       </c>
       <c r="M80" s="5" t="n">
-        <v>100</v>
+        <v>48.4</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="O80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>0</v>
@@ -6230,10 +6215,10 @@
         <v>0</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W80" s="3" t="n">
         <v>0</v>
@@ -6242,17 +6227,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MUS_VAI</t>
+          <t>MUS_ARC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Musée La Piscine - Parfumerie et savonnerie Vaissier</t>
+          <t>Musée La Piscine - Archives</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MUS_VAI </t>
+          <t xml:space="preserve">RBX_MUS_ARC </t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6261,21 +6246,21 @@
         </is>
       </c>
       <c r="J81" s="3" t="n">
-        <v>1918</v>
+        <v>318</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>47.42</v>
+        <v>3.42</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1918)</t>
+          <t>TRANSFERT_S3_OK (318)</t>
         </is>
       </c>
       <c r="M81" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>1859</v>
+        <v>134</v>
       </c>
       <c r="O81" s="3" t="n">
         <v>0</v>
@@ -6284,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>404</v>
+        <v>258</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>0</v>
@@ -6299,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>1514</v>
+        <v>60</v>
       </c>
       <c r="W81" s="3" t="n">
         <v>0</v>
@@ -6308,35 +6293,40 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MUS_XXX</t>
+          <t>MUS_VAI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Musée La Piscine - nouveau versement</t>
+          <t>Musée La Piscine - Parfumerie et savonnerie Vaissier</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MUS_VAI </t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J82" s="3" t="n">
-        <v>375</v>
+        <v>1918</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0.16</v>
+        <v>47.42</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>INCONNU (375)</t>
+          <t>TRANSFERT_S3_OK (1918)</t>
         </is>
       </c>
       <c r="M82" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>0</v>
+        <v>1859</v>
       </c>
       <c r="O82" s="3" t="n">
         <v>0</v>
@@ -6345,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>0</v>
@@ -6360,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>0</v>
+        <v>1514</v>
       </c>
       <c r="W82" s="3" t="n">
         <v>0</v>
@@ -6369,40 +6359,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OBS_JOU</t>
+          <t>MUS_XXX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_OBS_JOU </t>
+          <t>Musée La Piscine - nouveau versement</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J83" s="3" t="n">
-        <v>2802</v>
+        <v>375</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>31.32</v>
+        <v>0.16</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1925) ; EN LIGNE - À TRANSFERER ? (868) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (4)</t>
+          <t>INCONNU (375)</t>
         </is>
       </c>
       <c r="M83" s="5" t="n">
-        <v>68.8</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>2238</v>
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="n">
         <v>0</v>
@@ -6411,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>1808</v>
+        <v>375</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0</v>
@@ -6423,10 +6408,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="n">
         <v>0</v>
@@ -6435,22 +6420,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PRA_AVE</t>
+          <t>OBS_JOU</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
+          <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_AVE </t>
+          <t xml:space="preserve">RBX_OBS_JOU </t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6459,21 +6439,21 @@
         </is>
       </c>
       <c r="J84" s="3" t="n">
-        <v>176340</v>
+        <v>1800</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>778.75</v>
+        <v>20.38</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (176340)</t>
+          <t>TRANSFERT_S3_OK (1240) ; EN LIGNE - À TRANSFERER ? (553) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (2)</t>
         </is>
       </c>
       <c r="M84" s="5" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>87510</v>
+        <v>1238</v>
       </c>
       <c r="O84" s="3" t="n">
         <v>0</v>
@@ -6482,22 +6462,22 @@
         <v>0</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>44271</v>
+        <v>0</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>43519</v>
+        <v>0</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>44275</v>
+        <v>43</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>44275</v>
+        <v>601</v>
       </c>
       <c r="W84" s="3" t="n">
         <v>0</v>
@@ -6506,59 +6486,69 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PRA_BDR</t>
+          <t>PRA_AVE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Presse - Bulletin de Roubaix</t>
+          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_AVE </t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>3138</v>
+        <v>176340</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>16.9</v>
+        <v>778.75</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>INCONNU (2781) ; À SUPPRIMER (doublons S3 - az) (178) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (176340)</t>
         </is>
       </c>
       <c r="M85" s="5" t="n">
-        <v>11.4</v>
+        <v>100</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0</v>
+        <v>87510</v>
       </c>
       <c r="O85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>406</v>
+        <v>44271</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>407</v>
+        <v>43519</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>1218</v>
+        <v>44275</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>583</v>
+        <v>44275</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -6567,69 +6557,59 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PRA_CRT</t>
+          <t>PRA_BDR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Presse - La Croix de Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_CRT </t>
+          <t>Presse - Bulletin de Roubaix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J86" s="3" t="n">
-        <v>116806</v>
+        <v>3138</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1024.92</v>
+        <v>16.9</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (116806)</t>
+          <t>INCONNU (2781) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (doublons S3 - az) (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M86" s="5" t="n">
-        <v>100</v>
+        <v>11.4</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>48452</v>
+        <v>0</v>
       </c>
       <c r="O86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>29202</v>
+        <v>406</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>29200</v>
+        <v>407</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>29202</v>
+        <v>1218</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>29202</v>
+        <v>583</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>0</v>
@@ -6638,12 +6618,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PRA_CTG</t>
+          <t>PRA_CRT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Presse - Le Courrier de Tourcoing</t>
+          <t>Presse - La Croix de Roubaix-Tourcoing</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6653,7 +6633,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_CTG </t>
+          <t xml:space="preserve">RBX_PRA_CRT </t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6662,21 +6642,21 @@
         </is>
       </c>
       <c r="J87" s="3" t="n">
-        <v>5752</v>
+        <v>116806</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>45.98</v>
+        <v>1024.92</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (5752)</t>
+          <t>TRANSFERT_S3_OK (116806)</t>
         </is>
       </c>
       <c r="M87" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>2876</v>
+        <v>48452</v>
       </c>
       <c r="O87" s="3" t="n">
         <v>0</v>
@@ -6691,16 +6671,16 @@
         <v>0</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>1438</v>
+        <v>29202</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>1438</v>
+        <v>29200</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>1438</v>
+        <v>29202</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>1438</v>
+        <v>29202</v>
       </c>
       <c r="W87" s="3" t="n">
         <v>0</v>
@@ -6709,12 +6689,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PRA_ERT</t>
+          <t>PRA_CTG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
+          <t>Presse - Le Courrier de Tourcoing</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6724,7 +6704,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_ERT </t>
+          <t xml:space="preserve">RBX_PRA_CTG </t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6733,21 +6713,21 @@
         </is>
       </c>
       <c r="J88" s="3" t="n">
-        <v>377078</v>
+        <v>5752</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>3103.47</v>
+        <v>45.98</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (377078)</t>
+          <t>TRANSFERT_S3_OK (5752)</t>
         </is>
       </c>
       <c r="M88" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>185403</v>
+        <v>2876</v>
       </c>
       <c r="O88" s="3" t="n">
         <v>0</v>
@@ -6762,16 +6742,16 @@
         <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>94387</v>
+        <v>1438</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>93918</v>
+        <v>1438</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>94387</v>
+        <v>1438</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>94386</v>
+        <v>1438</v>
       </c>
       <c r="W88" s="3" t="n">
         <v>0</v>
@@ -6780,12 +6760,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PRA_IND</t>
+          <t>PRA_ERT</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
+          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6795,7 +6775,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_IND </t>
+          <t xml:space="preserve">RBX_PRA_ERT </t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6804,21 +6784,21 @@
         </is>
       </c>
       <c r="J89" s="3" t="n">
-        <v>64400</v>
+        <v>377078</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>199.84</v>
+        <v>3103.47</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (64400)</t>
+          <t>TRANSFERT_S3_OK (377078)</t>
         </is>
       </c>
       <c r="M89" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>32665</v>
+        <v>185403</v>
       </c>
       <c r="O89" s="3" t="n">
         <v>0</v>
@@ -6833,16 +6813,16 @@
         <v>0</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>15377</v>
+        <v>94387</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>16307</v>
+        <v>93918</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>16358</v>
+        <v>94387</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>16358</v>
+        <v>94386</v>
       </c>
       <c r="W89" s="3" t="n">
         <v>0</v>
@@ -6851,12 +6831,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PRA_JRX</t>
+          <t>PRA_IND</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Presse - Journal de Roubaix</t>
+          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6866,7 +6846,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_JRX </t>
+          <t xml:space="preserve">RBX_PRA_IND </t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6875,21 +6855,21 @@
         </is>
       </c>
       <c r="J90" s="3" t="n">
-        <v>595291</v>
+        <v>64400</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4704.6</v>
+        <v>199.84</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (595291)</t>
+          <t>TRANSFERT_S3_OK (64400)</t>
         </is>
       </c>
       <c r="M90" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>284717</v>
+        <v>32665</v>
       </c>
       <c r="O90" s="3" t="n">
         <v>0</v>
@@ -6904,16 +6884,16 @@
         <v>0</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>148174</v>
+        <v>15377</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>148814</v>
+        <v>16307</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>149132</v>
+        <v>16358</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>149171</v>
+        <v>16358</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
@@ -6922,12 +6902,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PRA_RTG</t>
+          <t>PRA_JRX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Presse - Roubaix-Tourcoing</t>
+          <t>Presse - Journal de Roubaix</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6937,7 +6917,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_VAH_PUB </t>
+          <t xml:space="preserve">RBX_PRA_JRX </t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6946,21 +6926,21 @@
         </is>
       </c>
       <c r="J91" s="3" t="n">
-        <v>3367</v>
+        <v>595291</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>19.37</v>
+        <v>4704.6</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (3367)</t>
+          <t>TRANSFERT_S3_OK (595291)</t>
         </is>
       </c>
       <c r="M91" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>1671</v>
+        <v>284717</v>
       </c>
       <c r="O91" s="3" t="n">
         <v>0</v>
@@ -6975,16 +6955,16 @@
         <v>0</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>848</v>
+        <v>148174</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>823</v>
+        <v>148814</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>848</v>
+        <v>149132</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>848</v>
+        <v>149171</v>
       </c>
       <c r="W91" s="3" t="n">
         <v>0</v>
@@ -6993,12 +6973,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VAH_PUB</t>
+          <t>PRA_RTG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ville d'art et d'histoire  - Publications</t>
+          <t>Presse - Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7012,21 +6997,21 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>457</v>
+        <v>3367</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>13.49</v>
+        <v>19.37</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (457)</t>
+          <t>TRANSFERT_S3_OK (3367)</t>
         </is>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>457</v>
+        <v>1671</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -7041,16 +7026,16 @@
         <v>0</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>0</v>
+        <v>823</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>0</v>
+        <v>848</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>457</v>
+        <v>848</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>
@@ -7059,120 +7044,186 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>VAH_PUB</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ville d'art et d'histoire  - Publications</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_VAH_PUB </t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="K93" s="4" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>EN LIGNE - À TRANSFERER ? (457)</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>_INCONNU</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="J93" s="3" t="n">
+      <c r="J94" s="3" t="n">
         <v>4080</v>
       </c>
-      <c r="K93" s="4" t="n">
+      <c r="K94" s="4" t="n">
         <v>86.63</v>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
         </is>
       </c>
-      <c r="M93" s="5" t="n">
+      <c r="M94" s="5" t="n">
         <v>59.3</v>
       </c>
-      <c r="N93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="3" t="n">
+      <c r="N94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P93" s="3" t="n">
+      <c r="P94" s="3" t="n">
         <v>2244</v>
       </c>
-      <c r="Q93" s="3" t="n">
+      <c r="Q94" s="3" t="n">
         <v>857</v>
       </c>
-      <c r="R93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" s="3" t="n">
+      <c r="R94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T93" s="3" t="n">
+      <c r="T94" s="3" t="n">
         <v>726</v>
       </c>
-      <c r="U93" s="3" t="n">
+      <c r="U94" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="V93" s="3" t="n">
+      <c r="V94" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="W93" s="3" t="n">
+      <c r="W94" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr"/>
-      <c r="C94" s="6" t="inlineStr"/>
-      <c r="D94" s="6" t="inlineStr"/>
-      <c r="E94" s="6" t="inlineStr"/>
-      <c r="F94" s="6" t="inlineStr"/>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr"/>
-      <c r="I94" s="6" t="inlineStr"/>
-      <c r="J94" s="7" t="n">
-        <v>2430327</v>
-      </c>
-      <c r="K94" s="8" t="n">
-        <v>20914.25</v>
-      </c>
-      <c r="L94" s="6" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (2068905) ; INCONNU (135934) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37324) ; EN LIGNE - À TRANSFERER ? (28584) ; À SUPPRIMER (remplacement par Verif / Tampon) (20336) ; À SUPPRIMER (doublons S3 - az) (6149) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118)</t>
-        </is>
-      </c>
-      <c r="M94" s="9" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="N94" s="7" t="n">
-        <v>994727</v>
-      </c>
-      <c r="O94" s="7" t="n">
+      <c r="B95" s="6" t="inlineStr"/>
+      <c r="C95" s="6" t="inlineStr"/>
+      <c r="D95" s="6" t="inlineStr"/>
+      <c r="E95" s="6" t="inlineStr"/>
+      <c r="F95" s="6" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr"/>
+      <c r="J95" s="7" t="n">
+        <v>2428075</v>
+      </c>
+      <c r="K95" s="8" t="n">
+        <v>20888.86</v>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (2076509) ; INCONNU (135385) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (13419) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5452) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; NON RENSEIGNÉ (441) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="N95" s="7" t="n">
+        <v>992737</v>
+      </c>
+      <c r="O95" s="7" t="n">
         <v>7347</v>
       </c>
-      <c r="P94" s="7" t="n">
+      <c r="P95" s="7" t="n">
         <v>2453</v>
       </c>
-      <c r="Q94" s="7" t="n">
-        <v>673674</v>
-      </c>
-      <c r="R94" s="7" t="n">
+      <c r="Q95" s="7" t="n">
+        <v>672526</v>
+      </c>
+      <c r="R95" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="S94" s="7" t="n">
+      <c r="S95" s="7" t="n">
         <v>334782</v>
       </c>
-      <c r="T94" s="7" t="n">
-        <v>452908</v>
-      </c>
-      <c r="U94" s="7" t="n">
-        <v>338162</v>
-      </c>
-      <c r="V94" s="7" t="n">
-        <v>620516</v>
-      </c>
-      <c r="W94" s="7" t="n">
+      <c r="T95" s="7" t="n">
+        <v>452592</v>
+      </c>
+      <c r="U95" s="7" t="n">
+        <v>338132</v>
+      </c>
+      <c r="V95" s="7" t="n">
+        <v>619758</v>
+      </c>
+      <c r="W95" s="7" t="n">
         <v>465</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M94">
+  <conditionalFormatting sqref="M2:M95">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W95"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1272,18 +1272,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMR_3FI</t>
+          <t>AMR_3O</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Archives - Permis de construire</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3O</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>non</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.02</v>
+        <v>2.71</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NON RENSEIGNÉ (1)</t>
+          <t>INCONNU (27)</t>
         </is>
       </c>
       <c r="M11" s="5" t="n">
@@ -1311,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>0</v>
@@ -1323,12 +1348,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMR_3O</t>
+          <t>AMR_3R</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Archives - Permis de construire</t>
+          <t>Archives - Sports</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1338,12 +1363,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3O</t>
+          <t>3R</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1352,14 +1377,14 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.71</v>
+        <v>0.42</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>INCONNU (27)</t>
+          <t>INCONNU (14)</t>
         </is>
       </c>
       <c r="M12" s="5" t="n">
@@ -1387,10 +1412,10 @@
         <v>0</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>0</v>
@@ -1399,12 +1424,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMR_3R</t>
+          <t>AMR_4H</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Archives - Sports</t>
+          <t>Archives - Guerres</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1414,12 +1439,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3R</t>
+          <t>4H</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1428,14 +1453,14 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>INCONNU (14)</t>
+          <t>INCONNU (5)</t>
         </is>
       </c>
       <c r="M13" s="5" t="n">
@@ -1466,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>0</v>
@@ -1475,12 +1500,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMR_4H</t>
+          <t>AMR_4M</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Archives - Guerres</t>
+          <t>Archives - Edifices à usage d’enseignement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1490,12 +1515,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4H</t>
+          <t>4M</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1504,14 +1529,14 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>INCONNU (5)</t>
+          <t>INCONNU (1)</t>
         </is>
       </c>
       <c r="M14" s="5" t="n">
@@ -1542,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>0</v>
@@ -1551,27 +1576,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMR_4M</t>
+          <t>AMR_507W</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Archives - Edifices à usage d’enseignement</t>
+          <t>Archives - Vues aériennes provenant du service Aménagement</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives contemporaines</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4M</t>
+          <t>507W</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1580,14 +1605,14 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1</v>
+        <v>496</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.21</v>
+        <v>21.3</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>INCONNU (1)</t>
+          <t>INCONNU (496)</t>
         </is>
       </c>
       <c r="M15" s="5" t="n">
@@ -1618,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>1</v>
+        <v>496</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1627,27 +1652,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMR_507W</t>
+          <t>AMR_5FI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Archives - Vues aériennes provenant du service Aménagement</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Archives contemporaines</t>
+          <t>Archives - photographies (format supérieur à 32 x 42 cm)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>507W</t>
+          <t>5Fi</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1656,14 +1676,14 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>496</v>
+        <v>2</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>21.3</v>
+        <v>0.17</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>INCONNU (496)</t>
+          <t>INCONNU (2)</t>
         </is>
       </c>
       <c r="M16" s="5" t="n">
@@ -1694,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>496</v>
+        <v>2</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0</v>
@@ -1703,22 +1723,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMR_5FI</t>
+          <t>AMR_5M</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Archives - photographies (format supérieur à 32 x 42 cm)</t>
+          <t>Archives - Bâtiments communaux</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5Fi</t>
+          <t>5M</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1727,31 +1752,31 @@
         </is>
       </c>
       <c r="J17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>INCONNU (3)</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K17" s="4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>INCONNU (2)</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="3" t="n">
         <v>0</v>
       </c>
@@ -1765,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>0</v>
@@ -1774,12 +1799,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMR_5M</t>
+          <t>AMR_6H</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Archives - Bâtiments communaux</t>
+          <t>Archives - Recensement de population sous l’occupation allemande de 1914-1918</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1789,12 +1814,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5M</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1803,18 +1828,18 @@
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3</v>
+        <v>76933</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.27</v>
+        <v>54.36</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>INCONNU (3)</t>
+          <t>TRANSFERT_S3_OK (76933)</t>
         </is>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>0</v>
@@ -1826,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>2</v>
+        <v>76933</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0</v>
@@ -1841,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>0</v>
@@ -1850,12 +1875,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMR_6H</t>
+          <t>AMR_6M</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Archives - Recensement de population sous l’occupation allemande de 1914-1918</t>
+          <t>Archives - Édifices communaux, monuments et établissements publics (compléments)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1865,12 +1890,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6H</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1879,18 +1904,18 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>76933</v>
+        <v>10</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>54.36</v>
+        <v>0.19</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (76933)</t>
+          <t>INCONNU (10)</t>
         </is>
       </c>
       <c r="M19" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>0</v>
@@ -1902,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>76933</v>
+        <v>0</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>0</v>
@@ -1914,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>0</v>
@@ -1926,27 +1951,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMR_6M</t>
+          <t>AMR_8C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Archives - Édifices communaux, monuments et établissements publics (compléments)</t>
+          <t>Archives - Dossiers documentaires</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Presse et ouvrages</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1958,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1990,10 +2015,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
@@ -2002,27 +2027,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMR_8C</t>
+          <t>AMR_8J</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Archives - Dossiers documentaires</t>
+          <t>Archives - Petits fonds privés</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Presse et ouvrages</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>8J</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2031,14 +2056,14 @@
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10</v>
+        <v>145</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.38</v>
+        <v>2.28</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>INCONNU (10)</t>
+          <t>INCONNU (145)</t>
         </is>
       </c>
       <c r="M21" s="5" t="n">
@@ -2054,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>0</v>
@@ -2069,7 +2094,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>0</v>
@@ -2078,50 +2103,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AMR_8J</t>
+          <t>AMR_AFF</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Archives - Petits fonds privés</t>
+          <t>Archives - Affiches : la guerre 1914-1918 à Roubaix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Archives privées</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8J</t>
+          <t>4H</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_AFF </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>145</v>
+        <v>3648</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.28</v>
+        <v>219.29</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>INCONNU (145)</t>
+          <t>TRANSFERT_S3_OK (1074) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
         </is>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0</v>
+        <v>1005</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>0</v>
@@ -2130,22 +2160,22 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>33</v>
+        <v>643</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>112</v>
+        <v>1506</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2154,12 +2184,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMR_AFF</t>
+          <t>AMR_ALI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Archives - Affiches : la guerre 1914-1918 à Roubaix</t>
+          <t>Archives - Plans d’alignement</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2169,40 +2199,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4H</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_AFF </t>
+          <t>8O</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>3648</v>
+        <v>604</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>219.29</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1074) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
+          <t>INCONNU (604)</t>
         </is>
       </c>
       <c r="M23" s="5" t="n">
-        <v>74.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1005</v>
+        <v>0</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>0</v>
@@ -2211,22 +2236,22 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>643</v>
+        <v>302</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>365</v>
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1506</v>
+        <v>302</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>0</v>
@@ -2235,27 +2260,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMR_ALI</t>
+          <t>AMR_AVI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Archives - Plans d’alignement</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>Archives - Documents vidéos</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8O</t>
+          <t>?</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2264,18 +2279,18 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>604</v>
+        <v>159</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>83.84999999999999</v>
+        <v>255.07</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>INCONNU (604)</t>
+          <t>TRANSFERT_S3_OK (159)</t>
         </is>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0</v>
@@ -2287,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>0</v>
@@ -2302,26 +2317,31 @@
         <v>0</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMR_AVI</t>
+          <t>AMR_BAR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Archives - Documents vidéos</t>
+          <t>Archives - Parc Barbieux</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2330,18 +2350,18 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>255.07</v>
+        <v>2.9</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (159)</t>
+          <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
         </is>
       </c>
       <c r="M25" s="5" t="n">
-        <v>100</v>
+        <v>47.8</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0</v>
@@ -2353,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2368,63 +2388,73 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMR_BAR</t>
+          <t>AMR_CAD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Archives - Parc Barbieux</t>
+          <t>Archives - Plans cadastraux</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>1G</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_CAD </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>92</v>
+        <v>515</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.9</v>
+        <v>26.3</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
+          <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M26" s="5" t="n">
-        <v>47.8</v>
+        <v>0.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>88</v>
+        <v>433</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>0</v>
@@ -2436,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>0</v>
@@ -2448,12 +2478,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMR_CAD</t>
+          <t>AMR_CIM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Archives - Plans cadastraux</t>
+          <t>Archives - Cimetière</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2463,49 +2493,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1G</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_CAD </t>
+          <t>N</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>515</v>
+        <v>18982</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>26.3</v>
+        <v>315.8</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
         </is>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.2</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>247</v>
+        <v>0</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>0</v>
@@ -2517,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>52</v>
+        <v>18982</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>0</v>
@@ -2529,12 +2554,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMR_CIM</t>
+          <t>AMR_CLL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Archives - Cimetière</t>
+          <t>Archives - Comité local de libération</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,12 +2569,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>4H</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2558,18 +2583,18 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>18982</v>
+        <v>358</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>315.8</v>
+        <v>6.8</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
+          <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
         </is>
       </c>
       <c r="M28" s="5" t="n">
-        <v>99.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -2581,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2590,13 +2615,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>18982</v>
+        <v>88</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>0</v>
@@ -2605,12 +2630,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMR_CLL</t>
+          <t>AMR_DEL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Archives - Comité local de libération</t>
+          <t>Archives - Registres de délibérations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2620,59 +2645,69 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4H</t>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_DEL </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>358</v>
+        <v>170130</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.8</v>
+        <v>2425.75</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
+          <t>TRANSFERT_S3_OK (122101) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (396) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M29" s="5" t="n">
-        <v>73.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0</v>
+        <v>122098</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>264</v>
+        <v>23676</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>3</v>
+        <v>78807</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>3</v>
+        <v>140</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>88</v>
+        <v>67366</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>0</v>
@@ -2681,84 +2716,74 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMR_DEL</t>
+          <t>AMR_DIA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Archives - Registres de délibérations</t>
+          <t>Archives - Diapositives</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Documents figurés</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1D</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_DEL </t>
+          <t>9Fi</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>170130</v>
+        <v>1761</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2425.75</v>
+        <v>44.68</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (122101) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (396) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
         </is>
       </c>
       <c r="M30" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>49.9</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>122098</v>
+        <v>0</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>23676</v>
+        <v>879</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>78807</v>
+        <v>0</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>67366</v>
+        <v>882</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
@@ -2767,27 +2792,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMR_DIA</t>
+          <t>AMR_EC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Archives - Diapositives</t>
+          <t>Archives -  État civil</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Documents figurés</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9Fi</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2796,18 +2821,18 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1761</v>
+        <v>357990</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>44.68</v>
+        <v>759.84</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
+          <t>TRANSFERT_S3_OK (248890) ; CORBEILLE (85333) ; INCONNU (23764) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M31" s="5" t="n">
-        <v>49.9</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
@@ -2816,16 +2841,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>879</v>
+        <v>357961</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>0</v>
@@ -2834,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>882</v>
+        <v>0</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>0</v>
@@ -2843,27 +2868,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMR_EC</t>
+          <t>AMR_GDL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Archives -  État civil</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
+          <t>Archives - Goutte de lait</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2872,18 +2892,18 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>357990</v>
+        <v>32</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>759.84</v>
+        <v>0.97</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (248890) ; CORBEILLE (85333) ; INCONNU (23325) ; NON RENSEIGNÉ (439) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
       <c r="M32" s="5" t="n">
-        <v>93.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0</v>
@@ -2892,16 +2912,16 @@
         <v>0</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>357961</v>
+        <v>32</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>0</v>
@@ -2919,45 +2939,55 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AMR_GDL</t>
+          <t>AMR_GUE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Archives - Goutte de lait</t>
+          <t>Archives - La guerre 1939-1945 à Roubaix</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>5H</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_GUE </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>32</v>
+        <v>678</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.97</v>
+        <v>1.78</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
+          <t>EN LIGNE - À TRANSFERER ? (678)</t>
         </is>
       </c>
       <c r="M33" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>0</v>
@@ -2966,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>32</v>
+        <v>339</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
@@ -2975,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>0</v>
@@ -2990,55 +3020,55 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMR_GUE</t>
+          <t>AMR_LEB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Archives - La guerre 1939-1945 à Roubaix</t>
+          <t>Archives - Collection de la famille Lebas - Hennion</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5H</t>
+          <t>11J</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_GUE </t>
+          <t xml:space="preserve">RBX_AMR_LEB </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>678</v>
+        <v>174</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (678)</t>
+          <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
         </is>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0</v>
+        <v>48.9</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>678</v>
+        <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
@@ -3047,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>339</v>
+        <v>85</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
@@ -3056,13 +3086,13 @@
         <v>0</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>0</v>
@@ -3071,32 +3101,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMR_LEB</t>
+          <t>AMR_O</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Archives - Collection de la famille Lebas - Hennion</t>
+          <t>Archives - Permis de construire</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Archives privées</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11J</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_LEB </t>
+          <t>3O</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3105,18 +3130,18 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
+          <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M35" s="5" t="n">
-        <v>48.9</v>
+        <v>19.4</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -3125,10 +3150,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0</v>
@@ -3143,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>0</v>
@@ -3152,59 +3177,64 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMR_O</t>
+          <t>AMR_OBJ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Archives - Permis de construire</t>
+          <t>Archives -  Médailles et petits objets</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Objets</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Obj</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3O</t>
+          <t>1Obj</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_OBJ </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>31</v>
+        <v>208</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1.39</v>
+        <v>0.92</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
         </is>
       </c>
       <c r="M36" s="5" t="n">
-        <v>19.4</v>
+        <v>96.2</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0</v>
@@ -3219,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0</v>
@@ -3228,55 +3258,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMR_OBJ</t>
+          <t>AMR_PAR</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Archives -  Médailles et petits objets</t>
+          <t>Archives - Particuliers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Objets</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Obj</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1Obj</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_OBJ </t>
+          <t>J ?</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>208</v>
+        <v>6894</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0.92</v>
+        <v>9.25</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
+          <t>CORBEILLE (DIFFUSION) (6421) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (doublons S3 - az) (228)</t>
         </is>
       </c>
       <c r="M37" s="5" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>0</v>
@@ -3285,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>6661</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0</v>
@@ -3300,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>0</v>
@@ -3309,27 +3334,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMR_PAR</t>
+          <t>AMR_PDS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Archives - Particuliers</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Archives privées</t>
+          <t>Archives - Parc des sports</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>J ?</t>
+          <t>collection</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3338,18 +3358,18 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>6894</v>
+        <v>68</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>9.25</v>
+        <v>3.87</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (6421) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (doublons S3 - az) (228)</t>
+          <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
         </is>
       </c>
       <c r="M38" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>0</v>
@@ -3361,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>6661</v>
+        <v>68</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0</v>
@@ -3376,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
@@ -3385,12 +3405,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMR_PDS</t>
+          <t>AMR_PHO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Archives - Parc des sports</t>
+          <t>Archives - Photographies du service Communication de la Ville</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3403,36 +3423,41 @@
           <t>collection</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PHO </t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>68</v>
+        <v>18596</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>3.87</v>
+        <v>135.99</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
+          <t>INCONNU (9294) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M39" s="5" t="n">
         <v>50</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0</v>
+        <v>1194</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>68</v>
+        <v>8035</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3447,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>0</v>
+        <v>10559</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>0</v>
@@ -3456,12 +3481,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMR_PHO</t>
+          <t>AMR_PLA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Archives - Photographies du service Communication de la Ville</t>
+          <t>Archives - Collection des cartes et plans des Archives</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3476,7 +3501,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_PHO </t>
+          <t xml:space="preserve">RBX_AMR_PLA </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3485,30 +3510,30 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>18595</v>
+        <v>376</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>135.98</v>
+        <v>48.9</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>INCONNU (9293) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
       <c r="M40" s="5" t="n">
-        <v>50</v>
+        <v>35.1</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>1194</v>
+        <v>126</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>8035</v>
+        <v>250</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
@@ -3523,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>10558</v>
+        <v>126</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
@@ -3532,27 +3557,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMR_PLA</t>
+          <t>AMR_POP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Archives - Collection des cartes et plans des Archives</t>
+          <t>Archives - Recensements de population</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>collection</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_PLA </t>
+          <t>1F</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3561,21 +3586,21 @@
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>376</v>
+        <v>121938</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>48.9</v>
+        <v>504.08</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
+          <t>TRANSFERT_S3_OK (85449) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
         </is>
       </c>
       <c r="M41" s="5" t="n">
-        <v>35.1</v>
+        <v>93.3</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>126</v>
+        <v>65107</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>0</v>
@@ -3584,22 +3609,22 @@
         <v>0</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>250</v>
+        <v>113798</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>126</v>
+        <v>8135</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>0</v>
@@ -3608,27 +3633,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AMR_POP</t>
+          <t>AMR_PR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Archives - Recensements de population</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
+          <t>Archives - Pièces remarquables des Archives municipales</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1F</t>
+          <t>collection</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_PR </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3637,45 +3662,45 @@
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>121938</v>
+        <v>4326</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>504.08</v>
+        <v>166.36</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (85449) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
+          <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M42" s="5" t="n">
-        <v>93.3</v>
+        <v>27.8</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>65107</v>
+        <v>668</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>113798</v>
+        <v>786</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>8135</v>
+        <v>3533</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>0</v>
@@ -3684,59 +3709,64 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMR_PR</t>
+          <t>AMR_PUV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Archives - Pièces remarquables des Archives municipales</t>
+          <t>Archives - Bulletin municipal d'information</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Presse et ouvrages</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>58-59PER</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_PR </t>
+          <t xml:space="preserve">RBX_AMR_PUV </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>4326</v>
+        <v>19189</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>166.36</v>
+        <v>338.53</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (16035) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M43" s="5" t="n">
-        <v>27.8</v>
+        <v>16.4</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>668</v>
+        <v>0</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>786</v>
+        <v>6302</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>0</v>
@@ -3745,13 +3775,13 @@
         <v>0</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>6</v>
+        <v>6302</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>3533</v>
+        <v>6302</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0</v>
@@ -3760,32 +3790,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMR_PUV</t>
+          <t>AMR_PV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Archives - Bulletin municipal d'information</t>
+          <t>Archives - Plaques de verre</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Presse et ouvrages</t>
+          <t>Documents figurés</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>58-59PER</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_PUV </t>
+          <t>8Fi</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3794,18 +3819,18 @@
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>19189</v>
+        <v>4</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>338.53</v>
+        <v>0.03</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>INCONNU (16034) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3) ; NON RENSEIGNÉ (1)</t>
+          <t>INCONNU (4)</t>
         </is>
       </c>
       <c r="M44" s="5" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>0</v>
@@ -3814,10 +3839,10 @@
         <v>0</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>6302</v>
+        <v>2</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>0</v>
@@ -3826,13 +3851,13 @@
         <v>0</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>6302</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>6302</v>
+        <v>2</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>0</v>
@@ -3841,27 +3866,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMR_PV</t>
+          <t>AMR_PVC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Archives - Plaques de verre</t>
+          <t>Archives - Procès verbaux du conseil municipal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Documents figurés</t>
+          <t>Archives contemporaines</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8Fi</t>
+          <t>246W</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3870,18 +3895,18 @@
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>4</v>
+        <v>19170</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0.03</v>
+        <v>42.81</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>INCONNU (4)</t>
+          <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
         </is>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>0</v>
@@ -3893,22 +3918,22 @@
         <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>2</v>
+        <v>9444</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>0</v>
+        <v>9444</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>0</v>
@@ -3917,50 +3942,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMR_PVC</t>
+          <t>AMR_RAM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Archives - Procès verbaux du conseil municipal</t>
+          <t>Archives - Rapports du maire</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Archives contemporaines</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>246W</t>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_RAM </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>19170</v>
+        <v>36817</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>42.81</v>
+        <v>445.32</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
+          <t>TRANSFERT_S3_OK (36817)</t>
         </is>
       </c>
       <c r="M46" s="5" t="n">
-        <v>49.3</v>
+        <v>100</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>0</v>
+        <v>36817</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0</v>
@@ -3969,22 +4004,22 @@
         <v>0</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>9444</v>
+        <v>0</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>9444</v>
+        <v>18409</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0</v>
+        <v>18408</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>0</v>
@@ -3993,60 +4028,40 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMR_RAM</t>
+          <t>AMR_ROU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Archives - Rapports du maire</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>D</t>
+          <t>Archives - Archives privées Roussel</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3D</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_RAM </t>
+          <t>?</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>36817</v>
+        <v>449</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>445.32</v>
+        <v>5.17</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (36817)</t>
+          <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
         </is>
       </c>
       <c r="M47" s="5" t="n">
-        <v>100</v>
+        <v>42.8</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>36817</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3" t="n">
         <v>0</v>
@@ -4055,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>0</v>
@@ -4064,13 +4079,13 @@
         <v>0</v>
       </c>
       <c r="T47" s="3" t="n">
-        <v>18409</v>
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>18408</v>
+        <v>257</v>
       </c>
       <c r="W47" s="3" t="n">
         <v>0</v>
@@ -4079,17 +4094,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMR_ROU</t>
+          <t>AMR_VIC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Archives - Archives privées Roussel</t>
+          <t>Archives - Roubaisiens victimes des guerres</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>H</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>5H</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_VIC </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4098,18 +4128,18 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>449</v>
+        <v>7072</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>5.17</v>
+        <v>12.12</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
+          <t>INCONNU (7072)</t>
         </is>
       </c>
       <c r="M48" s="5" t="n">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -4121,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>192</v>
+        <v>7072</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -4136,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="W48" s="3" t="n">
         <v>0</v>
@@ -4145,64 +4175,49 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AMR_VIC</t>
+          <t>ARA_CPS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Archives - Roubaisiens victimes des guerres</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>5H</t>
+          <t>ARA - Cartes postales sonores de l'ARA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_VIC </t>
+          <t xml:space="preserve">RBX_ARA_CPS </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>7072</v>
+        <v>174</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>12.12</v>
+        <v>1.26</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>INCONNU (7072)</t>
+          <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
         </is>
       </c>
       <c r="M49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>7072</v>
+        <v>94</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0</v>
@@ -4226,17 +4241,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ARA_CPS</t>
+          <t>CSV_PAL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ARA - Cartes postales sonores de l'ARA</t>
+          <t>Conservatoire - Palmarès annuels</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_ARA_CPS </t>
+          <t xml:space="preserve">RBX_CSV_PAL </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4245,30 +4260,30 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1.26</v>
+        <v>6.65</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
+          <t>TRANSFERT_S3_OK (242)</t>
         </is>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="O50" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>0</v>
@@ -4283,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="W50" s="3" t="n">
         <v>0</v>
@@ -4292,17 +4307,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CSV_PAL</t>
+          <t>LAI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Conservatoire - Palmarès annuels</t>
+          <t>Association des Amis de la Lainière et du Textile - Collection</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_CSV_PAL </t>
+          <t xml:space="preserve">RBX_LAI </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4311,21 +4326,21 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>242</v>
+        <v>2386</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>6.65</v>
+        <v>60.87</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (242)</t>
+          <t>TRANSFERT_S3_OK (1661) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
         </is>
       </c>
       <c r="M51" s="5" t="n">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>242</v>
+        <v>1145</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>0</v>
@@ -4340,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>0</v>
@@ -4349,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>242</v>
+        <v>2385</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>0</v>
@@ -4358,17 +4373,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LAI</t>
+          <t>LAR_PUB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Association des Amis de la Lainière et du Textile - Collection</t>
+          <t>Lire à Roubaix - Publications</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_LAI </t>
+          <t xml:space="preserve">RBX_LAR_PUB </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4377,21 +4392,21 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>2386</v>
+        <v>3811</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>60.87</v>
+        <v>18.33</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1661) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
+          <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
         </is>
       </c>
       <c r="M52" s="5" t="n">
-        <v>89.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>1145</v>
+        <v>3811</v>
       </c>
       <c r="O52" s="3" t="n">
         <v>0</v>
@@ -4406,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>0</v>
@@ -4415,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>2385</v>
+        <v>3811</v>
       </c>
       <c r="W52" s="3" t="n">
         <v>0</v>
@@ -4424,17 +4439,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LAR_PUB</t>
+          <t>MDF_MTX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lire à Roubaix - Publications</t>
+          <t>Manufacture des Flandres - Collectes de la mémoire des travailleurs du textile</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_LAR_PUB </t>
+          <t xml:space="preserve">RBX_MDF_MTX </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4443,21 +4458,21 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>3811</v>
+        <v>18</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>18.33</v>
+        <v>76.03</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
+          <t>TRANSFERT_S3_OK (18)</t>
         </is>
       </c>
       <c r="M53" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>3811</v>
+        <v>17</v>
       </c>
       <c r="O53" s="3" t="n">
         <v>0</v>
@@ -4481,26 +4496,26 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>3811</v>
+        <v>0</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MDF_MTX</t>
+          <t>MED_AFF</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Manufacture des Flandres - Collectes de la mémoire des travailleurs du textile</t>
+          <t>Médiathèque - Affiches de la Médiathèque</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MDF_MTX </t>
+          <t xml:space="preserve">RBX_MED_AFF </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4509,21 +4524,21 @@
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>18</v>
+        <v>11038</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>76.03</v>
+        <v>529.5599999999999</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (18)</t>
+          <t>CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (4222) ; À SUPPRIMER (doublons AZ) (1606) ; DOUBLON - À VOIR (32) ; INCONNU (2)</t>
         </is>
       </c>
       <c r="M54" s="5" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>17</v>
+        <v>4147</v>
       </c>
       <c r="O54" s="3" t="n">
         <v>0</v>
@@ -4532,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>0</v>
+        <v>5176</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0</v>
@@ -4547,58 +4562,53 @@
         <v>0</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>0</v>
+        <v>5862</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MED_AFF</t>
+          <t>MED_AVI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Médiathèque - Affiches de la Médiathèque</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_AFF </t>
+          <t>Médiathèque - Vidéos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>11038</v>
+        <v>33</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>529.5599999999999</v>
+        <v>48.21</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (4222) ; À SUPPRIMER (doublons AZ) (1606) ; DOUBLON - À VOIR (32) ; INCONNU (2)</t>
+          <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M55" s="5" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>5742</v>
+        <v>0</v>
       </c>
       <c r="O55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P55" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>5176</v>
+        <v>0</v>
       </c>
       <c r="R55" s="3" t="n">
         <v>0</v>
@@ -4613,50 +4623,55 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>5862</v>
+        <v>0</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MED_AVI</t>
+          <t>MED_CHA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Médiathèque - Vidéos</t>
+          <t>Médiathèque - Chansons de la Médiathèque de Roubaix</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_CHA </t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>33</v>
+        <v>723</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>48.21</v>
+        <v>17.58</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
+          <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
         </is>
       </c>
       <c r="M56" s="5" t="n">
-        <v>100</v>
+        <v>50.2</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P56" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="3" t="n">
         <v>0</v>
@@ -4674,26 +4689,26 @@
         <v>0</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MED_CHA</t>
+          <t>MED_CP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Médiathèque - Chansons de la Médiathèque de Roubaix</t>
+          <t>Médiathèque - Cartes postales de Roubaix</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_CHA </t>
+          <t xml:space="preserve">RBX_MED_CP </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4702,21 +4717,21 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>723</v>
+        <v>5999</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>17.58</v>
+        <v>34.82</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
+          <t>TRANSFERT_S3_OK (4525) ; INCONNU (650) ; À SUPPRIMER (doublons S3 - az) (535) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
         </is>
       </c>
       <c r="M57" s="5" t="n">
-        <v>50.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>360</v>
+        <v>4663</v>
       </c>
       <c r="O57" s="3" t="n">
         <v>0</v>
@@ -4725,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>0</v>
@@ -4740,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="3" t="n">
-        <v>723</v>
+        <v>5691</v>
       </c>
       <c r="W57" s="3" t="n">
         <v>0</v>
@@ -4749,55 +4764,55 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MED_CP</t>
+          <t>MED_DIL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Médiathèque - Cartes postales de Roubaix</t>
+          <t>Médiathèque - Fonds d'archives d'André Diligent</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_CP </t>
+          <t xml:space="preserve">RBX_MED_DIL </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>5999</v>
+        <v>365</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>34.82</v>
+        <v>480.6</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (4525) ; INCONNU (650) ; À SUPPRIMER (doublons S3 - az) (535) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
+          <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
         </is>
       </c>
       <c r="M58" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4663</v>
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>307</v>
+        <v>94</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S58" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>0</v>
@@ -4806,58 +4821,58 @@
         <v>0</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>5691</v>
+        <v>45</v>
       </c>
       <c r="W58" s="3" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MED_DIL</t>
+          <t>MED_EPH</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Médiathèque - Fonds d'archives d'André Diligent</t>
+          <t>Médiathèque - Ephémères de la Médiathèque</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_DIL </t>
+          <t xml:space="preserve">RBX_MED_EPH </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>365</v>
+        <v>846</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>480.6</v>
+        <v>10.17</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
+          <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
         </is>
       </c>
       <c r="M59" s="5" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="O59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="3" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>0</v>
@@ -4872,49 +4887,44 @@
         <v>0</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>45</v>
+        <v>846</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MED_EPH</t>
+          <t>MED_FAN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Médiathèque - Ephémères de la Médiathèque</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_EPH </t>
+          <t>Médiathèque - Cartes postales fantaisie</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>846</v>
+        <v>2666</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>10.17</v>
+        <v>32.93</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
+          <t>INCONNU (2666)</t>
         </is>
       </c>
       <c r="M60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="O60" s="3" t="n">
         <v>0</v>
@@ -4938,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>846</v>
+        <v>2666</v>
       </c>
       <c r="W60" s="3" t="n">
         <v>0</v>
@@ -4947,44 +4957,49 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MED_FAN</t>
+          <t>MED_FLR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Médiathèque - Cartes postales fantaisie</t>
+          <t>Médiathèque - Documents sonores régionaux</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_FLR </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2666</v>
+        <v>8487</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>32.93</v>
+        <v>304.96</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>INCONNU (2666)</t>
+          <t>TRANSFERT_S3_OK (8487)</t>
         </is>
       </c>
       <c r="M61" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>0</v>
+        <v>7228</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>0</v>
@@ -4999,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>2666</v>
+        <v>781</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>0</v>
@@ -5008,17 +5023,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MED_FLR</t>
+          <t>MED_FOO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents sonores régionaux</t>
+          <t>Médiathèque - Souvenirs de foot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_FLR </t>
+          <t xml:space="preserve">RBX_MED_FOO </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5027,30 +5042,30 @@
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>8487</v>
+        <v>41</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>304.96</v>
+        <v>0.66</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (8487)</t>
+          <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M62" s="5" t="n">
-        <v>100</v>
+        <v>12.2</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>7228</v>
+        <v>33</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="3" t="n">
-        <v>478</v>
+        <v>6</v>
       </c>
       <c r="R62" s="3" t="n">
         <v>0</v>
@@ -5065,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="n">
         <v>0</v>
@@ -5074,17 +5089,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MED_FOO</t>
+          <t>MED_IMA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Médiathèque - Souvenirs de foot</t>
+          <t>Médiathèque - Imagettes de la Médiathèque</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_FOO </t>
+          <t xml:space="preserve">RBX_MED_IMA </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5093,30 +5108,30 @@
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>41</v>
+        <v>9852</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0.66</v>
+        <v>131.45</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>TRANSFERT_S3_OK (5614) ; À SUPPRIMER (doublons AZ) (3846) ; EN LIGNE - À TRANSFERER ? (180) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45) ; DOUBLON - À VOIR (6)</t>
         </is>
       </c>
       <c r="M63" s="5" t="n">
-        <v>12.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>6</v>
+        <v>5773</v>
       </c>
       <c r="O63" s="3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P63" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>6</v>
+        <v>225</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>0</v>
@@ -5131,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>0</v>
+        <v>9627</v>
       </c>
       <c r="W63" s="3" t="n">
         <v>0</v>
@@ -5140,40 +5155,35 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MED_IMA</t>
+          <t>MED_JOU</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Médiathèque - Imagettes de la Médiathèque</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_IMA </t>
+          <t>Médiathèque - Journaux</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J64" s="3" t="n">
-        <v>9852</v>
+        <v>2174</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>131.45</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (5614) ; À SUPPRIMER (doublons AZ) (3846) ; EN LIGNE - À TRANSFERER ? (180) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45) ; DOUBLON - À VOIR (6)</t>
+          <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
         </is>
       </c>
       <c r="M64" s="5" t="n">
-        <v>97.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>9619</v>
+        <v>0</v>
       </c>
       <c r="O64" s="3" t="n">
         <v>0</v>
@@ -5182,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -5197,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>9627</v>
+        <v>2174</v>
       </c>
       <c r="W64" s="3" t="n">
         <v>0</v>
@@ -5206,35 +5216,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MED_JOU</t>
+          <t>MED_LET</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Médiathèque - Journaux</t>
+          <t>Médiathèque - Lettres à en-tête des commerces et industries roubaisiens</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_LET </t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J65" s="3" t="n">
-        <v>2174</v>
+        <v>604</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>67.51000000000001</v>
+        <v>12.81</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
+          <t>TRANSFERT_S3_OK (604)</t>
         </is>
       </c>
       <c r="M65" s="5" t="n">
-        <v>91.8</v>
+        <v>100</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O65" s="3" t="n">
         <v>0</v>
@@ -5258,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="3" t="n">
-        <v>2174</v>
+        <v>604</v>
       </c>
       <c r="W65" s="3" t="n">
         <v>0</v>
@@ -5267,17 +5282,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MED_LET</t>
+          <t>MED_MAR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Médiathèque - Lettres à en-tête des commerces et industries roubaisiens</t>
+          <t>Médiathèque - Marionnettes</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_LET </t>
+          <t xml:space="preserve">RBX_MED_MAR </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5286,21 +5301,21 @@
         </is>
       </c>
       <c r="J66" s="3" t="n">
-        <v>604</v>
+        <v>197</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>12.81</v>
+        <v>7.07</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (604)</t>
+          <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
         </is>
       </c>
       <c r="M66" s="5" t="n">
-        <v>100</v>
+        <v>49.7</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>559</v>
+        <v>62</v>
       </c>
       <c r="O66" s="3" t="n">
         <v>0</v>
@@ -5309,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>0</v>
@@ -5324,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>604</v>
+        <v>99</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>0</v>
@@ -5333,17 +5348,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MED_MAR</t>
+          <t>MED_MON</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Médiathèque - Marionnettes</t>
+          <t>Médiathèque - Livres et brochures</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MAR </t>
+          <t xml:space="preserve">RBX_MED_MON </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5352,21 +5367,21 @@
         </is>
       </c>
       <c r="J67" s="3" t="n">
-        <v>197</v>
+        <v>7553</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>7.07</v>
+        <v>205.74</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
+          <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
         </is>
       </c>
       <c r="M67" s="5" t="n">
-        <v>49.7</v>
+        <v>98.8</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>62</v>
+        <v>1384</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -5375,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
@@ -5384,13 +5399,13 @@
         <v>0</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>0</v>
+        <v>2721</v>
       </c>
       <c r="U67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="3" t="n">
-        <v>99</v>
+        <v>4832</v>
       </c>
       <c r="W67" s="3" t="n">
         <v>0</v>
@@ -5399,17 +5414,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MED_MON</t>
+          <t>MED_MS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Médiathèque - Livres et brochures</t>
+          <t>Médiathèque - Manuscrits de la Médiathèque de Roubaix</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MON </t>
+          <t xml:space="preserve">RBX_MED_MS </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5418,21 +5433,21 @@
         </is>
       </c>
       <c r="J68" s="3" t="n">
-        <v>7553</v>
+        <v>46262</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>205.74</v>
+        <v>1061.94</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
+          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
       <c r="M68" s="5" t="n">
-        <v>98.8</v>
+        <v>92.2</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>1384</v>
+        <v>33302</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>0</v>
@@ -5441,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0</v>
+        <v>12786</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0</v>
@@ -5450,13 +5465,13 @@
         <v>0</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>2721</v>
+        <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>4832</v>
+        <v>33476</v>
       </c>
       <c r="W68" s="3" t="n">
         <v>0</v>
@@ -5465,40 +5480,35 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MED_MS</t>
+          <t>MED_NPT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Médiathèque - Manuscrits de la Médiathèque de Roubaix</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_MS </t>
+          <t>Médiathèque - Documents non patrimoniaux</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J69" s="3" t="n">
-        <v>46262</v>
+        <v>4</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1061.94</v>
+        <v>17.09</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
+          <t>INCONNU (4)</t>
         </is>
       </c>
       <c r="M69" s="5" t="n">
-        <v>92.2</v>
+        <v>0</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>33302</v>
+        <v>0</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>0</v>
@@ -5507,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>12786</v>
+        <v>0</v>
       </c>
       <c r="R69" s="3" t="n">
         <v>0</v>
@@ -5522,53 +5532,58 @@
         <v>0</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>33476</v>
+        <v>0</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MED_NPT</t>
+          <t>MED_PAR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents non patrimoniaux</t>
+          <t>Médiathèque - Collections de particuliers</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PAR </t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J70" s="3" t="n">
-        <v>4</v>
+        <v>24426</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>17.09</v>
+        <v>543.34</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>INCONNU (4)</t>
+          <t>TRANSFERT_S3_OK (18223) ; EN LIGNE - À TRANSFERER ? (3267) ; À SUPPRIMER (doublons S3 - az) (1674) ; À SUPPRIMER (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; CORBEILLE (DIFFUSION) (21)</t>
         </is>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0</v>
+        <v>85.3</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>20715</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>5156</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0</v>
@@ -5583,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>0</v>
+        <v>19264</v>
       </c>
       <c r="W70" s="3" t="n">
         <v>4</v>
@@ -5592,49 +5607,44 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MED_PAR</t>
+          <t>MED_PBI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de particuliers</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_PAR </t>
+          <t>Médiathèque - Collections de particuliers (suite)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>24426</v>
+        <v>1084</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>543.34</v>
+        <v>7.94</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (18223) ; EN LIGNE - À TRANSFERER ? (3267) ; À SUPPRIMER (doublons S3 - az) (1674) ; À SUPPRIMER (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; CORBEILLE (DIFFUSION) (21)</t>
+          <t>INCONNU (1084)</t>
         </is>
       </c>
       <c r="M71" s="5" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>20715</v>
+        <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>5156</v>
+        <v>0</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0</v>
@@ -5649,21 +5659,21 @@
         <v>0</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>19264</v>
+        <v>1084</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MED_PBI</t>
+          <t>MED_PER</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de particuliers (suite)</t>
+          <t>Médiathèque - Périodiques</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5672,18 +5682,18 @@
         </is>
       </c>
       <c r="J72" s="3" t="n">
-        <v>1084</v>
+        <v>1596</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>7.94</v>
+        <v>29.68</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>INCONNU (1084)</t>
+          <t>TRANSFERT_S3_OK (1596)</t>
         </is>
       </c>
       <c r="M72" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>0</v>
@@ -5704,13 +5714,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="U72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>1084</v>
+        <v>767</v>
       </c>
       <c r="W72" s="3" t="n">
         <v>0</v>
@@ -5719,12 +5729,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MED_PER</t>
+          <t>MED_PHD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Médiathèque - Périodiques</t>
+          <t>Médiathèque - Collections de photographies</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5733,18 +5743,18 @@
         </is>
       </c>
       <c r="J73" s="3" t="n">
-        <v>1596</v>
+        <v>1946</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>29.68</v>
+        <v>28.49</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1596)</t>
+          <t>INCONNU (1946)</t>
         </is>
       </c>
       <c r="M73" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N73" s="3" t="n">
         <v>0</v>
@@ -5765,13 +5775,13 @@
         <v>0</v>
       </c>
       <c r="T73" s="3" t="n">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="U73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>767</v>
+        <v>1946</v>
       </c>
       <c r="W73" s="3" t="n">
         <v>0</v>
@@ -5780,44 +5790,49 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MED_PHD</t>
+          <t>MED_PHO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de photographies</t>
+          <t>Médiathèque - Regards de photographes</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PHO </t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J74" s="3" t="n">
-        <v>1946</v>
+        <v>18844</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>28.49</v>
+        <v>69.83</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>INCONNU (1946)</t>
+          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
         </is>
       </c>
       <c r="M74" s="5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="O74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>0</v>
+        <v>13861</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>0</v>
@@ -5829,29 +5844,29 @@
         <v>0</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>1946</v>
+        <v>4804</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MED_PHO</t>
+          <t>MED_PLA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Médiathèque - Regards de photographes</t>
+          <t>Médiathèque - Collection des cartes et plans de la Médiathèque</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_PHO </t>
+          <t xml:space="preserve">RBX_MED_PLA </t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5860,30 +5875,30 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>18844</v>
+        <v>548</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>69.83</v>
+        <v>38.23</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
+          <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
         </is>
       </c>
       <c r="M75" s="5" t="n">
-        <v>5.7</v>
+        <v>49.8</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>1140</v>
+        <v>271</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>13861</v>
+        <v>273</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5895,29 +5910,29 @@
         <v>0</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>4804</v>
+        <v>275</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MED_PLA</t>
+          <t>MED_PUB</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Médiathèque - Collection des cartes et plans de la Médiathèque</t>
+          <t>Médiathèque - Publications de la Médiathèque</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_PLA </t>
+          <t xml:space="preserve">RBX_MED_PUB </t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5926,21 +5941,21 @@
         </is>
       </c>
       <c r="J76" s="3" t="n">
-        <v>548</v>
+        <v>2419</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>38.23</v>
+        <v>49.96</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
+          <t>EN LIGNE - À TRANSFERER ? (2419)</t>
         </is>
       </c>
       <c r="M76" s="5" t="n">
-        <v>49.8</v>
+        <v>0</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>271</v>
+        <v>2419</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>0</v>
@@ -5949,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>0</v>
@@ -5964,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>275</v>
+        <v>2419</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>0</v>
@@ -5973,40 +5988,35 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MED_PUB</t>
+          <t>MED_VAI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Médiathèque - Publications de la Médiathèque</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_PUB </t>
+          <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J77" s="3" t="n">
-        <v>2419</v>
+        <v>238</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>49.96</v>
+        <v>9.57</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (2419)</t>
+          <t>INCONNU (238)</t>
         </is>
       </c>
       <c r="M77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>2419</v>
+        <v>0</v>
       </c>
       <c r="O77" s="3" t="n">
         <v>0</v>
@@ -6030,7 +6040,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>2419</v>
+        <v>238</v>
       </c>
       <c r="W77" s="3" t="n">
         <v>0</v>
@@ -6039,41 +6049,46 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MED_VAI</t>
+          <t>MED_VDM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
+          <t>Médiathèque - Fonds d'archives de Maxence Van der Meersch</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_VDM </t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>238</v>
+        <v>38231</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>9.57</v>
+        <v>956.36</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>INCONNU (238)</t>
+          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>0</v>
+        <v>31272</v>
       </c>
       <c r="O78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78" s="3" t="n">
         <v>0</v>
@@ -6082,7 +6097,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" s="3" t="n">
         <v>0</v>
@@ -6091,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>238</v>
+        <v>38229</v>
       </c>
       <c r="W78" s="3" t="n">
         <v>0</v>
@@ -6100,64 +6115,59 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MED_VDM</t>
+          <t>MED_VID</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Médiathèque - Fonds d'archives de Maxence Van der Meersch</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_VDM </t>
+          <t>Médiathèque - Documents vidéos</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J79" s="3" t="n">
-        <v>38231</v>
+        <v>31</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>956.36</v>
+        <v>8.82</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
         </is>
       </c>
       <c r="M79" s="5" t="n">
-        <v>100</v>
+        <v>48.4</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>31272</v>
+        <v>0</v>
       </c>
       <c r="O79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P79" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="V79" s="3" t="n">
-        <v>38229</v>
+        <v>0</v>
       </c>
       <c r="W79" s="3" t="n">
         <v>0</v>
@@ -6166,44 +6176,49 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MED_VID</t>
+          <t>MUS_ARC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents vidéos</t>
+          <t>Musée La Piscine - Archives</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MUS_ARC </t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>31</v>
+        <v>318</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>8.82</v>
+        <v>3.42</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
+          <t>TRANSFERT_S3_OK (318)</t>
         </is>
       </c>
       <c r="M80" s="5" t="n">
-        <v>48.4</v>
+        <v>100</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="O80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>0</v>
@@ -6215,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W80" s="3" t="n">
         <v>0</v>
@@ -6227,17 +6242,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MUS_ARC</t>
+          <t>MUS_VAI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Musée La Piscine - Archives</t>
+          <t>Musée La Piscine - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MUS_ARC </t>
+          <t xml:space="preserve">RBX_MUS_VAI </t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6246,21 +6261,21 @@
         </is>
       </c>
       <c r="J81" s="3" t="n">
-        <v>318</v>
+        <v>1918</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>3.42</v>
+        <v>47.42</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (318)</t>
+          <t>TRANSFERT_S3_OK (1918)</t>
         </is>
       </c>
       <c r="M81" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>134</v>
+        <v>1859</v>
       </c>
       <c r="O81" s="3" t="n">
         <v>0</v>
@@ -6269,7 +6284,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>258</v>
+        <v>404</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>0</v>
@@ -6284,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>60</v>
+        <v>1514</v>
       </c>
       <c r="W81" s="3" t="n">
         <v>0</v>
@@ -6293,40 +6308,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MUS_VAI</t>
+          <t>MUS_XXX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Musée La Piscine - Parfumerie et savonnerie Vaissier</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MUS_VAI </t>
+          <t>Musée La Piscine - nouveau versement</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J82" s="3" t="n">
-        <v>1918</v>
+        <v>375</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>47.42</v>
+        <v>0.16</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1918)</t>
+          <t>INCONNU (375)</t>
         </is>
       </c>
       <c r="M82" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N82" s="3" t="n">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="O82" s="3" t="n">
         <v>0</v>
@@ -6335,7 +6345,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>0</v>
@@ -6350,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>1514</v>
+        <v>0</v>
       </c>
       <c r="W82" s="3" t="n">
         <v>0</v>
@@ -6359,35 +6369,40 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MUS_XXX</t>
+          <t>OBS_JOU</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Musée La Piscine - nouveau versement</t>
+          <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_OBS_JOU </t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J83" s="3" t="n">
-        <v>375</v>
+        <v>1800</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0.16</v>
+        <v>20.38</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>INCONNU (375)</t>
+          <t>TRANSFERT_S3_OK (1240) ; EN LIGNE - À TRANSFERER ? (553) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (2)</t>
         </is>
       </c>
       <c r="M83" s="5" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>0</v>
+        <v>1238</v>
       </c>
       <c r="O83" s="3" t="n">
         <v>0</v>
@@ -6396,7 +6411,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>375</v>
+        <v>1156</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0</v>
@@ -6408,10 +6423,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>0</v>
+        <v>601</v>
       </c>
       <c r="W83" s="3" t="n">
         <v>0</v>
@@ -6420,17 +6435,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OBS_JOU</t>
+          <t>PRA_AVE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
+          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_OBS_JOU </t>
+          <t xml:space="preserve">RBX_PRA_AVE </t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6439,21 +6459,21 @@
         </is>
       </c>
       <c r="J84" s="3" t="n">
-        <v>1800</v>
+        <v>176340</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>20.38</v>
+        <v>778.75</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1240) ; EN LIGNE - À TRANSFERER ? (553) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (2)</t>
+          <t>TRANSFERT_S3_OK (176340)</t>
         </is>
       </c>
       <c r="M84" s="5" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>1238</v>
+        <v>87510</v>
       </c>
       <c r="O84" s="3" t="n">
         <v>0</v>
@@ -6462,22 +6482,22 @@
         <v>0</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>1156</v>
+        <v>0</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>0</v>
+        <v>44271</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>0</v>
+        <v>43519</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>43</v>
+        <v>44275</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>601</v>
+        <v>44275</v>
       </c>
       <c r="W84" s="3" t="n">
         <v>0</v>
@@ -6486,69 +6506,59 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PRA_AVE</t>
+          <t>PRA_BDR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_AVE </t>
+          <t>Presse - Bulletin de Roubaix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>176340</v>
+        <v>3138</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>778.75</v>
+        <v>16.9</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (176340)</t>
+          <t>INCONNU (2781) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (doublons S3 - az) (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M85" s="5" t="n">
-        <v>100</v>
+        <v>11.4</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>87510</v>
+        <v>0</v>
       </c>
       <c r="O85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>0</v>
+        <v>523</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>44271</v>
+        <v>406</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>43519</v>
+        <v>407</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>44275</v>
+        <v>1218</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>44275</v>
+        <v>583</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -6557,59 +6567,69 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PRA_BDR</t>
+          <t>PRA_CRT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Presse - Bulletin de Roubaix</t>
+          <t>Presse - La Croix de Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_CRT </t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J86" s="3" t="n">
-        <v>3138</v>
+        <v>116806</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>16.9</v>
+        <v>1024.92</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>INCONNU (2781) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (doublons S3 - az) (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (116806)</t>
         </is>
       </c>
       <c r="M86" s="5" t="n">
-        <v>11.4</v>
+        <v>100</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>0</v>
+        <v>48452</v>
       </c>
       <c r="O86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" s="3" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="R86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>406</v>
+        <v>29202</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>407</v>
+        <v>29200</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>1218</v>
+        <v>29202</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>583</v>
+        <v>29202</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>0</v>
@@ -6618,12 +6638,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PRA_CRT</t>
+          <t>PRA_CTG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Presse - La Croix de Roubaix-Tourcoing</t>
+          <t>Presse - Le Courrier de Tourcoing</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6633,7 +6653,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_CRT </t>
+          <t xml:space="preserve">RBX_PRA_CTG </t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6642,21 +6662,21 @@
         </is>
       </c>
       <c r="J87" s="3" t="n">
-        <v>116806</v>
+        <v>5752</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1024.92</v>
+        <v>45.98</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (116806)</t>
+          <t>TRANSFERT_S3_OK (5752)</t>
         </is>
       </c>
       <c r="M87" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>48452</v>
+        <v>2876</v>
       </c>
       <c r="O87" s="3" t="n">
         <v>0</v>
@@ -6671,16 +6691,16 @@
         <v>0</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>29202</v>
+        <v>1438</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>29200</v>
+        <v>1438</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>29202</v>
+        <v>1438</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>29202</v>
+        <v>1438</v>
       </c>
       <c r="W87" s="3" t="n">
         <v>0</v>
@@ -6689,12 +6709,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PRA_CTG</t>
+          <t>PRA_ERT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Presse - Le Courrier de Tourcoing</t>
+          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6704,7 +6724,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_CTG </t>
+          <t xml:space="preserve">RBX_PRA_ERT </t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6713,21 +6733,21 @@
         </is>
       </c>
       <c r="J88" s="3" t="n">
-        <v>5752</v>
+        <v>377078</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>45.98</v>
+        <v>3103.47</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (5752)</t>
+          <t>TRANSFERT_S3_OK (377078)</t>
         </is>
       </c>
       <c r="M88" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>2876</v>
+        <v>185403</v>
       </c>
       <c r="O88" s="3" t="n">
         <v>0</v>
@@ -6742,16 +6762,16 @@
         <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>1438</v>
+        <v>94387</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>1438</v>
+        <v>93918</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>1438</v>
+        <v>94387</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>1438</v>
+        <v>94386</v>
       </c>
       <c r="W88" s="3" t="n">
         <v>0</v>
@@ -6760,12 +6780,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PRA_ERT</t>
+          <t>PRA_IND</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
+          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -6775,7 +6795,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_ERT </t>
+          <t xml:space="preserve">RBX_PRA_IND </t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6784,21 +6804,21 @@
         </is>
       </c>
       <c r="J89" s="3" t="n">
-        <v>377078</v>
+        <v>64400</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>3103.47</v>
+        <v>199.84</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (377078)</t>
+          <t>TRANSFERT_S3_OK (64400)</t>
         </is>
       </c>
       <c r="M89" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>185403</v>
+        <v>32665</v>
       </c>
       <c r="O89" s="3" t="n">
         <v>0</v>
@@ -6813,16 +6833,16 @@
         <v>0</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>94387</v>
+        <v>15377</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>93918</v>
+        <v>16307</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>94387</v>
+        <v>16358</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>94386</v>
+        <v>16358</v>
       </c>
       <c r="W89" s="3" t="n">
         <v>0</v>
@@ -6831,12 +6851,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PRA_IND</t>
+          <t>PRA_JRX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
+          <t>Presse - Journal de Roubaix</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -6846,7 +6866,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_IND </t>
+          <t xml:space="preserve">RBX_PRA_JRX </t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6855,21 +6875,21 @@
         </is>
       </c>
       <c r="J90" s="3" t="n">
-        <v>64400</v>
+        <v>595291</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>199.84</v>
+        <v>4704.6</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (64400)</t>
+          <t>TRANSFERT_S3_OK (595291)</t>
         </is>
       </c>
       <c r="M90" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>32665</v>
+        <v>284717</v>
       </c>
       <c r="O90" s="3" t="n">
         <v>0</v>
@@ -6884,16 +6904,16 @@
         <v>0</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>15377</v>
+        <v>148174</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>16307</v>
+        <v>148814</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>16358</v>
+        <v>149132</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>16358</v>
+        <v>149171</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
@@ -6902,12 +6922,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PRA_JRX</t>
+          <t>PRA_RTG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Presse - Journal de Roubaix</t>
+          <t>Presse - Roubaix-Tourcoing</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -6917,7 +6937,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_JRX </t>
+          <t xml:space="preserve">RBX_VAH_PUB </t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6926,21 +6946,21 @@
         </is>
       </c>
       <c r="J91" s="3" t="n">
-        <v>595291</v>
+        <v>3367</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>4704.6</v>
+        <v>19.37</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (595291)</t>
+          <t>TRANSFERT_S3_OK (3367)</t>
         </is>
       </c>
       <c r="M91" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>284717</v>
+        <v>1671</v>
       </c>
       <c r="O91" s="3" t="n">
         <v>0</v>
@@ -6955,16 +6975,16 @@
         <v>0</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>148174</v>
+        <v>848</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>148814</v>
+        <v>823</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>149132</v>
+        <v>848</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>149171</v>
+        <v>848</v>
       </c>
       <c r="W91" s="3" t="n">
         <v>0</v>
@@ -6973,17 +6993,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PRA_RTG</t>
+          <t>VAH_PUB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Presse - Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
+          <t>Ville d'art et d'histoire  - Publications</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6997,21 +7012,21 @@
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>3367</v>
+        <v>457</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>19.37</v>
+        <v>13.49</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (3367)</t>
+          <t>EN LIGNE - À TRANSFERER ? (457)</t>
         </is>
       </c>
       <c r="M92" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>1671</v>
+        <v>457</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -7026,16 +7041,16 @@
         <v>0</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="T92" s="3" t="n">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="U92" s="3" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>848</v>
+        <v>457</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>
@@ -7044,186 +7059,120 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>VAH_PUB</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Ville d'art et d'histoire  - Publications</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_VAH_PUB </t>
+          <t>_INCONNU</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J93" s="3" t="n">
-        <v>457</v>
+        <v>4080</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>13.49</v>
+        <v>86.63</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (457)</t>
+          <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
         </is>
       </c>
       <c r="M93" s="5" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="N93" s="3" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="O93" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>0</v>
+        <v>2244</v>
       </c>
       <c r="Q93" s="3" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="R93" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S93" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T93" s="3" t="n">
-        <v>0</v>
+        <v>726</v>
       </c>
       <c r="U93" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V93" s="3" t="n">
-        <v>457</v>
+        <v>212</v>
       </c>
       <c r="W93" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>_INCONNU</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>4080</v>
-      </c>
-      <c r="K94" s="4" t="n">
-        <v>86.63</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
-        </is>
-      </c>
-      <c r="M94" s="5" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="N94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="P94" s="3" t="n">
-        <v>2244</v>
-      </c>
-      <c r="Q94" s="3" t="n">
-        <v>857</v>
-      </c>
-      <c r="R94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T94" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="U94" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="V94" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="W94" s="3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr"/>
-      <c r="C95" s="6" t="inlineStr"/>
-      <c r="D95" s="6" t="inlineStr"/>
-      <c r="E95" s="6" t="inlineStr"/>
-      <c r="F95" s="6" t="inlineStr"/>
-      <c r="G95" s="6" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr"/>
-      <c r="I95" s="6" t="inlineStr"/>
-      <c r="J95" s="7" t="n">
+      <c r="B94" s="6" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr"/>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="6" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr"/>
+      <c r="J94" s="7" t="n">
         <v>2428075</v>
       </c>
-      <c r="K95" s="8" t="n">
+      <c r="K94" s="8" t="n">
         <v>20888.86</v>
       </c>
-      <c r="L95" s="6" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (2076509) ; INCONNU (135385) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (13419) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5452) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; NON RENSEIGNÉ (441) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
-        </is>
-      </c>
-      <c r="M95" s="9" t="n">
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (2076509) ; INCONNU (135826) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (13419) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5452) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
+        </is>
+      </c>
+      <c r="M94" s="9" t="n">
         <v>93.8</v>
       </c>
-      <c r="N95" s="7" t="n">
-        <v>992737</v>
-      </c>
-      <c r="O95" s="7" t="n">
+      <c r="N94" s="7" t="n">
+        <v>987296</v>
+      </c>
+      <c r="O94" s="7" t="n">
         <v>7347</v>
       </c>
-      <c r="P95" s="7" t="n">
+      <c r="P94" s="7" t="n">
         <v>2453</v>
       </c>
-      <c r="Q95" s="7" t="n">
+      <c r="Q94" s="7" t="n">
         <v>672526</v>
       </c>
-      <c r="R95" s="7" t="n">
+      <c r="R94" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="S95" s="7" t="n">
+      <c r="S94" s="7" t="n">
         <v>334782</v>
       </c>
-      <c r="T95" s="7" t="n">
+      <c r="T94" s="7" t="n">
         <v>452592</v>
       </c>
-      <c r="U95" s="7" t="n">
+      <c r="U94" s="7" t="n">
         <v>338132</v>
       </c>
-      <c r="V95" s="7" t="n">
+      <c r="V94" s="7" t="n">
         <v>619758</v>
       </c>
-      <c r="W95" s="7" t="n">
+      <c r="W94" s="7" t="n">
         <v>465</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M95">
+  <conditionalFormatting sqref="M2:M94">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -4990,7 +4990,7 @@
         <v>100</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>1</v>
+        <v>3585</v>
       </c>
       <c r="O61" s="3" t="n">
         <v>7228</v>
@@ -5440,11 +5440,11 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (3440) ; À SUPPRIMER (Tests) (412) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
+          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; À TRANSFERER (2548) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (doublons AZ) (278) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
       <c r="M68" s="5" t="n">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="N68" s="3" t="n">
         <v>33302</v>
@@ -7134,14 +7134,14 @@
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (2076509) ; INCONNU (135826) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (13419) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5452) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
+          <t>TRANSFERT_S3_OK (2076509) ; INCONNU (135826) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (10593) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5730) ; À TRANSFERER (3034) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
         </is>
       </c>
       <c r="M94" s="9" t="n">
         <v>93.8</v>
       </c>
       <c r="N94" s="7" t="n">
-        <v>987296</v>
+        <v>990880</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>7347</v>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -5440,14 +5440,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (29866) ; CORBEILLE (DIFFUSION) (12229) ; À TRANSFERER (2548) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (doublons AZ) (278) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
+          <t>TRANSFERT_S3_OK (32414) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (doublons AZ) (278) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
         </is>
       </c>
       <c r="M68" s="5" t="n">
-        <v>92.8</v>
+        <v>98.3</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>33302</v>
+        <v>33024</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>0</v>
@@ -7134,14 +7134,14 @@
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (2076509) ; INCONNU (135826) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (10593) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5730) ; À TRANSFERER (3034) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
+          <t>TRANSFERT_S3_OK (2079057) ; INCONNU (135826) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (10593) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5730) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
         </is>
       </c>
       <c r="M94" s="9" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N94" s="7" t="n">
-        <v>990880</v>
+        <v>990602</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>7347</v>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -2828,11 +2828,11 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (248890) ; CORBEILLE (85333) ; INCONNU (23764) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>TRANSFERT_S3_OK (260629) ; CORBEILLE (85333) ; À SUPPRIMER (DOUBLON) (11971) ; S3_KEY À CONSTRUIRE (54) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M31" s="5" t="n">
-        <v>93.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
@@ -7134,11 +7134,11 @@
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (2079057) ; INCONNU (135826) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; EN LIGNE - À TRANSFERER ? (10593) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5730) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; DOUBLON - À VOIR (38)</t>
+          <t>TRANSFERT_S3_OK (2090796) ; INCONNU (112062) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; À SUPPRIMER (DOUBLON) (11971) ; EN LIGNE - À TRANSFERER ? (10593) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5730) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; S3_KEY À CONSTRUIRE (54) ; DOUBLON - À VOIR (38)</t>
         </is>
       </c>
       <c r="M94" s="9" t="n">
-        <v>93.90000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N94" s="7" t="n">
         <v>990602</v>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -629,7 +629,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>INCONNU (30) ; CORBEILLE (DIFFUSION) (30)</t>
+          <t>INCONNU (30) ; À SUPPRIMER (DIFFUSION) (30)</t>
         </is>
       </c>
       <c r="M2" s="5" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (50) ; INCONNU (47)</t>
+          <t>À SUPPRIMER (DIFFUSION) (50) ; INCONNU (47)</t>
         </is>
       </c>
       <c r="M3" s="5" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>INCONNU (6) ; CORBEILLE (DIFFUSION) (6)</t>
+          <t>INCONNU (6) ; À SUPPRIMER (DIFFUSION) (6)</t>
         </is>
       </c>
       <c r="M4" s="5" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>INCONNU (272) ; CORBEILLE (DIFFUSION) (24)</t>
+          <t>À TRANSFERER APRES VALIDATION (272) ; À SUPPRIMER (DIFFUSION) (24)</t>
         </is>
       </c>
       <c r="M10" s="5" t="n">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>INCONNU (496)</t>
+          <t>À TRANSFERER APRES VALIDATION (496)</t>
         </is>
       </c>
       <c r="M15" s="5" t="n">
@@ -2137,18 +2137,18 @@
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3648</v>
+        <v>1935</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>219.29</v>
+        <v>165.13</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1074) ; DDE - NE PAS GARDER (DIFFUSION) (776) ; DDE - NE PAS GARDER (DOUBLONS AZ) (747) ; INCONNU (560) ; À TRANSFERER (365) ; CORBEILLE (DIFFUSION) (126)</t>
+          <t>TRANSFERT_S3_OK (1074) ; INCONNU (552) ; À SUPPRIMER (DIFFUSION) (237) ; À SUPPRIMER (DOUBLON AZ) (48) ; À TRANSFERER APRES VALIDATION (24)</t>
         </is>
       </c>
       <c r="M22" s="5" t="n">
-        <v>74.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>1005</v>
@@ -2160,22 +2160,22 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>643</v>
+        <v>300</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>580</v>
+        <v>237</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>554</v>
+        <v>213</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>1506</v>
+        <v>1161</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>INCONNU (48) ; DDE - NE PAS GARDER (DIFFUSION) (40) ; CORBEILLE (DIFFUSION) (4)</t>
+          <t>INCONNU (48) ; À SUPPRIMER (DIFFUSION) (44)</t>
         </is>
       </c>
       <c r="M25" s="5" t="n">
@@ -2438,14 +2438,14 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>INCONNU (267) ; EN LIGNE - À TRANSFERER ? (247) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (296) ; INCONNU FRAD59 (180) ; À SUPPRIMER (DIFFUSION) (29) ; À SUPPRIMER (DOUBLON) (9) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.2</v>
+        <v>65</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (doublons S3 - az) (2739) ; INCONNU (173)</t>
+          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (DOUBLON S3-AZ) (2739) ; INCONNU (173)</t>
         </is>
       </c>
       <c r="M27" s="5" t="n">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (176) ; INCONNU (94) ; DDE - NE PAS GARDER (DIFFUSION) (88)</t>
+          <t>À SUPPRIMER (DIFFUSION) (264) ; INCONNU (94)</t>
         </is>
       </c>
       <c r="M28" s="5" t="n">
@@ -2676,11 +2676,11 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (122101) ; INCONNU (23956) ; DDE - NE PAS GARDER (DIFFUSION) (23676) ; À SUPPRIMER (doublons S3 - az) (396) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (122101) ; À TRANSFERER APRES VALIDATION (47632) ; À SUPPRIMER (DOUBLON S3-AZ) (396) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M29" s="5" t="n">
-        <v>85.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>122098</v>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>INCONNU (882) ; CORBEILLE (DIFFUSION) (879)</t>
+          <t>À TRANSFERER APRES VALIDATION (879) ; À SUPPRIMER (DIFFUSION) (879) ; À SUPPRIMER (DOUBLON) (3)</t>
         </is>
       </c>
       <c r="M30" s="5" t="n">
-        <v>49.9</v>
+        <v>50.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (260629) ; CORBEILLE (85333) ; À SUPPRIMER (DOUBLON) (11971) ; S3_KEY À CONSTRUIRE (54) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>TRANSFERT_S3_OK (260628) ; À SUPPRIMER (DIFFUSION) (85333) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (11972) ; S3_KEY À CONSTRUIRE (54) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M31" s="5" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>DDE - NE PAS GARDER (DIFFUSION) (16) ; INCONNU (16)</t>
+          <t>À SUPPRIMER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
       <c r="M32" s="5" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5H</t>
+          <t>7H</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2973,21 +2973,21 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>678</v>
+        <v>2391</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.78</v>
+        <v>55.94</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (678)</t>
+          <t>À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (682) ; EN LIGNE - À TRANSFERER ? (682) ; À SUPPRIMER (DIFFUSION) (665) ; TRANSFERT_S3_OK (340) ; À SUPPRIMER (DOUBLON AZ) (17) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
         </is>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0</v>
+        <v>71.3</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>0</v>
@@ -2996,22 +2996,22 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>339</v>
+        <v>682</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>339</v>
+        <v>682</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>INCONNU (89) ; CORBEILLE (DIFFUSION) (85)</t>
+          <t>INCONNU (89) ; À SUPPRIMER (DIFFUSION) (85)</t>
         </is>
       </c>
       <c r="M34" s="5" t="n">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>INCONNU (25) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (25) ; À SUPPRIMER (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M35" s="5" t="n">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (doublons S3 - az) (100) ; INCONNU (8)</t>
+          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (DOUBLON S3-AZ) (100) ; INCONNU (8)</t>
         </is>
       </c>
       <c r="M36" s="5" t="n">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (6421) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (doublons S3 - az) (228)</t>
+          <t>À SUPPRIMER (DIFFUSION) (6421) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (DOUBLON S3-AZ) (228)</t>
         </is>
       </c>
       <c r="M37" s="5" t="n">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>INCONNU (34) ; DDE - NE PAS GARDER (DIFFUSION) (34)</t>
+          <t>INCONNU (34) ; À SUPPRIMER (DIFFUSION) (34)</t>
         </is>
       </c>
       <c r="M38" s="5" t="n">
@@ -3441,11 +3441,11 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>INCONNU (9294) ; CORBEILLE (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>À TRANSFERER APRES VALIDATION (9238) ; À SUPPRIMER (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (DOUBLON) (55) ; À SUPPRIMER (FILE_TYPE) (2) ; INCONNU (1)</t>
         </is>
       </c>
       <c r="M39" s="5" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>1194</v>
@@ -3517,14 +3517,14 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>À TRANSFERER (121) ; DDE - NE PAS GARDER (DOUBLONS AZ) (119) ; EN LIGNE - À TRANSFERER ? (115) ; INCONNU (8) ; DDE - NE PAS GARDER (DIFFUSION) (7) ; CORBEILLE (DIFFUSION) (5) ; À SUPPRIMER (doublons S3 - az) (1)</t>
+          <t>TRANSFERT_S3_OK (239) ; À SUPPRIMER (DOUBLON AZ) (119) ; À SUPPRIMER (DIFFUSION) (12) ; À TRANSFERER APRES VALIDATION (5) ; À SUPPRIMER (DOUBLON S3-AZ) (1)</t>
         </is>
       </c>
       <c r="M40" s="5" t="n">
-        <v>35.1</v>
+        <v>98.7</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>126</v>
+        <v>244</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (85449) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; INCONNU (8127) ; DDE - NE PAS GARDER (DIFFUSION) (8086)</t>
+          <t>TRANSFERT_S3_OK (85449) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À TRANSFERER APRES VALIDATION (8127) ; À SUPPRIMER (DIFFUSION) (8086)</t>
         </is>
       </c>
       <c r="M41" s="5" t="n">
@@ -3669,11 +3669,11 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>INCONNU (3013) ; TRANSFERT_S3_OK (1101) ; EN LIGNE - À TRANSFERER ? (110) ; CORBEILLE (DIFFUSION) (100) ; À SUPPRIMER (doublons S3 - az) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (4199) ; À SUPPRIMER (DIFFUSION) (110) ; INCONNU (15) ; À SUPPRIMER (DOUBLON S3-AZ) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M42" s="5" t="n">
-        <v>27.8</v>
+        <v>99.7</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>668</v>
@@ -3750,11 +3750,11 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>INCONNU (16035) ; CORBEILLE (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>À TRANSFERER APRES VALIDATION (9733) ; À SUPPRIMER (DOUBLON) (6302) ; À SUPPRIMER (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M43" s="5" t="n">
-        <v>16.4</v>
+        <v>49.3</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>0</v>
@@ -3902,11 +3902,11 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>INCONNU (9726) ; DDE - NE PAS GARDER (DIFFUSION) (9444)</t>
+          <t>À TRANSFERER APRES VALIDATION (19170)</t>
         </is>
       </c>
       <c r="M45" s="5" t="n">
-        <v>49.3</v>
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>0</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>INCONNU (257) ; CORBEILLE (DIFFUSION) (96) ; DDE - NE PAS GARDER (DIFFUSION) (96)</t>
+          <t>INCONNU (257) ; À SUPPRIMER (DIFFUSION) (192)</t>
         </is>
       </c>
       <c r="M47" s="5" t="n">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>INCONNU (7072)</t>
+          <t>À TRANSFERER APRES VALIDATION (7072)</t>
         </is>
       </c>
       <c r="M48" s="5" t="n">
@@ -4201,14 +4201,14 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (146) ; INCONNU (28)</t>
+          <t>TRANSFERT_S3_OK (174)</t>
         </is>
       </c>
       <c r="M49" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="O49" s="3" t="n">
         <v>80</v>
@@ -4399,14 +4399,14 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (3730) ; EN LIGNE - À TRANSFERER ? (81)</t>
+          <t>TRANSFERT_S3_OK (3731) ; À SUPPRIMER (DOUBLON) (80)</t>
         </is>
       </c>
       <c r="M52" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3811</v>
+        <v>3731</v>
       </c>
       <c r="O52" s="3" t="n">
         <v>0</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (5176) ; TRANSFERT_S3_OK (4222) ; À SUPPRIMER (doublons AZ) (1606) ; DOUBLON - À VOIR (32) ; INCONNU (2)</t>
+          <t>À SUPPRIMER (DIFFUSION) (5176) ; TRANSFERT_S3_OK (4222) ; À SUPPRIMER (DOUBLON AZ) (1606) ; DOUBLON - À VOIR (32) ; INCONNU (2)</t>
         </is>
       </c>
       <c r="M54" s="5" t="n">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (31) ; DDE - NE PAS GARDER (FILE_TYPE) (2)</t>
+          <t>TRANSFERT_S3_OK (31) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M55" s="5" t="n">
@@ -4724,11 +4724,11 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (4525) ; INCONNU (650) ; À SUPPRIMER (doublons S3 - az) (535) ; EN LIGNE - À TRANSFERER ? (183) ; CORBEILLE (DIFFUSION) (106)</t>
+          <t>TRANSFERT_S3_OK (5318) ; À SUPPRIMER (DOUBLON S3-AZ) (535) ; À SUPPRIMER (DIFFUSION) (106) ; INCONNU (39) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M57" s="5" t="n">
-        <v>86.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>4663</v>
@@ -4856,11 +4856,11 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (840) ; INCONNU (6)</t>
+          <t>TRANSFERT_S3_OK (846)</t>
         </is>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>840</v>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>INCONNU (30) ; EN LIGNE - À TRANSFERER ? (6) ; CORBEILLE (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>INCONNU (30) ; TRANSFERT_S3_OK (6) ; À SUPPRIMER (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M62" s="5" t="n">
-        <v>12.2</v>
+        <v>26.8</v>
       </c>
       <c r="N62" s="3" t="n">
         <v>6</v>
@@ -5115,11 +5115,11 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (5614) ; À SUPPRIMER (doublons AZ) (3846) ; EN LIGNE - À TRANSFERER ? (180) ; À SUPPRIMER (doublons S3 - az) (113) ; INCONNU (48) ; CORBEILLE (DIFFUSION) (45) ; DOUBLON - À VOIR (6)</t>
+          <t>TRANSFERT_S3_OK (5821) ; À SUPPRIMER (DOUBLON AZ) (3846) ; À SUPPRIMER (DOUBLON S3-AZ) (113) ; À SUPPRIMER (DIFFUSION) (45) ; À SUPPRIMER (DOUBLON) (21) ; DOUBLON - À VOIR (6)</t>
         </is>
       </c>
       <c r="M63" s="5" t="n">
-        <v>97.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="N63" s="3" t="n">
         <v>5773</v>
@@ -5308,11 +5308,11 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (98) ; EN LIGNE - À TRANSFERER ? (62) ; INCONNU (37)</t>
+          <t>TRANSFERT_S3_OK (99) ; À SUPPRIMER (DIFFUSION) (98)</t>
         </is>
       </c>
       <c r="M66" s="5" t="n">
-        <v>49.7</v>
+        <v>100</v>
       </c>
       <c r="N66" s="3" t="n">
         <v>62</v>
@@ -5374,11 +5374,11 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (7462) ; EN LIGNE - À TRANSFERER ? (89) ; INCONNU (2)</t>
+          <t>TRANSFERT_S3_OK (7553)</t>
         </is>
       </c>
       <c r="M67" s="5" t="n">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>1384</v>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (32414) ; CORBEILLE (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (doublons AZ) (278) ; INCONNU (158) ; À SUPPRIMER (doublons S3 - az) (157)</t>
+          <t>TRANSFERT_S3_OK (32414) ; À SUPPRIMER (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (TESTS) (412) ; À SUPPRIMER (DOUBLON AZ) (278) ; INCONNU (158) ; À SUPPRIMER (DOUBLON S3-AZ) (157)</t>
         </is>
       </c>
       <c r="M68" s="5" t="n">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (18223) ; EN LIGNE - À TRANSFERER ? (3267) ; À SUPPRIMER (doublons S3 - az) (1674) ; À SUPPRIMER (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; CORBEILLE (DIFFUSION) (21)</t>
+          <t>TRANSFERT_S3_OK (18223) ; EN LIGNE - À TRANSFERER ? (3267) ; À SUPPRIMER (DOUBLON S3-AZ) (1674) ; À SUPPRIMER (MED_PAR) (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; À SUPPRIMER (DIFFUSION) (21)</t>
         </is>
       </c>
       <c r="M70" s="5" t="n">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>INCONNU (1084)</t>
+          <t>À TRANSFERER APRES VALIDATION (1084)</t>
         </is>
       </c>
       <c r="M71" s="5" t="n">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>INCONNU (1946)</t>
+          <t>À TRANSFERER APRES VALIDATION (1946)</t>
         </is>
       </c>
       <c r="M73" s="5" t="n">
@@ -5816,11 +5816,11 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1063) ; EN LIGNE - À TRANSFERER ? (275) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (doublons S3 - az) (1)</t>
+          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1338) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (DOUBLON S3-AZ) (1)</t>
         </is>
       </c>
       <c r="M74" s="5" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>1140</v>
@@ -5882,11 +5882,11 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CORBEILLE (DIFFUSION) (273) ; EN LIGNE - À TRANSFERER ? (271) ; INCONNU (4)</t>
+          <t>TRANSFERT_S3_OK (274) ; À SUPPRIMER (DIFFUSION) (273) ; À SUPPRIMER (DOUBLON) (1)</t>
         </is>
       </c>
       <c r="M75" s="5" t="n">
-        <v>49.8</v>
+        <v>100</v>
       </c>
       <c r="N75" s="3" t="n">
         <v>271</v>
@@ -5948,11 +5948,11 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (2419)</t>
+          <t>TRANSFERT_S3_OK (1274) ; À SUPPRIMER (DOUBLON) (1145)</t>
         </is>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>2419</v>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (doublons S3 - az) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (DOUBLON S3-AZ) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M78" s="5" t="n">
@@ -6395,14 +6395,14 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1240) ; EN LIGNE - À TRANSFERER ? (553) ; INCONNU (5) ; À SUPPRIMER (doublons S3 - az) (2)</t>
+          <t>TRANSFERT_S3_OK (1240) ; À TRANSFERER APRES VALIDATION (517) ; À SUPPRIMER (DOUBLON S3-AZ) (38) ; INCONNU (5)</t>
         </is>
       </c>
       <c r="M83" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>1238</v>
+        <v>1202</v>
       </c>
       <c r="O83" s="3" t="n">
         <v>0</v>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>INCONNU (2781) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (doublons S3 - az) (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (2781) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (DOUBLON S3-AZ) (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M85" s="5" t="n">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>DDE - NE PAS GARDER (FILE_TYPE) (2208) ; INCONNU (1661) ; CORBEILLE (DIFFUSION) (174) ; À SUPPRIMER (FILE_TYPE) (37)</t>
+          <t>À SUPPRIMER (FILE_TYPE) (2245) ; INCONNU (1661) ; À SUPPRIMER (DIFFUSION) (174)</t>
         </is>
       </c>
       <c r="M93" s="5" t="n">
@@ -7134,14 +7134,14 @@
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (2090796) ; INCONNU (112062) ; CORBEILLE (85333) ; DDE - NE PAS GARDER (DIFFUSION) (42263) ; CORBEILLE (DIFFUSION) (37317) ; À SUPPRIMER (remplacement par Verif / Tampon) (20276) ; À SUPPRIMER (DOUBLON) (11971) ; EN LIGNE - À TRANSFERER ? (10593) ; À SUPPRIMER (doublons S3 - az) (6143) ; À SUPPRIMER (doublons AZ) (5730) ; DDE - NE PAS GARDER (FILE_TYPE) (2210) ; DDE - NE PAS GARDER (DOUBLONS AZ) (866) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (686) ; À TRANSFERER (486) ; À SUPPRIMER (Tests) (412) ; À SUPPRIMER (FILE_TYPE) (118) ; S3_KEY À CONSTRUIRE (54) ; DOUBLON - À VOIR (38)</t>
+          <t>TRANSFERT_S3_OK (2098808) ; À SUPPRIMER (DIFFUSION) (131832) ; À TRANSFERER APRES VALIDATION (106195) ; INCONNU (29156) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (12654) ; À SUPPRIMER (DOUBLON) (7616) ; À SUPPRIMER (DOUBLON S3-AZ) (6179) ; À SUPPRIMER (DOUBLON AZ) (5914) ; EN LIGNE - À TRANSFERER ? (5020) ; À SUPPRIMER (FILE_TYPE) (2329) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (MED_PAR) (686) ; À SUPPRIMER (TESTS) (412) ; INCONNU FRAD59 (180) ; S3_KEY À CONSTRUIRE (54) ; DOUBLON - À VOIR (38) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
         </is>
       </c>
       <c r="M94" s="9" t="n">
-        <v>94.90000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="N94" s="7" t="n">
-        <v>990602</v>
+        <v>990685</v>
       </c>
       <c r="O94" s="7" t="n">
         <v>7347</v>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -593,47 +593,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMR_1AEFi</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Archives - Photographies numériques du service de l’urbanisme</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Documents figurés</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AEFi</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1AEFi</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_10FI</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>60</v>
+        <v>164</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.1</v>
+        <v>5.62</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>INCONNU (30) ; À SUPPRIMER (DIFFUSION) (30)</t>
+          <t>TRANSFERT_S3_OK (164)</t>
         </is>
       </c>
       <c r="M2" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>0</v>
@@ -645,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0</v>
@@ -660,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>0</v>
@@ -669,27 +644,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMR_1I</t>
+          <t>AMR_1AEFi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Archives - Police locale</t>
+          <t>Archives - Photographies numériques du service de l’urbanisme</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Documents figurés</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>AEFi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1I</t>
+          <t>1AEFi</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -698,18 +673,18 @@
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>0.1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>À SUPPRIMER (DIFFUSION) (50) ; INCONNU (47)</t>
+          <t>INCONNU (30) ; À SUPPRIMER (DIFFUSION) (30)</t>
         </is>
       </c>
       <c r="M3" s="5" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>0</v>
@@ -721,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>0</v>
@@ -745,27 +720,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMR_1NumFi</t>
+          <t>AMR_1I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Archives - Petits dons de numérisation de documents figurés</t>
+          <t>Archives - Police locale</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Documents figurés</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NumFi</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1NumFi</t>
+          <t>1I</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -774,18 +749,18 @@
         </is>
       </c>
       <c r="J4" s="3" t="n">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>INCONNU (6) ; À SUPPRIMER (DIFFUSION) (6)</t>
+          <t>À SUPPRIMER (DIFFUSION) (50) ; INCONNU (47)</t>
         </is>
       </c>
       <c r="M4" s="5" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
@@ -797,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
@@ -812,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>0</v>
@@ -821,27 +796,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMR_1PER3</t>
+          <t>AMR_1NumFi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Archives - Presse clandestine</t>
+          <t>Archives - Petits dons de numérisation de documents figurés</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Presse et ouvrages</t>
+          <t>Documents figurés</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>NumFi</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1PER3</t>
+          <t>1NumFi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -850,18 +825,18 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0.33</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>INCONNU (23)</t>
+          <t>INCONNU (6) ; À SUPPRIMER (DIFFUSION) (6)</t>
         </is>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>0</v>
@@ -873,10 +848,10 @@
         <v>0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>0</v>
@@ -888,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>0</v>
@@ -897,22 +872,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMR_2F</t>
+          <t>AMR_1PER3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Archives - Commerce et industrie</t>
+          <t>Archives - Presse clandestine</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Presse et ouvrages</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>1PER3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -921,14 +901,14 @@
         </is>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>INCONNU (1)</t>
+          <t>INCONNU (23)</t>
         </is>
       </c>
       <c r="M6" s="5" t="n">
@@ -944,10 +924,10 @@
         <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>0</v>
@@ -968,43 +948,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMR_2I</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Archives - Police générale</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2I</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_21J</t>
         </is>
       </c>
       <c r="J7" s="3" t="n">
-        <v>15703</v>
+        <v>285</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.08</v>
+        <v>2.63</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (15703)</t>
+          <t>TRANSFERT_S3_OK (285)</t>
         </is>
       </c>
       <c r="M7" s="5" t="n">
@@ -1020,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>15703</v>
+        <v>0</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>0</v>
@@ -1035,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>0</v>
@@ -1044,27 +999,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMR_308W</t>
+          <t>AMR_2F</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Archives - Permis de construire</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Archives contemporaines</t>
+          <t>Archives - Commerce et industrie</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>308W</t>
+          <t>2F</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1073,14 +1023,14 @@
         </is>
       </c>
       <c r="J8" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>INCONNU (7)</t>
+          <t>INCONNU (1)</t>
         </is>
       </c>
       <c r="M8" s="5" t="n">
@@ -1108,10 +1058,10 @@
         <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>0</v>
@@ -1120,27 +1070,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMR_381W</t>
+          <t>AMR_2I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Archives - Photographies issues des autorisations d’urbanisme et déclarations d’urbanisme</t>
+          <t>Archives - Police générale</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Archives contemporaines</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>381W</t>
+          <t>2I</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1149,18 +1099,18 @@
         </is>
       </c>
       <c r="J9" s="3" t="n">
-        <v>11</v>
+        <v>15703</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1</v>
+        <v>9.08</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>INCONNU (11)</t>
+          <t>TRANSFERT_S3_OK (15703)</t>
         </is>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0</v>
@@ -1172,7 +1122,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>15703</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0</v>
@@ -1187,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>0</v>
@@ -1196,27 +1146,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMR_3D</t>
+          <t>AMR_308W</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Archives - Administration de la commune</t>
+          <t>Archives - Permis de construire</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives contemporaines</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3D</t>
+          <t>308W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1225,18 +1175,18 @@
         </is>
       </c>
       <c r="J10" s="3" t="n">
-        <v>296</v>
+        <v>7</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>3.16</v>
+        <v>0.05</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (272) ; À SUPPRIMER (DIFFUSION) (24)</t>
+          <t>INCONNU (7)</t>
         </is>
       </c>
       <c r="M10" s="5" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0</v>
@@ -1248,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="n">
         <v>0</v>
@@ -1260,10 +1210,10 @@
         <v>0</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>0</v>
@@ -1272,47 +1222,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMR_3O</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Archives - Permis de construire</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3O</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_310W</t>
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>27</v>
+        <v>1136</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.71</v>
+        <v>10.79</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>INCONNU (27)</t>
+          <t>TRANSFERT_S3_OK (1136)</t>
         </is>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>0</v>
@@ -1336,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>20</v>
+        <v>1136</v>
       </c>
       <c r="W11" s="3" t="n">
         <v>0</v>
@@ -1348,27 +1273,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMR_3R</t>
+          <t>AMR_381W</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Archives - Sports</t>
+          <t>Archives - Photographies issues des autorisations d’urbanisme et déclarations d’urbanisme</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives contemporaines</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3R</t>
+          <t>381W</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1377,14 +1302,14 @@
         </is>
       </c>
       <c r="J12" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>INCONNU (14)</t>
+          <t>INCONNU (11)</t>
         </is>
       </c>
       <c r="M12" s="5" t="n">
@@ -1415,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="W12" s="3" t="n">
         <v>0</v>
@@ -1424,12 +1349,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMR_4H</t>
+          <t>AMR_3D</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Archives - Guerres</t>
+          <t>Archives - Administration de la commune</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1439,12 +1364,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4H</t>
+          <t>3D</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1453,18 +1378,18 @@
         </is>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5</v>
+        <v>270</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.12</v>
+        <v>1.32</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>INCONNU (5)</t>
+          <t>TRANSFERT_S3_OK (246) ; À SUPPRIMER (DIFFUSION) (24)</t>
         </is>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>0</v>
@@ -1476,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>0</v>
@@ -1491,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="W13" s="3" t="n">
         <v>0</v>
@@ -1500,47 +1425,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMR_4M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Archives - Edifices à usage d’enseignement</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>4M</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_3FI</t>
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1</v>
+        <v>4843</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.21</v>
+        <v>63.33</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>INCONNU (1)</t>
+          <t>TRANSFERT_S3_OK (4843)</t>
         </is>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>0</v>
@@ -1567,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>1</v>
+        <v>4843</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>0</v>
@@ -1576,27 +1476,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMR_507W</t>
+          <t>AMR_3O</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Archives - Vues aériennes provenant du service Aménagement</t>
+          <t>Archives - Permis de construire</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Archives contemporaines</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>507W</t>
+          <t>3O</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1605,14 +1505,14 @@
         </is>
       </c>
       <c r="J15" s="3" t="n">
-        <v>496</v>
+        <v>27</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>21.3</v>
+        <v>2.71</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (496)</t>
+          <t>INCONNU (27)</t>
         </is>
       </c>
       <c r="M15" s="5" t="n">
@@ -1640,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>496</v>
+        <v>20</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>0</v>
@@ -1652,22 +1552,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMR_5FI</t>
+          <t>AMR_3R</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Archives - photographies (format supérieur à 32 x 42 cm)</t>
+          <t>Archives - Sports</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5Fi</t>
+          <t>3R</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1676,14 +1581,14 @@
         </is>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>INCONNU (2)</t>
+          <t>INCONNU (14)</t>
         </is>
       </c>
       <c r="M16" s="5" t="n">
@@ -1714,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>0</v>
@@ -1723,47 +1628,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMR_5M</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Archives - Bâtiments communaux</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>5M</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_440W</t>
         </is>
       </c>
       <c r="J17" s="3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>INCONNU (3)</t>
+          <t>TRANSFERT_S3_OK (15)</t>
         </is>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>0</v>
@@ -1775,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="n">
         <v>0</v>
@@ -1790,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>0</v>
@@ -1799,43 +1679,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMR_6H</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Archives - Recensement de population sous l’occupation allemande de 1914-1918</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>6H</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_4FI</t>
         </is>
       </c>
       <c r="J18" s="3" t="n">
-        <v>76933</v>
+        <v>326</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>54.36</v>
+        <v>12.28</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (76933)</t>
+          <t>TRANSFERT_S3_OK (326)</t>
         </is>
       </c>
       <c r="M18" s="5" t="n">
@@ -1851,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>76933</v>
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>0</v>
@@ -1866,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>0</v>
@@ -1875,12 +1730,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMR_6M</t>
+          <t>AMR_4H</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Archives - Édifices communaux, monuments et établissements publics (compléments)</t>
+          <t>Archives - Guerres</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1890,12 +1745,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6M</t>
+          <t>4H</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1904,14 +1759,14 @@
         </is>
       </c>
       <c r="J19" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>INCONNU (10)</t>
+          <t>INCONNU (5)</t>
         </is>
       </c>
       <c r="M19" s="5" t="n">
@@ -1939,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>0</v>
@@ -1951,27 +1806,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMR_8C</t>
+          <t>AMR_4M</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Archives - Dossiers documentaires</t>
+          <t>Archives - Edifices à usage d’enseignement</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Presse et ouvrages</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>4M</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1980,14 +1835,14 @@
         </is>
       </c>
       <c r="J20" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>INCONNU (10)</t>
+          <t>INCONNU (1)</t>
         </is>
       </c>
       <c r="M20" s="5" t="n">
@@ -2018,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W20" s="3" t="n">
         <v>0</v>
@@ -2027,47 +1882,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMR_8J</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Archives - Petits fonds privés</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Archives privées</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>8J</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_500W</t>
         </is>
       </c>
       <c r="J21" s="3" t="n">
-        <v>145</v>
+        <v>1447</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.28</v>
+        <v>12.99</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>INCONNU (145)</t>
+          <t>TRANSFERT_S3_OK (1447)</t>
         </is>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>0</v>
@@ -2079,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>0</v>
@@ -2094,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>112</v>
+        <v>1447</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>0</v>
@@ -2103,55 +1933,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AMR_AFF</t>
+          <t>AMR_507W</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Archives - Affiches : la guerre 1914-1918 à Roubaix</t>
+          <t>Archives - Vues aériennes provenant du service Aménagement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives contemporaines</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4H</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_AFF </t>
+          <t>507W</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1935</v>
+        <v>496</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>165.13</v>
+        <v>21.3</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1074) ; INCONNU (552) ; À SUPPRIMER (DIFFUSION) (237) ; À SUPPRIMER (DOUBLON AZ) (48) ; À TRANSFERER APRES VALIDATION (24)</t>
+          <t>TRANSFERT_S3_OK (496)</t>
         </is>
       </c>
       <c r="M22" s="5" t="n">
-        <v>70.2</v>
+        <v>100</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1005</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>0</v>
@@ -2160,22 +1985,22 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>1161</v>
+        <v>496</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>0</v>
@@ -2184,47 +2009,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMR_ALI</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Archives - Plans d’alignement</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8O</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>non</t>
+          <t>AMR_512W</t>
         </is>
       </c>
       <c r="J23" s="3" t="n">
-        <v>604</v>
+        <v>857</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>83.84999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>INCONNU (604)</t>
+          <t>TRANSFERT_S3_OK (857)</t>
         </is>
       </c>
       <c r="M23" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>0</v>
@@ -2236,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="n">
         <v>0</v>
@@ -2251,7 +2051,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>302</v>
+        <v>857</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>0</v>
@@ -2260,17 +2060,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMR_AVI</t>
+          <t>AMR_5FI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Archives - Documents vidéos</t>
+          <t>Archives - photographies (format supérieur à 32 x 42 cm)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>5Fi</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2279,18 +2084,18 @@
         </is>
       </c>
       <c r="J24" s="3" t="n">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>255.07</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (159)</t>
+          <t>TRANSFERT_S3_OK (63) ; INCONNU (2)</t>
         </is>
       </c>
       <c r="M24" s="5" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>0</v>
@@ -2317,31 +2122,41 @@
         <v>0</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMR_BAR</t>
+          <t>AMR_5H</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Archives - Parc Barbieux</t>
+          <t>Archives - Roubaisiens victimes des guerres</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>5H</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_VIC </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2350,18 +2165,18 @@
         </is>
       </c>
       <c r="J25" s="3" t="n">
-        <v>92</v>
+        <v>7072</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.9</v>
+        <v>12.12</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>INCONNU (48) ; À SUPPRIMER (DIFFUSION) (44)</t>
+          <t>TRANSFERT_S3_OK (7072)</t>
         </is>
       </c>
       <c r="M25" s="5" t="n">
-        <v>47.8</v>
+        <v>100</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>0</v>
@@ -2373,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>88</v>
+        <v>7072</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>0</v>
@@ -2388,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>0</v>
@@ -2397,12 +2212,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMR_CAD</t>
+          <t>AMR_5M</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Archives - Plans cadastraux</t>
+          <t>Archives - Bâtiments communaux</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2412,64 +2227,59 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1G</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_CAD </t>
+          <t>5M</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>515</v>
+        <v>3</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>26.3</v>
+        <v>0.27</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (296) ; INCONNU FRAD59 (180) ; À SUPPRIMER (DIFFUSION) (29) ; À SUPPRIMER (DOUBLON) (9) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>INCONNU (3)</t>
         </is>
       </c>
       <c r="M26" s="5" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>433</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>52</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>0</v>
@@ -2478,12 +2288,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AMR_CIM</t>
+          <t>AMR_6H</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Archives - Cimetière</t>
+          <t>Archives - Recensement de population sous l’occupation allemande de 1914-1918</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2493,12 +2303,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>6H</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2507,18 +2317,18 @@
         </is>
       </c>
       <c r="J27" s="3" t="n">
-        <v>18982</v>
+        <v>76933</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>315.8</v>
+        <v>54.36</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (DOUBLON S3-AZ) (2739) ; INCONNU (173)</t>
+          <t>TRANSFERT_S3_OK (76933)</t>
         </is>
       </c>
       <c r="M27" s="5" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>0</v>
@@ -2530,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0</v>
+        <v>76933</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>0</v>
@@ -2545,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>18982</v>
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="n">
         <v>0</v>
@@ -2554,12 +2364,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMR_CLL</t>
+          <t>AMR_6M</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Archives - Comité local de libération</t>
+          <t>Archives - Édifices communaux, monuments et établissements publics (compléments)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2569,12 +2379,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>M</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4H</t>
+          <t>6M</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2583,18 +2393,18 @@
         </is>
       </c>
       <c r="J28" s="3" t="n">
-        <v>358</v>
+        <v>10</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6.8</v>
+        <v>0.19</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>À SUPPRIMER (DIFFUSION) (264) ; INCONNU (94)</t>
+          <t>INCONNU (10)</t>
         </is>
       </c>
       <c r="M28" s="5" t="n">
-        <v>73.7</v>
+        <v>0</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
@@ -2606,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2615,13 +2425,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>0</v>
@@ -2630,84 +2440,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMR_DEL</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Archives - Registres de délibérations</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1D</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_DEL </t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>oui</t>
+          <t>AMR_7J</t>
         </is>
       </c>
       <c r="J29" s="3" t="n">
-        <v>170130</v>
+        <v>4</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2425.75</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (122101) ; À TRANSFERER APRES VALIDATION (47632) ; À SUPPRIMER (DOUBLON S3-AZ) (396) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (4)</t>
         </is>
       </c>
       <c r="M29" s="5" t="n">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>122098</v>
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>23676</v>
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>78807</v>
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>67366</v>
+        <v>4</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>0</v>
@@ -2716,27 +2491,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMR_DIA</t>
+          <t>AMR_8C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Archives - Diapositives</t>
+          <t>Archives - Dossiers documentaires</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Documents figurés</t>
+          <t>Presse et ouvrages</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9Fi</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2745,18 +2520,18 @@
         </is>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1761</v>
+        <v>10</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>44.68</v>
+        <v>0.38</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (879) ; À SUPPRIMER (DIFFUSION) (879) ; À SUPPRIMER (DOUBLON) (3)</t>
+          <t>INCONNU (10)</t>
         </is>
       </c>
       <c r="M30" s="5" t="n">
-        <v>50.1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>0</v>
@@ -2768,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>879</v>
+        <v>0</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>0</v>
@@ -2783,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>882</v>
+        <v>10</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>0</v>
@@ -2792,27 +2567,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMR_EC</t>
+          <t>AMR_8J</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Archives -  État civil</t>
+          <t>Archives - Petits fonds privés</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>8J</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2821,18 +2596,18 @@
         </is>
       </c>
       <c r="J31" s="3" t="n">
-        <v>357990</v>
+        <v>243</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>759.84</v>
+        <v>6.37</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (260628) ; À SUPPRIMER (DIFFUSION) (85333) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (11972) ; S3_KEY À CONSTRUIRE (54) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>INCONNU (145) ; TRANSFERT_S3_OK (98)</t>
         </is>
       </c>
       <c r="M31" s="5" t="n">
-        <v>100</v>
+        <v>40.3</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0</v>
@@ -2841,16 +2616,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>357961</v>
+        <v>33</v>
       </c>
       <c r="R31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>0</v>
@@ -2859,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="W31" s="3" t="n">
         <v>0</v>
@@ -2868,22 +2643,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMR_GDL</t>
+          <t>AMR_9FI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Archives - Goutte de lait</t>
+          <t>Archives - Diapositives</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>Fi</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>9Fi</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2892,18 +2672,18 @@
         </is>
       </c>
       <c r="J32" s="3" t="n">
-        <v>32</v>
+        <v>879</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.97</v>
+        <v>44.23</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>À SUPPRIMER (DIFFUSION) (16) ; INCONNU (16)</t>
+          <t>TRANSFERT_S3_OK (879)</t>
         </is>
       </c>
       <c r="M32" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0</v>
@@ -2915,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>0</v>
@@ -2930,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>0</v>
@@ -2939,12 +2719,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AMR_GUE</t>
+          <t>AMR_AFF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Archives - La guerre 1939-1945 à Roubaix</t>
+          <t>Archives - Affiches : la guerre 1914-1918 à Roubaix</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2959,12 +2739,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7H</t>
+          <t>4H</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_GUE </t>
+          <t xml:space="preserve">RBX_AMR_AFF </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2973,21 +2753,21 @@
         </is>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2391</v>
+        <v>1935</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>55.94</v>
+        <v>165.13</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (682) ; EN LIGNE - À TRANSFERER ? (682) ; À SUPPRIMER (DIFFUSION) (665) ; TRANSFERT_S3_OK (340) ; À SUPPRIMER (DOUBLON AZ) (17) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
+          <t>TRANSFERT_S3_OK (1074) ; INCONNU (552) ; À SUPPRIMER (DIFFUSION) (237) ; À SUPPRIMER (DOUBLON AZ) (48) ; À TRANSFERER (24)</t>
         </is>
       </c>
       <c r="M33" s="5" t="n">
-        <v>71.3</v>
+        <v>70.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>682</v>
+        <v>1005</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>0</v>
@@ -2996,22 +2776,22 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>682</v>
+        <v>300</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>341</v>
+        <v>24</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>682</v>
+        <v>237</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>341</v>
+        <v>213</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>345</v>
+        <v>1161</v>
       </c>
       <c r="W33" s="3" t="n">
         <v>0</v>
@@ -3020,32 +2800,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMR_LEB</t>
+          <t>AMR_ALI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Archives - Collection de la famille Lebas - Hennion</t>
+          <t>Archives - Plans d’alignement</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Archives privées</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11J</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_LEB </t>
+          <t>8O</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3054,18 +2829,18 @@
         </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>174</v>
+        <v>604</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1.38</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>INCONNU (89) ; À SUPPRIMER (DIFFUSION) (85)</t>
+          <t>INCONNU (604)</t>
         </is>
       </c>
       <c r="M34" s="5" t="n">
-        <v>48.9</v>
+        <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
@@ -3077,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>85</v>
+        <v>302</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
@@ -3092,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>89</v>
+        <v>302</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>0</v>
@@ -3101,27 +2876,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMR_O</t>
+          <t>AMR_AVI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Archives - Permis de construire</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>Archives - Documents vidéos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3O</t>
+          <t>?</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3130,18 +2895,18 @@
         </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>31</v>
+        <v>159</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.39</v>
+        <v>255.07</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>INCONNU (25) ; À SUPPRIMER (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (159)</t>
         </is>
       </c>
       <c r="M35" s="5" t="n">
-        <v>19.4</v>
+        <v>100</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>0</v>
@@ -3150,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>0</v>
@@ -3168,64 +2933,54 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMR_OBJ</t>
+          <t>AMR_BAR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Archives -  Médailles et petits objets</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Objets</t>
+          <t>Archives - Parc Barbieux</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Obj</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1Obj</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_OBJ </t>
+          <t>collection</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J36" s="3" t="n">
-        <v>208</v>
+        <v>92</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0.92</v>
+        <v>2.9</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (DOUBLON S3-AZ) (100) ; INCONNU (8)</t>
+          <t>INCONNU (48) ; À SUPPRIMER (DIFFUSION) (44)</t>
         </is>
       </c>
       <c r="M36" s="5" t="n">
-        <v>96.2</v>
+        <v>47.8</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
@@ -3234,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0</v>
@@ -3249,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>208</v>
+        <v>4</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>0</v>
@@ -3258,59 +3013,64 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMR_PAR</t>
+          <t>AMR_CAD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Archives - Particuliers</t>
+          <t>Archives - Plans cadastraux</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Archives privées</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>J ?</t>
+          <t>1G</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_CAD </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J37" s="3" t="n">
-        <v>6894</v>
+        <v>515</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>9.25</v>
+        <v>26.3</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>À SUPPRIMER (DIFFUSION) (6421) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (DOUBLON S3-AZ) (228)</t>
+          <t>TRANSFERT_S3_OK (296) ; INCONNU FRAD59 (180) ; À SUPPRIMER (DIFFUSION) (29) ; À SUPPRIMER (DOUBLON) (9) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M37" s="5" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>6661</v>
+        <v>433</v>
       </c>
       <c r="R37" s="3" t="n">
         <v>0</v>
@@ -3322,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>233</v>
+        <v>52</v>
       </c>
       <c r="W37" s="3" t="n">
         <v>0</v>
@@ -3334,22 +3094,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMR_PDS</t>
+          <t>AMR_CIM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Archives - Parc des sports</t>
+          <t>Archives - Cimetière</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3358,18 +3123,18 @@
         </is>
       </c>
       <c r="J38" s="3" t="n">
-        <v>68</v>
+        <v>18982</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>3.87</v>
+        <v>315.8</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>INCONNU (34) ; À SUPPRIMER (DIFFUSION) (34)</t>
+          <t>TRANSFERT_S3_OK (16070) ; À SUPPRIMER (DOUBLON S3-AZ) (2739) ; INCONNU (173)</t>
         </is>
       </c>
       <c r="M38" s="5" t="n">
-        <v>50</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>0</v>
@@ -3381,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>0</v>
@@ -3396,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>0</v>
+        <v>18982</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>0</v>
@@ -3405,59 +3170,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMR_PHO</t>
+          <t>AMR_CLL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Archives - Photographies du service Communication de la Ville</t>
+          <t>Archives - Comité local de libération</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>collection</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_PHO </t>
+          <t>4H</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J39" s="3" t="n">
-        <v>18596</v>
+        <v>358</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>135.99</v>
+        <v>6.8</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (9238) ; À SUPPRIMER (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (DOUBLON) (55) ; À SUPPRIMER (FILE_TYPE) (2) ; INCONNU (1)</t>
+          <t>À SUPPRIMER (DIFFUSION) (264) ; INCONNU (94)</t>
         </is>
       </c>
       <c r="M39" s="5" t="n">
-        <v>50.3</v>
+        <v>73.7</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>1194</v>
+        <v>0</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>8035</v>
+        <v>264</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>0</v>
@@ -3466,13 +3231,13 @@
         <v>0</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>10559</v>
+        <v>88</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>0</v>
@@ -3481,27 +3246,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMR_PLA</t>
+          <t>AMR_DEL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Archives - Collection des cartes et plans des Archives</t>
+          <t>Archives - Registres de délibérations</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>collection</t>
+          <t>1D</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_AMR_PLA </t>
+          <t xml:space="preserve">RBX_AMR_DEL </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3510,45 +3285,45 @@
         </is>
       </c>
       <c r="J40" s="3" t="n">
-        <v>376</v>
+        <v>170130</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>48.9</v>
+        <v>2425.75</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (239) ; À SUPPRIMER (DOUBLON AZ) (119) ; À SUPPRIMER (DIFFUSION) (12) ; À TRANSFERER APRES VALIDATION (5) ; À SUPPRIMER (DOUBLON S3-AZ) (1)</t>
+          <t>TRANSFERT_S3_OK (165051) ; À CHERCHER (4682) ; À SUPPRIMER (DOUBLON S3-AZ) (396) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M40" s="5" t="n">
-        <v>98.7</v>
+        <v>97.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>244</v>
+        <v>122098</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>250</v>
+        <v>23676</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
+        <v>78807</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>126</v>
+        <v>67366</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>0</v>
@@ -3557,50 +3332,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMR_POP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Archives - Recensements de population</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Archives modernes</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>oui</t>
+          <t>AMR_DIA</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
-        <v>121938</v>
+        <v>882</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>504.08</v>
+        <v>0.45</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (85449) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À TRANSFERER APRES VALIDATION (8127) ; À SUPPRIMER (DIFFUSION) (8086)</t>
+          <t>À SUPPRIMER (DIFFUSION) (879) ; À SUPPRIMER (DOUBLON) (3)</t>
         </is>
       </c>
       <c r="M41" s="5" t="n">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>65107</v>
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="n">
         <v>0</v>
@@ -3609,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>113798</v>
+        <v>879</v>
       </c>
       <c r="R41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>8135</v>
+        <v>3</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>0</v>
@@ -3633,74 +3383,74 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AMR_PR</t>
+          <t>AMR_EC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Archives - Pièces remarquables des Archives municipales</t>
+          <t>Archives -  État civil</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>_collection</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>collection</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_PR </t>
+          <t>E</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J42" s="3" t="n">
-        <v>4326</v>
+        <v>357990</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>166.36</v>
+        <v>759.84</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (4199) ; À SUPPRIMER (DIFFUSION) (110) ; INCONNU (15) ; À SUPPRIMER (DOUBLON S3-AZ) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (260628) ; À SUPPRIMER (DIFFUSION) (85333) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (11972) ; S3_KEY À CONSTRUIRE (54) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M42" s="5" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>668</v>
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>786</v>
+        <v>357961</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>3533</v>
+        <v>0</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>0</v>
@@ -3709,32 +3459,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AMR_PUV</t>
+          <t>AMR_GDL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Archives - Bulletin municipal d'information</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Presse et ouvrages</t>
+          <t>Archives - Goutte de lait</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>_collection</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>58-59PER</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_PUV </t>
+          <t>collection</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3743,18 +3483,18 @@
         </is>
       </c>
       <c r="J43" s="3" t="n">
-        <v>19189</v>
+        <v>32</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>338.53</v>
+        <v>0.97</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (9733) ; À SUPPRIMER (DOUBLON) (6302) ; À SUPPRIMER (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
+          <t>À SUPPRIMER (DIFFUSION) (16) ; INCONNU (16)</t>
         </is>
       </c>
       <c r="M43" s="5" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>0</v>
@@ -3763,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>6302</v>
+        <v>32</v>
       </c>
       <c r="R43" s="3" t="n">
         <v>0</v>
@@ -3775,13 +3515,13 @@
         <v>0</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>6302</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>6302</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>0</v>
@@ -3790,50 +3530,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AMR_PV</t>
+          <t>AMR_GUE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Archives - Plaques de verre</t>
+          <t>Archives - La guerre 1939-1945 à Roubaix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Documents figurés</t>
+          <t>Archives modernes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fi</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8Fi</t>
+          <t>7H</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_GUE </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>4</v>
+        <v>2391</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.03</v>
+        <v>55.94</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>INCONNU (4)</t>
+          <t>À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (682) ; EN LIGNE - À TRANSFERER ? (682) ; À SUPPRIMER (DIFFUSION) (665) ; TRANSFERT_S3_OK (340) ; À SUPPRIMER (DOUBLON AZ) (17) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
         </is>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0</v>
+        <v>71.3</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>0</v>
+        <v>682</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>0</v>
@@ -3842,22 +3587,22 @@
         <v>0</v>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>2</v>
+        <v>682</v>
       </c>
       <c r="R44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>0</v>
+        <v>682</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>2</v>
+        <v>345</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>0</v>
@@ -3866,27 +3611,32 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMR_PVC</t>
+          <t>AMR_LEB</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Archives - Procès verbaux du conseil municipal</t>
+          <t>Archives - Collection de la famille Lebas - Hennion</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Archives contemporaines</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>246W</t>
+          <t>11J</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_LEB </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3895,18 +3645,18 @@
         </is>
       </c>
       <c r="J45" s="3" t="n">
-        <v>19170</v>
+        <v>174</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>42.81</v>
+        <v>1.38</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (19170)</t>
+          <t>INCONNU (89) ; À SUPPRIMER (DIFFUSION) (85)</t>
         </is>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0</v>
+        <v>48.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>0</v>
@@ -3918,22 +3668,22 @@
         <v>0</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>9444</v>
+        <v>85</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>9444</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>0</v>
@@ -3942,12 +3692,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AMR_RAM</t>
+          <t>AMR_O</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Archives - Rapports du maire</t>
+          <t>Archives - Permis de construire</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3957,54 +3707,44 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3D</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_RAM </t>
+          <t>3O</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J46" s="3" t="n">
-        <v>36817</v>
+        <v>31</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>445.32</v>
+        <v>1.39</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (36817)</t>
+          <t>INCONNU (25) ; À SUPPRIMER (DIFFUSION) (5) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M46" s="5" t="n">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>36817</v>
+        <v>0</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>0</v>
@@ -4013,13 +3753,13 @@
         <v>0</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>18409</v>
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>18408</v>
+        <v>25</v>
       </c>
       <c r="W46" s="3" t="n">
         <v>0</v>
@@ -4028,40 +3768,55 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AMR_ROU</t>
+          <t>AMR_OBJ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Archives - Archives privées Roussel</t>
+          <t>Archives -  Médailles et petits objets</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Objets</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Obj</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1Obj</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_AMR_OBJ </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J47" s="3" t="n">
-        <v>449</v>
+        <v>208</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>5.17</v>
+        <v>0.92</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>INCONNU (257) ; À SUPPRIMER (DIFFUSION) (192)</t>
+          <t>TRANSFERT_S3_OK (100) ; À SUPPRIMER (DOUBLON S3-AZ) (100) ; INCONNU (8)</t>
         </is>
       </c>
       <c r="M47" s="5" t="n">
-        <v>42.8</v>
+        <v>96.2</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="O47" s="3" t="n">
         <v>0</v>
@@ -4070,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="n">
         <v>0</v>
@@ -4085,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="3" t="n">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="W47" s="3" t="n">
         <v>0</v>
@@ -4094,32 +3849,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AMR_VIC</t>
+          <t>AMR_PAR</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Archives - Roubaisiens victimes des guerres</t>
+          <t>Archives - Particuliers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Archives modernes</t>
+          <t>Archives privées</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5H</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_AMR_VIC </t>
+          <t>J ?</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4128,18 +3878,18 @@
         </is>
       </c>
       <c r="J48" s="3" t="n">
-        <v>7072</v>
+        <v>6894</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>12.12</v>
+        <v>9.25</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (7072)</t>
+          <t>À SUPPRIMER (DIFFUSION) (6421) ; TRANSFERT_S3_OK (245) ; À SUPPRIMER (DOUBLON S3-AZ) (228)</t>
         </is>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0</v>
@@ -4151,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>7072</v>
+        <v>6661</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -4166,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="W48" s="3" t="n">
         <v>0</v>
@@ -4175,49 +3925,54 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ARA_CPS</t>
+          <t>AMR_PDS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ARA - Cartes postales sonores de l'ARA</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_ARA_CPS </t>
+          <t>Archives - Parc des sports</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>_collection</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>collection</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1.26</v>
+        <v>3.87</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (174)</t>
+          <t>INCONNU (34) ; À SUPPRIMER (DIFFUSION) (34)</t>
         </is>
       </c>
       <c r="M49" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="R49" s="3" t="n">
         <v>0</v>
@@ -4241,17 +3996,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CSV_PAL</t>
+          <t>AMR_PHO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Conservatoire - Palmarès annuels</t>
+          <t>Archives - Photographies du service Communication de la Ville</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>_collection</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>collection</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_CSV_PAL </t>
+          <t xml:space="preserve">RBX_AMR_PHO </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -4260,30 +4025,30 @@
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>242</v>
+        <v>9358</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>6.65</v>
+        <v>11.37</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (242)</t>
+          <t>À SUPPRIMER (DIFFUSION) (8034) ; TRANSFERT_S3_OK (1266) ; À SUPPRIMER (DOUBLON) (55) ; À SUPPRIMER (FILE_TYPE) (2) ; INCONNU (1)</t>
         </is>
       </c>
       <c r="M50" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>242</v>
+        <v>1194</v>
       </c>
       <c r="O50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>0</v>
+        <v>8035</v>
       </c>
       <c r="R50" s="3" t="n">
         <v>0</v>
@@ -4298,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="3" t="n">
-        <v>242</v>
+        <v>1321</v>
       </c>
       <c r="W50" s="3" t="n">
         <v>0</v>
@@ -4307,17 +4072,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LAI</t>
+          <t>AMR_PLA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Association des Amis de la Lainière et du Textile - Collection</t>
+          <t>Archives - Collection des cartes et plans des Archives</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>_collection</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>collection</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_LAI </t>
+          <t xml:space="preserve">RBX_AMR_PLA </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4326,21 +4101,21 @@
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>2386</v>
+        <v>376</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>60.87</v>
+        <v>48.9</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1661) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
+          <t>TRANSFERT_S3_OK (239) ; À SUPPRIMER (DOUBLON AZ) (119) ; À SUPPRIMER (DIFFUSION) (12) ; À TRANSFERER (5) ; À SUPPRIMER (DOUBLON S3-AZ) (1)</t>
         </is>
       </c>
       <c r="M51" s="5" t="n">
-        <v>89.8</v>
+        <v>98.7</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>1145</v>
+        <v>244</v>
       </c>
       <c r="O51" s="3" t="n">
         <v>0</v>
@@ -4349,13 +4124,13 @@
         <v>0</v>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="R51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S51" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>0</v>
@@ -4364,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="3" t="n">
-        <v>2385</v>
+        <v>126</v>
       </c>
       <c r="W51" s="3" t="n">
         <v>0</v>
@@ -4373,17 +4148,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LAR_PUB</t>
+          <t>AMR_POP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lire à Roubaix - Publications</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_LAR_PUB </t>
+          <t>Archives - Recensements de population</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1F</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4392,21 +4177,21 @@
         </is>
       </c>
       <c r="J52" s="3" t="n">
-        <v>3811</v>
+        <v>121938</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>18.33</v>
+        <v>504.08</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (3731) ; À SUPPRIMER (DOUBLON) (80)</t>
+          <t>TRANSFERT_S3_OK (85449) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À TRANSFERER (8127) ; À SUPPRIMER (DIFFUSION) (8086)</t>
         </is>
       </c>
       <c r="M52" s="5" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3731</v>
+        <v>65107</v>
       </c>
       <c r="O52" s="3" t="n">
         <v>0</v>
@@ -4415,22 +4200,22 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>0</v>
+        <v>113798</v>
       </c>
       <c r="R52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S52" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="3" t="n">
-        <v>3811</v>
+        <v>8135</v>
       </c>
       <c r="W52" s="3" t="n">
         <v>0</v>
@@ -4439,17 +4224,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MDF_MTX</t>
+          <t>AMR_PR</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Manufacture des Flandres - Collectes de la mémoire des travailleurs du textile</t>
+          <t>Archives - Pièces remarquables des Archives municipales</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>_collection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>collection</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MDF_MTX </t>
+          <t xml:space="preserve">RBX_AMR_PR </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -4458,30 +4253,30 @@
         </is>
       </c>
       <c r="J53" s="3" t="n">
-        <v>18</v>
+        <v>4326</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>76.03</v>
+        <v>166.36</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (18)</t>
+          <t>TRANSFERT_S3_OK (4199) ; À SUPPRIMER (DIFFUSION) (110) ; INCONNU (15) ; À SUPPRIMER (DOUBLON S3-AZ) (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M53" s="5" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>17</v>
+        <v>668</v>
       </c>
       <c r="O53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P53" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>0</v>
+        <v>786</v>
       </c>
       <c r="R53" s="3" t="n">
         <v>0</v>
@@ -4490,64 +4285,79 @@
         <v>0</v>
       </c>
       <c r="T53" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V53" s="3" t="n">
-        <v>0</v>
+        <v>3533</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MED_AFF</t>
+          <t>AMR_PUV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Médiathèque - Affiches de la Médiathèque</t>
+          <t>Archives - Bulletin municipal d'information</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Presse et ouvrages</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>58-59PER</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_AFF </t>
+          <t xml:space="preserve">RBX_AMR_PUV </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J54" s="3" t="n">
-        <v>11038</v>
+        <v>19189</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>529.5599999999999</v>
+        <v>338.53</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>À SUPPRIMER (DIFFUSION) (5176) ; TRANSFERT_S3_OK (4222) ; À SUPPRIMER (DOUBLON AZ) (1606) ; DOUBLON - À VOIR (32) ; INCONNU (2)</t>
+          <t>TRANSFERT_S3_OK (9733) ; À SUPPRIMER (DOUBLON) (6302) ; À SUPPRIMER (DIFFUSION) (3151) ; À SUPPRIMER (FILE_TYPE) (3)</t>
         </is>
       </c>
       <c r="M54" s="5" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="N54" s="3" t="n">
-        <v>4147</v>
+        <v>0</v>
       </c>
       <c r="O54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P54" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>5176</v>
+        <v>6302</v>
       </c>
       <c r="R54" s="3" t="n">
         <v>0</v>
@@ -4556,13 +4366,13 @@
         <v>0</v>
       </c>
       <c r="T54" s="3" t="n">
-        <v>0</v>
+        <v>6302</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="V54" s="3" t="n">
-        <v>5862</v>
+        <v>6302</v>
       </c>
       <c r="W54" s="3" t="n">
         <v>0</v>
@@ -4571,12 +4381,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MED_AVI</t>
+          <t>AMR_PV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Médiathèque - Vidéos</t>
+          <t>Archives - Plaques de verre</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Fi</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8Fi</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4585,18 +4410,18 @@
         </is>
       </c>
       <c r="J55" s="3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>48.21</v>
+        <v>0.03</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (31) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>INCONNU (4)</t>
         </is>
       </c>
       <c r="M55" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>0</v>
@@ -4605,11 +4430,11 @@
         <v>0</v>
       </c>
       <c r="P55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" s="3" t="n">
         <v>0</v>
       </c>
@@ -4623,49 +4448,59 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MED_CHA</t>
+          <t>AMR_PVC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Médiathèque - Chansons de la Médiathèque de Roubaix</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_CHA </t>
+          <t>Archives - Procès verbaux du conseil municipal</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Archives contemporaines</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>246W</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J56" s="3" t="n">
-        <v>723</v>
+        <v>19170</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>17.58</v>
+        <v>42.81</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
+          <t>TRANSFERT_S3_OK (19170)</t>
         </is>
       </c>
       <c r="M56" s="5" t="n">
-        <v>50.2</v>
+        <v>100</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="O56" s="3" t="n">
         <v>0</v>
@@ -4674,22 +4509,22 @@
         <v>0</v>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>0</v>
+        <v>9444</v>
       </c>
       <c r="R56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S56" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="T56" s="3" t="n">
-        <v>0</v>
+        <v>9444</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="V56" s="3" t="n">
-        <v>723</v>
+        <v>0</v>
       </c>
       <c r="W56" s="3" t="n">
         <v>0</v>
@@ -4698,17 +4533,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MED_CP</t>
+          <t>AMR_RAM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Médiathèque - Cartes postales de Roubaix</t>
+          <t>Archives - Rapports du maire</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Archives modernes</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_CP </t>
+          <t xml:space="preserve">RBX_AMR_RAM </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4717,21 +4572,21 @@
         </is>
       </c>
       <c r="J57" s="3" t="n">
-        <v>5999</v>
+        <v>36843</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>34.82</v>
+        <v>447.16</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (5318) ; À SUPPRIMER (DOUBLON S3-AZ) (535) ; À SUPPRIMER (DIFFUSION) (106) ; INCONNU (39) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (36843)</t>
         </is>
       </c>
       <c r="M57" s="5" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>4663</v>
+        <v>36817</v>
       </c>
       <c r="O57" s="3" t="n">
         <v>0</v>
@@ -4740,22 +4595,22 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>307</v>
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S57" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="n">
-        <v>0</v>
+        <v>18409</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="V57" s="3" t="n">
-        <v>5691</v>
+        <v>18408</v>
       </c>
       <c r="W57" s="3" t="n">
         <v>0</v>
@@ -4764,17 +4619,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MED_DIL</t>
+          <t>AMR_ROU</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Médiathèque - Fonds d'archives d'André Diligent</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_DIL </t>
+          <t>Archives - Archives privées Roussel</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4783,18 +4638,18 @@
         </is>
       </c>
       <c r="J58" s="3" t="n">
-        <v>365</v>
+        <v>449</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>480.6</v>
+        <v>5.17</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
+          <t>INCONNU (257) ; À SUPPRIMER (DIFFUSION) (192)</t>
         </is>
       </c>
       <c r="M58" s="5" t="n">
-        <v>12.1</v>
+        <v>42.8</v>
       </c>
       <c r="N58" s="3" t="n">
         <v>0</v>
@@ -4803,10 +4658,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="R58" s="3" t="n">
         <v>0</v>
@@ -4821,26 +4676,26 @@
         <v>0</v>
       </c>
       <c r="V58" s="3" t="n">
-        <v>45</v>
+        <v>257</v>
       </c>
       <c r="W58" s="3" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MED_EPH</t>
+          <t>ARA_CPS</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Médiathèque - Ephémères de la Médiathèque</t>
+          <t>ARA - Cartes postales sonores de l'ARA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_EPH </t>
+          <t xml:space="preserve">RBX_ARA_CPS </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4849,30 +4704,30 @@
         </is>
       </c>
       <c r="J59" s="3" t="n">
-        <v>846</v>
+        <v>174</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>10.17</v>
+        <v>1.26</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (846)</t>
+          <t>TRANSFERT_S3_OK (174)</t>
         </is>
       </c>
       <c r="M59" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>840</v>
+        <v>174</v>
       </c>
       <c r="O59" s="3" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="R59" s="3" t="n">
         <v>0</v>
@@ -4887,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="3" t="n">
-        <v>846</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3" t="n">
         <v>0</v>
@@ -4896,35 +4751,40 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MED_FAN</t>
+          <t>CSV_PAL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Médiathèque - Cartes postales fantaisie</t>
+          <t>Conservatoire - Palmarès annuels</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_CSV_PAL </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J60" s="3" t="n">
-        <v>2666</v>
+        <v>242</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>32.93</v>
+        <v>6.65</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>INCONNU (2666)</t>
+          <t>TRANSFERT_S3_OK (242)</t>
         </is>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="O60" s="3" t="n">
         <v>0</v>
@@ -4948,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="3" t="n">
-        <v>2666</v>
+        <v>242</v>
       </c>
       <c r="W60" s="3" t="n">
         <v>0</v>
@@ -4957,17 +4817,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MED_FLR</t>
+          <t>LAI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents sonores régionaux</t>
+          <t>Association des Amis de la Lainière et du Textile - Collection</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_FLR </t>
+          <t xml:space="preserve">RBX_LAI </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4976,36 +4836,36 @@
         </is>
       </c>
       <c r="J61" s="3" t="n">
-        <v>8487</v>
+        <v>2386</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>304.96</v>
+        <v>60.87</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (8487)</t>
+          <t>TRANSFERT_S3_OK (1661) ; À SUPPRIMER (RENOMMAGE) (482) ; INCONNU (243)</t>
         </is>
       </c>
       <c r="M61" s="5" t="n">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>3585</v>
+        <v>1145</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>7228</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>478</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S61" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>0</v>
@@ -5014,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3" t="n">
-        <v>781</v>
+        <v>2385</v>
       </c>
       <c r="W61" s="3" t="n">
         <v>0</v>
@@ -5023,17 +4883,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MED_FOO</t>
+          <t>LAR_PUB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Médiathèque - Souvenirs de foot</t>
+          <t>Lire à Roubaix - Publications</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_FOO </t>
+          <t xml:space="preserve">RBX_LAR_PUB </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5042,30 +4902,30 @@
         </is>
       </c>
       <c r="J62" s="3" t="n">
-        <v>41</v>
+        <v>3811</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.66</v>
+        <v>18.33</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>INCONNU (30) ; TRANSFERT_S3_OK (6) ; À SUPPRIMER (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
+          <t>TRANSFERT_S3_OK (3731) ; À SUPPRIMER (DOUBLON) (80)</t>
         </is>
       </c>
       <c r="M62" s="5" t="n">
-        <v>26.8</v>
+        <v>100</v>
       </c>
       <c r="N62" s="3" t="n">
-        <v>6</v>
+        <v>3731</v>
       </c>
       <c r="O62" s="3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="n">
         <v>0</v>
@@ -5080,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3" t="n">
-        <v>0</v>
+        <v>3811</v>
       </c>
       <c r="W62" s="3" t="n">
         <v>0</v>
@@ -5089,17 +4949,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MED_IMA</t>
+          <t>MDF_MTX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Médiathèque - Imagettes de la Médiathèque</t>
+          <t>Manufacture des Flandres - Collectes de la mémoire des travailleurs du textile</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_IMA </t>
+          <t xml:space="preserve">RBX_MDF_MTX </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5108,21 +4968,21 @@
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>9852</v>
+        <v>18</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>131.45</v>
+        <v>76.03</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (5821) ; À SUPPRIMER (DOUBLON AZ) (3846) ; À SUPPRIMER (DOUBLON S3-AZ) (113) ; À SUPPRIMER (DIFFUSION) (45) ; À SUPPRIMER (DOUBLON) (21) ; DOUBLON - À VOIR (6)</t>
+          <t>TRANSFERT_S3_OK (18)</t>
         </is>
       </c>
       <c r="M63" s="5" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>5773</v>
+        <v>17</v>
       </c>
       <c r="O63" s="3" t="n">
         <v>0</v>
@@ -5131,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="3" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="R63" s="3" t="n">
         <v>0</v>
@@ -5146,44 +5006,49 @@
         <v>0</v>
       </c>
       <c r="V63" s="3" t="n">
-        <v>9627</v>
+        <v>0</v>
       </c>
       <c r="W63" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MED_JOU</t>
+          <t>MED_AFF</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Médiathèque - Journaux</t>
+          <t>Médiathèque - Affiches de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_AFF </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J64" s="3" t="n">
-        <v>2174</v>
+        <v>11038</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>67.51000000000001</v>
+        <v>529.5599999999999</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
+          <t>À SUPPRIMER (DIFFUSION) (5176) ; TRANSFERT_S3_OK (4222) ; À SUPPRIMER (DOUBLON AZ) (1606) ; DOUBLON - À VOIR (32) ; INCONNU (2)</t>
         </is>
       </c>
       <c r="M64" s="5" t="n">
-        <v>91.8</v>
+        <v>99.7</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>4147</v>
       </c>
       <c r="O64" s="3" t="n">
         <v>0</v>
@@ -5192,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>5176</v>
       </c>
       <c r="R64" s="3" t="n">
         <v>0</v>
@@ -5207,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="3" t="n">
-        <v>2174</v>
+        <v>5862</v>
       </c>
       <c r="W64" s="3" t="n">
         <v>0</v>
@@ -5216,46 +5081,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MED_LET</t>
+          <t>MED_AVI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Médiathèque - Lettres à en-tête des commerces et industries roubaisiens</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_LET </t>
+          <t>Médiathèque - Vidéos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J65" s="3" t="n">
-        <v>604</v>
+        <v>33</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>12.81</v>
+        <v>48.21</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (604)</t>
+          <t>TRANSFERT_S3_OK (31) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M65" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O65" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q65" s="3" t="n">
         <v>0</v>
@@ -5273,26 +5133,26 @@
         <v>0</v>
       </c>
       <c r="V65" s="3" t="n">
-        <v>604</v>
+        <v>0</v>
       </c>
       <c r="W65" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MED_MAR</t>
+          <t>MED_CHA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Médiathèque - Marionnettes</t>
+          <t>Médiathèque - Chansons de la Médiathèque de Roubaix</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MAR </t>
+          <t xml:space="preserve">RBX_MED_CHA </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5301,21 +5161,21 @@
         </is>
       </c>
       <c r="J66" s="3" t="n">
-        <v>197</v>
+        <v>723</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>7.07</v>
+        <v>17.58</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (99) ; À SUPPRIMER (DIFFUSION) (98)</t>
+          <t>TRANSFERT_S3_OK (363) ; INCONNU (360)</t>
         </is>
       </c>
       <c r="M66" s="5" t="n">
-        <v>100</v>
+        <v>50.2</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>62</v>
+        <v>360</v>
       </c>
       <c r="O66" s="3" t="n">
         <v>0</v>
@@ -5324,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="R66" s="3" t="n">
         <v>0</v>
@@ -5339,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="3" t="n">
-        <v>99</v>
+        <v>723</v>
       </c>
       <c r="W66" s="3" t="n">
         <v>0</v>
@@ -5348,17 +5208,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MED_MON</t>
+          <t>MED_CP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Médiathèque - Livres et brochures</t>
+          <t>Médiathèque - Cartes postales de Roubaix</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MON </t>
+          <t xml:space="preserve">RBX_MED_CP </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5367,21 +5227,21 @@
         </is>
       </c>
       <c r="J67" s="3" t="n">
-        <v>7553</v>
+        <v>5999</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>205.74</v>
+        <v>34.82</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (7553)</t>
+          <t>TRANSFERT_S3_OK (5318) ; À SUPPRIMER (DOUBLON S3-AZ) (535) ; À SUPPRIMER (DIFFUSION) (106) ; INCONNU (39) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M67" s="5" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>1384</v>
+        <v>4663</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -5390,22 +5250,22 @@
         <v>0</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="R67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>2721</v>
+        <v>0</v>
       </c>
       <c r="U67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V67" s="3" t="n">
-        <v>4832</v>
+        <v>5691</v>
       </c>
       <c r="W67" s="3" t="n">
         <v>0</v>
@@ -5414,49 +5274,49 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MED_MS</t>
+          <t>MED_DIL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Médiathèque - Manuscrits de la Médiathèque de Roubaix</t>
+          <t>Médiathèque - Fonds d'archives d'André Diligent</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_MS </t>
+          <t xml:space="preserve">RBX_MED_DIL </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J68" s="3" t="n">
-        <v>46262</v>
+        <v>365</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1061.94</v>
+        <v>480.6</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (32414) ; À SUPPRIMER (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (TESTS) (412) ; À SUPPRIMER (DOUBLON AZ) (278) ; INCONNU (158) ; À SUPPRIMER (DOUBLON S3-AZ) (157)</t>
+          <t>INCONNU (321) ; À SUPPRIMER (FILE_TYPE) (44)</t>
         </is>
       </c>
       <c r="M68" s="5" t="n">
-        <v>98.3</v>
+        <v>12.1</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>33024</v>
+        <v>0</v>
       </c>
       <c r="O68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>12786</v>
+        <v>94</v>
       </c>
       <c r="R68" s="3" t="n">
         <v>0</v>
@@ -5471,44 +5331,49 @@
         <v>0</v>
       </c>
       <c r="V68" s="3" t="n">
-        <v>33476</v>
+        <v>45</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MED_NPT</t>
+          <t>MED_EPH</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents non patrimoniaux</t>
+          <t>Médiathèque - Ephémères de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_EPH </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J69" s="3" t="n">
-        <v>4</v>
+        <v>846</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>17.09</v>
+        <v>10.17</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>INCONNU (4)</t>
+          <t>TRANSFERT_S3_OK (846)</t>
         </is>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="O69" s="3" t="n">
         <v>0</v>
@@ -5532,58 +5397,53 @@
         <v>0</v>
       </c>
       <c r="V69" s="3" t="n">
-        <v>0</v>
+        <v>846</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MED_PAR</t>
+          <t>MED_FAN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de particuliers</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_PAR </t>
+          <t>Médiathèque - Cartes postales fantaisie</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J70" s="3" t="n">
-        <v>24426</v>
+        <v>2666</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>543.34</v>
+        <v>32.93</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (18223) ; EN LIGNE - À TRANSFERER ? (3267) ; À SUPPRIMER (DOUBLON S3-AZ) (1674) ; À SUPPRIMER (MED_PAR) (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; À SUPPRIMER (DIFFUSION) (21)</t>
+          <t>INCONNU (2666)</t>
         </is>
       </c>
       <c r="M70" s="5" t="n">
-        <v>85.3</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>20715</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>5156</v>
+        <v>0</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0</v>
@@ -5598,53 +5458,58 @@
         <v>0</v>
       </c>
       <c r="V70" s="3" t="n">
-        <v>19264</v>
+        <v>2666</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MED_PBI</t>
+          <t>MED_FLR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de particuliers (suite)</t>
+          <t>Médiathèque - Documents sonores régionaux</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_FLR </t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J71" s="3" t="n">
-        <v>1084</v>
+        <v>8487</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>7.94</v>
+        <v>304.96</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (1084)</t>
+          <t>TRANSFERT_S3_OK (8487)</t>
         </is>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>3585</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>7228</v>
       </c>
       <c r="P71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0</v>
@@ -5659,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="3" t="n">
-        <v>1084</v>
+        <v>781</v>
       </c>
       <c r="W71" s="3" t="n">
         <v>0</v>
@@ -5668,44 +5533,49 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MED_PER</t>
+          <t>MED_FOO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Médiathèque - Périodiques</t>
+          <t>Médiathèque - Souvenirs de foot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_FOO </t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J72" s="3" t="n">
-        <v>1596</v>
+        <v>41</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>29.68</v>
+        <v>0.66</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1596)</t>
+          <t>INCONNU (30) ; TRANSFERT_S3_OK (6) ; À SUPPRIMER (DIFFUSION) (3) ; À SUPPRIMER (FILE_TYPE) (2)</t>
         </is>
       </c>
       <c r="M72" s="5" t="n">
-        <v>100</v>
+        <v>26.8</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O72" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="P72" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R72" s="3" t="n">
         <v>0</v>
@@ -5714,13 +5584,13 @@
         <v>0</v>
       </c>
       <c r="T72" s="3" t="n">
-        <v>829</v>
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V72" s="3" t="n">
-        <v>767</v>
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="n">
         <v>0</v>
@@ -5729,35 +5599,40 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MED_PHD</t>
+          <t>MED_IMA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Médiathèque - Collections de photographies</t>
+          <t>Médiathèque - Imagettes de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_IMA </t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J73" s="3" t="n">
-        <v>1946</v>
+        <v>9852</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>28.49</v>
+        <v>131.45</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>À TRANSFERER APRES VALIDATION (1946)</t>
+          <t>TRANSFERT_S3_OK (5821) ; À SUPPRIMER (DOUBLON AZ) (3846) ; À SUPPRIMER (DOUBLON S3-AZ) (113) ; À SUPPRIMER (DIFFUSION) (45) ; À SUPPRIMER (DOUBLON) (21) ; DOUBLON - À VOIR (6)</t>
         </is>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>0</v>
+        <v>5773</v>
       </c>
       <c r="O73" s="3" t="n">
         <v>0</v>
@@ -5766,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="R73" s="3" t="n">
         <v>0</v>
@@ -5781,7 +5656,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="3" t="n">
-        <v>1946</v>
+        <v>9627</v>
       </c>
       <c r="W73" s="3" t="n">
         <v>0</v>
@@ -5790,49 +5665,44 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MED_PHO</t>
+          <t>MED_JOU</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Médiathèque - Regards de photographes</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MED_PHO </t>
+          <t>Médiathèque - Journaux</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J74" s="3" t="n">
-        <v>18844</v>
+        <v>2174</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>69.83</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1338) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (DOUBLON S3-AZ) (1)</t>
+          <t>TRANSFERT_S3_OK (1995) ; INCONNU (179)</t>
         </is>
       </c>
       <c r="M74" s="5" t="n">
-        <v>7.1</v>
+        <v>91.8</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="O74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="3" t="n">
-        <v>13861</v>
+        <v>0</v>
       </c>
       <c r="R74" s="3" t="n">
         <v>0</v>
@@ -5844,29 +5714,29 @@
         <v>0</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V74" s="3" t="n">
-        <v>4804</v>
+        <v>2174</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MED_PLA</t>
+          <t>MED_LET</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Médiathèque - Collection des cartes et plans de la Médiathèque</t>
+          <t>Médiathèque - Lettres à en-tête des commerces et industries roubaisiens</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_PLA </t>
+          <t xml:space="preserve">RBX_MED_LET </t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5875,21 +5745,21 @@
         </is>
       </c>
       <c r="J75" s="3" t="n">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>38.23</v>
+        <v>12.81</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (274) ; À SUPPRIMER (DIFFUSION) (273) ; À SUPPRIMER (DOUBLON) (1)</t>
+          <t>TRANSFERT_S3_OK (604)</t>
         </is>
       </c>
       <c r="M75" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>271</v>
+        <v>559</v>
       </c>
       <c r="O75" s="3" t="n">
         <v>0</v>
@@ -5898,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>0</v>
@@ -5913,7 +5783,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="3" t="n">
-        <v>275</v>
+        <v>604</v>
       </c>
       <c r="W75" s="3" t="n">
         <v>0</v>
@@ -5922,17 +5792,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MED_PUB</t>
+          <t>MED_MAR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Médiathèque - Publications de la Médiathèque</t>
+          <t>Médiathèque - Marionnettes</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_PUB </t>
+          <t xml:space="preserve">RBX_MED_MAR </t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5941,21 +5811,21 @@
         </is>
       </c>
       <c r="J76" s="3" t="n">
-        <v>2419</v>
+        <v>197</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>49.96</v>
+        <v>7.07</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1274) ; À SUPPRIMER (DOUBLON) (1145)</t>
+          <t>TRANSFERT_S3_OK (99) ; À SUPPRIMER (DIFFUSION) (98)</t>
         </is>
       </c>
       <c r="M76" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>2419</v>
+        <v>62</v>
       </c>
       <c r="O76" s="3" t="n">
         <v>0</v>
@@ -5964,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="3" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="R76" s="3" t="n">
         <v>0</v>
@@ -5979,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="3" t="n">
-        <v>2419</v>
+        <v>99</v>
       </c>
       <c r="W76" s="3" t="n">
         <v>0</v>
@@ -5988,35 +5858,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MED_VAI</t>
+          <t>MED_MON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
+          <t>Médiathèque - Livres et brochures</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_MON </t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J77" s="3" t="n">
-        <v>238</v>
+        <v>7553</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>9.57</v>
+        <v>205.74</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>INCONNU (238)</t>
+          <t>TRANSFERT_S3_OK (7553)</t>
         </is>
       </c>
       <c r="M77" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>0</v>
+        <v>1384</v>
       </c>
       <c r="O77" s="3" t="n">
         <v>0</v>
@@ -6034,13 +5909,13 @@
         <v>0</v>
       </c>
       <c r="T77" s="3" t="n">
-        <v>0</v>
+        <v>2721</v>
       </c>
       <c r="U77" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V77" s="3" t="n">
-        <v>238</v>
+        <v>4832</v>
       </c>
       <c r="W77" s="3" t="n">
         <v>0</v>
@@ -6049,17 +5924,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MED_VDM</t>
+          <t>MED_MS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Médiathèque - Fonds d'archives de Maxence Van der Meersch</t>
+          <t>Médiathèque - Manuscrits de la Médiathèque de Roubaix</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MED_VDM </t>
+          <t xml:space="preserve">RBX_MED_MS </t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6068,36 +5943,36 @@
         </is>
       </c>
       <c r="J78" s="3" t="n">
-        <v>38231</v>
+        <v>46262</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>956.36</v>
+        <v>1061.94</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (DOUBLON S3-AZ) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (32414) ; À SUPPRIMER (DIFFUSION) (12229) ; EN LIGNE - À TRANSFERER ? (614) ; À SUPPRIMER (TESTS) (412) ; À SUPPRIMER (DOUBLON AZ) (278) ; INCONNU (158) ; À SUPPRIMER (DOUBLON S3-AZ) (157)</t>
         </is>
       </c>
       <c r="M78" s="5" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="N78" s="3" t="n">
-        <v>31272</v>
+        <v>33024</v>
       </c>
       <c r="O78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>0</v>
+        <v>12786</v>
       </c>
       <c r="R78" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S78" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T78" s="3" t="n">
         <v>0</v>
@@ -6106,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="3" t="n">
-        <v>38229</v>
+        <v>33476</v>
       </c>
       <c r="W78" s="3" t="n">
         <v>0</v>
@@ -6115,12 +5990,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MED_VID</t>
+          <t>MED_NPT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Médiathèque - Documents vidéos</t>
+          <t>Médiathèque - Documents non patrimoniaux</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6129,18 +6004,18 @@
         </is>
       </c>
       <c r="J79" s="3" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>8.82</v>
+        <v>17.09</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
+          <t>INCONNU (4)</t>
         </is>
       </c>
       <c r="M79" s="5" t="n">
-        <v>48.4</v>
+        <v>0</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>0</v>
@@ -6149,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="P79" s="3" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="3" t="n">
         <v>0</v>
@@ -6164,29 +6039,29 @@
         <v>0</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MUS_ARC</t>
+          <t>MED_PAR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Musée La Piscine - Archives</t>
+          <t>Médiathèque - Collections de particuliers</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_MUS_ARC </t>
+          <t xml:space="preserve">RBX_MED_PAR </t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6195,30 +6070,30 @@
         </is>
       </c>
       <c r="J80" s="3" t="n">
-        <v>318</v>
+        <v>24426</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>3.42</v>
+        <v>543.34</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (318)</t>
+          <t>TRANSFERT_S3_OK (18223) ; EN LIGNE - À TRANSFERER ? (3267) ; À SUPPRIMER (DOUBLON S3-AZ) (1674) ; À SUPPRIMER (MED_PAR) (686) ; INCONNU (316) ; À SUPPRIMER (RENOMMAGE) (239) ; À SUPPRIMER (DIFFUSION) (21)</t>
         </is>
       </c>
       <c r="M80" s="5" t="n">
-        <v>100</v>
+        <v>85.3</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>134</v>
+        <v>20715</v>
       </c>
       <c r="O80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>258</v>
+        <v>5156</v>
       </c>
       <c r="R80" s="3" t="n">
         <v>0</v>
@@ -6233,49 +6108,44 @@
         <v>0</v>
       </c>
       <c r="V80" s="3" t="n">
-        <v>60</v>
+        <v>19264</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MUS_VAI</t>
+          <t>MED_PBI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Musée La Piscine - Parfumerie et savonnerie Vaissier</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_MUS_VAI </t>
+          <t>Médiathèque - Collections de particuliers (suite)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J81" s="3" t="n">
-        <v>1918</v>
+        <v>1084</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>47.42</v>
+        <v>7.94</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1918)</t>
+          <t>TRANSFERT_S3_OK (1084)</t>
         </is>
       </c>
       <c r="M81" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>1859</v>
+        <v>0</v>
       </c>
       <c r="O81" s="3" t="n">
         <v>0</v>
@@ -6284,7 +6154,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="n">
         <v>0</v>
@@ -6299,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="3" t="n">
-        <v>1514</v>
+        <v>1084</v>
       </c>
       <c r="W81" s="3" t="n">
         <v>0</v>
@@ -6308,12 +6178,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MUS_XXX</t>
+          <t>MED_PER</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Musée La Piscine - nouveau versement</t>
+          <t>Médiathèque - Périodiques</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6322,18 +6192,18 @@
         </is>
       </c>
       <c r="J82" s="3" t="n">
-        <v>375</v>
+        <v>1596</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0.16</v>
+        <v>29.68</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>INCONNU (375)</t>
+          <t>TRANSFERT_S3_OK (1596)</t>
         </is>
       </c>
       <c r="M82" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N82" s="3" t="n">
         <v>0</v>
@@ -6345,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="3" t="n">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="R82" s="3" t="n">
         <v>0</v>
@@ -6354,13 +6224,13 @@
         <v>0</v>
       </c>
       <c r="T82" s="3" t="n">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="U82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="V82" s="3" t="n">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="W82" s="3" t="n">
         <v>0</v>
@@ -6369,40 +6239,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OBS_JOU</t>
+          <t>MED_PHD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_OBS_JOU </t>
+          <t>Médiathèque - Collections de photographies</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J83" s="3" t="n">
-        <v>1800</v>
+        <v>1946</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>20.38</v>
+        <v>28.49</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (1240) ; À TRANSFERER APRES VALIDATION (517) ; À SUPPRIMER (DOUBLON S3-AZ) (38) ; INCONNU (5)</t>
+          <t>TRANSFERT_S3_OK (1946)</t>
         </is>
       </c>
       <c r="M83" s="5" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>1202</v>
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="n">
         <v>0</v>
@@ -6411,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3" t="n">
-        <v>1156</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="n">
         <v>0</v>
@@ -6423,10 +6288,10 @@
         <v>0</v>
       </c>
       <c r="U83" s="3" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="n">
-        <v>601</v>
+        <v>1946</v>
       </c>
       <c r="W83" s="3" t="n">
         <v>0</v>
@@ -6435,22 +6300,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PRA_AVE</t>
+          <t>MED_PHO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
+          <t>Médiathèque - Regards de photographes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_AVE </t>
+          <t xml:space="preserve">RBX_MED_PHO </t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6459,106 +6319,111 @@
         </is>
       </c>
       <c r="J84" s="3" t="n">
-        <v>176340</v>
+        <v>18844</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>778.75</v>
+        <v>69.83</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (176340)</t>
+          <t>INCONNU (17499) ; TRANSFERT_S3_OK (1338) ; À SUPPRIMER (FILE_TYPE) (6) ; À SUPPRIMER (DOUBLON S3-AZ) (1)</t>
         </is>
       </c>
       <c r="M84" s="5" t="n">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="N84" s="3" t="n">
-        <v>87510</v>
+        <v>1140</v>
       </c>
       <c r="O84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="3" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="Q84" s="3" t="n">
-        <v>0</v>
+        <v>13861</v>
       </c>
       <c r="R84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S84" s="3" t="n">
-        <v>44271</v>
+        <v>0</v>
       </c>
       <c r="T84" s="3" t="n">
-        <v>43519</v>
+        <v>0</v>
       </c>
       <c r="U84" s="3" t="n">
-        <v>44275</v>
+        <v>3</v>
       </c>
       <c r="V84" s="3" t="n">
-        <v>44275</v>
+        <v>4804</v>
       </c>
       <c r="W84" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PRA_BDR</t>
+          <t>MED_PLA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Presse - Bulletin de Roubaix</t>
+          <t>Médiathèque - Collection des cartes et plans de la Médiathèque</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_MED_PLA </t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="J85" s="3" t="n">
-        <v>3138</v>
+        <v>548</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>16.9</v>
+        <v>38.23</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>INCONNU (2781) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (DOUBLON S3-AZ) (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+          <t>TRANSFERT_S3_OK (274) ; À SUPPRIMER (DIFFUSION) (273) ; À SUPPRIMER (DOUBLON) (1)</t>
         </is>
       </c>
       <c r="M85" s="5" t="n">
-        <v>11.4</v>
+        <v>100</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="O85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" s="3" t="n">
-        <v>523</v>
+        <v>273</v>
       </c>
       <c r="R85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S85" s="3" t="n">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="T85" s="3" t="n">
-        <v>407</v>
+        <v>0</v>
       </c>
       <c r="U85" s="3" t="n">
-        <v>1218</v>
+        <v>0</v>
       </c>
       <c r="V85" s="3" t="n">
-        <v>583</v>
+        <v>275</v>
       </c>
       <c r="W85" s="3" t="n">
         <v>0</v>
@@ -6567,22 +6432,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PRA_CRT</t>
+          <t>MED_PUB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Presse - La Croix de Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
+          <t>Médiathèque - Publications de la Médiathèque</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_CRT </t>
+          <t xml:space="preserve">RBX_MED_PUB </t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6591,21 +6451,21 @@
         </is>
       </c>
       <c r="J86" s="3" t="n">
-        <v>116806</v>
+        <v>2419</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1024.92</v>
+        <v>49.96</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (116806)</t>
+          <t>TRANSFERT_S3_OK (1274) ; À SUPPRIMER (DOUBLON) (1145)</t>
         </is>
       </c>
       <c r="M86" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>48452</v>
+        <v>2419</v>
       </c>
       <c r="O86" s="3" t="n">
         <v>0</v>
@@ -6620,16 +6480,16 @@
         <v>0</v>
       </c>
       <c r="S86" s="3" t="n">
-        <v>29202</v>
+        <v>0</v>
       </c>
       <c r="T86" s="3" t="n">
-        <v>29200</v>
+        <v>0</v>
       </c>
       <c r="U86" s="3" t="n">
-        <v>29202</v>
+        <v>0</v>
       </c>
       <c r="V86" s="3" t="n">
-        <v>29202</v>
+        <v>2419</v>
       </c>
       <c r="W86" s="3" t="n">
         <v>0</v>
@@ -6638,45 +6498,35 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PRA_CTG</t>
+          <t>MED_VAI</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Presse - Le Courrier de Tourcoing</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_CTG </t>
+          <t>Médiathèque - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J87" s="3" t="n">
-        <v>5752</v>
+        <v>238</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>45.98</v>
+        <v>9.57</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (5752)</t>
+          <t>INCONNU (238)</t>
         </is>
       </c>
       <c r="M87" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N87" s="3" t="n">
-        <v>2876</v>
+        <v>0</v>
       </c>
       <c r="O87" s="3" t="n">
         <v>0</v>
@@ -6691,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="S87" s="3" t="n">
-        <v>1438</v>
+        <v>0</v>
       </c>
       <c r="T87" s="3" t="n">
-        <v>1438</v>
+        <v>0</v>
       </c>
       <c r="U87" s="3" t="n">
-        <v>1438</v>
+        <v>0</v>
       </c>
       <c r="V87" s="3" t="n">
-        <v>1438</v>
+        <v>238</v>
       </c>
       <c r="W87" s="3" t="n">
         <v>0</v>
@@ -6709,22 +6559,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PRA_ERT</t>
+          <t>MED_VDM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
+          <t>Médiathèque - Fonds d'archives de Maxence Van der Meersch</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_ERT </t>
+          <t xml:space="preserve">RBX_MED_VDM </t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6733,27 +6578,27 @@
         </is>
       </c>
       <c r="J88" s="3" t="n">
-        <v>377078</v>
+        <v>38231</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>3103.47</v>
+        <v>956.36</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (377078)</t>
+          <t>TRANSFERT_S3_OK (38211) ; À SUPPRIMER (DOUBLON S3-AZ) (18) ; INCONNU (1) ; À SUPPRIMER (FILE_TYPE) (1)</t>
         </is>
       </c>
       <c r="M88" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>185403</v>
+        <v>31272</v>
       </c>
       <c r="O88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" s="3" t="n">
         <v>0</v>
@@ -6762,16 +6607,16 @@
         <v>0</v>
       </c>
       <c r="S88" s="3" t="n">
-        <v>94387</v>
+        <v>1</v>
       </c>
       <c r="T88" s="3" t="n">
-        <v>93918</v>
+        <v>0</v>
       </c>
       <c r="U88" s="3" t="n">
-        <v>94387</v>
+        <v>0</v>
       </c>
       <c r="V88" s="3" t="n">
-        <v>94386</v>
+        <v>38229</v>
       </c>
       <c r="W88" s="3" t="n">
         <v>0</v>
@@ -6780,51 +6625,41 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PRA_IND</t>
+          <t>MED_VID</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_PRA_IND </t>
+          <t>Médiathèque - Documents vidéos</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J89" s="3" t="n">
-        <v>64400</v>
+        <v>31</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>199.84</v>
+        <v>8.82</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (64400)</t>
+          <t>INCONNU (16) ; À SUPPRIMER (FILE_TYPE) (15)</t>
         </is>
       </c>
       <c r="M89" s="5" t="n">
-        <v>100</v>
+        <v>48.4</v>
       </c>
       <c r="N89" s="3" t="n">
-        <v>32665</v>
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q89" s="3" t="n">
         <v>0</v>
@@ -6833,16 +6668,16 @@
         <v>0</v>
       </c>
       <c r="S89" s="3" t="n">
-        <v>15377</v>
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="n">
-        <v>16307</v>
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="n">
-        <v>16358</v>
+        <v>1</v>
       </c>
       <c r="V89" s="3" t="n">
-        <v>16358</v>
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="n">
         <v>0</v>
@@ -6851,22 +6686,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PRA_JRX</t>
+          <t>MUS_ARC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Presse - Journal de Roubaix</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
+          <t>Musée La Piscine - Archives</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_PRA_JRX </t>
+          <t xml:space="preserve">RBX_MUS_ARC </t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6875,21 +6705,21 @@
         </is>
       </c>
       <c r="J90" s="3" t="n">
-        <v>595291</v>
+        <v>318</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4704.6</v>
+        <v>3.42</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (595291)</t>
+          <t>TRANSFERT_S3_OK (318)</t>
         </is>
       </c>
       <c r="M90" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>284717</v>
+        <v>134</v>
       </c>
       <c r="O90" s="3" t="n">
         <v>0</v>
@@ -6898,22 +6728,22 @@
         <v>0</v>
       </c>
       <c r="Q90" s="3" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="R90" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S90" s="3" t="n">
-        <v>148174</v>
+        <v>0</v>
       </c>
       <c r="T90" s="3" t="n">
-        <v>148814</v>
+        <v>0</v>
       </c>
       <c r="U90" s="3" t="n">
-        <v>149132</v>
+        <v>0</v>
       </c>
       <c r="V90" s="3" t="n">
-        <v>149171</v>
+        <v>60</v>
       </c>
       <c r="W90" s="3" t="n">
         <v>0</v>
@@ -6922,22 +6752,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PRA_RTG</t>
+          <t>MUS_VAI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Presse - Roubaix-Tourcoing</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>à créer par script</t>
+          <t>Musée La Piscine - Parfumerie et savonnerie Vaissier</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">RBX_VAH_PUB </t>
+          <t xml:space="preserve">RBX_MUS_VAI </t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6946,21 +6771,21 @@
         </is>
       </c>
       <c r="J91" s="3" t="n">
-        <v>3367</v>
+        <v>1918</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>19.37</v>
+        <v>47.42</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>TRANSFERT_S3_OK (3367)</t>
+          <t>TRANSFERT_S3_OK (1918)</t>
         </is>
       </c>
       <c r="M91" s="5" t="n">
         <v>100</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>1671</v>
+        <v>1859</v>
       </c>
       <c r="O91" s="3" t="n">
         <v>0</v>
@@ -6969,22 +6794,22 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="R91" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>823</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="n">
-        <v>848</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="n">
-        <v>848</v>
+        <v>1514</v>
       </c>
       <c r="W91" s="3" t="n">
         <v>0</v>
@@ -6993,40 +6818,35 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VAH_PUB</t>
+          <t>MUS_XXX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ville d'art et d'histoire  - Publications</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RBX_VAH_PUB </t>
+          <t>Musée La Piscine - nouveau versement</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J92" s="3" t="n">
-        <v>457</v>
+        <v>375</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>13.49</v>
+        <v>0.16</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>EN LIGNE - À TRANSFERER ? (457)</t>
+          <t>INCONNU (375)</t>
         </is>
       </c>
       <c r="M92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -7035,7 +6855,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="R92" s="3" t="n">
         <v>0</v>
@@ -7050,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="3" t="n">
-        <v>457</v>
+        <v>0</v>
       </c>
       <c r="W92" s="3" t="n">
         <v>0</v>
@@ -7059,120 +6879,810 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>OBS_JOU</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Observatoire urbain de Roubaix  - Journaux de quartier</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_OBS_JOU </t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K93" s="4" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (1240) ; À TRANSFERER APRES VALIDATION (517) ; À SUPPRIMER (DOUBLON S3-AZ) (38) ; INCONNU (5)</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3" t="n">
+        <v>1156</v>
+      </c>
+      <c r="R93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>601</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PRA_AVE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Presse - L’Avenir de Roubaix Tourcoing</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_AVE </t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>176340</v>
+      </c>
+      <c r="K94" s="4" t="n">
+        <v>778.75</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (176340)</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>87510</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="n">
+        <v>44271</v>
+      </c>
+      <c r="T94" s="3" t="n">
+        <v>43519</v>
+      </c>
+      <c r="U94" s="3" t="n">
+        <v>44275</v>
+      </c>
+      <c r="V94" s="3" t="n">
+        <v>44275</v>
+      </c>
+      <c r="W94" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PRA_BDR</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Presse - Bulletin de Roubaix</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>3138</v>
+      </c>
+      <c r="K95" s="4" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>INCONNU (2781) ; TRANSFERT_S3_OK (178) ; À SUPPRIMER (DOUBLON S3-AZ) (178) ; À SUPPRIMER (FILE_TYPE) (1)</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" s="3" t="n">
+        <v>523</v>
+      </c>
+      <c r="R95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="3" t="n">
+        <v>406</v>
+      </c>
+      <c r="T95" s="3" t="n">
+        <v>407</v>
+      </c>
+      <c r="U95" s="3" t="n">
+        <v>1218</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="W95" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PRA_CRT</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Presse - La Croix de Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_CRT </t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>116806</v>
+      </c>
+      <c r="K96" s="4" t="n">
+        <v>1024.92</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (116806)</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>48452</v>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3" t="n">
+        <v>29202</v>
+      </c>
+      <c r="T96" s="3" t="n">
+        <v>29200</v>
+      </c>
+      <c r="U96" s="3" t="n">
+        <v>29202</v>
+      </c>
+      <c r="V96" s="3" t="n">
+        <v>29202</v>
+      </c>
+      <c r="W96" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PRA_CTG</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Presse - Le Courrier de Tourcoing</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_CTG </t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>5752</v>
+      </c>
+      <c r="K97" s="4" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (5752)</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>2876</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="T97" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="U97" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="V97" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="W97" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PRA_ERT</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Presse - L’Egalité Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_ERT </t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>377078</v>
+      </c>
+      <c r="K98" s="4" t="n">
+        <v>3103.47</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (377078)</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>185403</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3" t="n">
+        <v>94387</v>
+      </c>
+      <c r="T98" s="3" t="n">
+        <v>93918</v>
+      </c>
+      <c r="U98" s="3" t="n">
+        <v>94387</v>
+      </c>
+      <c r="V98" s="3" t="n">
+        <v>94386</v>
+      </c>
+      <c r="W98" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PRA_IND</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Presse - L’Indicateur de Roubaix et de Tourcoing</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_IND </t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>64400</v>
+      </c>
+      <c r="K99" s="4" t="n">
+        <v>199.84</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (64400)</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>32665</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3" t="n">
+        <v>15377</v>
+      </c>
+      <c r="T99" s="3" t="n">
+        <v>16307</v>
+      </c>
+      <c r="U99" s="3" t="n">
+        <v>16358</v>
+      </c>
+      <c r="V99" s="3" t="n">
+        <v>16358</v>
+      </c>
+      <c r="W99" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PRA_JRX</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Presse - Journal de Roubaix</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_PRA_JRX </t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>595291</v>
+      </c>
+      <c r="K100" s="4" t="n">
+        <v>4704.6</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (595291)</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>284717</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="n">
+        <v>148174</v>
+      </c>
+      <c r="T100" s="3" t="n">
+        <v>148814</v>
+      </c>
+      <c r="U100" s="3" t="n">
+        <v>149132</v>
+      </c>
+      <c r="V100" s="3" t="n">
+        <v>149171</v>
+      </c>
+      <c r="W100" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PRA_RTG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Presse - Roubaix-Tourcoing</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>à créer par script</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>RBX_PRA_RTG</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>3367</v>
+      </c>
+      <c r="K101" s="4" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (3367)</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="T101" s="3" t="n">
+        <v>823</v>
+      </c>
+      <c r="U101" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="V101" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="W101" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>VAH_PUB</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ville d'art et d'histoire  - Publications</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RBX_VAH_PUB </t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="K102" s="4" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>EN LIGNE - À TRANSFERER ? (457)</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="W102" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>_INCONNU</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="J93" s="3" t="n">
+      <c r="J103" s="3" t="n">
         <v>4080</v>
       </c>
-      <c r="K93" s="4" t="n">
+      <c r="K103" s="4" t="n">
         <v>86.63</v>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>À SUPPRIMER (FILE_TYPE) (2245) ; INCONNU (1661) ; À SUPPRIMER (DIFFUSION) (174)</t>
         </is>
       </c>
-      <c r="M93" s="5" t="n">
+      <c r="M103" s="5" t="n">
         <v>59.3</v>
       </c>
-      <c r="N93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="3" t="n">
+      <c r="N103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="P93" s="3" t="n">
+      <c r="P103" s="3" t="n">
         <v>2244</v>
       </c>
-      <c r="Q93" s="3" t="n">
+      <c r="Q103" s="3" t="n">
         <v>857</v>
       </c>
-      <c r="R93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" s="3" t="n">
+      <c r="R103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="T93" s="3" t="n">
+      <c r="T103" s="3" t="n">
         <v>726</v>
       </c>
-      <c r="U93" s="3" t="n">
+      <c r="U103" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="V93" s="3" t="n">
+      <c r="V103" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="W93" s="3" t="n">
+      <c r="W103" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr"/>
-      <c r="C94" s="6" t="inlineStr"/>
-      <c r="D94" s="6" t="inlineStr"/>
-      <c r="E94" s="6" t="inlineStr"/>
-      <c r="F94" s="6" t="inlineStr"/>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr"/>
-      <c r="I94" s="6" t="inlineStr"/>
-      <c r="J94" s="7" t="n">
+      <c r="B104" s="6" t="inlineStr"/>
+      <c r="C104" s="6" t="inlineStr"/>
+      <c r="D104" s="6" t="inlineStr"/>
+      <c r="E104" s="6" t="inlineStr"/>
+      <c r="F104" s="6" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr"/>
+      <c r="I104" s="6" t="inlineStr"/>
+      <c r="J104" s="7" t="n">
         <v>2428075</v>
       </c>
-      <c r="K94" s="8" t="n">
+      <c r="K104" s="8" t="n">
         <v>20888.86</v>
       </c>
-      <c r="L94" s="6" t="inlineStr">
-        <is>
-          <t>TRANSFERT_S3_OK (2098808) ; À SUPPRIMER (DIFFUSION) (131832) ; À TRANSFERER APRES VALIDATION (106195) ; INCONNU (29156) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (12654) ; À SUPPRIMER (DOUBLON) (7616) ; À SUPPRIMER (DOUBLON S3-AZ) (6179) ; À SUPPRIMER (DOUBLON AZ) (5914) ; EN LIGNE - À TRANSFERER ? (5020) ; À SUPPRIMER (FILE_TYPE) (2329) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (MED_PAR) (686) ; À SUPPRIMER (TESTS) (412) ; INCONNU FRAD59 (180) ; S3_KEY À CONSTRUIRE (54) ; DOUBLON - À VOIR (38) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
-        </is>
-      </c>
-      <c r="M94" s="9" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="N94" s="7" t="n">
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>TRANSFERT_S3_OK (2191648) ; À SUPPRIMER (DIFFUSION) (131832) ; INCONNU (29156) ; À SUPPRIMER (REMPLACEMENT) (20276) ; À SUPPRIMER (DOUBLON SOURCE - À VERIFIER) (12654) ; À TRANSFERER (8156) ; À SUPPRIMER (DOUBLON) (7616) ; À SUPPRIMER (DOUBLON S3-AZ) (6179) ; À SUPPRIMER (DOUBLON AZ) (5914) ; EN LIGNE - À TRANSFERER ? (5020) ; À CHERCHER (4682) ; À SUPPRIMER (FILE_TYPE) (2329) ; À SUPPRIMER (RENOMMAGE) (721) ; À SUPPRIMER (MED_PAR) (686) ; À TRANSFERER APRES VALIDATION (517) ; À SUPPRIMER (TESTS) (412) ; INCONNU FRAD59 (180) ; S3_KEY À CONSTRUIRE (54) ; DOUBLON - À VOIR (38) ; INCONNU VOIR MARIE (4) ; À TRANSFERER VOIR MARIE (1)</t>
+        </is>
+      </c>
+      <c r="M104" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="N104" s="7" t="n">
         <v>990685</v>
       </c>
-      <c r="O94" s="7" t="n">
+      <c r="O104" s="7" t="n">
         <v>7347</v>
       </c>
-      <c r="P94" s="7" t="n">
+      <c r="P104" s="7" t="n">
         <v>2453</v>
       </c>
-      <c r="Q94" s="7" t="n">
+      <c r="Q104" s="7" t="n">
         <v>672526</v>
       </c>
-      <c r="R94" s="7" t="n">
+      <c r="R104" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="S94" s="7" t="n">
+      <c r="S104" s="7" t="n">
         <v>334782</v>
       </c>
-      <c r="T94" s="7" t="n">
+      <c r="T104" s="7" t="n">
         <v>452592</v>
       </c>
-      <c r="U94" s="7" t="n">
+      <c r="U104" s="7" t="n">
         <v>338132</v>
       </c>
-      <c r="V94" s="7" t="n">
+      <c r="V104" s="7" t="n">
         <v>619758</v>
       </c>
-      <c r="W94" s="7" t="n">
+      <c r="W104" s="7" t="n">
         <v>465</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M94">
+  <conditionalFormatting sqref="M2:M104">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/results/corpus_liste/suivi_corpus.xlsx
+++ b/results/corpus_liste/suivi_corpus.xlsx
@@ -596,6 +596,26 @@
           <t>AMR_10FI</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Archives - Don de photographies de M. Lepoutre</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Fi</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10Fi</t>
+        </is>
+      </c>
       <c r="J2" s="3" t="n">
         <v>164</v>
       </c>
@@ -951,6 +971,26 @@
           <t>AMR_21J</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Archives - La Roubaisienne - fonds photographique</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>21J</t>
+        </is>
+      </c>
       <c r="J7" s="3" t="n">
         <v>285</v>
       </c>
@@ -1225,6 +1265,26 @@
           <t>AMR_310W</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Archives - 310 W - Photographies</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>310W</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="n">
         <v>1136</v>
       </c>
@@ -1428,6 +1488,26 @@
           <t>AMR_3FI</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Archives - Photographies des archives (format inférieur à 24 x 30 cm)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3Fi</t>
+        </is>
+      </c>
       <c r="J14" s="3" t="n">
         <v>4843</v>
       </c>
@@ -1631,6 +1711,26 @@
           <t>AMR_440W</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Archives - Photographies et objets de l'Office municipal des sports de la ville de Roubaix</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>440W</t>
+        </is>
+      </c>
       <c r="J17" s="3" t="n">
         <v>15</v>
       </c>
@@ -1682,6 +1782,26 @@
           <t>AMR_4FI</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Archives - Photographies des archives (format est compris entre 24 x 30 cm et 32 x 42 cm)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Fi</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4FI</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="n">
         <v>326</v>
       </c>
@@ -1885,6 +2005,26 @@
           <t>AMR_500W</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Archives - 500W - Photographies</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>500W</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="n">
         <v>1447</v>
       </c>
@@ -2012,6 +2152,26 @@
           <t>AMR_512W</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Archives - 512W - Photographies</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>512W</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="n">
         <v>857</v>
       </c>
@@ -2443,6 +2603,26 @@
           <t>AMR_7J</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Archives - Archives d'Edmond Derreumaux</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Archives privées</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>7J</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="n">
         <v>4</v>
       </c>
@@ -3333,6 +3513,26 @@
       <c r="A41" t="inlineStr">
         <is>
           <t>AMR_DIA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Archives - Diapositives des archives</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Documents figurés</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Fi</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>9Fi</t>
         </is>
       </c>
       <c r="J41" s="3" t="n">
